--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -473,7 +473,7 @@
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
         <is>
-          <t>刀図鑑</t>
+          <t>刀剣男士番号</t>
         </is>
       </c>
       <c r="B1" s="0" t="inlineStr">
@@ -481,12 +481,12 @@
           <t>刀剣男士</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>衣装</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>レア</t>
         </is>
@@ -551,7 +551,7 @@
           <t>三日月宗近</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>戦装束</t>
         </is>
@@ -559,19 +559,19 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
           <t>三日月宗近</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>戦装束</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -586,7 +586,7 @@
           <t>小狐丸</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>戦装束</t>
         </is>
@@ -606,7 +606,7 @@
           <t>石切丸</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>戦装束</t>
         </is>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -1,19 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10920"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13EA2B7-32B2-3B47-B808-5A6390C94E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="1000" yWindow="660" windowWidth="30240" windowHeight="18260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="キャラクター名" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="素材" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="合成レシピ" state="visible" r:id="rId6"/>
+    <sheet name="キャラクター名" sheetId="1" r:id="rId1"/>
+    <sheet name="素材" sheetId="2" r:id="rId2"/>
+    <sheet name="合成レシピ" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="90">
   <si>
     <t>刀剣男士番号</t>
   </si>
@@ -33,137 +37,343 @@
     <t>ゆかり</t>
   </si>
   <si>
-    <t>奥義色(赤,黄,青)</t>
+    <t>奥義色</t>
   </si>
   <si>
     <t>奥義lv1説明文</t>
   </si>
   <si>
+    <t>三日月宗近</t>
+  </si>
+  <si>
+    <t>戦装束</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>太刀</t>
+  </si>
+  <si>
+    <t>夜,天下五剣</t>
+  </si>
+  <si>
+    <t>赤</t>
+  </si>
+  <si>
+    <t>小狐丸</t>
+  </si>
+  <si>
+    <t>石切丸</t>
+  </si>
+  <si>
+    <t>分類</t>
+  </si>
+  <si>
+    <t>名前</t>
+  </si>
+  <si>
+    <t>入手方法</t>
+  </si>
+  <si>
+    <t>贈物</t>
+  </si>
+  <si>
+    <t>お花</t>
+  </si>
+  <si>
+    <t>ドロップ</t>
+  </si>
+  <si>
+    <t>葉っぱ</t>
+  </si>
+  <si>
+    <t>火打ち石</t>
+  </si>
+  <si>
+    <t>桃</t>
+  </si>
+  <si>
+    <t>木の枝</t>
+  </si>
+  <si>
+    <t>卵</t>
+  </si>
+  <si>
+    <t>お魚</t>
+  </si>
+  <si>
+    <t>サンゴ</t>
+  </si>
+  <si>
+    <t>丸太</t>
+  </si>
+  <si>
+    <t>骨付き肉</t>
+  </si>
+  <si>
+    <t>粘土</t>
+  </si>
+  <si>
+    <t>お米</t>
+  </si>
+  <si>
+    <t>鉄</t>
+  </si>
+  <si>
+    <t>昆布</t>
+  </si>
+  <si>
+    <t>ふさふさの毛</t>
+  </si>
+  <si>
+    <t>麦</t>
+  </si>
+  <si>
+    <t>塩</t>
+  </si>
+  <si>
+    <t>サイコロ</t>
+  </si>
+  <si>
+    <t>油</t>
+  </si>
+  <si>
+    <t>ネジ</t>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>紙</t>
+  </si>
+  <si>
+    <t>合成</t>
+  </si>
+  <si>
+    <t>必要素材,個数</t>
+  </si>
+  <si>
+    <t>[木の枝,1][丸太,1][水,1]</t>
+  </si>
+  <si>
+    <t>【すべて】のト餓鬼を消去し、敵に【特小++】ダメージを与える</t>
+    <rPh sb="17" eb="19">
+      <t>トクショウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>アタエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>1lv[体力,攻撃]</t>
-  </si>
-  <si>
-    <t>2lv</t>
-  </si>
-  <si>
-    <t>3lv</t>
-  </si>
-  <si>
-    <t>三日月宗近</t>
-  </si>
-  <si>
-    <t>戦装束</t>
-  </si>
-  <si>
-    <t>○</t>
-  </si>
-  <si>
-    <t>小狐丸</t>
-  </si>
-  <si>
-    <t>石切丸</t>
-  </si>
-  <si>
-    <t>分類</t>
-  </si>
-  <si>
-    <t>名前</t>
-  </si>
-  <si>
-    <t>入手方法</t>
-  </si>
-  <si>
-    <t>贈物</t>
-  </si>
-  <si>
-    <t>お花</t>
-  </si>
-  <si>
-    <t>ドロップ</t>
-  </si>
-  <si>
-    <t>葉っぱ</t>
-  </si>
-  <si>
-    <t>火打ち石</t>
-  </si>
-  <si>
-    <t>桃</t>
-  </si>
-  <si>
-    <t>木の枝</t>
-  </si>
-  <si>
-    <t>卵</t>
-  </si>
-  <si>
-    <t>お魚</t>
-  </si>
-  <si>
-    <t>サンゴ</t>
-  </si>
-  <si>
-    <t>丸太</t>
-  </si>
-  <si>
-    <t>骨付き肉</t>
-  </si>
-  <si>
-    <t>粘土</t>
-  </si>
-  <si>
-    <t>お米</t>
-  </si>
-  <si>
-    <t>鉄</t>
-  </si>
-  <si>
-    <t>昆布</t>
-  </si>
-  <si>
-    <t>ふさふさの毛</t>
-  </si>
-  <si>
-    <t>麦</t>
-  </si>
-  <si>
-    <t>塩</t>
-  </si>
-  <si>
-    <t>サイコロ</t>
-  </si>
-  <si>
-    <t>油</t>
-  </si>
-  <si>
-    <t>ネジ</t>
-  </si>
-  <si>
-    <t>水</t>
-  </si>
-  <si>
-    <t>紙</t>
-  </si>
-  <si>
-    <t>合成</t>
-  </si>
-  <si>
-    <t>必要素材,個数</t>
-  </si>
-  <si>
-    <t>[木の枝,1][丸太,1][水,1]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>3lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>4lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>5lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>6lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>7lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>8lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>9lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>10lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>11lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>12lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>13lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>14lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>15lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>16lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>17lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>18lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>19lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>20lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>21lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>22lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>23lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>24lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>25lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>26lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>27lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>28lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>29lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>30lv[体力,攻撃]</t>
+  </si>
+  <si>
+    <t>奥義lv2説明文</t>
+  </si>
+  <si>
+    <t>奥義lv3説明文</t>
+  </si>
+  <si>
+    <t>奥義lv4説明文</t>
+  </si>
+  <si>
+    <t>奥義lv5説明文</t>
+  </si>
+  <si>
+    <t>大太刀</t>
+    <rPh sb="0" eb="1">
+      <t>オオキイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>けもの</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥義数値</t>
+    <rPh sb="0" eb="4">
+      <t>オウギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボムを【3個】生成する</t>
+    <rPh sb="5" eb="6">
+      <t xml:space="preserve">コ </t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイセイスル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>740,77</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ご神刀</t>
+    <rPh sb="2" eb="3">
+      <t>カタナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>青</t>
+  </si>
+  <si>
+    <t>【扇型・中範囲】のト餓鬼を消去し、敵に【特小-】ダメージを与える。味方全体に被ダメージ軽減【極小+・3手】を付与する</t>
+    <rPh sb="2" eb="3">
+      <t>オウギ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ショウキョ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>テキニ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>トクショウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>アタエ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ヒダメ-</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ゴク</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>_x0000__x0002_</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t/>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>561,61</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -186,11 +396,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -526,22 +737,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AQ5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="9.285714285714286" customWidth="1"/>
-    <col min="5" max="6" width="13.571428571428571" customWidth="1"/>
-    <col min="7" max="7" width="13.285714285714286" customWidth="1"/>
-    <col min="8" max="8" width="13.714285714285714" customWidth="1"/>
-    <col min="9" max="9" width="12.571428571428571" customWidth="1"/>
-    <col min="10" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="5" max="6" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12.5" customWidth="1"/>
+    <col min="10" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="42" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -564,44 +776,158 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="L1" t="s">
+        <v>79</v>
+      </c>
+      <c r="M1" t="s">
+        <v>80</v>
+      </c>
+      <c r="N1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U1" t="s">
+        <v>54</v>
+      </c>
+      <c r="V1" t="s">
+        <v>55</v>
+      </c>
+      <c r="W1" t="s">
+        <v>56</v>
+      </c>
+      <c r="X1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43">
       <c r="A2">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:43">
       <c r="A3">
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="H3">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>1060140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:43">
       <c r="A4">
         <v>5</v>
       </c>
@@ -609,10 +935,28 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>84</v>
+      </c>
+      <c r="R4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43">
       <c r="A5">
         <v>7</v>
       </c>
@@ -620,32 +964,51 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>88</v>
+      </c>
+      <c r="N5" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D564">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D564" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"○"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G564">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G564" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"赤,黄,青"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="24" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -656,7 +1019,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -667,7 +1030,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -678,7 +1041,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -689,7 +1052,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -700,7 +1063,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -711,7 +1074,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -722,7 +1085,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -733,7 +1096,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -744,7 +1107,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -755,7 +1118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -766,7 +1129,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -777,7 +1140,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -788,7 +1151,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -799,7 +1162,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -810,7 +1173,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -821,7 +1184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -832,7 +1195,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -843,7 +1206,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -854,7 +1217,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -865,7 +1228,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -876,7 +1239,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -887,7 +1250,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -899,22 +1262,23 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
-    <col min="2" max="2" width="22.571428571428573" customWidth="1"/>
-    <col min="3" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
+    <col min="2" max="2" width="22.5" customWidth="1"/>
+    <col min="3" max="24" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -922,7 +1286,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -931,7 +1295,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -3,21 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10920"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13EA2B7-32B2-3B47-B808-5A6390C94E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF441687-2415-814D-A82D-5729D491CD54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="660" windowWidth="30240" windowHeight="18260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="キャラクター名" sheetId="1" r:id="rId1"/>
     <sheet name="素材" sheetId="2" r:id="rId2"/>
     <sheet name="合成レシピ" sheetId="3" r:id="rId3"/>
+    <sheet name="ステージドロップ品" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="104">
   <si>
     <t>刀剣男士番号</t>
   </si>
@@ -353,6 +354,98 @@
   </si>
   <si>
     <t>561,61</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大豆</t>
+    <rPh sb="0" eb="2">
+      <t>ダイズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1-2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>葉っぱ</t>
+    <rPh sb="0" eb="1">
+      <t>ハッパ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水</t>
+    <rPh sb="0" eb="1">
+      <t>ミズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>桃</t>
+    <rPh sb="0" eb="1">
+      <t>モモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[絵馬]塩おにぎり</t>
+    <rPh sb="1" eb="3">
+      <t xml:space="preserve">エマ </t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>シオオニギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1-4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ふさふさの毛</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>丸太</t>
+    <rPh sb="0" eb="2">
+      <t>マルタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>骨付き肉</t>
+    <rPh sb="0" eb="2">
+      <t>ホネ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>卵</t>
+    <rPh sb="0" eb="1">
+      <t>タマゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1-7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>麦</t>
+    <rPh sb="0" eb="1">
+      <t>ムギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>丸太</t>
+    <rPh sb="0" eb="1">
+      <t>マルタ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -396,9 +489,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1002,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="24" width="13.5" customWidth="1"/>
@@ -1255,9 +1350,20 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" t="s">
         <v>42</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C24" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1299,4 +1405,75 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E6EFB7-103E-8544-BD47-26A12266B5D4}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col min="5" max="5" width="15.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ564"/>
+  <dimension ref="A1:AT564"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -476,6 +476,9 @@
     <col width="12.5" customWidth="1" min="9" max="9"/>
     <col width="13.5" customWidth="1" min="10" max="12"/>
     <col width="12.83203125" customWidth="1" min="13" max="42"/>
+    <col width="28" customWidth="1" min="44" max="44"/>
+    <col width="28" customWidth="1" min="45" max="45"/>
+    <col width="28" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,6 +697,21 @@
           <t>30lv[体力,攻撃]</t>
         </is>
       </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>上限突破10→20</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>上限突破20→30</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>上限突破30→35</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -739,6 +757,9 @@
       <c r="AO2" s="4" t="n"/>
       <c r="AP2" s="4" t="n"/>
       <c r="AQ2" s="4" t="n"/>
+      <c r="AR2" s="4" t="n"/>
+      <c r="AS2" s="4" t="n"/>
+      <c r="AT2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -816,6 +837,9 @@
       <c r="AO3" s="4" t="n"/>
       <c r="AP3" s="4" t="n"/>
       <c r="AQ3" s="4" t="n"/>
+      <c r="AR3" s="4" t="n"/>
+      <c r="AS3" s="4" t="n"/>
+      <c r="AT3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -888,6 +912,9 @@
       <c r="AO4" s="4" t="n"/>
       <c r="AP4" s="4" t="n"/>
       <c r="AQ4" s="4" t="n"/>
+      <c r="AR4" s="4" t="n"/>
+      <c r="AS4" s="4" t="n"/>
+      <c r="AT4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -960,6 +987,9 @@
       <c r="AO5" s="4" t="n"/>
       <c r="AP5" s="4" t="n"/>
       <c r="AQ5" s="4" t="n"/>
+      <c r="AR5" s="4" t="n"/>
+      <c r="AS5" s="4" t="n"/>
+      <c r="AT5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="N6" s="4" t="n"/>
@@ -992,6 +1022,9 @@
       <c r="AO6" s="4" t="n"/>
       <c r="AP6" s="4" t="n"/>
       <c r="AQ6" s="4" t="n"/>
+      <c r="AR6" s="4" t="n"/>
+      <c r="AS6" s="4" t="n"/>
+      <c r="AT6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="N7" s="4" t="n"/>
@@ -1024,6 +1057,9 @@
       <c r="AO7" s="4" t="n"/>
       <c r="AP7" s="4" t="n"/>
       <c r="AQ7" s="4" t="n"/>
+      <c r="AR7" s="4" t="n"/>
+      <c r="AS7" s="4" t="n"/>
+      <c r="AT7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="N8" s="4" t="n"/>
@@ -1056,6 +1092,9 @@
       <c r="AO8" s="4" t="n"/>
       <c r="AP8" s="4" t="n"/>
       <c r="AQ8" s="4" t="n"/>
+      <c r="AR8" s="4" t="n"/>
+      <c r="AS8" s="4" t="n"/>
+      <c r="AT8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="N9" s="4" t="n"/>
@@ -1088,6 +1127,9 @@
       <c r="AO9" s="4" t="n"/>
       <c r="AP9" s="4" t="n"/>
       <c r="AQ9" s="4" t="n"/>
+      <c r="AR9" s="4" t="n"/>
+      <c r="AS9" s="4" t="n"/>
+      <c r="AT9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="N10" s="4" t="n"/>
@@ -1120,6 +1162,9 @@
       <c r="AO10" s="4" t="n"/>
       <c r="AP10" s="4" t="n"/>
       <c r="AQ10" s="4" t="n"/>
+      <c r="AR10" s="4" t="n"/>
+      <c r="AS10" s="4" t="n"/>
+      <c r="AT10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="N11" s="4" t="n"/>
@@ -1152,6 +1197,9 @@
       <c r="AO11" s="4" t="n"/>
       <c r="AP11" s="4" t="n"/>
       <c r="AQ11" s="4" t="n"/>
+      <c r="AR11" s="4" t="n"/>
+      <c r="AS11" s="4" t="n"/>
+      <c r="AT11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="N12" s="4" t="n"/>
@@ -1184,6 +1232,9 @@
       <c r="AO12" s="4" t="n"/>
       <c r="AP12" s="4" t="n"/>
       <c r="AQ12" s="4" t="n"/>
+      <c r="AR12" s="4" t="n"/>
+      <c r="AS12" s="4" t="n"/>
+      <c r="AT12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="N13" s="4" t="n"/>
@@ -1216,6 +1267,9 @@
       <c r="AO13" s="4" t="n"/>
       <c r="AP13" s="4" t="n"/>
       <c r="AQ13" s="4" t="n"/>
+      <c r="AR13" s="4" t="n"/>
+      <c r="AS13" s="4" t="n"/>
+      <c r="AT13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="N14" s="4" t="n"/>
@@ -1248,6 +1302,9 @@
       <c r="AO14" s="4" t="n"/>
       <c r="AP14" s="4" t="n"/>
       <c r="AQ14" s="4" t="n"/>
+      <c r="AR14" s="4" t="n"/>
+      <c r="AS14" s="4" t="n"/>
+      <c r="AT14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="N15" s="4" t="n"/>
@@ -1280,6 +1337,9 @@
       <c r="AO15" s="4" t="n"/>
       <c r="AP15" s="4" t="n"/>
       <c r="AQ15" s="4" t="n"/>
+      <c r="AR15" s="4" t="n"/>
+      <c r="AS15" s="4" t="n"/>
+      <c r="AT15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="N16" s="4" t="n"/>
@@ -1312,6 +1372,9 @@
       <c r="AO16" s="4" t="n"/>
       <c r="AP16" s="4" t="n"/>
       <c r="AQ16" s="4" t="n"/>
+      <c r="AR16" s="4" t="n"/>
+      <c r="AS16" s="4" t="n"/>
+      <c r="AT16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="N17" s="4" t="n"/>
@@ -1344,6 +1407,9 @@
       <c r="AO17" s="4" t="n"/>
       <c r="AP17" s="4" t="n"/>
       <c r="AQ17" s="4" t="n"/>
+      <c r="AR17" s="4" t="n"/>
+      <c r="AS17" s="4" t="n"/>
+      <c r="AT17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="N18" s="4" t="n"/>
@@ -1376,6 +1442,9 @@
       <c r="AO18" s="4" t="n"/>
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
+      <c r="AR18" s="4" t="n"/>
+      <c r="AS18" s="4" t="n"/>
+      <c r="AT18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="N19" s="4" t="n"/>
@@ -1408,6 +1477,9 @@
       <c r="AO19" s="4" t="n"/>
       <c r="AP19" s="4" t="n"/>
       <c r="AQ19" s="4" t="n"/>
+      <c r="AR19" s="4" t="n"/>
+      <c r="AS19" s="4" t="n"/>
+      <c r="AT19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="N20" s="4" t="n"/>
@@ -1440,6 +1512,9 @@
       <c r="AO20" s="4" t="n"/>
       <c r="AP20" s="4" t="n"/>
       <c r="AQ20" s="4" t="n"/>
+      <c r="AR20" s="4" t="n"/>
+      <c r="AS20" s="4" t="n"/>
+      <c r="AT20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="N21" s="4" t="n"/>
@@ -1472,6 +1547,9 @@
       <c r="AO21" s="4" t="n"/>
       <c r="AP21" s="4" t="n"/>
       <c r="AQ21" s="4" t="n"/>
+      <c r="AR21" s="4" t="n"/>
+      <c r="AS21" s="4" t="n"/>
+      <c r="AT21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="N22" s="4" t="n"/>
@@ -1504,6 +1582,9 @@
       <c r="AO22" s="4" t="n"/>
       <c r="AP22" s="4" t="n"/>
       <c r="AQ22" s="4" t="n"/>
+      <c r="AR22" s="4" t="n"/>
+      <c r="AS22" s="4" t="n"/>
+      <c r="AT22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="N23" s="4" t="n"/>
@@ -1536,6 +1617,9 @@
       <c r="AO23" s="4" t="n"/>
       <c r="AP23" s="4" t="n"/>
       <c r="AQ23" s="4" t="n"/>
+      <c r="AR23" s="4" t="n"/>
+      <c r="AS23" s="4" t="n"/>
+      <c r="AT23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="N24" s="4" t="n"/>
@@ -1568,6 +1652,9 @@
       <c r="AO24" s="4" t="n"/>
       <c r="AP24" s="4" t="n"/>
       <c r="AQ24" s="4" t="n"/>
+      <c r="AR24" s="4" t="n"/>
+      <c r="AS24" s="4" t="n"/>
+      <c r="AT24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="N25" s="4" t="n"/>
@@ -1600,6 +1687,9 @@
       <c r="AO25" s="4" t="n"/>
       <c r="AP25" s="4" t="n"/>
       <c r="AQ25" s="4" t="n"/>
+      <c r="AR25" s="4" t="n"/>
+      <c r="AS25" s="4" t="n"/>
+      <c r="AT25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="N26" s="4" t="n"/>
@@ -1632,6 +1722,9 @@
       <c r="AO26" s="4" t="n"/>
       <c r="AP26" s="4" t="n"/>
       <c r="AQ26" s="4" t="n"/>
+      <c r="AR26" s="4" t="n"/>
+      <c r="AS26" s="4" t="n"/>
+      <c r="AT26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="N27" s="4" t="n"/>
@@ -1664,6 +1757,9 @@
       <c r="AO27" s="4" t="n"/>
       <c r="AP27" s="4" t="n"/>
       <c r="AQ27" s="4" t="n"/>
+      <c r="AR27" s="4" t="n"/>
+      <c r="AS27" s="4" t="n"/>
+      <c r="AT27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="N28" s="4" t="n"/>
@@ -1696,6 +1792,9 @@
       <c r="AO28" s="4" t="n"/>
       <c r="AP28" s="4" t="n"/>
       <c r="AQ28" s="4" t="n"/>
+      <c r="AR28" s="4" t="n"/>
+      <c r="AS28" s="4" t="n"/>
+      <c r="AT28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="N29" s="4" t="n"/>
@@ -1728,6 +1827,9 @@
       <c r="AO29" s="4" t="n"/>
       <c r="AP29" s="4" t="n"/>
       <c r="AQ29" s="4" t="n"/>
+      <c r="AR29" s="4" t="n"/>
+      <c r="AS29" s="4" t="n"/>
+      <c r="AT29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="N30" s="4" t="n"/>
@@ -1760,6 +1862,9 @@
       <c r="AO30" s="4" t="n"/>
       <c r="AP30" s="4" t="n"/>
       <c r="AQ30" s="4" t="n"/>
+      <c r="AR30" s="4" t="n"/>
+      <c r="AS30" s="4" t="n"/>
+      <c r="AT30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="N31" s="4" t="n"/>
@@ -1792,6 +1897,9 @@
       <c r="AO31" s="4" t="n"/>
       <c r="AP31" s="4" t="n"/>
       <c r="AQ31" s="4" t="n"/>
+      <c r="AR31" s="4" t="n"/>
+      <c r="AS31" s="4" t="n"/>
+      <c r="AT31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="N32" s="4" t="n"/>
@@ -1824,6 +1932,9 @@
       <c r="AO32" s="4" t="n"/>
       <c r="AP32" s="4" t="n"/>
       <c r="AQ32" s="4" t="n"/>
+      <c r="AR32" s="4" t="n"/>
+      <c r="AS32" s="4" t="n"/>
+      <c r="AT32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="N33" s="4" t="n"/>
@@ -1856,6 +1967,9 @@
       <c r="AO33" s="4" t="n"/>
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
+      <c r="AR33" s="4" t="n"/>
+      <c r="AS33" s="4" t="n"/>
+      <c r="AT33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="N34" s="4" t="n"/>
@@ -1888,6 +2002,9 @@
       <c r="AO34" s="4" t="n"/>
       <c r="AP34" s="4" t="n"/>
       <c r="AQ34" s="4" t="n"/>
+      <c r="AR34" s="4" t="n"/>
+      <c r="AS34" s="4" t="n"/>
+      <c r="AT34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="N35" s="4" t="n"/>
@@ -1920,6 +2037,9 @@
       <c r="AO35" s="4" t="n"/>
       <c r="AP35" s="4" t="n"/>
       <c r="AQ35" s="4" t="n"/>
+      <c r="AR35" s="4" t="n"/>
+      <c r="AS35" s="4" t="n"/>
+      <c r="AT35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="N36" s="4" t="n"/>
@@ -1952,6 +2072,9 @@
       <c r="AO36" s="4" t="n"/>
       <c r="AP36" s="4" t="n"/>
       <c r="AQ36" s="4" t="n"/>
+      <c r="AR36" s="4" t="n"/>
+      <c r="AS36" s="4" t="n"/>
+      <c r="AT36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="N37" s="4" t="n"/>
@@ -1984,6 +2107,9 @@
       <c r="AO37" s="4" t="n"/>
       <c r="AP37" s="4" t="n"/>
       <c r="AQ37" s="4" t="n"/>
+      <c r="AR37" s="4" t="n"/>
+      <c r="AS37" s="4" t="n"/>
+      <c r="AT37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="N38" s="4" t="n"/>
@@ -2016,6 +2142,9 @@
       <c r="AO38" s="4" t="n"/>
       <c r="AP38" s="4" t="n"/>
       <c r="AQ38" s="4" t="n"/>
+      <c r="AR38" s="4" t="n"/>
+      <c r="AS38" s="4" t="n"/>
+      <c r="AT38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="N39" s="4" t="n"/>
@@ -2048,6 +2177,9 @@
       <c r="AO39" s="4" t="n"/>
       <c r="AP39" s="4" t="n"/>
       <c r="AQ39" s="4" t="n"/>
+      <c r="AR39" s="4" t="n"/>
+      <c r="AS39" s="4" t="n"/>
+      <c r="AT39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="N40" s="4" t="n"/>
@@ -2080,6 +2212,9 @@
       <c r="AO40" s="4" t="n"/>
       <c r="AP40" s="4" t="n"/>
       <c r="AQ40" s="4" t="n"/>
+      <c r="AR40" s="4" t="n"/>
+      <c r="AS40" s="4" t="n"/>
+      <c r="AT40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="N41" s="4" t="n"/>
@@ -2112,6 +2247,9 @@
       <c r="AO41" s="4" t="n"/>
       <c r="AP41" s="4" t="n"/>
       <c r="AQ41" s="4" t="n"/>
+      <c r="AR41" s="4" t="n"/>
+      <c r="AS41" s="4" t="n"/>
+      <c r="AT41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="N42" s="4" t="n"/>
@@ -2144,6 +2282,9 @@
       <c r="AO42" s="4" t="n"/>
       <c r="AP42" s="4" t="n"/>
       <c r="AQ42" s="4" t="n"/>
+      <c r="AR42" s="4" t="n"/>
+      <c r="AS42" s="4" t="n"/>
+      <c r="AT42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="N43" s="4" t="n"/>
@@ -2176,6 +2317,9 @@
       <c r="AO43" s="4" t="n"/>
       <c r="AP43" s="4" t="n"/>
       <c r="AQ43" s="4" t="n"/>
+      <c r="AR43" s="4" t="n"/>
+      <c r="AS43" s="4" t="n"/>
+      <c r="AT43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="N44" s="4" t="n"/>
@@ -2208,6 +2352,9 @@
       <c r="AO44" s="4" t="n"/>
       <c r="AP44" s="4" t="n"/>
       <c r="AQ44" s="4" t="n"/>
+      <c r="AR44" s="4" t="n"/>
+      <c r="AS44" s="4" t="n"/>
+      <c r="AT44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="N45" s="4" t="n"/>
@@ -2240,6 +2387,9 @@
       <c r="AO45" s="4" t="n"/>
       <c r="AP45" s="4" t="n"/>
       <c r="AQ45" s="4" t="n"/>
+      <c r="AR45" s="4" t="n"/>
+      <c r="AS45" s="4" t="n"/>
+      <c r="AT45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="N46" s="4" t="n"/>
@@ -2272,6 +2422,9 @@
       <c r="AO46" s="4" t="n"/>
       <c r="AP46" s="4" t="n"/>
       <c r="AQ46" s="4" t="n"/>
+      <c r="AR46" s="4" t="n"/>
+      <c r="AS46" s="4" t="n"/>
+      <c r="AT46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="N47" s="4" t="n"/>
@@ -2304,6 +2457,9 @@
       <c r="AO47" s="4" t="n"/>
       <c r="AP47" s="4" t="n"/>
       <c r="AQ47" s="4" t="n"/>
+      <c r="AR47" s="4" t="n"/>
+      <c r="AS47" s="4" t="n"/>
+      <c r="AT47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="N48" s="4" t="n"/>
@@ -2336,6 +2492,9 @@
       <c r="AO48" s="4" t="n"/>
       <c r="AP48" s="4" t="n"/>
       <c r="AQ48" s="4" t="n"/>
+      <c r="AR48" s="4" t="n"/>
+      <c r="AS48" s="4" t="n"/>
+      <c r="AT48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="N49" s="4" t="n"/>
@@ -2368,6 +2527,9 @@
       <c r="AO49" s="4" t="n"/>
       <c r="AP49" s="4" t="n"/>
       <c r="AQ49" s="4" t="n"/>
+      <c r="AR49" s="4" t="n"/>
+      <c r="AS49" s="4" t="n"/>
+      <c r="AT49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="N50" s="4" t="n"/>
@@ -2400,6 +2562,9 @@
       <c r="AO50" s="4" t="n"/>
       <c r="AP50" s="4" t="n"/>
       <c r="AQ50" s="4" t="n"/>
+      <c r="AR50" s="4" t="n"/>
+      <c r="AS50" s="4" t="n"/>
+      <c r="AT50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="N51" s="4" t="n"/>
@@ -2432,6 +2597,9 @@
       <c r="AO51" s="4" t="n"/>
       <c r="AP51" s="4" t="n"/>
       <c r="AQ51" s="4" t="n"/>
+      <c r="AR51" s="4" t="n"/>
+      <c r="AS51" s="4" t="n"/>
+      <c r="AT51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="N52" s="4" t="n"/>
@@ -2464,6 +2632,9 @@
       <c r="AO52" s="4" t="n"/>
       <c r="AP52" s="4" t="n"/>
       <c r="AQ52" s="4" t="n"/>
+      <c r="AR52" s="4" t="n"/>
+      <c r="AS52" s="4" t="n"/>
+      <c r="AT52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="N53" s="4" t="n"/>
@@ -2496,6 +2667,9 @@
       <c r="AO53" s="4" t="n"/>
       <c r="AP53" s="4" t="n"/>
       <c r="AQ53" s="4" t="n"/>
+      <c r="AR53" s="4" t="n"/>
+      <c r="AS53" s="4" t="n"/>
+      <c r="AT53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="N54" s="4" t="n"/>
@@ -2528,6 +2702,9 @@
       <c r="AO54" s="4" t="n"/>
       <c r="AP54" s="4" t="n"/>
       <c r="AQ54" s="4" t="n"/>
+      <c r="AR54" s="4" t="n"/>
+      <c r="AS54" s="4" t="n"/>
+      <c r="AT54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="N55" s="4" t="n"/>
@@ -2560,6 +2737,9 @@
       <c r="AO55" s="4" t="n"/>
       <c r="AP55" s="4" t="n"/>
       <c r="AQ55" s="4" t="n"/>
+      <c r="AR55" s="4" t="n"/>
+      <c r="AS55" s="4" t="n"/>
+      <c r="AT55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="N56" s="4" t="n"/>
@@ -2592,6 +2772,9 @@
       <c r="AO56" s="4" t="n"/>
       <c r="AP56" s="4" t="n"/>
       <c r="AQ56" s="4" t="n"/>
+      <c r="AR56" s="4" t="n"/>
+      <c r="AS56" s="4" t="n"/>
+      <c r="AT56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="N57" s="4" t="n"/>
@@ -2624,6 +2807,9 @@
       <c r="AO57" s="4" t="n"/>
       <c r="AP57" s="4" t="n"/>
       <c r="AQ57" s="4" t="n"/>
+      <c r="AR57" s="4" t="n"/>
+      <c r="AS57" s="4" t="n"/>
+      <c r="AT57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="N58" s="4" t="n"/>
@@ -2656,6 +2842,9 @@
       <c r="AO58" s="4" t="n"/>
       <c r="AP58" s="4" t="n"/>
       <c r="AQ58" s="4" t="n"/>
+      <c r="AR58" s="4" t="n"/>
+      <c r="AS58" s="4" t="n"/>
+      <c r="AT58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="N59" s="4" t="n"/>
@@ -2688,6 +2877,9 @@
       <c r="AO59" s="4" t="n"/>
       <c r="AP59" s="4" t="n"/>
       <c r="AQ59" s="4" t="n"/>
+      <c r="AR59" s="4" t="n"/>
+      <c r="AS59" s="4" t="n"/>
+      <c r="AT59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="N60" s="4" t="n"/>
@@ -2720,6 +2912,9 @@
       <c r="AO60" s="4" t="n"/>
       <c r="AP60" s="4" t="n"/>
       <c r="AQ60" s="4" t="n"/>
+      <c r="AR60" s="4" t="n"/>
+      <c r="AS60" s="4" t="n"/>
+      <c r="AT60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="N61" s="4" t="n"/>
@@ -2752,6 +2947,9 @@
       <c r="AO61" s="4" t="n"/>
       <c r="AP61" s="4" t="n"/>
       <c r="AQ61" s="4" t="n"/>
+      <c r="AR61" s="4" t="n"/>
+      <c r="AS61" s="4" t="n"/>
+      <c r="AT61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="N62" s="4" t="n"/>
@@ -2784,6 +2982,9 @@
       <c r="AO62" s="4" t="n"/>
       <c r="AP62" s="4" t="n"/>
       <c r="AQ62" s="4" t="n"/>
+      <c r="AR62" s="4" t="n"/>
+      <c r="AS62" s="4" t="n"/>
+      <c r="AT62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="N63" s="4" t="n"/>
@@ -2816,6 +3017,9 @@
       <c r="AO63" s="4" t="n"/>
       <c r="AP63" s="4" t="n"/>
       <c r="AQ63" s="4" t="n"/>
+      <c r="AR63" s="4" t="n"/>
+      <c r="AS63" s="4" t="n"/>
+      <c r="AT63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="N64" s="4" t="n"/>
@@ -2848,6 +3052,9 @@
       <c r="AO64" s="4" t="n"/>
       <c r="AP64" s="4" t="n"/>
       <c r="AQ64" s="4" t="n"/>
+      <c r="AR64" s="4" t="n"/>
+      <c r="AS64" s="4" t="n"/>
+      <c r="AT64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="N65" s="4" t="n"/>
@@ -2880,6 +3087,9 @@
       <c r="AO65" s="4" t="n"/>
       <c r="AP65" s="4" t="n"/>
       <c r="AQ65" s="4" t="n"/>
+      <c r="AR65" s="4" t="n"/>
+      <c r="AS65" s="4" t="n"/>
+      <c r="AT65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="N66" s="4" t="n"/>
@@ -2912,6 +3122,9 @@
       <c r="AO66" s="4" t="n"/>
       <c r="AP66" s="4" t="n"/>
       <c r="AQ66" s="4" t="n"/>
+      <c r="AR66" s="4" t="n"/>
+      <c r="AS66" s="4" t="n"/>
+      <c r="AT66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="N67" s="4" t="n"/>
@@ -2944,6 +3157,9 @@
       <c r="AO67" s="4" t="n"/>
       <c r="AP67" s="4" t="n"/>
       <c r="AQ67" s="4" t="n"/>
+      <c r="AR67" s="4" t="n"/>
+      <c r="AS67" s="4" t="n"/>
+      <c r="AT67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="N68" s="4" t="n"/>
@@ -2976,6 +3192,9 @@
       <c r="AO68" s="4" t="n"/>
       <c r="AP68" s="4" t="n"/>
       <c r="AQ68" s="4" t="n"/>
+      <c r="AR68" s="4" t="n"/>
+      <c r="AS68" s="4" t="n"/>
+      <c r="AT68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="N69" s="4" t="n"/>
@@ -3008,6 +3227,9 @@
       <c r="AO69" s="4" t="n"/>
       <c r="AP69" s="4" t="n"/>
       <c r="AQ69" s="4" t="n"/>
+      <c r="AR69" s="4" t="n"/>
+      <c r="AS69" s="4" t="n"/>
+      <c r="AT69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="N70" s="4" t="n"/>
@@ -3040,6 +3262,9 @@
       <c r="AO70" s="4" t="n"/>
       <c r="AP70" s="4" t="n"/>
       <c r="AQ70" s="4" t="n"/>
+      <c r="AR70" s="4" t="n"/>
+      <c r="AS70" s="4" t="n"/>
+      <c r="AT70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="N71" s="4" t="n"/>
@@ -3072,6 +3297,9 @@
       <c r="AO71" s="4" t="n"/>
       <c r="AP71" s="4" t="n"/>
       <c r="AQ71" s="4" t="n"/>
+      <c r="AR71" s="4" t="n"/>
+      <c r="AS71" s="4" t="n"/>
+      <c r="AT71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="N72" s="4" t="n"/>
@@ -3104,6 +3332,9 @@
       <c r="AO72" s="4" t="n"/>
       <c r="AP72" s="4" t="n"/>
       <c r="AQ72" s="4" t="n"/>
+      <c r="AR72" s="4" t="n"/>
+      <c r="AS72" s="4" t="n"/>
+      <c r="AT72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="N73" s="4" t="n"/>
@@ -3136,6 +3367,9 @@
       <c r="AO73" s="4" t="n"/>
       <c r="AP73" s="4" t="n"/>
       <c r="AQ73" s="4" t="n"/>
+      <c r="AR73" s="4" t="n"/>
+      <c r="AS73" s="4" t="n"/>
+      <c r="AT73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="N74" s="4" t="n"/>
@@ -3168,6 +3402,9 @@
       <c r="AO74" s="4" t="n"/>
       <c r="AP74" s="4" t="n"/>
       <c r="AQ74" s="4" t="n"/>
+      <c r="AR74" s="4" t="n"/>
+      <c r="AS74" s="4" t="n"/>
+      <c r="AT74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="N75" s="4" t="n"/>
@@ -3200,6 +3437,9 @@
       <c r="AO75" s="4" t="n"/>
       <c r="AP75" s="4" t="n"/>
       <c r="AQ75" s="4" t="n"/>
+      <c r="AR75" s="4" t="n"/>
+      <c r="AS75" s="4" t="n"/>
+      <c r="AT75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="N76" s="4" t="n"/>
@@ -3232,6 +3472,9 @@
       <c r="AO76" s="4" t="n"/>
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
+      <c r="AR76" s="4" t="n"/>
+      <c r="AS76" s="4" t="n"/>
+      <c r="AT76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="N77" s="4" t="n"/>
@@ -3264,6 +3507,9 @@
       <c r="AO77" s="4" t="n"/>
       <c r="AP77" s="4" t="n"/>
       <c r="AQ77" s="4" t="n"/>
+      <c r="AR77" s="4" t="n"/>
+      <c r="AS77" s="4" t="n"/>
+      <c r="AT77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="N78" s="4" t="n"/>
@@ -3296,6 +3542,9 @@
       <c r="AO78" s="4" t="n"/>
       <c r="AP78" s="4" t="n"/>
       <c r="AQ78" s="4" t="n"/>
+      <c r="AR78" s="4" t="n"/>
+      <c r="AS78" s="4" t="n"/>
+      <c r="AT78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="N79" s="4" t="n"/>
@@ -3328,6 +3577,9 @@
       <c r="AO79" s="4" t="n"/>
       <c r="AP79" s="4" t="n"/>
       <c r="AQ79" s="4" t="n"/>
+      <c r="AR79" s="4" t="n"/>
+      <c r="AS79" s="4" t="n"/>
+      <c r="AT79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="N80" s="4" t="n"/>
@@ -3360,6 +3612,9 @@
       <c r="AO80" s="4" t="n"/>
       <c r="AP80" s="4" t="n"/>
       <c r="AQ80" s="4" t="n"/>
+      <c r="AR80" s="4" t="n"/>
+      <c r="AS80" s="4" t="n"/>
+      <c r="AT80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="N81" s="4" t="n"/>
@@ -3392,6 +3647,9 @@
       <c r="AO81" s="4" t="n"/>
       <c r="AP81" s="4" t="n"/>
       <c r="AQ81" s="4" t="n"/>
+      <c r="AR81" s="4" t="n"/>
+      <c r="AS81" s="4" t="n"/>
+      <c r="AT81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="N82" s="4" t="n"/>
@@ -3424,6 +3682,9 @@
       <c r="AO82" s="4" t="n"/>
       <c r="AP82" s="4" t="n"/>
       <c r="AQ82" s="4" t="n"/>
+      <c r="AR82" s="4" t="n"/>
+      <c r="AS82" s="4" t="n"/>
+      <c r="AT82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="N83" s="4" t="n"/>
@@ -3456,6 +3717,9 @@
       <c r="AO83" s="4" t="n"/>
       <c r="AP83" s="4" t="n"/>
       <c r="AQ83" s="4" t="n"/>
+      <c r="AR83" s="4" t="n"/>
+      <c r="AS83" s="4" t="n"/>
+      <c r="AT83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="N84" s="4" t="n"/>
@@ -3488,6 +3752,9 @@
       <c r="AO84" s="4" t="n"/>
       <c r="AP84" s="4" t="n"/>
       <c r="AQ84" s="4" t="n"/>
+      <c r="AR84" s="4" t="n"/>
+      <c r="AS84" s="4" t="n"/>
+      <c r="AT84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="N85" s="4" t="n"/>
@@ -3520,6 +3787,9 @@
       <c r="AO85" s="4" t="n"/>
       <c r="AP85" s="4" t="n"/>
       <c r="AQ85" s="4" t="n"/>
+      <c r="AR85" s="4" t="n"/>
+      <c r="AS85" s="4" t="n"/>
+      <c r="AT85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="N86" s="4" t="n"/>
@@ -3552,6 +3822,9 @@
       <c r="AO86" s="4" t="n"/>
       <c r="AP86" s="4" t="n"/>
       <c r="AQ86" s="4" t="n"/>
+      <c r="AR86" s="4" t="n"/>
+      <c r="AS86" s="4" t="n"/>
+      <c r="AT86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="N87" s="4" t="n"/>
@@ -3584,6 +3857,9 @@
       <c r="AO87" s="4" t="n"/>
       <c r="AP87" s="4" t="n"/>
       <c r="AQ87" s="4" t="n"/>
+      <c r="AR87" s="4" t="n"/>
+      <c r="AS87" s="4" t="n"/>
+      <c r="AT87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="N88" s="4" t="n"/>
@@ -3616,6 +3892,9 @@
       <c r="AO88" s="4" t="n"/>
       <c r="AP88" s="4" t="n"/>
       <c r="AQ88" s="4" t="n"/>
+      <c r="AR88" s="4" t="n"/>
+      <c r="AS88" s="4" t="n"/>
+      <c r="AT88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="N89" s="4" t="n"/>
@@ -3648,6 +3927,9 @@
       <c r="AO89" s="4" t="n"/>
       <c r="AP89" s="4" t="n"/>
       <c r="AQ89" s="4" t="n"/>
+      <c r="AR89" s="4" t="n"/>
+      <c r="AS89" s="4" t="n"/>
+      <c r="AT89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="N90" s="4" t="n"/>
@@ -3680,6 +3962,9 @@
       <c r="AO90" s="4" t="n"/>
       <c r="AP90" s="4" t="n"/>
       <c r="AQ90" s="4" t="n"/>
+      <c r="AR90" s="4" t="n"/>
+      <c r="AS90" s="4" t="n"/>
+      <c r="AT90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="N91" s="4" t="n"/>
@@ -3712,6 +3997,9 @@
       <c r="AO91" s="4" t="n"/>
       <c r="AP91" s="4" t="n"/>
       <c r="AQ91" s="4" t="n"/>
+      <c r="AR91" s="4" t="n"/>
+      <c r="AS91" s="4" t="n"/>
+      <c r="AT91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="N92" s="4" t="n"/>
@@ -3744,6 +4032,9 @@
       <c r="AO92" s="4" t="n"/>
       <c r="AP92" s="4" t="n"/>
       <c r="AQ92" s="4" t="n"/>
+      <c r="AR92" s="4" t="n"/>
+      <c r="AS92" s="4" t="n"/>
+      <c r="AT92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="N93" s="4" t="n"/>
@@ -3776,6 +4067,9 @@
       <c r="AO93" s="4" t="n"/>
       <c r="AP93" s="4" t="n"/>
       <c r="AQ93" s="4" t="n"/>
+      <c r="AR93" s="4" t="n"/>
+      <c r="AS93" s="4" t="n"/>
+      <c r="AT93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="N94" s="4" t="n"/>
@@ -3808,6 +4102,9 @@
       <c r="AO94" s="4" t="n"/>
       <c r="AP94" s="4" t="n"/>
       <c r="AQ94" s="4" t="n"/>
+      <c r="AR94" s="4" t="n"/>
+      <c r="AS94" s="4" t="n"/>
+      <c r="AT94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="N95" s="4" t="n"/>
@@ -3840,6 +4137,9 @@
       <c r="AO95" s="4" t="n"/>
       <c r="AP95" s="4" t="n"/>
       <c r="AQ95" s="4" t="n"/>
+      <c r="AR95" s="4" t="n"/>
+      <c r="AS95" s="4" t="n"/>
+      <c r="AT95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="N96" s="4" t="n"/>
@@ -3872,6 +4172,9 @@
       <c r="AO96" s="4" t="n"/>
       <c r="AP96" s="4" t="n"/>
       <c r="AQ96" s="4" t="n"/>
+      <c r="AR96" s="4" t="n"/>
+      <c r="AS96" s="4" t="n"/>
+      <c r="AT96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="N97" s="4" t="n"/>
@@ -3904,6 +4207,9 @@
       <c r="AO97" s="4" t="n"/>
       <c r="AP97" s="4" t="n"/>
       <c r="AQ97" s="4" t="n"/>
+      <c r="AR97" s="4" t="n"/>
+      <c r="AS97" s="4" t="n"/>
+      <c r="AT97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="N98" s="4" t="n"/>
@@ -3936,6 +4242,9 @@
       <c r="AO98" s="4" t="n"/>
       <c r="AP98" s="4" t="n"/>
       <c r="AQ98" s="4" t="n"/>
+      <c r="AR98" s="4" t="n"/>
+      <c r="AS98" s="4" t="n"/>
+      <c r="AT98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="N99" s="4" t="n"/>
@@ -3968,6 +4277,9 @@
       <c r="AO99" s="4" t="n"/>
       <c r="AP99" s="4" t="n"/>
       <c r="AQ99" s="4" t="n"/>
+      <c r="AR99" s="4" t="n"/>
+      <c r="AS99" s="4" t="n"/>
+      <c r="AT99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="N100" s="4" t="n"/>
@@ -4000,6 +4312,9 @@
       <c r="AO100" s="4" t="n"/>
       <c r="AP100" s="4" t="n"/>
       <c r="AQ100" s="4" t="n"/>
+      <c r="AR100" s="4" t="n"/>
+      <c r="AS100" s="4" t="n"/>
+      <c r="AT100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="N101" s="4" t="n"/>
@@ -4032,6 +4347,9 @@
       <c r="AO101" s="4" t="n"/>
       <c r="AP101" s="4" t="n"/>
       <c r="AQ101" s="4" t="n"/>
+      <c r="AR101" s="4" t="n"/>
+      <c r="AS101" s="4" t="n"/>
+      <c r="AT101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="N102" s="4" t="n"/>
@@ -4064,6 +4382,9 @@
       <c r="AO102" s="4" t="n"/>
       <c r="AP102" s="4" t="n"/>
       <c r="AQ102" s="4" t="n"/>
+      <c r="AR102" s="4" t="n"/>
+      <c r="AS102" s="4" t="n"/>
+      <c r="AT102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="N103" s="4" t="n"/>
@@ -4096,6 +4417,9 @@
       <c r="AO103" s="4" t="n"/>
       <c r="AP103" s="4" t="n"/>
       <c r="AQ103" s="4" t="n"/>
+      <c r="AR103" s="4" t="n"/>
+      <c r="AS103" s="4" t="n"/>
+      <c r="AT103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="N104" s="4" t="n"/>
@@ -4128,6 +4452,9 @@
       <c r="AO104" s="4" t="n"/>
       <c r="AP104" s="4" t="n"/>
       <c r="AQ104" s="4" t="n"/>
+      <c r="AR104" s="4" t="n"/>
+      <c r="AS104" s="4" t="n"/>
+      <c r="AT104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="N105" s="4" t="n"/>
@@ -4160,6 +4487,9 @@
       <c r="AO105" s="4" t="n"/>
       <c r="AP105" s="4" t="n"/>
       <c r="AQ105" s="4" t="n"/>
+      <c r="AR105" s="4" t="n"/>
+      <c r="AS105" s="4" t="n"/>
+      <c r="AT105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="N106" s="4" t="n"/>
@@ -4192,6 +4522,9 @@
       <c r="AO106" s="4" t="n"/>
       <c r="AP106" s="4" t="n"/>
       <c r="AQ106" s="4" t="n"/>
+      <c r="AR106" s="4" t="n"/>
+      <c r="AS106" s="4" t="n"/>
+      <c r="AT106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="N107" s="4" t="n"/>
@@ -4224,6 +4557,9 @@
       <c r="AO107" s="4" t="n"/>
       <c r="AP107" s="4" t="n"/>
       <c r="AQ107" s="4" t="n"/>
+      <c r="AR107" s="4" t="n"/>
+      <c r="AS107" s="4" t="n"/>
+      <c r="AT107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="N108" s="4" t="n"/>
@@ -4256,6 +4592,9 @@
       <c r="AO108" s="4" t="n"/>
       <c r="AP108" s="4" t="n"/>
       <c r="AQ108" s="4" t="n"/>
+      <c r="AR108" s="4" t="n"/>
+      <c r="AS108" s="4" t="n"/>
+      <c r="AT108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="N109" s="4" t="n"/>
@@ -4288,6 +4627,9 @@
       <c r="AO109" s="4" t="n"/>
       <c r="AP109" s="4" t="n"/>
       <c r="AQ109" s="4" t="n"/>
+      <c r="AR109" s="4" t="n"/>
+      <c r="AS109" s="4" t="n"/>
+      <c r="AT109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="N110" s="4" t="n"/>
@@ -4320,6 +4662,9 @@
       <c r="AO110" s="4" t="n"/>
       <c r="AP110" s="4" t="n"/>
       <c r="AQ110" s="4" t="n"/>
+      <c r="AR110" s="4" t="n"/>
+      <c r="AS110" s="4" t="n"/>
+      <c r="AT110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="N111" s="4" t="n"/>
@@ -4352,6 +4697,9 @@
       <c r="AO111" s="4" t="n"/>
       <c r="AP111" s="4" t="n"/>
       <c r="AQ111" s="4" t="n"/>
+      <c r="AR111" s="4" t="n"/>
+      <c r="AS111" s="4" t="n"/>
+      <c r="AT111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="N112" s="4" t="n"/>
@@ -4384,6 +4732,9 @@
       <c r="AO112" s="4" t="n"/>
       <c r="AP112" s="4" t="n"/>
       <c r="AQ112" s="4" t="n"/>
+      <c r="AR112" s="4" t="n"/>
+      <c r="AS112" s="4" t="n"/>
+      <c r="AT112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="N113" s="4" t="n"/>
@@ -4416,6 +4767,9 @@
       <c r="AO113" s="4" t="n"/>
       <c r="AP113" s="4" t="n"/>
       <c r="AQ113" s="4" t="n"/>
+      <c r="AR113" s="4" t="n"/>
+      <c r="AS113" s="4" t="n"/>
+      <c r="AT113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="N114" s="4" t="n"/>
@@ -4448,6 +4802,9 @@
       <c r="AO114" s="4" t="n"/>
       <c r="AP114" s="4" t="n"/>
       <c r="AQ114" s="4" t="n"/>
+      <c r="AR114" s="4" t="n"/>
+      <c r="AS114" s="4" t="n"/>
+      <c r="AT114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="N115" s="4" t="n"/>
@@ -4480,6 +4837,9 @@
       <c r="AO115" s="4" t="n"/>
       <c r="AP115" s="4" t="n"/>
       <c r="AQ115" s="4" t="n"/>
+      <c r="AR115" s="4" t="n"/>
+      <c r="AS115" s="4" t="n"/>
+      <c r="AT115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="N116" s="4" t="n"/>
@@ -4512,6 +4872,9 @@
       <c r="AO116" s="4" t="n"/>
       <c r="AP116" s="4" t="n"/>
       <c r="AQ116" s="4" t="n"/>
+      <c r="AR116" s="4" t="n"/>
+      <c r="AS116" s="4" t="n"/>
+      <c r="AT116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="N117" s="4" t="n"/>
@@ -4544,6 +4907,9 @@
       <c r="AO117" s="4" t="n"/>
       <c r="AP117" s="4" t="n"/>
       <c r="AQ117" s="4" t="n"/>
+      <c r="AR117" s="4" t="n"/>
+      <c r="AS117" s="4" t="n"/>
+      <c r="AT117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="N118" s="4" t="n"/>
@@ -4576,6 +4942,9 @@
       <c r="AO118" s="4" t="n"/>
       <c r="AP118" s="4" t="n"/>
       <c r="AQ118" s="4" t="n"/>
+      <c r="AR118" s="4" t="n"/>
+      <c r="AS118" s="4" t="n"/>
+      <c r="AT118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="N119" s="4" t="n"/>
@@ -4608,6 +4977,9 @@
       <c r="AO119" s="4" t="n"/>
       <c r="AP119" s="4" t="n"/>
       <c r="AQ119" s="4" t="n"/>
+      <c r="AR119" s="4" t="n"/>
+      <c r="AS119" s="4" t="n"/>
+      <c r="AT119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="N120" s="4" t="n"/>
@@ -4640,6 +5012,9 @@
       <c r="AO120" s="4" t="n"/>
       <c r="AP120" s="4" t="n"/>
       <c r="AQ120" s="4" t="n"/>
+      <c r="AR120" s="4" t="n"/>
+      <c r="AS120" s="4" t="n"/>
+      <c r="AT120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="N121" s="4" t="n"/>
@@ -4672,6 +5047,9 @@
       <c r="AO121" s="4" t="n"/>
       <c r="AP121" s="4" t="n"/>
       <c r="AQ121" s="4" t="n"/>
+      <c r="AR121" s="4" t="n"/>
+      <c r="AS121" s="4" t="n"/>
+      <c r="AT121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="N122" s="4" t="n"/>
@@ -4704,6 +5082,9 @@
       <c r="AO122" s="4" t="n"/>
       <c r="AP122" s="4" t="n"/>
       <c r="AQ122" s="4" t="n"/>
+      <c r="AR122" s="4" t="n"/>
+      <c r="AS122" s="4" t="n"/>
+      <c r="AT122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="N123" s="4" t="n"/>
@@ -4736,6 +5117,9 @@
       <c r="AO123" s="4" t="n"/>
       <c r="AP123" s="4" t="n"/>
       <c r="AQ123" s="4" t="n"/>
+      <c r="AR123" s="4" t="n"/>
+      <c r="AS123" s="4" t="n"/>
+      <c r="AT123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="N124" s="4" t="n"/>
@@ -4768,6 +5152,9 @@
       <c r="AO124" s="4" t="n"/>
       <c r="AP124" s="4" t="n"/>
       <c r="AQ124" s="4" t="n"/>
+      <c r="AR124" s="4" t="n"/>
+      <c r="AS124" s="4" t="n"/>
+      <c r="AT124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="N125" s="4" t="n"/>
@@ -4800,6 +5187,9 @@
       <c r="AO125" s="4" t="n"/>
       <c r="AP125" s="4" t="n"/>
       <c r="AQ125" s="4" t="n"/>
+      <c r="AR125" s="4" t="n"/>
+      <c r="AS125" s="4" t="n"/>
+      <c r="AT125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="N126" s="4" t="n"/>
@@ -4832,6 +5222,9 @@
       <c r="AO126" s="4" t="n"/>
       <c r="AP126" s="4" t="n"/>
       <c r="AQ126" s="4" t="n"/>
+      <c r="AR126" s="4" t="n"/>
+      <c r="AS126" s="4" t="n"/>
+      <c r="AT126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="N127" s="4" t="n"/>
@@ -4864,6 +5257,9 @@
       <c r="AO127" s="4" t="n"/>
       <c r="AP127" s="4" t="n"/>
       <c r="AQ127" s="4" t="n"/>
+      <c r="AR127" s="4" t="n"/>
+      <c r="AS127" s="4" t="n"/>
+      <c r="AT127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="N128" s="4" t="n"/>
@@ -4896,6 +5292,9 @@
       <c r="AO128" s="4" t="n"/>
       <c r="AP128" s="4" t="n"/>
       <c r="AQ128" s="4" t="n"/>
+      <c r="AR128" s="4" t="n"/>
+      <c r="AS128" s="4" t="n"/>
+      <c r="AT128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="N129" s="4" t="n"/>
@@ -4928,6 +5327,9 @@
       <c r="AO129" s="4" t="n"/>
       <c r="AP129" s="4" t="n"/>
       <c r="AQ129" s="4" t="n"/>
+      <c r="AR129" s="4" t="n"/>
+      <c r="AS129" s="4" t="n"/>
+      <c r="AT129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="N130" s="4" t="n"/>
@@ -4960,6 +5362,9 @@
       <c r="AO130" s="4" t="n"/>
       <c r="AP130" s="4" t="n"/>
       <c r="AQ130" s="4" t="n"/>
+      <c r="AR130" s="4" t="n"/>
+      <c r="AS130" s="4" t="n"/>
+      <c r="AT130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="N131" s="4" t="n"/>
@@ -4992,6 +5397,9 @@
       <c r="AO131" s="4" t="n"/>
       <c r="AP131" s="4" t="n"/>
       <c r="AQ131" s="4" t="n"/>
+      <c r="AR131" s="4" t="n"/>
+      <c r="AS131" s="4" t="n"/>
+      <c r="AT131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="N132" s="4" t="n"/>
@@ -5024,6 +5432,9 @@
       <c r="AO132" s="4" t="n"/>
       <c r="AP132" s="4" t="n"/>
       <c r="AQ132" s="4" t="n"/>
+      <c r="AR132" s="4" t="n"/>
+      <c r="AS132" s="4" t="n"/>
+      <c r="AT132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="N133" s="4" t="n"/>
@@ -5056,6 +5467,9 @@
       <c r="AO133" s="4" t="n"/>
       <c r="AP133" s="4" t="n"/>
       <c r="AQ133" s="4" t="n"/>
+      <c r="AR133" s="4" t="n"/>
+      <c r="AS133" s="4" t="n"/>
+      <c r="AT133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="N134" s="4" t="n"/>
@@ -5088,6 +5502,9 @@
       <c r="AO134" s="4" t="n"/>
       <c r="AP134" s="4" t="n"/>
       <c r="AQ134" s="4" t="n"/>
+      <c r="AR134" s="4" t="n"/>
+      <c r="AS134" s="4" t="n"/>
+      <c r="AT134" s="4" t="n"/>
     </row>
     <row r="135">
       <c r="N135" s="4" t="n"/>
@@ -5120,6 +5537,9 @@
       <c r="AO135" s="4" t="n"/>
       <c r="AP135" s="4" t="n"/>
       <c r="AQ135" s="4" t="n"/>
+      <c r="AR135" s="4" t="n"/>
+      <c r="AS135" s="4" t="n"/>
+      <c r="AT135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="N136" s="4" t="n"/>
@@ -5152,6 +5572,9 @@
       <c r="AO136" s="4" t="n"/>
       <c r="AP136" s="4" t="n"/>
       <c r="AQ136" s="4" t="n"/>
+      <c r="AR136" s="4" t="n"/>
+      <c r="AS136" s="4" t="n"/>
+      <c r="AT136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="N137" s="4" t="n"/>
@@ -5184,6 +5607,9 @@
       <c r="AO137" s="4" t="n"/>
       <c r="AP137" s="4" t="n"/>
       <c r="AQ137" s="4" t="n"/>
+      <c r="AR137" s="4" t="n"/>
+      <c r="AS137" s="4" t="n"/>
+      <c r="AT137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="N138" s="4" t="n"/>
@@ -5216,6 +5642,9 @@
       <c r="AO138" s="4" t="n"/>
       <c r="AP138" s="4" t="n"/>
       <c r="AQ138" s="4" t="n"/>
+      <c r="AR138" s="4" t="n"/>
+      <c r="AS138" s="4" t="n"/>
+      <c r="AT138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="N139" s="4" t="n"/>
@@ -5248,6 +5677,9 @@
       <c r="AO139" s="4" t="n"/>
       <c r="AP139" s="4" t="n"/>
       <c r="AQ139" s="4" t="n"/>
+      <c r="AR139" s="4" t="n"/>
+      <c r="AS139" s="4" t="n"/>
+      <c r="AT139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="N140" s="4" t="n"/>
@@ -5280,6 +5712,9 @@
       <c r="AO140" s="4" t="n"/>
       <c r="AP140" s="4" t="n"/>
       <c r="AQ140" s="4" t="n"/>
+      <c r="AR140" s="4" t="n"/>
+      <c r="AS140" s="4" t="n"/>
+      <c r="AT140" s="4" t="n"/>
     </row>
     <row r="141">
       <c r="N141" s="4" t="n"/>
@@ -5312,6 +5747,9 @@
       <c r="AO141" s="4" t="n"/>
       <c r="AP141" s="4" t="n"/>
       <c r="AQ141" s="4" t="n"/>
+      <c r="AR141" s="4" t="n"/>
+      <c r="AS141" s="4" t="n"/>
+      <c r="AT141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="N142" s="4" t="n"/>
@@ -5344,6 +5782,9 @@
       <c r="AO142" s="4" t="n"/>
       <c r="AP142" s="4" t="n"/>
       <c r="AQ142" s="4" t="n"/>
+      <c r="AR142" s="4" t="n"/>
+      <c r="AS142" s="4" t="n"/>
+      <c r="AT142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="N143" s="4" t="n"/>
@@ -5376,6 +5817,9 @@
       <c r="AO143" s="4" t="n"/>
       <c r="AP143" s="4" t="n"/>
       <c r="AQ143" s="4" t="n"/>
+      <c r="AR143" s="4" t="n"/>
+      <c r="AS143" s="4" t="n"/>
+      <c r="AT143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="N144" s="4" t="n"/>
@@ -5408,6 +5852,9 @@
       <c r="AO144" s="4" t="n"/>
       <c r="AP144" s="4" t="n"/>
       <c r="AQ144" s="4" t="n"/>
+      <c r="AR144" s="4" t="n"/>
+      <c r="AS144" s="4" t="n"/>
+      <c r="AT144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="N145" s="4" t="n"/>
@@ -5440,6 +5887,9 @@
       <c r="AO145" s="4" t="n"/>
       <c r="AP145" s="4" t="n"/>
       <c r="AQ145" s="4" t="n"/>
+      <c r="AR145" s="4" t="n"/>
+      <c r="AS145" s="4" t="n"/>
+      <c r="AT145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="N146" s="4" t="n"/>
@@ -5472,6 +5922,9 @@
       <c r="AO146" s="4" t="n"/>
       <c r="AP146" s="4" t="n"/>
       <c r="AQ146" s="4" t="n"/>
+      <c r="AR146" s="4" t="n"/>
+      <c r="AS146" s="4" t="n"/>
+      <c r="AT146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="N147" s="4" t="n"/>
@@ -5504,6 +5957,9 @@
       <c r="AO147" s="4" t="n"/>
       <c r="AP147" s="4" t="n"/>
       <c r="AQ147" s="4" t="n"/>
+      <c r="AR147" s="4" t="n"/>
+      <c r="AS147" s="4" t="n"/>
+      <c r="AT147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="N148" s="4" t="n"/>
@@ -5536,6 +5992,9 @@
       <c r="AO148" s="4" t="n"/>
       <c r="AP148" s="4" t="n"/>
       <c r="AQ148" s="4" t="n"/>
+      <c r="AR148" s="4" t="n"/>
+      <c r="AS148" s="4" t="n"/>
+      <c r="AT148" s="4" t="n"/>
     </row>
     <row r="149">
       <c r="N149" s="4" t="n"/>
@@ -5568,6 +6027,9 @@
       <c r="AO149" s="4" t="n"/>
       <c r="AP149" s="4" t="n"/>
       <c r="AQ149" s="4" t="n"/>
+      <c r="AR149" s="4" t="n"/>
+      <c r="AS149" s="4" t="n"/>
+      <c r="AT149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="N150" s="4" t="n"/>
@@ -5600,6 +6062,9 @@
       <c r="AO150" s="4" t="n"/>
       <c r="AP150" s="4" t="n"/>
       <c r="AQ150" s="4" t="n"/>
+      <c r="AR150" s="4" t="n"/>
+      <c r="AS150" s="4" t="n"/>
+      <c r="AT150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="N151" s="4" t="n"/>
@@ -5632,6 +6097,9 @@
       <c r="AO151" s="4" t="n"/>
       <c r="AP151" s="4" t="n"/>
       <c r="AQ151" s="4" t="n"/>
+      <c r="AR151" s="4" t="n"/>
+      <c r="AS151" s="4" t="n"/>
+      <c r="AT151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="N152" s="4" t="n"/>
@@ -5664,6 +6132,9 @@
       <c r="AO152" s="4" t="n"/>
       <c r="AP152" s="4" t="n"/>
       <c r="AQ152" s="4" t="n"/>
+      <c r="AR152" s="4" t="n"/>
+      <c r="AS152" s="4" t="n"/>
+      <c r="AT152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="N153" s="4" t="n"/>
@@ -5696,6 +6167,9 @@
       <c r="AO153" s="4" t="n"/>
       <c r="AP153" s="4" t="n"/>
       <c r="AQ153" s="4" t="n"/>
+      <c r="AR153" s="4" t="n"/>
+      <c r="AS153" s="4" t="n"/>
+      <c r="AT153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="N154" s="4" t="n"/>
@@ -5728,6 +6202,9 @@
       <c r="AO154" s="4" t="n"/>
       <c r="AP154" s="4" t="n"/>
       <c r="AQ154" s="4" t="n"/>
+      <c r="AR154" s="4" t="n"/>
+      <c r="AS154" s="4" t="n"/>
+      <c r="AT154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="N155" s="4" t="n"/>
@@ -5760,6 +6237,9 @@
       <c r="AO155" s="4" t="n"/>
       <c r="AP155" s="4" t="n"/>
       <c r="AQ155" s="4" t="n"/>
+      <c r="AR155" s="4" t="n"/>
+      <c r="AS155" s="4" t="n"/>
+      <c r="AT155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="N156" s="4" t="n"/>
@@ -5792,6 +6272,9 @@
       <c r="AO156" s="4" t="n"/>
       <c r="AP156" s="4" t="n"/>
       <c r="AQ156" s="4" t="n"/>
+      <c r="AR156" s="4" t="n"/>
+      <c r="AS156" s="4" t="n"/>
+      <c r="AT156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="N157" s="4" t="n"/>
@@ -5824,6 +6307,9 @@
       <c r="AO157" s="4" t="n"/>
       <c r="AP157" s="4" t="n"/>
       <c r="AQ157" s="4" t="n"/>
+      <c r="AR157" s="4" t="n"/>
+      <c r="AS157" s="4" t="n"/>
+      <c r="AT157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="N158" s="4" t="n"/>
@@ -5856,6 +6342,9 @@
       <c r="AO158" s="4" t="n"/>
       <c r="AP158" s="4" t="n"/>
       <c r="AQ158" s="4" t="n"/>
+      <c r="AR158" s="4" t="n"/>
+      <c r="AS158" s="4" t="n"/>
+      <c r="AT158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="N159" s="4" t="n"/>
@@ -5888,6 +6377,9 @@
       <c r="AO159" s="4" t="n"/>
       <c r="AP159" s="4" t="n"/>
       <c r="AQ159" s="4" t="n"/>
+      <c r="AR159" s="4" t="n"/>
+      <c r="AS159" s="4" t="n"/>
+      <c r="AT159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="N160" s="4" t="n"/>
@@ -5920,6 +6412,9 @@
       <c r="AO160" s="4" t="n"/>
       <c r="AP160" s="4" t="n"/>
       <c r="AQ160" s="4" t="n"/>
+      <c r="AR160" s="4" t="n"/>
+      <c r="AS160" s="4" t="n"/>
+      <c r="AT160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="N161" s="4" t="n"/>
@@ -5952,6 +6447,9 @@
       <c r="AO161" s="4" t="n"/>
       <c r="AP161" s="4" t="n"/>
       <c r="AQ161" s="4" t="n"/>
+      <c r="AR161" s="4" t="n"/>
+      <c r="AS161" s="4" t="n"/>
+      <c r="AT161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="N162" s="4" t="n"/>
@@ -5984,6 +6482,9 @@
       <c r="AO162" s="4" t="n"/>
       <c r="AP162" s="4" t="n"/>
       <c r="AQ162" s="4" t="n"/>
+      <c r="AR162" s="4" t="n"/>
+      <c r="AS162" s="4" t="n"/>
+      <c r="AT162" s="4" t="n"/>
     </row>
     <row r="163">
       <c r="N163" s="4" t="n"/>
@@ -6016,6 +6517,9 @@
       <c r="AO163" s="4" t="n"/>
       <c r="AP163" s="4" t="n"/>
       <c r="AQ163" s="4" t="n"/>
+      <c r="AR163" s="4" t="n"/>
+      <c r="AS163" s="4" t="n"/>
+      <c r="AT163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="N164" s="4" t="n"/>
@@ -6048,6 +6552,9 @@
       <c r="AO164" s="4" t="n"/>
       <c r="AP164" s="4" t="n"/>
       <c r="AQ164" s="4" t="n"/>
+      <c r="AR164" s="4" t="n"/>
+      <c r="AS164" s="4" t="n"/>
+      <c r="AT164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="N165" s="4" t="n"/>
@@ -6080,6 +6587,9 @@
       <c r="AO165" s="4" t="n"/>
       <c r="AP165" s="4" t="n"/>
       <c r="AQ165" s="4" t="n"/>
+      <c r="AR165" s="4" t="n"/>
+      <c r="AS165" s="4" t="n"/>
+      <c r="AT165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="N166" s="4" t="n"/>
@@ -6112,6 +6622,9 @@
       <c r="AO166" s="4" t="n"/>
       <c r="AP166" s="4" t="n"/>
       <c r="AQ166" s="4" t="n"/>
+      <c r="AR166" s="4" t="n"/>
+      <c r="AS166" s="4" t="n"/>
+      <c r="AT166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="N167" s="4" t="n"/>
@@ -6144,6 +6657,9 @@
       <c r="AO167" s="4" t="n"/>
       <c r="AP167" s="4" t="n"/>
       <c r="AQ167" s="4" t="n"/>
+      <c r="AR167" s="4" t="n"/>
+      <c r="AS167" s="4" t="n"/>
+      <c r="AT167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="N168" s="4" t="n"/>
@@ -6176,6 +6692,9 @@
       <c r="AO168" s="4" t="n"/>
       <c r="AP168" s="4" t="n"/>
       <c r="AQ168" s="4" t="n"/>
+      <c r="AR168" s="4" t="n"/>
+      <c r="AS168" s="4" t="n"/>
+      <c r="AT168" s="4" t="n"/>
     </row>
     <row r="169">
       <c r="N169" s="4" t="n"/>
@@ -6208,6 +6727,9 @@
       <c r="AO169" s="4" t="n"/>
       <c r="AP169" s="4" t="n"/>
       <c r="AQ169" s="4" t="n"/>
+      <c r="AR169" s="4" t="n"/>
+      <c r="AS169" s="4" t="n"/>
+      <c r="AT169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="N170" s="4" t="n"/>
@@ -6240,6 +6762,9 @@
       <c r="AO170" s="4" t="n"/>
       <c r="AP170" s="4" t="n"/>
       <c r="AQ170" s="4" t="n"/>
+      <c r="AR170" s="4" t="n"/>
+      <c r="AS170" s="4" t="n"/>
+      <c r="AT170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="N171" s="4" t="n"/>
@@ -6272,6 +6797,9 @@
       <c r="AO171" s="4" t="n"/>
       <c r="AP171" s="4" t="n"/>
       <c r="AQ171" s="4" t="n"/>
+      <c r="AR171" s="4" t="n"/>
+      <c r="AS171" s="4" t="n"/>
+      <c r="AT171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="N172" s="4" t="n"/>
@@ -6304,6 +6832,9 @@
       <c r="AO172" s="4" t="n"/>
       <c r="AP172" s="4" t="n"/>
       <c r="AQ172" s="4" t="n"/>
+      <c r="AR172" s="4" t="n"/>
+      <c r="AS172" s="4" t="n"/>
+      <c r="AT172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="N173" s="4" t="n"/>
@@ -6336,6 +6867,9 @@
       <c r="AO173" s="4" t="n"/>
       <c r="AP173" s="4" t="n"/>
       <c r="AQ173" s="4" t="n"/>
+      <c r="AR173" s="4" t="n"/>
+      <c r="AS173" s="4" t="n"/>
+      <c r="AT173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="N174" s="4" t="n"/>
@@ -6368,6 +6902,9 @@
       <c r="AO174" s="4" t="n"/>
       <c r="AP174" s="4" t="n"/>
       <c r="AQ174" s="4" t="n"/>
+      <c r="AR174" s="4" t="n"/>
+      <c r="AS174" s="4" t="n"/>
+      <c r="AT174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="N175" s="4" t="n"/>
@@ -6400,6 +6937,9 @@
       <c r="AO175" s="4" t="n"/>
       <c r="AP175" s="4" t="n"/>
       <c r="AQ175" s="4" t="n"/>
+      <c r="AR175" s="4" t="n"/>
+      <c r="AS175" s="4" t="n"/>
+      <c r="AT175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="N176" s="4" t="n"/>
@@ -6432,6 +6972,9 @@
       <c r="AO176" s="4" t="n"/>
       <c r="AP176" s="4" t="n"/>
       <c r="AQ176" s="4" t="n"/>
+      <c r="AR176" s="4" t="n"/>
+      <c r="AS176" s="4" t="n"/>
+      <c r="AT176" s="4" t="n"/>
     </row>
     <row r="177">
       <c r="N177" s="4" t="n"/>
@@ -6464,6 +7007,9 @@
       <c r="AO177" s="4" t="n"/>
       <c r="AP177" s="4" t="n"/>
       <c r="AQ177" s="4" t="n"/>
+      <c r="AR177" s="4" t="n"/>
+      <c r="AS177" s="4" t="n"/>
+      <c r="AT177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="N178" s="4" t="n"/>
@@ -6496,6 +7042,9 @@
       <c r="AO178" s="4" t="n"/>
       <c r="AP178" s="4" t="n"/>
       <c r="AQ178" s="4" t="n"/>
+      <c r="AR178" s="4" t="n"/>
+      <c r="AS178" s="4" t="n"/>
+      <c r="AT178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="N179" s="4" t="n"/>
@@ -6528,6 +7077,9 @@
       <c r="AO179" s="4" t="n"/>
       <c r="AP179" s="4" t="n"/>
       <c r="AQ179" s="4" t="n"/>
+      <c r="AR179" s="4" t="n"/>
+      <c r="AS179" s="4" t="n"/>
+      <c r="AT179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="N180" s="4" t="n"/>
@@ -6560,6 +7112,9 @@
       <c r="AO180" s="4" t="n"/>
       <c r="AP180" s="4" t="n"/>
       <c r="AQ180" s="4" t="n"/>
+      <c r="AR180" s="4" t="n"/>
+      <c r="AS180" s="4" t="n"/>
+      <c r="AT180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="N181" s="4" t="n"/>
@@ -6592,6 +7147,9 @@
       <c r="AO181" s="4" t="n"/>
       <c r="AP181" s="4" t="n"/>
       <c r="AQ181" s="4" t="n"/>
+      <c r="AR181" s="4" t="n"/>
+      <c r="AS181" s="4" t="n"/>
+      <c r="AT181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="N182" s="4" t="n"/>
@@ -6624,6 +7182,9 @@
       <c r="AO182" s="4" t="n"/>
       <c r="AP182" s="4" t="n"/>
       <c r="AQ182" s="4" t="n"/>
+      <c r="AR182" s="4" t="n"/>
+      <c r="AS182" s="4" t="n"/>
+      <c r="AT182" s="4" t="n"/>
     </row>
     <row r="183">
       <c r="N183" s="4" t="n"/>
@@ -6656,6 +7217,9 @@
       <c r="AO183" s="4" t="n"/>
       <c r="AP183" s="4" t="n"/>
       <c r="AQ183" s="4" t="n"/>
+      <c r="AR183" s="4" t="n"/>
+      <c r="AS183" s="4" t="n"/>
+      <c r="AT183" s="4" t="n"/>
     </row>
     <row r="184">
       <c r="N184" s="4" t="n"/>
@@ -6688,6 +7252,9 @@
       <c r="AO184" s="4" t="n"/>
       <c r="AP184" s="4" t="n"/>
       <c r="AQ184" s="4" t="n"/>
+      <c r="AR184" s="4" t="n"/>
+      <c r="AS184" s="4" t="n"/>
+      <c r="AT184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="N185" s="4" t="n"/>
@@ -6720,6 +7287,9 @@
       <c r="AO185" s="4" t="n"/>
       <c r="AP185" s="4" t="n"/>
       <c r="AQ185" s="4" t="n"/>
+      <c r="AR185" s="4" t="n"/>
+      <c r="AS185" s="4" t="n"/>
+      <c r="AT185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="N186" s="4" t="n"/>
@@ -6752,6 +7322,9 @@
       <c r="AO186" s="4" t="n"/>
       <c r="AP186" s="4" t="n"/>
       <c r="AQ186" s="4" t="n"/>
+      <c r="AR186" s="4" t="n"/>
+      <c r="AS186" s="4" t="n"/>
+      <c r="AT186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="N187" s="4" t="n"/>
@@ -6784,6 +7357,9 @@
       <c r="AO187" s="4" t="n"/>
       <c r="AP187" s="4" t="n"/>
       <c r="AQ187" s="4" t="n"/>
+      <c r="AR187" s="4" t="n"/>
+      <c r="AS187" s="4" t="n"/>
+      <c r="AT187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="N188" s="4" t="n"/>
@@ -6816,6 +7392,9 @@
       <c r="AO188" s="4" t="n"/>
       <c r="AP188" s="4" t="n"/>
       <c r="AQ188" s="4" t="n"/>
+      <c r="AR188" s="4" t="n"/>
+      <c r="AS188" s="4" t="n"/>
+      <c r="AT188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="N189" s="4" t="n"/>
@@ -6848,6 +7427,9 @@
       <c r="AO189" s="4" t="n"/>
       <c r="AP189" s="4" t="n"/>
       <c r="AQ189" s="4" t="n"/>
+      <c r="AR189" s="4" t="n"/>
+      <c r="AS189" s="4" t="n"/>
+      <c r="AT189" s="4" t="n"/>
     </row>
     <row r="190">
       <c r="N190" s="4" t="n"/>
@@ -6880,6 +7462,9 @@
       <c r="AO190" s="4" t="n"/>
       <c r="AP190" s="4" t="n"/>
       <c r="AQ190" s="4" t="n"/>
+      <c r="AR190" s="4" t="n"/>
+      <c r="AS190" s="4" t="n"/>
+      <c r="AT190" s="4" t="n"/>
     </row>
     <row r="191">
       <c r="N191" s="4" t="n"/>
@@ -6912,6 +7497,9 @@
       <c r="AO191" s="4" t="n"/>
       <c r="AP191" s="4" t="n"/>
       <c r="AQ191" s="4" t="n"/>
+      <c r="AR191" s="4" t="n"/>
+      <c r="AS191" s="4" t="n"/>
+      <c r="AT191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="N192" s="4" t="n"/>
@@ -6944,6 +7532,9 @@
       <c r="AO192" s="4" t="n"/>
       <c r="AP192" s="4" t="n"/>
       <c r="AQ192" s="4" t="n"/>
+      <c r="AR192" s="4" t="n"/>
+      <c r="AS192" s="4" t="n"/>
+      <c r="AT192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="N193" s="4" t="n"/>
@@ -6976,6 +7567,9 @@
       <c r="AO193" s="4" t="n"/>
       <c r="AP193" s="4" t="n"/>
       <c r="AQ193" s="4" t="n"/>
+      <c r="AR193" s="4" t="n"/>
+      <c r="AS193" s="4" t="n"/>
+      <c r="AT193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="N194" s="4" t="n"/>
@@ -7008,6 +7602,9 @@
       <c r="AO194" s="4" t="n"/>
       <c r="AP194" s="4" t="n"/>
       <c r="AQ194" s="4" t="n"/>
+      <c r="AR194" s="4" t="n"/>
+      <c r="AS194" s="4" t="n"/>
+      <c r="AT194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="N195" s="4" t="n"/>
@@ -7040,6 +7637,9 @@
       <c r="AO195" s="4" t="n"/>
       <c r="AP195" s="4" t="n"/>
       <c r="AQ195" s="4" t="n"/>
+      <c r="AR195" s="4" t="n"/>
+      <c r="AS195" s="4" t="n"/>
+      <c r="AT195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="N196" s="4" t="n"/>
@@ -7072,6 +7672,9 @@
       <c r="AO196" s="4" t="n"/>
       <c r="AP196" s="4" t="n"/>
       <c r="AQ196" s="4" t="n"/>
+      <c r="AR196" s="4" t="n"/>
+      <c r="AS196" s="4" t="n"/>
+      <c r="AT196" s="4" t="n"/>
     </row>
     <row r="197">
       <c r="N197" s="4" t="n"/>
@@ -7104,6 +7707,9 @@
       <c r="AO197" s="4" t="n"/>
       <c r="AP197" s="4" t="n"/>
       <c r="AQ197" s="4" t="n"/>
+      <c r="AR197" s="4" t="n"/>
+      <c r="AS197" s="4" t="n"/>
+      <c r="AT197" s="4" t="n"/>
     </row>
     <row r="198">
       <c r="N198" s="4" t="n"/>
@@ -7136,6 +7742,9 @@
       <c r="AO198" s="4" t="n"/>
       <c r="AP198" s="4" t="n"/>
       <c r="AQ198" s="4" t="n"/>
+      <c r="AR198" s="4" t="n"/>
+      <c r="AS198" s="4" t="n"/>
+      <c r="AT198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="N199" s="4" t="n"/>
@@ -7168,6 +7777,9 @@
       <c r="AO199" s="4" t="n"/>
       <c r="AP199" s="4" t="n"/>
       <c r="AQ199" s="4" t="n"/>
+      <c r="AR199" s="4" t="n"/>
+      <c r="AS199" s="4" t="n"/>
+      <c r="AT199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="N200" s="4" t="n"/>
@@ -7200,6 +7812,9 @@
       <c r="AO200" s="4" t="n"/>
       <c r="AP200" s="4" t="n"/>
       <c r="AQ200" s="4" t="n"/>
+      <c r="AR200" s="4" t="n"/>
+      <c r="AS200" s="4" t="n"/>
+      <c r="AT200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="N201" s="4" t="n"/>
@@ -7232,6 +7847,9 @@
       <c r="AO201" s="4" t="n"/>
       <c r="AP201" s="4" t="n"/>
       <c r="AQ201" s="4" t="n"/>
+      <c r="AR201" s="4" t="n"/>
+      <c r="AS201" s="4" t="n"/>
+      <c r="AT201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="N202" s="4" t="n"/>
@@ -7264,6 +7882,9 @@
       <c r="AO202" s="4" t="n"/>
       <c r="AP202" s="4" t="n"/>
       <c r="AQ202" s="4" t="n"/>
+      <c r="AR202" s="4" t="n"/>
+      <c r="AS202" s="4" t="n"/>
+      <c r="AT202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="N203" s="4" t="n"/>
@@ -7296,6 +7917,9 @@
       <c r="AO203" s="4" t="n"/>
       <c r="AP203" s="4" t="n"/>
       <c r="AQ203" s="4" t="n"/>
+      <c r="AR203" s="4" t="n"/>
+      <c r="AS203" s="4" t="n"/>
+      <c r="AT203" s="4" t="n"/>
     </row>
     <row r="204">
       <c r="N204" s="4" t="n"/>
@@ -7328,6 +7952,9 @@
       <c r="AO204" s="4" t="n"/>
       <c r="AP204" s="4" t="n"/>
       <c r="AQ204" s="4" t="n"/>
+      <c r="AR204" s="4" t="n"/>
+      <c r="AS204" s="4" t="n"/>
+      <c r="AT204" s="4" t="n"/>
     </row>
     <row r="205">
       <c r="N205" s="4" t="n"/>
@@ -7360,6 +7987,9 @@
       <c r="AO205" s="4" t="n"/>
       <c r="AP205" s="4" t="n"/>
       <c r="AQ205" s="4" t="n"/>
+      <c r="AR205" s="4" t="n"/>
+      <c r="AS205" s="4" t="n"/>
+      <c r="AT205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="N206" s="4" t="n"/>
@@ -7392,6 +8022,9 @@
       <c r="AO206" s="4" t="n"/>
       <c r="AP206" s="4" t="n"/>
       <c r="AQ206" s="4" t="n"/>
+      <c r="AR206" s="4" t="n"/>
+      <c r="AS206" s="4" t="n"/>
+      <c r="AT206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="N207" s="4" t="n"/>
@@ -7424,6 +8057,9 @@
       <c r="AO207" s="4" t="n"/>
       <c r="AP207" s="4" t="n"/>
       <c r="AQ207" s="4" t="n"/>
+      <c r="AR207" s="4" t="n"/>
+      <c r="AS207" s="4" t="n"/>
+      <c r="AT207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="N208" s="4" t="n"/>
@@ -7456,6 +8092,9 @@
       <c r="AO208" s="4" t="n"/>
       <c r="AP208" s="4" t="n"/>
       <c r="AQ208" s="4" t="n"/>
+      <c r="AR208" s="4" t="n"/>
+      <c r="AS208" s="4" t="n"/>
+      <c r="AT208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="N209" s="4" t="n"/>
@@ -7488,6 +8127,9 @@
       <c r="AO209" s="4" t="n"/>
       <c r="AP209" s="4" t="n"/>
       <c r="AQ209" s="4" t="n"/>
+      <c r="AR209" s="4" t="n"/>
+      <c r="AS209" s="4" t="n"/>
+      <c r="AT209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="N210" s="4" t="n"/>
@@ -7520,6 +8162,9 @@
       <c r="AO210" s="4" t="n"/>
       <c r="AP210" s="4" t="n"/>
       <c r="AQ210" s="4" t="n"/>
+      <c r="AR210" s="4" t="n"/>
+      <c r="AS210" s="4" t="n"/>
+      <c r="AT210" s="4" t="n"/>
     </row>
     <row r="211">
       <c r="N211" s="4" t="n"/>
@@ -7552,6 +8197,9 @@
       <c r="AO211" s="4" t="n"/>
       <c r="AP211" s="4" t="n"/>
       <c r="AQ211" s="4" t="n"/>
+      <c r="AR211" s="4" t="n"/>
+      <c r="AS211" s="4" t="n"/>
+      <c r="AT211" s="4" t="n"/>
     </row>
     <row r="212">
       <c r="N212" s="4" t="n"/>
@@ -7584,6 +8232,9 @@
       <c r="AO212" s="4" t="n"/>
       <c r="AP212" s="4" t="n"/>
       <c r="AQ212" s="4" t="n"/>
+      <c r="AR212" s="4" t="n"/>
+      <c r="AS212" s="4" t="n"/>
+      <c r="AT212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="N213" s="4" t="n"/>
@@ -7616,6 +8267,9 @@
       <c r="AO213" s="4" t="n"/>
       <c r="AP213" s="4" t="n"/>
       <c r="AQ213" s="4" t="n"/>
+      <c r="AR213" s="4" t="n"/>
+      <c r="AS213" s="4" t="n"/>
+      <c r="AT213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="N214" s="4" t="n"/>
@@ -7648,6 +8302,9 @@
       <c r="AO214" s="4" t="n"/>
       <c r="AP214" s="4" t="n"/>
       <c r="AQ214" s="4" t="n"/>
+      <c r="AR214" s="4" t="n"/>
+      <c r="AS214" s="4" t="n"/>
+      <c r="AT214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="N215" s="4" t="n"/>
@@ -7680,6 +8337,9 @@
       <c r="AO215" s="4" t="n"/>
       <c r="AP215" s="4" t="n"/>
       <c r="AQ215" s="4" t="n"/>
+      <c r="AR215" s="4" t="n"/>
+      <c r="AS215" s="4" t="n"/>
+      <c r="AT215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="N216" s="4" t="n"/>
@@ -7712,6 +8372,9 @@
       <c r="AO216" s="4" t="n"/>
       <c r="AP216" s="4" t="n"/>
       <c r="AQ216" s="4" t="n"/>
+      <c r="AR216" s="4" t="n"/>
+      <c r="AS216" s="4" t="n"/>
+      <c r="AT216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="N217" s="4" t="n"/>
@@ -7744,6 +8407,9 @@
       <c r="AO217" s="4" t="n"/>
       <c r="AP217" s="4" t="n"/>
       <c r="AQ217" s="4" t="n"/>
+      <c r="AR217" s="4" t="n"/>
+      <c r="AS217" s="4" t="n"/>
+      <c r="AT217" s="4" t="n"/>
     </row>
     <row r="218">
       <c r="N218" s="4" t="n"/>
@@ -7776,6 +8442,9 @@
       <c r="AO218" s="4" t="n"/>
       <c r="AP218" s="4" t="n"/>
       <c r="AQ218" s="4" t="n"/>
+      <c r="AR218" s="4" t="n"/>
+      <c r="AS218" s="4" t="n"/>
+      <c r="AT218" s="4" t="n"/>
     </row>
     <row r="219">
       <c r="N219" s="4" t="n"/>
@@ -7808,6 +8477,9 @@
       <c r="AO219" s="4" t="n"/>
       <c r="AP219" s="4" t="n"/>
       <c r="AQ219" s="4" t="n"/>
+      <c r="AR219" s="4" t="n"/>
+      <c r="AS219" s="4" t="n"/>
+      <c r="AT219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="N220" s="4" t="n"/>
@@ -7840,6 +8512,9 @@
       <c r="AO220" s="4" t="n"/>
       <c r="AP220" s="4" t="n"/>
       <c r="AQ220" s="4" t="n"/>
+      <c r="AR220" s="4" t="n"/>
+      <c r="AS220" s="4" t="n"/>
+      <c r="AT220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="N221" s="4" t="n"/>
@@ -7872,6 +8547,9 @@
       <c r="AO221" s="4" t="n"/>
       <c r="AP221" s="4" t="n"/>
       <c r="AQ221" s="4" t="n"/>
+      <c r="AR221" s="4" t="n"/>
+      <c r="AS221" s="4" t="n"/>
+      <c r="AT221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="N222" s="4" t="n"/>
@@ -7904,6 +8582,9 @@
       <c r="AO222" s="4" t="n"/>
       <c r="AP222" s="4" t="n"/>
       <c r="AQ222" s="4" t="n"/>
+      <c r="AR222" s="4" t="n"/>
+      <c r="AS222" s="4" t="n"/>
+      <c r="AT222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="N223" s="4" t="n"/>
@@ -7936,6 +8617,9 @@
       <c r="AO223" s="4" t="n"/>
       <c r="AP223" s="4" t="n"/>
       <c r="AQ223" s="4" t="n"/>
+      <c r="AR223" s="4" t="n"/>
+      <c r="AS223" s="4" t="n"/>
+      <c r="AT223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="N224" s="4" t="n"/>
@@ -7968,6 +8652,9 @@
       <c r="AO224" s="4" t="n"/>
       <c r="AP224" s="4" t="n"/>
       <c r="AQ224" s="4" t="n"/>
+      <c r="AR224" s="4" t="n"/>
+      <c r="AS224" s="4" t="n"/>
+      <c r="AT224" s="4" t="n"/>
     </row>
     <row r="225">
       <c r="N225" s="4" t="n"/>
@@ -8000,6 +8687,9 @@
       <c r="AO225" s="4" t="n"/>
       <c r="AP225" s="4" t="n"/>
       <c r="AQ225" s="4" t="n"/>
+      <c r="AR225" s="4" t="n"/>
+      <c r="AS225" s="4" t="n"/>
+      <c r="AT225" s="4" t="n"/>
     </row>
     <row r="226">
       <c r="N226" s="4" t="n"/>
@@ -8032,6 +8722,9 @@
       <c r="AO226" s="4" t="n"/>
       <c r="AP226" s="4" t="n"/>
       <c r="AQ226" s="4" t="n"/>
+      <c r="AR226" s="4" t="n"/>
+      <c r="AS226" s="4" t="n"/>
+      <c r="AT226" s="4" t="n"/>
     </row>
     <row r="227">
       <c r="N227" s="4" t="n"/>
@@ -8064,6 +8757,9 @@
       <c r="AO227" s="4" t="n"/>
       <c r="AP227" s="4" t="n"/>
       <c r="AQ227" s="4" t="n"/>
+      <c r="AR227" s="4" t="n"/>
+      <c r="AS227" s="4" t="n"/>
+      <c r="AT227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="N228" s="4" t="n"/>
@@ -8096,6 +8792,9 @@
       <c r="AO228" s="4" t="n"/>
       <c r="AP228" s="4" t="n"/>
       <c r="AQ228" s="4" t="n"/>
+      <c r="AR228" s="4" t="n"/>
+      <c r="AS228" s="4" t="n"/>
+      <c r="AT228" s="4" t="n"/>
     </row>
     <row r="229">
       <c r="N229" s="4" t="n"/>
@@ -8128,6 +8827,9 @@
       <c r="AO229" s="4" t="n"/>
       <c r="AP229" s="4" t="n"/>
       <c r="AQ229" s="4" t="n"/>
+      <c r="AR229" s="4" t="n"/>
+      <c r="AS229" s="4" t="n"/>
+      <c r="AT229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="N230" s="4" t="n"/>
@@ -8160,6 +8862,9 @@
       <c r="AO230" s="4" t="n"/>
       <c r="AP230" s="4" t="n"/>
       <c r="AQ230" s="4" t="n"/>
+      <c r="AR230" s="4" t="n"/>
+      <c r="AS230" s="4" t="n"/>
+      <c r="AT230" s="4" t="n"/>
     </row>
     <row r="231">
       <c r="N231" s="4" t="n"/>
@@ -8192,6 +8897,9 @@
       <c r="AO231" s="4" t="n"/>
       <c r="AP231" s="4" t="n"/>
       <c r="AQ231" s="4" t="n"/>
+      <c r="AR231" s="4" t="n"/>
+      <c r="AS231" s="4" t="n"/>
+      <c r="AT231" s="4" t="n"/>
     </row>
     <row r="232">
       <c r="N232" s="4" t="n"/>
@@ -8224,6 +8932,9 @@
       <c r="AO232" s="4" t="n"/>
       <c r="AP232" s="4" t="n"/>
       <c r="AQ232" s="4" t="n"/>
+      <c r="AR232" s="4" t="n"/>
+      <c r="AS232" s="4" t="n"/>
+      <c r="AT232" s="4" t="n"/>
     </row>
     <row r="233">
       <c r="N233" s="4" t="n"/>
@@ -8256,6 +8967,9 @@
       <c r="AO233" s="4" t="n"/>
       <c r="AP233" s="4" t="n"/>
       <c r="AQ233" s="4" t="n"/>
+      <c r="AR233" s="4" t="n"/>
+      <c r="AS233" s="4" t="n"/>
+      <c r="AT233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="N234" s="4" t="n"/>
@@ -8288,6 +9002,9 @@
       <c r="AO234" s="4" t="n"/>
       <c r="AP234" s="4" t="n"/>
       <c r="AQ234" s="4" t="n"/>
+      <c r="AR234" s="4" t="n"/>
+      <c r="AS234" s="4" t="n"/>
+      <c r="AT234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="N235" s="4" t="n"/>
@@ -8320,6 +9037,9 @@
       <c r="AO235" s="4" t="n"/>
       <c r="AP235" s="4" t="n"/>
       <c r="AQ235" s="4" t="n"/>
+      <c r="AR235" s="4" t="n"/>
+      <c r="AS235" s="4" t="n"/>
+      <c r="AT235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="N236" s="4" t="n"/>
@@ -8352,6 +9072,9 @@
       <c r="AO236" s="4" t="n"/>
       <c r="AP236" s="4" t="n"/>
       <c r="AQ236" s="4" t="n"/>
+      <c r="AR236" s="4" t="n"/>
+      <c r="AS236" s="4" t="n"/>
+      <c r="AT236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="N237" s="4" t="n"/>
@@ -8384,6 +9107,9 @@
       <c r="AO237" s="4" t="n"/>
       <c r="AP237" s="4" t="n"/>
       <c r="AQ237" s="4" t="n"/>
+      <c r="AR237" s="4" t="n"/>
+      <c r="AS237" s="4" t="n"/>
+      <c r="AT237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="N238" s="4" t="n"/>
@@ -8416,6 +9142,9 @@
       <c r="AO238" s="4" t="n"/>
       <c r="AP238" s="4" t="n"/>
       <c r="AQ238" s="4" t="n"/>
+      <c r="AR238" s="4" t="n"/>
+      <c r="AS238" s="4" t="n"/>
+      <c r="AT238" s="4" t="n"/>
     </row>
     <row r="239">
       <c r="N239" s="4" t="n"/>
@@ -8448,6 +9177,9 @@
       <c r="AO239" s="4" t="n"/>
       <c r="AP239" s="4" t="n"/>
       <c r="AQ239" s="4" t="n"/>
+      <c r="AR239" s="4" t="n"/>
+      <c r="AS239" s="4" t="n"/>
+      <c r="AT239" s="4" t="n"/>
     </row>
     <row r="240">
       <c r="N240" s="4" t="n"/>
@@ -8480,6 +9212,9 @@
       <c r="AO240" s="4" t="n"/>
       <c r="AP240" s="4" t="n"/>
       <c r="AQ240" s="4" t="n"/>
+      <c r="AR240" s="4" t="n"/>
+      <c r="AS240" s="4" t="n"/>
+      <c r="AT240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="N241" s="4" t="n"/>
@@ -8512,6 +9247,9 @@
       <c r="AO241" s="4" t="n"/>
       <c r="AP241" s="4" t="n"/>
       <c r="AQ241" s="4" t="n"/>
+      <c r="AR241" s="4" t="n"/>
+      <c r="AS241" s="4" t="n"/>
+      <c r="AT241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="N242" s="4" t="n"/>
@@ -8544,6 +9282,9 @@
       <c r="AO242" s="4" t="n"/>
       <c r="AP242" s="4" t="n"/>
       <c r="AQ242" s="4" t="n"/>
+      <c r="AR242" s="4" t="n"/>
+      <c r="AS242" s="4" t="n"/>
+      <c r="AT242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="N243" s="4" t="n"/>
@@ -8576,6 +9317,9 @@
       <c r="AO243" s="4" t="n"/>
       <c r="AP243" s="4" t="n"/>
       <c r="AQ243" s="4" t="n"/>
+      <c r="AR243" s="4" t="n"/>
+      <c r="AS243" s="4" t="n"/>
+      <c r="AT243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="N244" s="4" t="n"/>
@@ -8608,6 +9352,9 @@
       <c r="AO244" s="4" t="n"/>
       <c r="AP244" s="4" t="n"/>
       <c r="AQ244" s="4" t="n"/>
+      <c r="AR244" s="4" t="n"/>
+      <c r="AS244" s="4" t="n"/>
+      <c r="AT244" s="4" t="n"/>
     </row>
     <row r="245">
       <c r="N245" s="4" t="n"/>
@@ -8640,6 +9387,9 @@
       <c r="AO245" s="4" t="n"/>
       <c r="AP245" s="4" t="n"/>
       <c r="AQ245" s="4" t="n"/>
+      <c r="AR245" s="4" t="n"/>
+      <c r="AS245" s="4" t="n"/>
+      <c r="AT245" s="4" t="n"/>
     </row>
     <row r="246">
       <c r="N246" s="4" t="n"/>
@@ -8672,6 +9422,9 @@
       <c r="AO246" s="4" t="n"/>
       <c r="AP246" s="4" t="n"/>
       <c r="AQ246" s="4" t="n"/>
+      <c r="AR246" s="4" t="n"/>
+      <c r="AS246" s="4" t="n"/>
+      <c r="AT246" s="4" t="n"/>
     </row>
     <row r="247">
       <c r="N247" s="4" t="n"/>
@@ -8704,6 +9457,9 @@
       <c r="AO247" s="4" t="n"/>
       <c r="AP247" s="4" t="n"/>
       <c r="AQ247" s="4" t="n"/>
+      <c r="AR247" s="4" t="n"/>
+      <c r="AS247" s="4" t="n"/>
+      <c r="AT247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="N248" s="4" t="n"/>
@@ -8736,6 +9492,9 @@
       <c r="AO248" s="4" t="n"/>
       <c r="AP248" s="4" t="n"/>
       <c r="AQ248" s="4" t="n"/>
+      <c r="AR248" s="4" t="n"/>
+      <c r="AS248" s="4" t="n"/>
+      <c r="AT248" s="4" t="n"/>
     </row>
     <row r="249">
       <c r="N249" s="4" t="n"/>
@@ -8768,6 +9527,9 @@
       <c r="AO249" s="4" t="n"/>
       <c r="AP249" s="4" t="n"/>
       <c r="AQ249" s="4" t="n"/>
+      <c r="AR249" s="4" t="n"/>
+      <c r="AS249" s="4" t="n"/>
+      <c r="AT249" s="4" t="n"/>
     </row>
     <row r="250">
       <c r="N250" s="4" t="n"/>
@@ -8800,6 +9562,9 @@
       <c r="AO250" s="4" t="n"/>
       <c r="AP250" s="4" t="n"/>
       <c r="AQ250" s="4" t="n"/>
+      <c r="AR250" s="4" t="n"/>
+      <c r="AS250" s="4" t="n"/>
+      <c r="AT250" s="4" t="n"/>
     </row>
     <row r="251">
       <c r="N251" s="4" t="n"/>
@@ -8832,6 +9597,9 @@
       <c r="AO251" s="4" t="n"/>
       <c r="AP251" s="4" t="n"/>
       <c r="AQ251" s="4" t="n"/>
+      <c r="AR251" s="4" t="n"/>
+      <c r="AS251" s="4" t="n"/>
+      <c r="AT251" s="4" t="n"/>
     </row>
     <row r="252">
       <c r="N252" s="4" t="n"/>
@@ -8864,6 +9632,9 @@
       <c r="AO252" s="4" t="n"/>
       <c r="AP252" s="4" t="n"/>
       <c r="AQ252" s="4" t="n"/>
+      <c r="AR252" s="4" t="n"/>
+      <c r="AS252" s="4" t="n"/>
+      <c r="AT252" s="4" t="n"/>
     </row>
     <row r="253">
       <c r="N253" s="4" t="n"/>
@@ -8896,6 +9667,9 @@
       <c r="AO253" s="4" t="n"/>
       <c r="AP253" s="4" t="n"/>
       <c r="AQ253" s="4" t="n"/>
+      <c r="AR253" s="4" t="n"/>
+      <c r="AS253" s="4" t="n"/>
+      <c r="AT253" s="4" t="n"/>
     </row>
     <row r="254">
       <c r="N254" s="4" t="n"/>
@@ -8928,6 +9702,9 @@
       <c r="AO254" s="4" t="n"/>
       <c r="AP254" s="4" t="n"/>
       <c r="AQ254" s="4" t="n"/>
+      <c r="AR254" s="4" t="n"/>
+      <c r="AS254" s="4" t="n"/>
+      <c r="AT254" s="4" t="n"/>
     </row>
     <row r="255">
       <c r="N255" s="4" t="n"/>
@@ -8960,6 +9737,9 @@
       <c r="AO255" s="4" t="n"/>
       <c r="AP255" s="4" t="n"/>
       <c r="AQ255" s="4" t="n"/>
+      <c r="AR255" s="4" t="n"/>
+      <c r="AS255" s="4" t="n"/>
+      <c r="AT255" s="4" t="n"/>
     </row>
     <row r="256">
       <c r="N256" s="4" t="n"/>
@@ -8992,6 +9772,9 @@
       <c r="AO256" s="4" t="n"/>
       <c r="AP256" s="4" t="n"/>
       <c r="AQ256" s="4" t="n"/>
+      <c r="AR256" s="4" t="n"/>
+      <c r="AS256" s="4" t="n"/>
+      <c r="AT256" s="4" t="n"/>
     </row>
     <row r="257">
       <c r="N257" s="4" t="n"/>
@@ -9024,6 +9807,9 @@
       <c r="AO257" s="4" t="n"/>
       <c r="AP257" s="4" t="n"/>
       <c r="AQ257" s="4" t="n"/>
+      <c r="AR257" s="4" t="n"/>
+      <c r="AS257" s="4" t="n"/>
+      <c r="AT257" s="4" t="n"/>
     </row>
     <row r="258">
       <c r="N258" s="4" t="n"/>
@@ -9056,6 +9842,9 @@
       <c r="AO258" s="4" t="n"/>
       <c r="AP258" s="4" t="n"/>
       <c r="AQ258" s="4" t="n"/>
+      <c r="AR258" s="4" t="n"/>
+      <c r="AS258" s="4" t="n"/>
+      <c r="AT258" s="4" t="n"/>
     </row>
     <row r="259">
       <c r="N259" s="4" t="n"/>
@@ -9088,6 +9877,9 @@
       <c r="AO259" s="4" t="n"/>
       <c r="AP259" s="4" t="n"/>
       <c r="AQ259" s="4" t="n"/>
+      <c r="AR259" s="4" t="n"/>
+      <c r="AS259" s="4" t="n"/>
+      <c r="AT259" s="4" t="n"/>
     </row>
     <row r="260">
       <c r="N260" s="4" t="n"/>
@@ -9120,6 +9912,9 @@
       <c r="AO260" s="4" t="n"/>
       <c r="AP260" s="4" t="n"/>
       <c r="AQ260" s="4" t="n"/>
+      <c r="AR260" s="4" t="n"/>
+      <c r="AS260" s="4" t="n"/>
+      <c r="AT260" s="4" t="n"/>
     </row>
     <row r="261">
       <c r="N261" s="4" t="n"/>
@@ -9152,6 +9947,9 @@
       <c r="AO261" s="4" t="n"/>
       <c r="AP261" s="4" t="n"/>
       <c r="AQ261" s="4" t="n"/>
+      <c r="AR261" s="4" t="n"/>
+      <c r="AS261" s="4" t="n"/>
+      <c r="AT261" s="4" t="n"/>
     </row>
     <row r="262">
       <c r="N262" s="4" t="n"/>
@@ -9184,6 +9982,9 @@
       <c r="AO262" s="4" t="n"/>
       <c r="AP262" s="4" t="n"/>
       <c r="AQ262" s="4" t="n"/>
+      <c r="AR262" s="4" t="n"/>
+      <c r="AS262" s="4" t="n"/>
+      <c r="AT262" s="4" t="n"/>
     </row>
     <row r="263">
       <c r="N263" s="4" t="n"/>
@@ -9216,6 +10017,9 @@
       <c r="AO263" s="4" t="n"/>
       <c r="AP263" s="4" t="n"/>
       <c r="AQ263" s="4" t="n"/>
+      <c r="AR263" s="4" t="n"/>
+      <c r="AS263" s="4" t="n"/>
+      <c r="AT263" s="4" t="n"/>
     </row>
     <row r="264">
       <c r="N264" s="4" t="n"/>
@@ -9248,6 +10052,9 @@
       <c r="AO264" s="4" t="n"/>
       <c r="AP264" s="4" t="n"/>
       <c r="AQ264" s="4" t="n"/>
+      <c r="AR264" s="4" t="n"/>
+      <c r="AS264" s="4" t="n"/>
+      <c r="AT264" s="4" t="n"/>
     </row>
     <row r="265">
       <c r="N265" s="4" t="n"/>
@@ -9280,6 +10087,9 @@
       <c r="AO265" s="4" t="n"/>
       <c r="AP265" s="4" t="n"/>
       <c r="AQ265" s="4" t="n"/>
+      <c r="AR265" s="4" t="n"/>
+      <c r="AS265" s="4" t="n"/>
+      <c r="AT265" s="4" t="n"/>
     </row>
     <row r="266">
       <c r="N266" s="4" t="n"/>
@@ -9312,6 +10122,9 @@
       <c r="AO266" s="4" t="n"/>
       <c r="AP266" s="4" t="n"/>
       <c r="AQ266" s="4" t="n"/>
+      <c r="AR266" s="4" t="n"/>
+      <c r="AS266" s="4" t="n"/>
+      <c r="AT266" s="4" t="n"/>
     </row>
     <row r="267">
       <c r="N267" s="4" t="n"/>
@@ -9344,6 +10157,9 @@
       <c r="AO267" s="4" t="n"/>
       <c r="AP267" s="4" t="n"/>
       <c r="AQ267" s="4" t="n"/>
+      <c r="AR267" s="4" t="n"/>
+      <c r="AS267" s="4" t="n"/>
+      <c r="AT267" s="4" t="n"/>
     </row>
     <row r="268">
       <c r="N268" s="4" t="n"/>
@@ -9376,6 +10192,9 @@
       <c r="AO268" s="4" t="n"/>
       <c r="AP268" s="4" t="n"/>
       <c r="AQ268" s="4" t="n"/>
+      <c r="AR268" s="4" t="n"/>
+      <c r="AS268" s="4" t="n"/>
+      <c r="AT268" s="4" t="n"/>
     </row>
     <row r="269">
       <c r="N269" s="4" t="n"/>
@@ -9408,6 +10227,9 @@
       <c r="AO269" s="4" t="n"/>
       <c r="AP269" s="4" t="n"/>
       <c r="AQ269" s="4" t="n"/>
+      <c r="AR269" s="4" t="n"/>
+      <c r="AS269" s="4" t="n"/>
+      <c r="AT269" s="4" t="n"/>
     </row>
     <row r="270">
       <c r="N270" s="4" t="n"/>
@@ -9440,6 +10262,9 @@
       <c r="AO270" s="4" t="n"/>
       <c r="AP270" s="4" t="n"/>
       <c r="AQ270" s="4" t="n"/>
+      <c r="AR270" s="4" t="n"/>
+      <c r="AS270" s="4" t="n"/>
+      <c r="AT270" s="4" t="n"/>
     </row>
     <row r="271">
       <c r="N271" s="4" t="n"/>
@@ -9472,6 +10297,9 @@
       <c r="AO271" s="4" t="n"/>
       <c r="AP271" s="4" t="n"/>
       <c r="AQ271" s="4" t="n"/>
+      <c r="AR271" s="4" t="n"/>
+      <c r="AS271" s="4" t="n"/>
+      <c r="AT271" s="4" t="n"/>
     </row>
     <row r="272">
       <c r="N272" s="4" t="n"/>
@@ -9504,6 +10332,9 @@
       <c r="AO272" s="4" t="n"/>
       <c r="AP272" s="4" t="n"/>
       <c r="AQ272" s="4" t="n"/>
+      <c r="AR272" s="4" t="n"/>
+      <c r="AS272" s="4" t="n"/>
+      <c r="AT272" s="4" t="n"/>
     </row>
     <row r="273">
       <c r="N273" s="4" t="n"/>
@@ -9536,6 +10367,9 @@
       <c r="AO273" s="4" t="n"/>
       <c r="AP273" s="4" t="n"/>
       <c r="AQ273" s="4" t="n"/>
+      <c r="AR273" s="4" t="n"/>
+      <c r="AS273" s="4" t="n"/>
+      <c r="AT273" s="4" t="n"/>
     </row>
     <row r="274">
       <c r="N274" s="4" t="n"/>
@@ -9568,6 +10402,9 @@
       <c r="AO274" s="4" t="n"/>
       <c r="AP274" s="4" t="n"/>
       <c r="AQ274" s="4" t="n"/>
+      <c r="AR274" s="4" t="n"/>
+      <c r="AS274" s="4" t="n"/>
+      <c r="AT274" s="4" t="n"/>
     </row>
     <row r="275">
       <c r="N275" s="4" t="n"/>
@@ -9600,6 +10437,9 @@
       <c r="AO275" s="4" t="n"/>
       <c r="AP275" s="4" t="n"/>
       <c r="AQ275" s="4" t="n"/>
+      <c r="AR275" s="4" t="n"/>
+      <c r="AS275" s="4" t="n"/>
+      <c r="AT275" s="4" t="n"/>
     </row>
     <row r="276">
       <c r="N276" s="4" t="n"/>
@@ -9632,6 +10472,9 @@
       <c r="AO276" s="4" t="n"/>
       <c r="AP276" s="4" t="n"/>
       <c r="AQ276" s="4" t="n"/>
+      <c r="AR276" s="4" t="n"/>
+      <c r="AS276" s="4" t="n"/>
+      <c r="AT276" s="4" t="n"/>
     </row>
     <row r="277">
       <c r="N277" s="4" t="n"/>
@@ -9664,6 +10507,9 @@
       <c r="AO277" s="4" t="n"/>
       <c r="AP277" s="4" t="n"/>
       <c r="AQ277" s="4" t="n"/>
+      <c r="AR277" s="4" t="n"/>
+      <c r="AS277" s="4" t="n"/>
+      <c r="AT277" s="4" t="n"/>
     </row>
     <row r="278">
       <c r="N278" s="4" t="n"/>
@@ -9696,6 +10542,9 @@
       <c r="AO278" s="4" t="n"/>
       <c r="AP278" s="4" t="n"/>
       <c r="AQ278" s="4" t="n"/>
+      <c r="AR278" s="4" t="n"/>
+      <c r="AS278" s="4" t="n"/>
+      <c r="AT278" s="4" t="n"/>
     </row>
     <row r="279">
       <c r="N279" s="4" t="n"/>
@@ -9728,6 +10577,9 @@
       <c r="AO279" s="4" t="n"/>
       <c r="AP279" s="4" t="n"/>
       <c r="AQ279" s="4" t="n"/>
+      <c r="AR279" s="4" t="n"/>
+      <c r="AS279" s="4" t="n"/>
+      <c r="AT279" s="4" t="n"/>
     </row>
     <row r="280">
       <c r="N280" s="4" t="n"/>
@@ -9760,6 +10612,9 @@
       <c r="AO280" s="4" t="n"/>
       <c r="AP280" s="4" t="n"/>
       <c r="AQ280" s="4" t="n"/>
+      <c r="AR280" s="4" t="n"/>
+      <c r="AS280" s="4" t="n"/>
+      <c r="AT280" s="4" t="n"/>
     </row>
     <row r="281">
       <c r="N281" s="4" t="n"/>
@@ -9792,6 +10647,9 @@
       <c r="AO281" s="4" t="n"/>
       <c r="AP281" s="4" t="n"/>
       <c r="AQ281" s="4" t="n"/>
+      <c r="AR281" s="4" t="n"/>
+      <c r="AS281" s="4" t="n"/>
+      <c r="AT281" s="4" t="n"/>
     </row>
     <row r="282">
       <c r="N282" s="4" t="n"/>
@@ -9824,6 +10682,9 @@
       <c r="AO282" s="4" t="n"/>
       <c r="AP282" s="4" t="n"/>
       <c r="AQ282" s="4" t="n"/>
+      <c r="AR282" s="4" t="n"/>
+      <c r="AS282" s="4" t="n"/>
+      <c r="AT282" s="4" t="n"/>
     </row>
     <row r="283">
       <c r="N283" s="4" t="n"/>
@@ -9856,6 +10717,9 @@
       <c r="AO283" s="4" t="n"/>
       <c r="AP283" s="4" t="n"/>
       <c r="AQ283" s="4" t="n"/>
+      <c r="AR283" s="4" t="n"/>
+      <c r="AS283" s="4" t="n"/>
+      <c r="AT283" s="4" t="n"/>
     </row>
     <row r="284">
       <c r="N284" s="4" t="n"/>
@@ -9888,6 +10752,9 @@
       <c r="AO284" s="4" t="n"/>
       <c r="AP284" s="4" t="n"/>
       <c r="AQ284" s="4" t="n"/>
+      <c r="AR284" s="4" t="n"/>
+      <c r="AS284" s="4" t="n"/>
+      <c r="AT284" s="4" t="n"/>
     </row>
     <row r="285">
       <c r="N285" s="4" t="n"/>
@@ -9920,6 +10787,9 @@
       <c r="AO285" s="4" t="n"/>
       <c r="AP285" s="4" t="n"/>
       <c r="AQ285" s="4" t="n"/>
+      <c r="AR285" s="4" t="n"/>
+      <c r="AS285" s="4" t="n"/>
+      <c r="AT285" s="4" t="n"/>
     </row>
     <row r="286">
       <c r="N286" s="4" t="n"/>
@@ -9952,6 +10822,9 @@
       <c r="AO286" s="4" t="n"/>
       <c r="AP286" s="4" t="n"/>
       <c r="AQ286" s="4" t="n"/>
+      <c r="AR286" s="4" t="n"/>
+      <c r="AS286" s="4" t="n"/>
+      <c r="AT286" s="4" t="n"/>
     </row>
     <row r="287">
       <c r="N287" s="4" t="n"/>
@@ -9984,6 +10857,9 @@
       <c r="AO287" s="4" t="n"/>
       <c r="AP287" s="4" t="n"/>
       <c r="AQ287" s="4" t="n"/>
+      <c r="AR287" s="4" t="n"/>
+      <c r="AS287" s="4" t="n"/>
+      <c r="AT287" s="4" t="n"/>
     </row>
     <row r="288">
       <c r="N288" s="4" t="n"/>
@@ -10016,6 +10892,9 @@
       <c r="AO288" s="4" t="n"/>
       <c r="AP288" s="4" t="n"/>
       <c r="AQ288" s="4" t="n"/>
+      <c r="AR288" s="4" t="n"/>
+      <c r="AS288" s="4" t="n"/>
+      <c r="AT288" s="4" t="n"/>
     </row>
     <row r="289">
       <c r="N289" s="4" t="n"/>
@@ -10048,6 +10927,9 @@
       <c r="AO289" s="4" t="n"/>
       <c r="AP289" s="4" t="n"/>
       <c r="AQ289" s="4" t="n"/>
+      <c r="AR289" s="4" t="n"/>
+      <c r="AS289" s="4" t="n"/>
+      <c r="AT289" s="4" t="n"/>
     </row>
     <row r="290">
       <c r="N290" s="4" t="n"/>
@@ -10080,6 +10962,9 @@
       <c r="AO290" s="4" t="n"/>
       <c r="AP290" s="4" t="n"/>
       <c r="AQ290" s="4" t="n"/>
+      <c r="AR290" s="4" t="n"/>
+      <c r="AS290" s="4" t="n"/>
+      <c r="AT290" s="4" t="n"/>
     </row>
     <row r="291">
       <c r="N291" s="4" t="n"/>
@@ -10112,6 +10997,9 @@
       <c r="AO291" s="4" t="n"/>
       <c r="AP291" s="4" t="n"/>
       <c r="AQ291" s="4" t="n"/>
+      <c r="AR291" s="4" t="n"/>
+      <c r="AS291" s="4" t="n"/>
+      <c r="AT291" s="4" t="n"/>
     </row>
     <row r="292">
       <c r="N292" s="4" t="n"/>
@@ -10144,6 +11032,9 @@
       <c r="AO292" s="4" t="n"/>
       <c r="AP292" s="4" t="n"/>
       <c r="AQ292" s="4" t="n"/>
+      <c r="AR292" s="4" t="n"/>
+      <c r="AS292" s="4" t="n"/>
+      <c r="AT292" s="4" t="n"/>
     </row>
     <row r="293">
       <c r="N293" s="4" t="n"/>
@@ -10176,6 +11067,9 @@
       <c r="AO293" s="4" t="n"/>
       <c r="AP293" s="4" t="n"/>
       <c r="AQ293" s="4" t="n"/>
+      <c r="AR293" s="4" t="n"/>
+      <c r="AS293" s="4" t="n"/>
+      <c r="AT293" s="4" t="n"/>
     </row>
     <row r="294">
       <c r="N294" s="4" t="n"/>
@@ -10208,6 +11102,9 @@
       <c r="AO294" s="4" t="n"/>
       <c r="AP294" s="4" t="n"/>
       <c r="AQ294" s="4" t="n"/>
+      <c r="AR294" s="4" t="n"/>
+      <c r="AS294" s="4" t="n"/>
+      <c r="AT294" s="4" t="n"/>
     </row>
     <row r="295">
       <c r="N295" s="4" t="n"/>
@@ -10240,6 +11137,9 @@
       <c r="AO295" s="4" t="n"/>
       <c r="AP295" s="4" t="n"/>
       <c r="AQ295" s="4" t="n"/>
+      <c r="AR295" s="4" t="n"/>
+      <c r="AS295" s="4" t="n"/>
+      <c r="AT295" s="4" t="n"/>
     </row>
     <row r="296">
       <c r="N296" s="4" t="n"/>
@@ -10272,6 +11172,9 @@
       <c r="AO296" s="4" t="n"/>
       <c r="AP296" s="4" t="n"/>
       <c r="AQ296" s="4" t="n"/>
+      <c r="AR296" s="4" t="n"/>
+      <c r="AS296" s="4" t="n"/>
+      <c r="AT296" s="4" t="n"/>
     </row>
     <row r="297">
       <c r="N297" s="4" t="n"/>
@@ -10304,6 +11207,9 @@
       <c r="AO297" s="4" t="n"/>
       <c r="AP297" s="4" t="n"/>
       <c r="AQ297" s="4" t="n"/>
+      <c r="AR297" s="4" t="n"/>
+      <c r="AS297" s="4" t="n"/>
+      <c r="AT297" s="4" t="n"/>
     </row>
     <row r="298">
       <c r="N298" s="4" t="n"/>
@@ -10336,6 +11242,9 @@
       <c r="AO298" s="4" t="n"/>
       <c r="AP298" s="4" t="n"/>
       <c r="AQ298" s="4" t="n"/>
+      <c r="AR298" s="4" t="n"/>
+      <c r="AS298" s="4" t="n"/>
+      <c r="AT298" s="4" t="n"/>
     </row>
     <row r="299">
       <c r="N299" s="4" t="n"/>
@@ -10368,6 +11277,9 @@
       <c r="AO299" s="4" t="n"/>
       <c r="AP299" s="4" t="n"/>
       <c r="AQ299" s="4" t="n"/>
+      <c r="AR299" s="4" t="n"/>
+      <c r="AS299" s="4" t="n"/>
+      <c r="AT299" s="4" t="n"/>
     </row>
     <row r="300">
       <c r="N300" s="4" t="n"/>
@@ -10400,6 +11312,9 @@
       <c r="AO300" s="4" t="n"/>
       <c r="AP300" s="4" t="n"/>
       <c r="AQ300" s="4" t="n"/>
+      <c r="AR300" s="4" t="n"/>
+      <c r="AS300" s="4" t="n"/>
+      <c r="AT300" s="4" t="n"/>
     </row>
     <row r="301">
       <c r="N301" s="4" t="n"/>
@@ -10432,6 +11347,9 @@
       <c r="AO301" s="4" t="n"/>
       <c r="AP301" s="4" t="n"/>
       <c r="AQ301" s="4" t="n"/>
+      <c r="AR301" s="4" t="n"/>
+      <c r="AS301" s="4" t="n"/>
+      <c r="AT301" s="4" t="n"/>
     </row>
     <row r="302">
       <c r="N302" s="4" t="n"/>
@@ -10464,6 +11382,9 @@
       <c r="AO302" s="4" t="n"/>
       <c r="AP302" s="4" t="n"/>
       <c r="AQ302" s="4" t="n"/>
+      <c r="AR302" s="4" t="n"/>
+      <c r="AS302" s="4" t="n"/>
+      <c r="AT302" s="4" t="n"/>
     </row>
     <row r="303">
       <c r="N303" s="4" t="n"/>
@@ -10496,6 +11417,9 @@
       <c r="AO303" s="4" t="n"/>
       <c r="AP303" s="4" t="n"/>
       <c r="AQ303" s="4" t="n"/>
+      <c r="AR303" s="4" t="n"/>
+      <c r="AS303" s="4" t="n"/>
+      <c r="AT303" s="4" t="n"/>
     </row>
     <row r="304">
       <c r="N304" s="4" t="n"/>
@@ -10528,6 +11452,9 @@
       <c r="AO304" s="4" t="n"/>
       <c r="AP304" s="4" t="n"/>
       <c r="AQ304" s="4" t="n"/>
+      <c r="AR304" s="4" t="n"/>
+      <c r="AS304" s="4" t="n"/>
+      <c r="AT304" s="4" t="n"/>
     </row>
     <row r="305">
       <c r="N305" s="4" t="n"/>
@@ -10560,6 +11487,9 @@
       <c r="AO305" s="4" t="n"/>
       <c r="AP305" s="4" t="n"/>
       <c r="AQ305" s="4" t="n"/>
+      <c r="AR305" s="4" t="n"/>
+      <c r="AS305" s="4" t="n"/>
+      <c r="AT305" s="4" t="n"/>
     </row>
     <row r="306">
       <c r="N306" s="4" t="n"/>
@@ -10592,6 +11522,9 @@
       <c r="AO306" s="4" t="n"/>
       <c r="AP306" s="4" t="n"/>
       <c r="AQ306" s="4" t="n"/>
+      <c r="AR306" s="4" t="n"/>
+      <c r="AS306" s="4" t="n"/>
+      <c r="AT306" s="4" t="n"/>
     </row>
     <row r="307">
       <c r="N307" s="4" t="n"/>
@@ -10624,6 +11557,9 @@
       <c r="AO307" s="4" t="n"/>
       <c r="AP307" s="4" t="n"/>
       <c r="AQ307" s="4" t="n"/>
+      <c r="AR307" s="4" t="n"/>
+      <c r="AS307" s="4" t="n"/>
+      <c r="AT307" s="4" t="n"/>
     </row>
     <row r="308">
       <c r="N308" s="4" t="n"/>
@@ -10656,6 +11592,9 @@
       <c r="AO308" s="4" t="n"/>
       <c r="AP308" s="4" t="n"/>
       <c r="AQ308" s="4" t="n"/>
+      <c r="AR308" s="4" t="n"/>
+      <c r="AS308" s="4" t="n"/>
+      <c r="AT308" s="4" t="n"/>
     </row>
     <row r="309">
       <c r="N309" s="4" t="n"/>
@@ -10688,6 +11627,9 @@
       <c r="AO309" s="4" t="n"/>
       <c r="AP309" s="4" t="n"/>
       <c r="AQ309" s="4" t="n"/>
+      <c r="AR309" s="4" t="n"/>
+      <c r="AS309" s="4" t="n"/>
+      <c r="AT309" s="4" t="n"/>
     </row>
     <row r="310">
       <c r="N310" s="4" t="n"/>
@@ -10720,6 +11662,9 @@
       <c r="AO310" s="4" t="n"/>
       <c r="AP310" s="4" t="n"/>
       <c r="AQ310" s="4" t="n"/>
+      <c r="AR310" s="4" t="n"/>
+      <c r="AS310" s="4" t="n"/>
+      <c r="AT310" s="4" t="n"/>
     </row>
     <row r="311">
       <c r="N311" s="4" t="n"/>
@@ -10752,6 +11697,9 @@
       <c r="AO311" s="4" t="n"/>
       <c r="AP311" s="4" t="n"/>
       <c r="AQ311" s="4" t="n"/>
+      <c r="AR311" s="4" t="n"/>
+      <c r="AS311" s="4" t="n"/>
+      <c r="AT311" s="4" t="n"/>
     </row>
     <row r="312">
       <c r="N312" s="4" t="n"/>
@@ -10784,6 +11732,9 @@
       <c r="AO312" s="4" t="n"/>
       <c r="AP312" s="4" t="n"/>
       <c r="AQ312" s="4" t="n"/>
+      <c r="AR312" s="4" t="n"/>
+      <c r="AS312" s="4" t="n"/>
+      <c r="AT312" s="4" t="n"/>
     </row>
     <row r="313">
       <c r="N313" s="4" t="n"/>
@@ -10816,6 +11767,9 @@
       <c r="AO313" s="4" t="n"/>
       <c r="AP313" s="4" t="n"/>
       <c r="AQ313" s="4" t="n"/>
+      <c r="AR313" s="4" t="n"/>
+      <c r="AS313" s="4" t="n"/>
+      <c r="AT313" s="4" t="n"/>
     </row>
     <row r="314">
       <c r="N314" s="4" t="n"/>
@@ -10848,6 +11802,9 @@
       <c r="AO314" s="4" t="n"/>
       <c r="AP314" s="4" t="n"/>
       <c r="AQ314" s="4" t="n"/>
+      <c r="AR314" s="4" t="n"/>
+      <c r="AS314" s="4" t="n"/>
+      <c r="AT314" s="4" t="n"/>
     </row>
     <row r="315">
       <c r="N315" s="4" t="n"/>
@@ -10880,6 +11837,9 @@
       <c r="AO315" s="4" t="n"/>
       <c r="AP315" s="4" t="n"/>
       <c r="AQ315" s="4" t="n"/>
+      <c r="AR315" s="4" t="n"/>
+      <c r="AS315" s="4" t="n"/>
+      <c r="AT315" s="4" t="n"/>
     </row>
     <row r="316">
       <c r="N316" s="4" t="n"/>
@@ -10912,6 +11872,9 @@
       <c r="AO316" s="4" t="n"/>
       <c r="AP316" s="4" t="n"/>
       <c r="AQ316" s="4" t="n"/>
+      <c r="AR316" s="4" t="n"/>
+      <c r="AS316" s="4" t="n"/>
+      <c r="AT316" s="4" t="n"/>
     </row>
     <row r="317">
       <c r="N317" s="4" t="n"/>
@@ -10944,6 +11907,9 @@
       <c r="AO317" s="4" t="n"/>
       <c r="AP317" s="4" t="n"/>
       <c r="AQ317" s="4" t="n"/>
+      <c r="AR317" s="4" t="n"/>
+      <c r="AS317" s="4" t="n"/>
+      <c r="AT317" s="4" t="n"/>
     </row>
     <row r="318">
       <c r="N318" s="4" t="n"/>
@@ -10976,6 +11942,9 @@
       <c r="AO318" s="4" t="n"/>
       <c r="AP318" s="4" t="n"/>
       <c r="AQ318" s="4" t="n"/>
+      <c r="AR318" s="4" t="n"/>
+      <c r="AS318" s="4" t="n"/>
+      <c r="AT318" s="4" t="n"/>
     </row>
     <row r="319">
       <c r="N319" s="4" t="n"/>
@@ -11008,6 +11977,9 @@
       <c r="AO319" s="4" t="n"/>
       <c r="AP319" s="4" t="n"/>
       <c r="AQ319" s="4" t="n"/>
+      <c r="AR319" s="4" t="n"/>
+      <c r="AS319" s="4" t="n"/>
+      <c r="AT319" s="4" t="n"/>
     </row>
     <row r="320">
       <c r="N320" s="4" t="n"/>
@@ -11040,6 +12012,9 @@
       <c r="AO320" s="4" t="n"/>
       <c r="AP320" s="4" t="n"/>
       <c r="AQ320" s="4" t="n"/>
+      <c r="AR320" s="4" t="n"/>
+      <c r="AS320" s="4" t="n"/>
+      <c r="AT320" s="4" t="n"/>
     </row>
     <row r="321">
       <c r="N321" s="4" t="n"/>
@@ -11072,6 +12047,9 @@
       <c r="AO321" s="4" t="n"/>
       <c r="AP321" s="4" t="n"/>
       <c r="AQ321" s="4" t="n"/>
+      <c r="AR321" s="4" t="n"/>
+      <c r="AS321" s="4" t="n"/>
+      <c r="AT321" s="4" t="n"/>
     </row>
     <row r="322">
       <c r="N322" s="4" t="n"/>
@@ -11104,6 +12082,9 @@
       <c r="AO322" s="4" t="n"/>
       <c r="AP322" s="4" t="n"/>
       <c r="AQ322" s="4" t="n"/>
+      <c r="AR322" s="4" t="n"/>
+      <c r="AS322" s="4" t="n"/>
+      <c r="AT322" s="4" t="n"/>
     </row>
     <row r="323">
       <c r="N323" s="4" t="n"/>
@@ -11136,6 +12117,9 @@
       <c r="AO323" s="4" t="n"/>
       <c r="AP323" s="4" t="n"/>
       <c r="AQ323" s="4" t="n"/>
+      <c r="AR323" s="4" t="n"/>
+      <c r="AS323" s="4" t="n"/>
+      <c r="AT323" s="4" t="n"/>
     </row>
     <row r="324">
       <c r="N324" s="4" t="n"/>
@@ -11168,6 +12152,9 @@
       <c r="AO324" s="4" t="n"/>
       <c r="AP324" s="4" t="n"/>
       <c r="AQ324" s="4" t="n"/>
+      <c r="AR324" s="4" t="n"/>
+      <c r="AS324" s="4" t="n"/>
+      <c r="AT324" s="4" t="n"/>
     </row>
     <row r="325">
       <c r="N325" s="4" t="n"/>
@@ -11200,6 +12187,9 @@
       <c r="AO325" s="4" t="n"/>
       <c r="AP325" s="4" t="n"/>
       <c r="AQ325" s="4" t="n"/>
+      <c r="AR325" s="4" t="n"/>
+      <c r="AS325" s="4" t="n"/>
+      <c r="AT325" s="4" t="n"/>
     </row>
     <row r="326">
       <c r="N326" s="4" t="n"/>
@@ -11232,6 +12222,9 @@
       <c r="AO326" s="4" t="n"/>
       <c r="AP326" s="4" t="n"/>
       <c r="AQ326" s="4" t="n"/>
+      <c r="AR326" s="4" t="n"/>
+      <c r="AS326" s="4" t="n"/>
+      <c r="AT326" s="4" t="n"/>
     </row>
     <row r="327">
       <c r="N327" s="4" t="n"/>
@@ -11264,6 +12257,9 @@
       <c r="AO327" s="4" t="n"/>
       <c r="AP327" s="4" t="n"/>
       <c r="AQ327" s="4" t="n"/>
+      <c r="AR327" s="4" t="n"/>
+      <c r="AS327" s="4" t="n"/>
+      <c r="AT327" s="4" t="n"/>
     </row>
     <row r="328">
       <c r="N328" s="4" t="n"/>
@@ -11296,6 +12292,9 @@
       <c r="AO328" s="4" t="n"/>
       <c r="AP328" s="4" t="n"/>
       <c r="AQ328" s="4" t="n"/>
+      <c r="AR328" s="4" t="n"/>
+      <c r="AS328" s="4" t="n"/>
+      <c r="AT328" s="4" t="n"/>
     </row>
     <row r="329">
       <c r="N329" s="4" t="n"/>
@@ -11328,6 +12327,9 @@
       <c r="AO329" s="4" t="n"/>
       <c r="AP329" s="4" t="n"/>
       <c r="AQ329" s="4" t="n"/>
+      <c r="AR329" s="4" t="n"/>
+      <c r="AS329" s="4" t="n"/>
+      <c r="AT329" s="4" t="n"/>
     </row>
     <row r="330">
       <c r="N330" s="4" t="n"/>
@@ -11360,6 +12362,9 @@
       <c r="AO330" s="4" t="n"/>
       <c r="AP330" s="4" t="n"/>
       <c r="AQ330" s="4" t="n"/>
+      <c r="AR330" s="4" t="n"/>
+      <c r="AS330" s="4" t="n"/>
+      <c r="AT330" s="4" t="n"/>
     </row>
     <row r="331">
       <c r="N331" s="4" t="n"/>
@@ -11392,6 +12397,9 @@
       <c r="AO331" s="4" t="n"/>
       <c r="AP331" s="4" t="n"/>
       <c r="AQ331" s="4" t="n"/>
+      <c r="AR331" s="4" t="n"/>
+      <c r="AS331" s="4" t="n"/>
+      <c r="AT331" s="4" t="n"/>
     </row>
     <row r="332">
       <c r="N332" s="4" t="n"/>
@@ -11424,6 +12432,9 @@
       <c r="AO332" s="4" t="n"/>
       <c r="AP332" s="4" t="n"/>
       <c r="AQ332" s="4" t="n"/>
+      <c r="AR332" s="4" t="n"/>
+      <c r="AS332" s="4" t="n"/>
+      <c r="AT332" s="4" t="n"/>
     </row>
     <row r="333">
       <c r="N333" s="4" t="n"/>
@@ -11456,6 +12467,9 @@
       <c r="AO333" s="4" t="n"/>
       <c r="AP333" s="4" t="n"/>
       <c r="AQ333" s="4" t="n"/>
+      <c r="AR333" s="4" t="n"/>
+      <c r="AS333" s="4" t="n"/>
+      <c r="AT333" s="4" t="n"/>
     </row>
     <row r="334">
       <c r="N334" s="4" t="n"/>
@@ -11488,6 +12502,9 @@
       <c r="AO334" s="4" t="n"/>
       <c r="AP334" s="4" t="n"/>
       <c r="AQ334" s="4" t="n"/>
+      <c r="AR334" s="4" t="n"/>
+      <c r="AS334" s="4" t="n"/>
+      <c r="AT334" s="4" t="n"/>
     </row>
     <row r="335">
       <c r="N335" s="4" t="n"/>
@@ -11520,6 +12537,9 @@
       <c r="AO335" s="4" t="n"/>
       <c r="AP335" s="4" t="n"/>
       <c r="AQ335" s="4" t="n"/>
+      <c r="AR335" s="4" t="n"/>
+      <c r="AS335" s="4" t="n"/>
+      <c r="AT335" s="4" t="n"/>
     </row>
     <row r="336">
       <c r="N336" s="4" t="n"/>
@@ -11552,6 +12572,9 @@
       <c r="AO336" s="4" t="n"/>
       <c r="AP336" s="4" t="n"/>
       <c r="AQ336" s="4" t="n"/>
+      <c r="AR336" s="4" t="n"/>
+      <c r="AS336" s="4" t="n"/>
+      <c r="AT336" s="4" t="n"/>
     </row>
     <row r="337">
       <c r="N337" s="4" t="n"/>
@@ -11584,6 +12607,9 @@
       <c r="AO337" s="4" t="n"/>
       <c r="AP337" s="4" t="n"/>
       <c r="AQ337" s="4" t="n"/>
+      <c r="AR337" s="4" t="n"/>
+      <c r="AS337" s="4" t="n"/>
+      <c r="AT337" s="4" t="n"/>
     </row>
     <row r="338">
       <c r="N338" s="4" t="n"/>
@@ -11616,6 +12642,9 @@
       <c r="AO338" s="4" t="n"/>
       <c r="AP338" s="4" t="n"/>
       <c r="AQ338" s="4" t="n"/>
+      <c r="AR338" s="4" t="n"/>
+      <c r="AS338" s="4" t="n"/>
+      <c r="AT338" s="4" t="n"/>
     </row>
     <row r="339">
       <c r="N339" s="4" t="n"/>
@@ -11648,6 +12677,9 @@
       <c r="AO339" s="4" t="n"/>
       <c r="AP339" s="4" t="n"/>
       <c r="AQ339" s="4" t="n"/>
+      <c r="AR339" s="4" t="n"/>
+      <c r="AS339" s="4" t="n"/>
+      <c r="AT339" s="4" t="n"/>
     </row>
     <row r="340">
       <c r="N340" s="4" t="n"/>
@@ -11680,6 +12712,9 @@
       <c r="AO340" s="4" t="n"/>
       <c r="AP340" s="4" t="n"/>
       <c r="AQ340" s="4" t="n"/>
+      <c r="AR340" s="4" t="n"/>
+      <c r="AS340" s="4" t="n"/>
+      <c r="AT340" s="4" t="n"/>
     </row>
     <row r="341">
       <c r="N341" s="4" t="n"/>
@@ -11712,6 +12747,9 @@
       <c r="AO341" s="4" t="n"/>
       <c r="AP341" s="4" t="n"/>
       <c r="AQ341" s="4" t="n"/>
+      <c r="AR341" s="4" t="n"/>
+      <c r="AS341" s="4" t="n"/>
+      <c r="AT341" s="4" t="n"/>
     </row>
     <row r="342">
       <c r="N342" s="4" t="n"/>
@@ -11744,6 +12782,9 @@
       <c r="AO342" s="4" t="n"/>
       <c r="AP342" s="4" t="n"/>
       <c r="AQ342" s="4" t="n"/>
+      <c r="AR342" s="4" t="n"/>
+      <c r="AS342" s="4" t="n"/>
+      <c r="AT342" s="4" t="n"/>
     </row>
     <row r="343">
       <c r="N343" s="4" t="n"/>
@@ -11776,6 +12817,9 @@
       <c r="AO343" s="4" t="n"/>
       <c r="AP343" s="4" t="n"/>
       <c r="AQ343" s="4" t="n"/>
+      <c r="AR343" s="4" t="n"/>
+      <c r="AS343" s="4" t="n"/>
+      <c r="AT343" s="4" t="n"/>
     </row>
     <row r="344">
       <c r="N344" s="4" t="n"/>
@@ -11808,6 +12852,9 @@
       <c r="AO344" s="4" t="n"/>
       <c r="AP344" s="4" t="n"/>
       <c r="AQ344" s="4" t="n"/>
+      <c r="AR344" s="4" t="n"/>
+      <c r="AS344" s="4" t="n"/>
+      <c r="AT344" s="4" t="n"/>
     </row>
     <row r="345">
       <c r="N345" s="4" t="n"/>
@@ -11840,6 +12887,9 @@
       <c r="AO345" s="4" t="n"/>
       <c r="AP345" s="4" t="n"/>
       <c r="AQ345" s="4" t="n"/>
+      <c r="AR345" s="4" t="n"/>
+      <c r="AS345" s="4" t="n"/>
+      <c r="AT345" s="4" t="n"/>
     </row>
     <row r="346">
       <c r="N346" s="4" t="n"/>
@@ -11872,6 +12922,9 @@
       <c r="AO346" s="4" t="n"/>
       <c r="AP346" s="4" t="n"/>
       <c r="AQ346" s="4" t="n"/>
+      <c r="AR346" s="4" t="n"/>
+      <c r="AS346" s="4" t="n"/>
+      <c r="AT346" s="4" t="n"/>
     </row>
     <row r="347">
       <c r="N347" s="4" t="n"/>
@@ -11904,6 +12957,9 @@
       <c r="AO347" s="4" t="n"/>
       <c r="AP347" s="4" t="n"/>
       <c r="AQ347" s="4" t="n"/>
+      <c r="AR347" s="4" t="n"/>
+      <c r="AS347" s="4" t="n"/>
+      <c r="AT347" s="4" t="n"/>
     </row>
     <row r="348">
       <c r="N348" s="4" t="n"/>
@@ -11936,6 +12992,9 @@
       <c r="AO348" s="4" t="n"/>
       <c r="AP348" s="4" t="n"/>
       <c r="AQ348" s="4" t="n"/>
+      <c r="AR348" s="4" t="n"/>
+      <c r="AS348" s="4" t="n"/>
+      <c r="AT348" s="4" t="n"/>
     </row>
     <row r="349">
       <c r="N349" s="4" t="n"/>
@@ -11968,6 +13027,9 @@
       <c r="AO349" s="4" t="n"/>
       <c r="AP349" s="4" t="n"/>
       <c r="AQ349" s="4" t="n"/>
+      <c r="AR349" s="4" t="n"/>
+      <c r="AS349" s="4" t="n"/>
+      <c r="AT349" s="4" t="n"/>
     </row>
     <row r="350">
       <c r="N350" s="4" t="n"/>
@@ -12000,6 +13062,9 @@
       <c r="AO350" s="4" t="n"/>
       <c r="AP350" s="4" t="n"/>
       <c r="AQ350" s="4" t="n"/>
+      <c r="AR350" s="4" t="n"/>
+      <c r="AS350" s="4" t="n"/>
+      <c r="AT350" s="4" t="n"/>
     </row>
     <row r="351">
       <c r="N351" s="4" t="n"/>
@@ -12032,6 +13097,9 @@
       <c r="AO351" s="4" t="n"/>
       <c r="AP351" s="4" t="n"/>
       <c r="AQ351" s="4" t="n"/>
+      <c r="AR351" s="4" t="n"/>
+      <c r="AS351" s="4" t="n"/>
+      <c r="AT351" s="4" t="n"/>
     </row>
     <row r="352">
       <c r="N352" s="4" t="n"/>
@@ -12064,6 +13132,9 @@
       <c r="AO352" s="4" t="n"/>
       <c r="AP352" s="4" t="n"/>
       <c r="AQ352" s="4" t="n"/>
+      <c r="AR352" s="4" t="n"/>
+      <c r="AS352" s="4" t="n"/>
+      <c r="AT352" s="4" t="n"/>
     </row>
     <row r="353">
       <c r="N353" s="4" t="n"/>
@@ -12096,6 +13167,9 @@
       <c r="AO353" s="4" t="n"/>
       <c r="AP353" s="4" t="n"/>
       <c r="AQ353" s="4" t="n"/>
+      <c r="AR353" s="4" t="n"/>
+      <c r="AS353" s="4" t="n"/>
+      <c r="AT353" s="4" t="n"/>
     </row>
     <row r="354">
       <c r="N354" s="4" t="n"/>
@@ -12128,6 +13202,9 @@
       <c r="AO354" s="4" t="n"/>
       <c r="AP354" s="4" t="n"/>
       <c r="AQ354" s="4" t="n"/>
+      <c r="AR354" s="4" t="n"/>
+      <c r="AS354" s="4" t="n"/>
+      <c r="AT354" s="4" t="n"/>
     </row>
     <row r="355">
       <c r="N355" s="4" t="n"/>
@@ -12160,6 +13237,9 @@
       <c r="AO355" s="4" t="n"/>
       <c r="AP355" s="4" t="n"/>
       <c r="AQ355" s="4" t="n"/>
+      <c r="AR355" s="4" t="n"/>
+      <c r="AS355" s="4" t="n"/>
+      <c r="AT355" s="4" t="n"/>
     </row>
     <row r="356">
       <c r="N356" s="4" t="n"/>
@@ -12192,6 +13272,9 @@
       <c r="AO356" s="4" t="n"/>
       <c r="AP356" s="4" t="n"/>
       <c r="AQ356" s="4" t="n"/>
+      <c r="AR356" s="4" t="n"/>
+      <c r="AS356" s="4" t="n"/>
+      <c r="AT356" s="4" t="n"/>
     </row>
     <row r="357">
       <c r="N357" s="4" t="n"/>
@@ -12224,6 +13307,9 @@
       <c r="AO357" s="4" t="n"/>
       <c r="AP357" s="4" t="n"/>
       <c r="AQ357" s="4" t="n"/>
+      <c r="AR357" s="4" t="n"/>
+      <c r="AS357" s="4" t="n"/>
+      <c r="AT357" s="4" t="n"/>
     </row>
     <row r="358">
       <c r="N358" s="4" t="n"/>
@@ -12256,6 +13342,9 @@
       <c r="AO358" s="4" t="n"/>
       <c r="AP358" s="4" t="n"/>
       <c r="AQ358" s="4" t="n"/>
+      <c r="AR358" s="4" t="n"/>
+      <c r="AS358" s="4" t="n"/>
+      <c r="AT358" s="4" t="n"/>
     </row>
     <row r="359">
       <c r="N359" s="4" t="n"/>
@@ -12288,6 +13377,9 @@
       <c r="AO359" s="4" t="n"/>
       <c r="AP359" s="4" t="n"/>
       <c r="AQ359" s="4" t="n"/>
+      <c r="AR359" s="4" t="n"/>
+      <c r="AS359" s="4" t="n"/>
+      <c r="AT359" s="4" t="n"/>
     </row>
     <row r="360">
       <c r="N360" s="4" t="n"/>
@@ -12320,6 +13412,9 @@
       <c r="AO360" s="4" t="n"/>
       <c r="AP360" s="4" t="n"/>
       <c r="AQ360" s="4" t="n"/>
+      <c r="AR360" s="4" t="n"/>
+      <c r="AS360" s="4" t="n"/>
+      <c r="AT360" s="4" t="n"/>
     </row>
     <row r="361">
       <c r="N361" s="4" t="n"/>
@@ -12352,6 +13447,9 @@
       <c r="AO361" s="4" t="n"/>
       <c r="AP361" s="4" t="n"/>
       <c r="AQ361" s="4" t="n"/>
+      <c r="AR361" s="4" t="n"/>
+      <c r="AS361" s="4" t="n"/>
+      <c r="AT361" s="4" t="n"/>
     </row>
     <row r="362">
       <c r="N362" s="4" t="n"/>
@@ -12384,6 +13482,9 @@
       <c r="AO362" s="4" t="n"/>
       <c r="AP362" s="4" t="n"/>
       <c r="AQ362" s="4" t="n"/>
+      <c r="AR362" s="4" t="n"/>
+      <c r="AS362" s="4" t="n"/>
+      <c r="AT362" s="4" t="n"/>
     </row>
     <row r="363">
       <c r="N363" s="4" t="n"/>
@@ -12416,6 +13517,9 @@
       <c r="AO363" s="4" t="n"/>
       <c r="AP363" s="4" t="n"/>
       <c r="AQ363" s="4" t="n"/>
+      <c r="AR363" s="4" t="n"/>
+      <c r="AS363" s="4" t="n"/>
+      <c r="AT363" s="4" t="n"/>
     </row>
     <row r="364">
       <c r="N364" s="4" t="n"/>
@@ -12448,6 +13552,9 @@
       <c r="AO364" s="4" t="n"/>
       <c r="AP364" s="4" t="n"/>
       <c r="AQ364" s="4" t="n"/>
+      <c r="AR364" s="4" t="n"/>
+      <c r="AS364" s="4" t="n"/>
+      <c r="AT364" s="4" t="n"/>
     </row>
     <row r="365">
       <c r="N365" s="4" t="n"/>
@@ -12480,6 +13587,9 @@
       <c r="AO365" s="4" t="n"/>
       <c r="AP365" s="4" t="n"/>
       <c r="AQ365" s="4" t="n"/>
+      <c r="AR365" s="4" t="n"/>
+      <c r="AS365" s="4" t="n"/>
+      <c r="AT365" s="4" t="n"/>
     </row>
     <row r="366">
       <c r="N366" s="4" t="n"/>
@@ -12512,6 +13622,9 @@
       <c r="AO366" s="4" t="n"/>
       <c r="AP366" s="4" t="n"/>
       <c r="AQ366" s="4" t="n"/>
+      <c r="AR366" s="4" t="n"/>
+      <c r="AS366" s="4" t="n"/>
+      <c r="AT366" s="4" t="n"/>
     </row>
     <row r="367">
       <c r="N367" s="4" t="n"/>
@@ -12544,6 +13657,9 @@
       <c r="AO367" s="4" t="n"/>
       <c r="AP367" s="4" t="n"/>
       <c r="AQ367" s="4" t="n"/>
+      <c r="AR367" s="4" t="n"/>
+      <c r="AS367" s="4" t="n"/>
+      <c r="AT367" s="4" t="n"/>
     </row>
     <row r="368">
       <c r="N368" s="4" t="n"/>
@@ -12576,6 +13692,9 @@
       <c r="AO368" s="4" t="n"/>
       <c r="AP368" s="4" t="n"/>
       <c r="AQ368" s="4" t="n"/>
+      <c r="AR368" s="4" t="n"/>
+      <c r="AS368" s="4" t="n"/>
+      <c r="AT368" s="4" t="n"/>
     </row>
     <row r="369">
       <c r="N369" s="4" t="n"/>
@@ -12608,6 +13727,9 @@
       <c r="AO369" s="4" t="n"/>
       <c r="AP369" s="4" t="n"/>
       <c r="AQ369" s="4" t="n"/>
+      <c r="AR369" s="4" t="n"/>
+      <c r="AS369" s="4" t="n"/>
+      <c r="AT369" s="4" t="n"/>
     </row>
     <row r="370">
       <c r="N370" s="4" t="n"/>
@@ -12640,6 +13762,9 @@
       <c r="AO370" s="4" t="n"/>
       <c r="AP370" s="4" t="n"/>
       <c r="AQ370" s="4" t="n"/>
+      <c r="AR370" s="4" t="n"/>
+      <c r="AS370" s="4" t="n"/>
+      <c r="AT370" s="4" t="n"/>
     </row>
     <row r="371">
       <c r="N371" s="4" t="n"/>
@@ -12672,6 +13797,9 @@
       <c r="AO371" s="4" t="n"/>
       <c r="AP371" s="4" t="n"/>
       <c r="AQ371" s="4" t="n"/>
+      <c r="AR371" s="4" t="n"/>
+      <c r="AS371" s="4" t="n"/>
+      <c r="AT371" s="4" t="n"/>
     </row>
     <row r="372">
       <c r="N372" s="4" t="n"/>
@@ -12704,6 +13832,9 @@
       <c r="AO372" s="4" t="n"/>
       <c r="AP372" s="4" t="n"/>
       <c r="AQ372" s="4" t="n"/>
+      <c r="AR372" s="4" t="n"/>
+      <c r="AS372" s="4" t="n"/>
+      <c r="AT372" s="4" t="n"/>
     </row>
     <row r="373">
       <c r="N373" s="4" t="n"/>
@@ -12736,6 +13867,9 @@
       <c r="AO373" s="4" t="n"/>
       <c r="AP373" s="4" t="n"/>
       <c r="AQ373" s="4" t="n"/>
+      <c r="AR373" s="4" t="n"/>
+      <c r="AS373" s="4" t="n"/>
+      <c r="AT373" s="4" t="n"/>
     </row>
     <row r="374">
       <c r="N374" s="4" t="n"/>
@@ -12768,6 +13902,9 @@
       <c r="AO374" s="4" t="n"/>
       <c r="AP374" s="4" t="n"/>
       <c r="AQ374" s="4" t="n"/>
+      <c r="AR374" s="4" t="n"/>
+      <c r="AS374" s="4" t="n"/>
+      <c r="AT374" s="4" t="n"/>
     </row>
     <row r="375">
       <c r="N375" s="4" t="n"/>
@@ -12800,6 +13937,9 @@
       <c r="AO375" s="4" t="n"/>
       <c r="AP375" s="4" t="n"/>
       <c r="AQ375" s="4" t="n"/>
+      <c r="AR375" s="4" t="n"/>
+      <c r="AS375" s="4" t="n"/>
+      <c r="AT375" s="4" t="n"/>
     </row>
     <row r="376">
       <c r="N376" s="4" t="n"/>
@@ -12832,6 +13972,9 @@
       <c r="AO376" s="4" t="n"/>
       <c r="AP376" s="4" t="n"/>
       <c r="AQ376" s="4" t="n"/>
+      <c r="AR376" s="4" t="n"/>
+      <c r="AS376" s="4" t="n"/>
+      <c r="AT376" s="4" t="n"/>
     </row>
     <row r="377">
       <c r="N377" s="4" t="n"/>
@@ -12864,6 +14007,9 @@
       <c r="AO377" s="4" t="n"/>
       <c r="AP377" s="4" t="n"/>
       <c r="AQ377" s="4" t="n"/>
+      <c r="AR377" s="4" t="n"/>
+      <c r="AS377" s="4" t="n"/>
+      <c r="AT377" s="4" t="n"/>
     </row>
     <row r="378">
       <c r="N378" s="4" t="n"/>
@@ -12896,6 +14042,9 @@
       <c r="AO378" s="4" t="n"/>
       <c r="AP378" s="4" t="n"/>
       <c r="AQ378" s="4" t="n"/>
+      <c r="AR378" s="4" t="n"/>
+      <c r="AS378" s="4" t="n"/>
+      <c r="AT378" s="4" t="n"/>
     </row>
     <row r="379">
       <c r="N379" s="4" t="n"/>
@@ -12928,6 +14077,9 @@
       <c r="AO379" s="4" t="n"/>
       <c r="AP379" s="4" t="n"/>
       <c r="AQ379" s="4" t="n"/>
+      <c r="AR379" s="4" t="n"/>
+      <c r="AS379" s="4" t="n"/>
+      <c r="AT379" s="4" t="n"/>
     </row>
     <row r="380">
       <c r="N380" s="4" t="n"/>
@@ -12960,6 +14112,9 @@
       <c r="AO380" s="4" t="n"/>
       <c r="AP380" s="4" t="n"/>
       <c r="AQ380" s="4" t="n"/>
+      <c r="AR380" s="4" t="n"/>
+      <c r="AS380" s="4" t="n"/>
+      <c r="AT380" s="4" t="n"/>
     </row>
     <row r="381">
       <c r="N381" s="4" t="n"/>
@@ -12992,6 +14147,9 @@
       <c r="AO381" s="4" t="n"/>
       <c r="AP381" s="4" t="n"/>
       <c r="AQ381" s="4" t="n"/>
+      <c r="AR381" s="4" t="n"/>
+      <c r="AS381" s="4" t="n"/>
+      <c r="AT381" s="4" t="n"/>
     </row>
     <row r="382">
       <c r="N382" s="4" t="n"/>
@@ -13024,6 +14182,9 @@
       <c r="AO382" s="4" t="n"/>
       <c r="AP382" s="4" t="n"/>
       <c r="AQ382" s="4" t="n"/>
+      <c r="AR382" s="4" t="n"/>
+      <c r="AS382" s="4" t="n"/>
+      <c r="AT382" s="4" t="n"/>
     </row>
     <row r="383">
       <c r="N383" s="4" t="n"/>
@@ -13056,6 +14217,9 @@
       <c r="AO383" s="4" t="n"/>
       <c r="AP383" s="4" t="n"/>
       <c r="AQ383" s="4" t="n"/>
+      <c r="AR383" s="4" t="n"/>
+      <c r="AS383" s="4" t="n"/>
+      <c r="AT383" s="4" t="n"/>
     </row>
     <row r="384">
       <c r="N384" s="4" t="n"/>
@@ -13088,6 +14252,9 @@
       <c r="AO384" s="4" t="n"/>
       <c r="AP384" s="4" t="n"/>
       <c r="AQ384" s="4" t="n"/>
+      <c r="AR384" s="4" t="n"/>
+      <c r="AS384" s="4" t="n"/>
+      <c r="AT384" s="4" t="n"/>
     </row>
     <row r="385">
       <c r="N385" s="4" t="n"/>
@@ -13120,6 +14287,9 @@
       <c r="AO385" s="4" t="n"/>
       <c r="AP385" s="4" t="n"/>
       <c r="AQ385" s="4" t="n"/>
+      <c r="AR385" s="4" t="n"/>
+      <c r="AS385" s="4" t="n"/>
+      <c r="AT385" s="4" t="n"/>
     </row>
     <row r="386">
       <c r="N386" s="4" t="n"/>
@@ -13152,6 +14322,9 @@
       <c r="AO386" s="4" t="n"/>
       <c r="AP386" s="4" t="n"/>
       <c r="AQ386" s="4" t="n"/>
+      <c r="AR386" s="4" t="n"/>
+      <c r="AS386" s="4" t="n"/>
+      <c r="AT386" s="4" t="n"/>
     </row>
     <row r="387">
       <c r="N387" s="4" t="n"/>
@@ -13184,6 +14357,9 @@
       <c r="AO387" s="4" t="n"/>
       <c r="AP387" s="4" t="n"/>
       <c r="AQ387" s="4" t="n"/>
+      <c r="AR387" s="4" t="n"/>
+      <c r="AS387" s="4" t="n"/>
+      <c r="AT387" s="4" t="n"/>
     </row>
     <row r="388">
       <c r="N388" s="4" t="n"/>
@@ -13216,6 +14392,9 @@
       <c r="AO388" s="4" t="n"/>
       <c r="AP388" s="4" t="n"/>
       <c r="AQ388" s="4" t="n"/>
+      <c r="AR388" s="4" t="n"/>
+      <c r="AS388" s="4" t="n"/>
+      <c r="AT388" s="4" t="n"/>
     </row>
     <row r="389">
       <c r="N389" s="4" t="n"/>
@@ -13248,6 +14427,9 @@
       <c r="AO389" s="4" t="n"/>
       <c r="AP389" s="4" t="n"/>
       <c r="AQ389" s="4" t="n"/>
+      <c r="AR389" s="4" t="n"/>
+      <c r="AS389" s="4" t="n"/>
+      <c r="AT389" s="4" t="n"/>
     </row>
     <row r="390">
       <c r="N390" s="4" t="n"/>
@@ -13280,6 +14462,9 @@
       <c r="AO390" s="4" t="n"/>
       <c r="AP390" s="4" t="n"/>
       <c r="AQ390" s="4" t="n"/>
+      <c r="AR390" s="4" t="n"/>
+      <c r="AS390" s="4" t="n"/>
+      <c r="AT390" s="4" t="n"/>
     </row>
     <row r="391">
       <c r="N391" s="4" t="n"/>
@@ -13312,6 +14497,9 @@
       <c r="AO391" s="4" t="n"/>
       <c r="AP391" s="4" t="n"/>
       <c r="AQ391" s="4" t="n"/>
+      <c r="AR391" s="4" t="n"/>
+      <c r="AS391" s="4" t="n"/>
+      <c r="AT391" s="4" t="n"/>
     </row>
     <row r="392">
       <c r="N392" s="4" t="n"/>
@@ -13344,6 +14532,9 @@
       <c r="AO392" s="4" t="n"/>
       <c r="AP392" s="4" t="n"/>
       <c r="AQ392" s="4" t="n"/>
+      <c r="AR392" s="4" t="n"/>
+      <c r="AS392" s="4" t="n"/>
+      <c r="AT392" s="4" t="n"/>
     </row>
     <row r="393">
       <c r="N393" s="4" t="n"/>
@@ -13376,6 +14567,9 @@
       <c r="AO393" s="4" t="n"/>
       <c r="AP393" s="4" t="n"/>
       <c r="AQ393" s="4" t="n"/>
+      <c r="AR393" s="4" t="n"/>
+      <c r="AS393" s="4" t="n"/>
+      <c r="AT393" s="4" t="n"/>
     </row>
     <row r="394">
       <c r="N394" s="4" t="n"/>
@@ -13408,6 +14602,9 @@
       <c r="AO394" s="4" t="n"/>
       <c r="AP394" s="4" t="n"/>
       <c r="AQ394" s="4" t="n"/>
+      <c r="AR394" s="4" t="n"/>
+      <c r="AS394" s="4" t="n"/>
+      <c r="AT394" s="4" t="n"/>
     </row>
     <row r="395">
       <c r="N395" s="4" t="n"/>
@@ -13440,6 +14637,9 @@
       <c r="AO395" s="4" t="n"/>
       <c r="AP395" s="4" t="n"/>
       <c r="AQ395" s="4" t="n"/>
+      <c r="AR395" s="4" t="n"/>
+      <c r="AS395" s="4" t="n"/>
+      <c r="AT395" s="4" t="n"/>
     </row>
     <row r="396">
       <c r="N396" s="4" t="n"/>
@@ -13472,6 +14672,9 @@
       <c r="AO396" s="4" t="n"/>
       <c r="AP396" s="4" t="n"/>
       <c r="AQ396" s="4" t="n"/>
+      <c r="AR396" s="4" t="n"/>
+      <c r="AS396" s="4" t="n"/>
+      <c r="AT396" s="4" t="n"/>
     </row>
     <row r="397">
       <c r="N397" s="4" t="n"/>
@@ -13504,6 +14707,9 @@
       <c r="AO397" s="4" t="n"/>
       <c r="AP397" s="4" t="n"/>
       <c r="AQ397" s="4" t="n"/>
+      <c r="AR397" s="4" t="n"/>
+      <c r="AS397" s="4" t="n"/>
+      <c r="AT397" s="4" t="n"/>
     </row>
     <row r="398">
       <c r="N398" s="4" t="n"/>
@@ -13536,6 +14742,9 @@
       <c r="AO398" s="4" t="n"/>
       <c r="AP398" s="4" t="n"/>
       <c r="AQ398" s="4" t="n"/>
+      <c r="AR398" s="4" t="n"/>
+      <c r="AS398" s="4" t="n"/>
+      <c r="AT398" s="4" t="n"/>
     </row>
     <row r="399">
       <c r="N399" s="4" t="n"/>
@@ -13568,6 +14777,9 @@
       <c r="AO399" s="4" t="n"/>
       <c r="AP399" s="4" t="n"/>
       <c r="AQ399" s="4" t="n"/>
+      <c r="AR399" s="4" t="n"/>
+      <c r="AS399" s="4" t="n"/>
+      <c r="AT399" s="4" t="n"/>
     </row>
     <row r="400">
       <c r="N400" s="4" t="n"/>
@@ -13600,6 +14812,9 @@
       <c r="AO400" s="4" t="n"/>
       <c r="AP400" s="4" t="n"/>
       <c r="AQ400" s="4" t="n"/>
+      <c r="AR400" s="4" t="n"/>
+      <c r="AS400" s="4" t="n"/>
+      <c r="AT400" s="4" t="n"/>
     </row>
     <row r="401">
       <c r="N401" s="4" t="n"/>
@@ -13632,6 +14847,9 @@
       <c r="AO401" s="4" t="n"/>
       <c r="AP401" s="4" t="n"/>
       <c r="AQ401" s="4" t="n"/>
+      <c r="AR401" s="4" t="n"/>
+      <c r="AS401" s="4" t="n"/>
+      <c r="AT401" s="4" t="n"/>
     </row>
     <row r="402">
       <c r="N402" s="4" t="n"/>
@@ -13664,6 +14882,9 @@
       <c r="AO402" s="4" t="n"/>
       <c r="AP402" s="4" t="n"/>
       <c r="AQ402" s="4" t="n"/>
+      <c r="AR402" s="4" t="n"/>
+      <c r="AS402" s="4" t="n"/>
+      <c r="AT402" s="4" t="n"/>
     </row>
     <row r="403">
       <c r="N403" s="4" t="n"/>
@@ -13696,6 +14917,9 @@
       <c r="AO403" s="4" t="n"/>
       <c r="AP403" s="4" t="n"/>
       <c r="AQ403" s="4" t="n"/>
+      <c r="AR403" s="4" t="n"/>
+      <c r="AS403" s="4" t="n"/>
+      <c r="AT403" s="4" t="n"/>
     </row>
     <row r="404">
       <c r="N404" s="4" t="n"/>
@@ -13728,6 +14952,9 @@
       <c r="AO404" s="4" t="n"/>
       <c r="AP404" s="4" t="n"/>
       <c r="AQ404" s="4" t="n"/>
+      <c r="AR404" s="4" t="n"/>
+      <c r="AS404" s="4" t="n"/>
+      <c r="AT404" s="4" t="n"/>
     </row>
     <row r="405">
       <c r="N405" s="4" t="n"/>
@@ -13760,6 +14987,9 @@
       <c r="AO405" s="4" t="n"/>
       <c r="AP405" s="4" t="n"/>
       <c r="AQ405" s="4" t="n"/>
+      <c r="AR405" s="4" t="n"/>
+      <c r="AS405" s="4" t="n"/>
+      <c r="AT405" s="4" t="n"/>
     </row>
     <row r="406">
       <c r="N406" s="4" t="n"/>
@@ -13792,6 +15022,9 @@
       <c r="AO406" s="4" t="n"/>
       <c r="AP406" s="4" t="n"/>
       <c r="AQ406" s="4" t="n"/>
+      <c r="AR406" s="4" t="n"/>
+      <c r="AS406" s="4" t="n"/>
+      <c r="AT406" s="4" t="n"/>
     </row>
     <row r="407">
       <c r="N407" s="4" t="n"/>
@@ -13824,6 +15057,9 @@
       <c r="AO407" s="4" t="n"/>
       <c r="AP407" s="4" t="n"/>
       <c r="AQ407" s="4" t="n"/>
+      <c r="AR407" s="4" t="n"/>
+      <c r="AS407" s="4" t="n"/>
+      <c r="AT407" s="4" t="n"/>
     </row>
     <row r="408">
       <c r="N408" s="4" t="n"/>
@@ -13856,6 +15092,9 @@
       <c r="AO408" s="4" t="n"/>
       <c r="AP408" s="4" t="n"/>
       <c r="AQ408" s="4" t="n"/>
+      <c r="AR408" s="4" t="n"/>
+      <c r="AS408" s="4" t="n"/>
+      <c r="AT408" s="4" t="n"/>
     </row>
     <row r="409">
       <c r="N409" s="4" t="n"/>
@@ -13888,6 +15127,9 @@
       <c r="AO409" s="4" t="n"/>
       <c r="AP409" s="4" t="n"/>
       <c r="AQ409" s="4" t="n"/>
+      <c r="AR409" s="4" t="n"/>
+      <c r="AS409" s="4" t="n"/>
+      <c r="AT409" s="4" t="n"/>
     </row>
     <row r="410">
       <c r="N410" s="4" t="n"/>
@@ -13920,6 +15162,9 @@
       <c r="AO410" s="4" t="n"/>
       <c r="AP410" s="4" t="n"/>
       <c r="AQ410" s="4" t="n"/>
+      <c r="AR410" s="4" t="n"/>
+      <c r="AS410" s="4" t="n"/>
+      <c r="AT410" s="4" t="n"/>
     </row>
     <row r="411">
       <c r="N411" s="4" t="n"/>
@@ -13952,6 +15197,9 @@
       <c r="AO411" s="4" t="n"/>
       <c r="AP411" s="4" t="n"/>
       <c r="AQ411" s="4" t="n"/>
+      <c r="AR411" s="4" t="n"/>
+      <c r="AS411" s="4" t="n"/>
+      <c r="AT411" s="4" t="n"/>
     </row>
     <row r="412">
       <c r="N412" s="4" t="n"/>
@@ -13984,6 +15232,9 @@
       <c r="AO412" s="4" t="n"/>
       <c r="AP412" s="4" t="n"/>
       <c r="AQ412" s="4" t="n"/>
+      <c r="AR412" s="4" t="n"/>
+      <c r="AS412" s="4" t="n"/>
+      <c r="AT412" s="4" t="n"/>
     </row>
     <row r="413">
       <c r="N413" s="4" t="n"/>
@@ -14016,6 +15267,9 @@
       <c r="AO413" s="4" t="n"/>
       <c r="AP413" s="4" t="n"/>
       <c r="AQ413" s="4" t="n"/>
+      <c r="AR413" s="4" t="n"/>
+      <c r="AS413" s="4" t="n"/>
+      <c r="AT413" s="4" t="n"/>
     </row>
     <row r="414">
       <c r="N414" s="4" t="n"/>
@@ -14048,6 +15302,9 @@
       <c r="AO414" s="4" t="n"/>
       <c r="AP414" s="4" t="n"/>
       <c r="AQ414" s="4" t="n"/>
+      <c r="AR414" s="4" t="n"/>
+      <c r="AS414" s="4" t="n"/>
+      <c r="AT414" s="4" t="n"/>
     </row>
     <row r="415">
       <c r="N415" s="4" t="n"/>
@@ -14080,6 +15337,9 @@
       <c r="AO415" s="4" t="n"/>
       <c r="AP415" s="4" t="n"/>
       <c r="AQ415" s="4" t="n"/>
+      <c r="AR415" s="4" t="n"/>
+      <c r="AS415" s="4" t="n"/>
+      <c r="AT415" s="4" t="n"/>
     </row>
     <row r="416">
       <c r="N416" s="4" t="n"/>
@@ -14112,6 +15372,9 @@
       <c r="AO416" s="4" t="n"/>
       <c r="AP416" s="4" t="n"/>
       <c r="AQ416" s="4" t="n"/>
+      <c r="AR416" s="4" t="n"/>
+      <c r="AS416" s="4" t="n"/>
+      <c r="AT416" s="4" t="n"/>
     </row>
     <row r="417">
       <c r="N417" s="4" t="n"/>
@@ -14144,6 +15407,9 @@
       <c r="AO417" s="4" t="n"/>
       <c r="AP417" s="4" t="n"/>
       <c r="AQ417" s="4" t="n"/>
+      <c r="AR417" s="4" t="n"/>
+      <c r="AS417" s="4" t="n"/>
+      <c r="AT417" s="4" t="n"/>
     </row>
     <row r="418">
       <c r="N418" s="4" t="n"/>
@@ -14176,6 +15442,9 @@
       <c r="AO418" s="4" t="n"/>
       <c r="AP418" s="4" t="n"/>
       <c r="AQ418" s="4" t="n"/>
+      <c r="AR418" s="4" t="n"/>
+      <c r="AS418" s="4" t="n"/>
+      <c r="AT418" s="4" t="n"/>
     </row>
     <row r="419">
       <c r="N419" s="4" t="n"/>
@@ -14208,6 +15477,9 @@
       <c r="AO419" s="4" t="n"/>
       <c r="AP419" s="4" t="n"/>
       <c r="AQ419" s="4" t="n"/>
+      <c r="AR419" s="4" t="n"/>
+      <c r="AS419" s="4" t="n"/>
+      <c r="AT419" s="4" t="n"/>
     </row>
     <row r="420">
       <c r="N420" s="4" t="n"/>
@@ -14240,6 +15512,9 @@
       <c r="AO420" s="4" t="n"/>
       <c r="AP420" s="4" t="n"/>
       <c r="AQ420" s="4" t="n"/>
+      <c r="AR420" s="4" t="n"/>
+      <c r="AS420" s="4" t="n"/>
+      <c r="AT420" s="4" t="n"/>
     </row>
     <row r="421">
       <c r="N421" s="4" t="n"/>
@@ -14272,6 +15547,9 @@
       <c r="AO421" s="4" t="n"/>
       <c r="AP421" s="4" t="n"/>
       <c r="AQ421" s="4" t="n"/>
+      <c r="AR421" s="4" t="n"/>
+      <c r="AS421" s="4" t="n"/>
+      <c r="AT421" s="4" t="n"/>
     </row>
     <row r="422">
       <c r="N422" s="4" t="n"/>
@@ -14304,6 +15582,9 @@
       <c r="AO422" s="4" t="n"/>
       <c r="AP422" s="4" t="n"/>
       <c r="AQ422" s="4" t="n"/>
+      <c r="AR422" s="4" t="n"/>
+      <c r="AS422" s="4" t="n"/>
+      <c r="AT422" s="4" t="n"/>
     </row>
     <row r="423">
       <c r="N423" s="4" t="n"/>
@@ -14336,6 +15617,9 @@
       <c r="AO423" s="4" t="n"/>
       <c r="AP423" s="4" t="n"/>
       <c r="AQ423" s="4" t="n"/>
+      <c r="AR423" s="4" t="n"/>
+      <c r="AS423" s="4" t="n"/>
+      <c r="AT423" s="4" t="n"/>
     </row>
     <row r="424">
       <c r="N424" s="4" t="n"/>
@@ -14368,6 +15652,9 @@
       <c r="AO424" s="4" t="n"/>
       <c r="AP424" s="4" t="n"/>
       <c r="AQ424" s="4" t="n"/>
+      <c r="AR424" s="4" t="n"/>
+      <c r="AS424" s="4" t="n"/>
+      <c r="AT424" s="4" t="n"/>
     </row>
     <row r="425">
       <c r="N425" s="4" t="n"/>
@@ -14400,6 +15687,9 @@
       <c r="AO425" s="4" t="n"/>
       <c r="AP425" s="4" t="n"/>
       <c r="AQ425" s="4" t="n"/>
+      <c r="AR425" s="4" t="n"/>
+      <c r="AS425" s="4" t="n"/>
+      <c r="AT425" s="4" t="n"/>
     </row>
     <row r="426">
       <c r="N426" s="4" t="n"/>
@@ -14432,6 +15722,9 @@
       <c r="AO426" s="4" t="n"/>
       <c r="AP426" s="4" t="n"/>
       <c r="AQ426" s="4" t="n"/>
+      <c r="AR426" s="4" t="n"/>
+      <c r="AS426" s="4" t="n"/>
+      <c r="AT426" s="4" t="n"/>
     </row>
     <row r="427">
       <c r="N427" s="4" t="n"/>
@@ -14464,6 +15757,9 @@
       <c r="AO427" s="4" t="n"/>
       <c r="AP427" s="4" t="n"/>
       <c r="AQ427" s="4" t="n"/>
+      <c r="AR427" s="4" t="n"/>
+      <c r="AS427" s="4" t="n"/>
+      <c r="AT427" s="4" t="n"/>
     </row>
     <row r="428">
       <c r="N428" s="4" t="n"/>
@@ -14496,6 +15792,9 @@
       <c r="AO428" s="4" t="n"/>
       <c r="AP428" s="4" t="n"/>
       <c r="AQ428" s="4" t="n"/>
+      <c r="AR428" s="4" t="n"/>
+      <c r="AS428" s="4" t="n"/>
+      <c r="AT428" s="4" t="n"/>
     </row>
     <row r="429">
       <c r="N429" s="4" t="n"/>
@@ -14528,6 +15827,9 @@
       <c r="AO429" s="4" t="n"/>
       <c r="AP429" s="4" t="n"/>
       <c r="AQ429" s="4" t="n"/>
+      <c r="AR429" s="4" t="n"/>
+      <c r="AS429" s="4" t="n"/>
+      <c r="AT429" s="4" t="n"/>
     </row>
     <row r="430">
       <c r="N430" s="4" t="n"/>
@@ -14560,6 +15862,9 @@
       <c r="AO430" s="4" t="n"/>
       <c r="AP430" s="4" t="n"/>
       <c r="AQ430" s="4" t="n"/>
+      <c r="AR430" s="4" t="n"/>
+      <c r="AS430" s="4" t="n"/>
+      <c r="AT430" s="4" t="n"/>
     </row>
     <row r="431">
       <c r="N431" s="4" t="n"/>
@@ -14592,6 +15897,9 @@
       <c r="AO431" s="4" t="n"/>
       <c r="AP431" s="4" t="n"/>
       <c r="AQ431" s="4" t="n"/>
+      <c r="AR431" s="4" t="n"/>
+      <c r="AS431" s="4" t="n"/>
+      <c r="AT431" s="4" t="n"/>
     </row>
     <row r="432">
       <c r="N432" s="4" t="n"/>
@@ -14624,6 +15932,9 @@
       <c r="AO432" s="4" t="n"/>
       <c r="AP432" s="4" t="n"/>
       <c r="AQ432" s="4" t="n"/>
+      <c r="AR432" s="4" t="n"/>
+      <c r="AS432" s="4" t="n"/>
+      <c r="AT432" s="4" t="n"/>
     </row>
     <row r="433">
       <c r="N433" s="4" t="n"/>
@@ -14656,6 +15967,9 @@
       <c r="AO433" s="4" t="n"/>
       <c r="AP433" s="4" t="n"/>
       <c r="AQ433" s="4" t="n"/>
+      <c r="AR433" s="4" t="n"/>
+      <c r="AS433" s="4" t="n"/>
+      <c r="AT433" s="4" t="n"/>
     </row>
     <row r="434">
       <c r="N434" s="4" t="n"/>
@@ -14688,6 +16002,9 @@
       <c r="AO434" s="4" t="n"/>
       <c r="AP434" s="4" t="n"/>
       <c r="AQ434" s="4" t="n"/>
+      <c r="AR434" s="4" t="n"/>
+      <c r="AS434" s="4" t="n"/>
+      <c r="AT434" s="4" t="n"/>
     </row>
     <row r="435">
       <c r="N435" s="4" t="n"/>
@@ -14720,6 +16037,9 @@
       <c r="AO435" s="4" t="n"/>
       <c r="AP435" s="4" t="n"/>
       <c r="AQ435" s="4" t="n"/>
+      <c r="AR435" s="4" t="n"/>
+      <c r="AS435" s="4" t="n"/>
+      <c r="AT435" s="4" t="n"/>
     </row>
     <row r="436">
       <c r="N436" s="4" t="n"/>
@@ -14752,6 +16072,9 @@
       <c r="AO436" s="4" t="n"/>
       <c r="AP436" s="4" t="n"/>
       <c r="AQ436" s="4" t="n"/>
+      <c r="AR436" s="4" t="n"/>
+      <c r="AS436" s="4" t="n"/>
+      <c r="AT436" s="4" t="n"/>
     </row>
     <row r="437">
       <c r="N437" s="4" t="n"/>
@@ -14784,6 +16107,9 @@
       <c r="AO437" s="4" t="n"/>
       <c r="AP437" s="4" t="n"/>
       <c r="AQ437" s="4" t="n"/>
+      <c r="AR437" s="4" t="n"/>
+      <c r="AS437" s="4" t="n"/>
+      <c r="AT437" s="4" t="n"/>
     </row>
     <row r="438">
       <c r="N438" s="4" t="n"/>
@@ -14816,6 +16142,9 @@
       <c r="AO438" s="4" t="n"/>
       <c r="AP438" s="4" t="n"/>
       <c r="AQ438" s="4" t="n"/>
+      <c r="AR438" s="4" t="n"/>
+      <c r="AS438" s="4" t="n"/>
+      <c r="AT438" s="4" t="n"/>
     </row>
     <row r="439">
       <c r="N439" s="4" t="n"/>
@@ -14848,6 +16177,9 @@
       <c r="AO439" s="4" t="n"/>
       <c r="AP439" s="4" t="n"/>
       <c r="AQ439" s="4" t="n"/>
+      <c r="AR439" s="4" t="n"/>
+      <c r="AS439" s="4" t="n"/>
+      <c r="AT439" s="4" t="n"/>
     </row>
     <row r="440">
       <c r="N440" s="4" t="n"/>
@@ -14880,6 +16212,9 @@
       <c r="AO440" s="4" t="n"/>
       <c r="AP440" s="4" t="n"/>
       <c r="AQ440" s="4" t="n"/>
+      <c r="AR440" s="4" t="n"/>
+      <c r="AS440" s="4" t="n"/>
+      <c r="AT440" s="4" t="n"/>
     </row>
     <row r="441">
       <c r="N441" s="4" t="n"/>
@@ -14912,6 +16247,9 @@
       <c r="AO441" s="4" t="n"/>
       <c r="AP441" s="4" t="n"/>
       <c r="AQ441" s="4" t="n"/>
+      <c r="AR441" s="4" t="n"/>
+      <c r="AS441" s="4" t="n"/>
+      <c r="AT441" s="4" t="n"/>
     </row>
     <row r="442">
       <c r="N442" s="4" t="n"/>
@@ -14944,6 +16282,9 @@
       <c r="AO442" s="4" t="n"/>
       <c r="AP442" s="4" t="n"/>
       <c r="AQ442" s="4" t="n"/>
+      <c r="AR442" s="4" t="n"/>
+      <c r="AS442" s="4" t="n"/>
+      <c r="AT442" s="4" t="n"/>
     </row>
     <row r="443">
       <c r="N443" s="4" t="n"/>
@@ -14976,6 +16317,9 @@
       <c r="AO443" s="4" t="n"/>
       <c r="AP443" s="4" t="n"/>
       <c r="AQ443" s="4" t="n"/>
+      <c r="AR443" s="4" t="n"/>
+      <c r="AS443" s="4" t="n"/>
+      <c r="AT443" s="4" t="n"/>
     </row>
     <row r="444">
       <c r="N444" s="4" t="n"/>
@@ -15008,6 +16352,9 @@
       <c r="AO444" s="4" t="n"/>
       <c r="AP444" s="4" t="n"/>
       <c r="AQ444" s="4" t="n"/>
+      <c r="AR444" s="4" t="n"/>
+      <c r="AS444" s="4" t="n"/>
+      <c r="AT444" s="4" t="n"/>
     </row>
     <row r="445">
       <c r="N445" s="4" t="n"/>
@@ -15040,6 +16387,9 @@
       <c r="AO445" s="4" t="n"/>
       <c r="AP445" s="4" t="n"/>
       <c r="AQ445" s="4" t="n"/>
+      <c r="AR445" s="4" t="n"/>
+      <c r="AS445" s="4" t="n"/>
+      <c r="AT445" s="4" t="n"/>
     </row>
     <row r="446">
       <c r="N446" s="4" t="n"/>
@@ -15072,6 +16422,9 @@
       <c r="AO446" s="4" t="n"/>
       <c r="AP446" s="4" t="n"/>
       <c r="AQ446" s="4" t="n"/>
+      <c r="AR446" s="4" t="n"/>
+      <c r="AS446" s="4" t="n"/>
+      <c r="AT446" s="4" t="n"/>
     </row>
     <row r="447">
       <c r="N447" s="4" t="n"/>
@@ -15104,6 +16457,9 @@
       <c r="AO447" s="4" t="n"/>
       <c r="AP447" s="4" t="n"/>
       <c r="AQ447" s="4" t="n"/>
+      <c r="AR447" s="4" t="n"/>
+      <c r="AS447" s="4" t="n"/>
+      <c r="AT447" s="4" t="n"/>
     </row>
     <row r="448">
       <c r="N448" s="4" t="n"/>
@@ -15136,6 +16492,9 @@
       <c r="AO448" s="4" t="n"/>
       <c r="AP448" s="4" t="n"/>
       <c r="AQ448" s="4" t="n"/>
+      <c r="AR448" s="4" t="n"/>
+      <c r="AS448" s="4" t="n"/>
+      <c r="AT448" s="4" t="n"/>
     </row>
     <row r="449">
       <c r="N449" s="4" t="n"/>
@@ -15168,6 +16527,9 @@
       <c r="AO449" s="4" t="n"/>
       <c r="AP449" s="4" t="n"/>
       <c r="AQ449" s="4" t="n"/>
+      <c r="AR449" s="4" t="n"/>
+      <c r="AS449" s="4" t="n"/>
+      <c r="AT449" s="4" t="n"/>
     </row>
     <row r="450">
       <c r="N450" s="4" t="n"/>
@@ -15200,6 +16562,9 @@
       <c r="AO450" s="4" t="n"/>
       <c r="AP450" s="4" t="n"/>
       <c r="AQ450" s="4" t="n"/>
+      <c r="AR450" s="4" t="n"/>
+      <c r="AS450" s="4" t="n"/>
+      <c r="AT450" s="4" t="n"/>
     </row>
     <row r="451">
       <c r="N451" s="4" t="n"/>
@@ -15232,6 +16597,9 @@
       <c r="AO451" s="4" t="n"/>
       <c r="AP451" s="4" t="n"/>
       <c r="AQ451" s="4" t="n"/>
+      <c r="AR451" s="4" t="n"/>
+      <c r="AS451" s="4" t="n"/>
+      <c r="AT451" s="4" t="n"/>
     </row>
     <row r="452">
       <c r="N452" s="4" t="n"/>
@@ -15264,6 +16632,9 @@
       <c r="AO452" s="4" t="n"/>
       <c r="AP452" s="4" t="n"/>
       <c r="AQ452" s="4" t="n"/>
+      <c r="AR452" s="4" t="n"/>
+      <c r="AS452" s="4" t="n"/>
+      <c r="AT452" s="4" t="n"/>
     </row>
     <row r="453">
       <c r="N453" s="4" t="n"/>
@@ -15296,6 +16667,9 @@
       <c r="AO453" s="4" t="n"/>
       <c r="AP453" s="4" t="n"/>
       <c r="AQ453" s="4" t="n"/>
+      <c r="AR453" s="4" t="n"/>
+      <c r="AS453" s="4" t="n"/>
+      <c r="AT453" s="4" t="n"/>
     </row>
     <row r="454">
       <c r="N454" s="4" t="n"/>
@@ -15328,6 +16702,9 @@
       <c r="AO454" s="4" t="n"/>
       <c r="AP454" s="4" t="n"/>
       <c r="AQ454" s="4" t="n"/>
+      <c r="AR454" s="4" t="n"/>
+      <c r="AS454" s="4" t="n"/>
+      <c r="AT454" s="4" t="n"/>
     </row>
     <row r="455">
       <c r="N455" s="4" t="n"/>
@@ -15360,6 +16737,9 @@
       <c r="AO455" s="4" t="n"/>
       <c r="AP455" s="4" t="n"/>
       <c r="AQ455" s="4" t="n"/>
+      <c r="AR455" s="4" t="n"/>
+      <c r="AS455" s="4" t="n"/>
+      <c r="AT455" s="4" t="n"/>
     </row>
     <row r="456">
       <c r="N456" s="4" t="n"/>
@@ -15392,6 +16772,9 @@
       <c r="AO456" s="4" t="n"/>
       <c r="AP456" s="4" t="n"/>
       <c r="AQ456" s="4" t="n"/>
+      <c r="AR456" s="4" t="n"/>
+      <c r="AS456" s="4" t="n"/>
+      <c r="AT456" s="4" t="n"/>
     </row>
     <row r="457">
       <c r="N457" s="4" t="n"/>
@@ -15424,6 +16807,9 @@
       <c r="AO457" s="4" t="n"/>
       <c r="AP457" s="4" t="n"/>
       <c r="AQ457" s="4" t="n"/>
+      <c r="AR457" s="4" t="n"/>
+      <c r="AS457" s="4" t="n"/>
+      <c r="AT457" s="4" t="n"/>
     </row>
     <row r="458">
       <c r="N458" s="4" t="n"/>
@@ -15456,6 +16842,9 @@
       <c r="AO458" s="4" t="n"/>
       <c r="AP458" s="4" t="n"/>
       <c r="AQ458" s="4" t="n"/>
+      <c r="AR458" s="4" t="n"/>
+      <c r="AS458" s="4" t="n"/>
+      <c r="AT458" s="4" t="n"/>
     </row>
     <row r="459">
       <c r="N459" s="4" t="n"/>
@@ -15488,6 +16877,9 @@
       <c r="AO459" s="4" t="n"/>
       <c r="AP459" s="4" t="n"/>
       <c r="AQ459" s="4" t="n"/>
+      <c r="AR459" s="4" t="n"/>
+      <c r="AS459" s="4" t="n"/>
+      <c r="AT459" s="4" t="n"/>
     </row>
     <row r="460">
       <c r="N460" s="4" t="n"/>
@@ -15520,6 +16912,9 @@
       <c r="AO460" s="4" t="n"/>
       <c r="AP460" s="4" t="n"/>
       <c r="AQ460" s="4" t="n"/>
+      <c r="AR460" s="4" t="n"/>
+      <c r="AS460" s="4" t="n"/>
+      <c r="AT460" s="4" t="n"/>
     </row>
     <row r="461">
       <c r="N461" s="4" t="n"/>
@@ -15552,6 +16947,9 @@
       <c r="AO461" s="4" t="n"/>
       <c r="AP461" s="4" t="n"/>
       <c r="AQ461" s="4" t="n"/>
+      <c r="AR461" s="4" t="n"/>
+      <c r="AS461" s="4" t="n"/>
+      <c r="AT461" s="4" t="n"/>
     </row>
     <row r="462">
       <c r="N462" s="4" t="n"/>
@@ -15584,6 +16982,9 @@
       <c r="AO462" s="4" t="n"/>
       <c r="AP462" s="4" t="n"/>
       <c r="AQ462" s="4" t="n"/>
+      <c r="AR462" s="4" t="n"/>
+      <c r="AS462" s="4" t="n"/>
+      <c r="AT462" s="4" t="n"/>
     </row>
     <row r="463">
       <c r="N463" s="4" t="n"/>
@@ -15616,6 +17017,9 @@
       <c r="AO463" s="4" t="n"/>
       <c r="AP463" s="4" t="n"/>
       <c r="AQ463" s="4" t="n"/>
+      <c r="AR463" s="4" t="n"/>
+      <c r="AS463" s="4" t="n"/>
+      <c r="AT463" s="4" t="n"/>
     </row>
     <row r="464">
       <c r="N464" s="4" t="n"/>
@@ -15648,6 +17052,9 @@
       <c r="AO464" s="4" t="n"/>
       <c r="AP464" s="4" t="n"/>
       <c r="AQ464" s="4" t="n"/>
+      <c r="AR464" s="4" t="n"/>
+      <c r="AS464" s="4" t="n"/>
+      <c r="AT464" s="4" t="n"/>
     </row>
     <row r="465">
       <c r="N465" s="4" t="n"/>
@@ -15680,6 +17087,9 @@
       <c r="AO465" s="4" t="n"/>
       <c r="AP465" s="4" t="n"/>
       <c r="AQ465" s="4" t="n"/>
+      <c r="AR465" s="4" t="n"/>
+      <c r="AS465" s="4" t="n"/>
+      <c r="AT465" s="4" t="n"/>
     </row>
     <row r="466">
       <c r="N466" s="4" t="n"/>
@@ -15712,6 +17122,9 @@
       <c r="AO466" s="4" t="n"/>
       <c r="AP466" s="4" t="n"/>
       <c r="AQ466" s="4" t="n"/>
+      <c r="AR466" s="4" t="n"/>
+      <c r="AS466" s="4" t="n"/>
+      <c r="AT466" s="4" t="n"/>
     </row>
     <row r="467">
       <c r="N467" s="4" t="n"/>
@@ -15744,6 +17157,9 @@
       <c r="AO467" s="4" t="n"/>
       <c r="AP467" s="4" t="n"/>
       <c r="AQ467" s="4" t="n"/>
+      <c r="AR467" s="4" t="n"/>
+      <c r="AS467" s="4" t="n"/>
+      <c r="AT467" s="4" t="n"/>
     </row>
     <row r="468">
       <c r="N468" s="4" t="n"/>
@@ -15776,6 +17192,9 @@
       <c r="AO468" s="4" t="n"/>
       <c r="AP468" s="4" t="n"/>
       <c r="AQ468" s="4" t="n"/>
+      <c r="AR468" s="4" t="n"/>
+      <c r="AS468" s="4" t="n"/>
+      <c r="AT468" s="4" t="n"/>
     </row>
     <row r="469">
       <c r="N469" s="4" t="n"/>
@@ -15808,6 +17227,9 @@
       <c r="AO469" s="4" t="n"/>
       <c r="AP469" s="4" t="n"/>
       <c r="AQ469" s="4" t="n"/>
+      <c r="AR469" s="4" t="n"/>
+      <c r="AS469" s="4" t="n"/>
+      <c r="AT469" s="4" t="n"/>
     </row>
     <row r="470">
       <c r="N470" s="4" t="n"/>
@@ -15840,6 +17262,9 @@
       <c r="AO470" s="4" t="n"/>
       <c r="AP470" s="4" t="n"/>
       <c r="AQ470" s="4" t="n"/>
+      <c r="AR470" s="4" t="n"/>
+      <c r="AS470" s="4" t="n"/>
+      <c r="AT470" s="4" t="n"/>
     </row>
     <row r="471">
       <c r="N471" s="4" t="n"/>
@@ -15872,6 +17297,9 @@
       <c r="AO471" s="4" t="n"/>
       <c r="AP471" s="4" t="n"/>
       <c r="AQ471" s="4" t="n"/>
+      <c r="AR471" s="4" t="n"/>
+      <c r="AS471" s="4" t="n"/>
+      <c r="AT471" s="4" t="n"/>
     </row>
     <row r="472">
       <c r="N472" s="4" t="n"/>
@@ -15904,6 +17332,9 @@
       <c r="AO472" s="4" t="n"/>
       <c r="AP472" s="4" t="n"/>
       <c r="AQ472" s="4" t="n"/>
+      <c r="AR472" s="4" t="n"/>
+      <c r="AS472" s="4" t="n"/>
+      <c r="AT472" s="4" t="n"/>
     </row>
     <row r="473">
       <c r="N473" s="4" t="n"/>
@@ -15936,6 +17367,9 @@
       <c r="AO473" s="4" t="n"/>
       <c r="AP473" s="4" t="n"/>
       <c r="AQ473" s="4" t="n"/>
+      <c r="AR473" s="4" t="n"/>
+      <c r="AS473" s="4" t="n"/>
+      <c r="AT473" s="4" t="n"/>
     </row>
     <row r="474">
       <c r="N474" s="4" t="n"/>
@@ -15968,6 +17402,9 @@
       <c r="AO474" s="4" t="n"/>
       <c r="AP474" s="4" t="n"/>
       <c r="AQ474" s="4" t="n"/>
+      <c r="AR474" s="4" t="n"/>
+      <c r="AS474" s="4" t="n"/>
+      <c r="AT474" s="4" t="n"/>
     </row>
     <row r="475">
       <c r="N475" s="4" t="n"/>
@@ -16000,6 +17437,9 @@
       <c r="AO475" s="4" t="n"/>
       <c r="AP475" s="4" t="n"/>
       <c r="AQ475" s="4" t="n"/>
+      <c r="AR475" s="4" t="n"/>
+      <c r="AS475" s="4" t="n"/>
+      <c r="AT475" s="4" t="n"/>
     </row>
     <row r="476">
       <c r="N476" s="4" t="n"/>
@@ -16032,6 +17472,9 @@
       <c r="AO476" s="4" t="n"/>
       <c r="AP476" s="4" t="n"/>
       <c r="AQ476" s="4" t="n"/>
+      <c r="AR476" s="4" t="n"/>
+      <c r="AS476" s="4" t="n"/>
+      <c r="AT476" s="4" t="n"/>
     </row>
     <row r="477">
       <c r="N477" s="4" t="n"/>
@@ -16064,6 +17507,9 @@
       <c r="AO477" s="4" t="n"/>
       <c r="AP477" s="4" t="n"/>
       <c r="AQ477" s="4" t="n"/>
+      <c r="AR477" s="4" t="n"/>
+      <c r="AS477" s="4" t="n"/>
+      <c r="AT477" s="4" t="n"/>
     </row>
     <row r="478">
       <c r="N478" s="4" t="n"/>
@@ -16096,6 +17542,9 @@
       <c r="AO478" s="4" t="n"/>
       <c r="AP478" s="4" t="n"/>
       <c r="AQ478" s="4" t="n"/>
+      <c r="AR478" s="4" t="n"/>
+      <c r="AS478" s="4" t="n"/>
+      <c r="AT478" s="4" t="n"/>
     </row>
     <row r="479">
       <c r="N479" s="4" t="n"/>
@@ -16128,6 +17577,9 @@
       <c r="AO479" s="4" t="n"/>
       <c r="AP479" s="4" t="n"/>
       <c r="AQ479" s="4" t="n"/>
+      <c r="AR479" s="4" t="n"/>
+      <c r="AS479" s="4" t="n"/>
+      <c r="AT479" s="4" t="n"/>
     </row>
     <row r="480">
       <c r="N480" s="4" t="n"/>
@@ -16160,6 +17612,9 @@
       <c r="AO480" s="4" t="n"/>
       <c r="AP480" s="4" t="n"/>
       <c r="AQ480" s="4" t="n"/>
+      <c r="AR480" s="4" t="n"/>
+      <c r="AS480" s="4" t="n"/>
+      <c r="AT480" s="4" t="n"/>
     </row>
     <row r="481">
       <c r="N481" s="4" t="n"/>
@@ -16192,6 +17647,9 @@
       <c r="AO481" s="4" t="n"/>
       <c r="AP481" s="4" t="n"/>
       <c r="AQ481" s="4" t="n"/>
+      <c r="AR481" s="4" t="n"/>
+      <c r="AS481" s="4" t="n"/>
+      <c r="AT481" s="4" t="n"/>
     </row>
     <row r="482">
       <c r="N482" s="4" t="n"/>
@@ -16224,6 +17682,9 @@
       <c r="AO482" s="4" t="n"/>
       <c r="AP482" s="4" t="n"/>
       <c r="AQ482" s="4" t="n"/>
+      <c r="AR482" s="4" t="n"/>
+      <c r="AS482" s="4" t="n"/>
+      <c r="AT482" s="4" t="n"/>
     </row>
     <row r="483">
       <c r="N483" s="4" t="n"/>
@@ -16256,6 +17717,9 @@
       <c r="AO483" s="4" t="n"/>
       <c r="AP483" s="4" t="n"/>
       <c r="AQ483" s="4" t="n"/>
+      <c r="AR483" s="4" t="n"/>
+      <c r="AS483" s="4" t="n"/>
+      <c r="AT483" s="4" t="n"/>
     </row>
     <row r="484">
       <c r="N484" s="4" t="n"/>
@@ -16288,6 +17752,9 @@
       <c r="AO484" s="4" t="n"/>
       <c r="AP484" s="4" t="n"/>
       <c r="AQ484" s="4" t="n"/>
+      <c r="AR484" s="4" t="n"/>
+      <c r="AS484" s="4" t="n"/>
+      <c r="AT484" s="4" t="n"/>
     </row>
     <row r="485">
       <c r="N485" s="4" t="n"/>
@@ -16320,6 +17787,9 @@
       <c r="AO485" s="4" t="n"/>
       <c r="AP485" s="4" t="n"/>
       <c r="AQ485" s="4" t="n"/>
+      <c r="AR485" s="4" t="n"/>
+      <c r="AS485" s="4" t="n"/>
+      <c r="AT485" s="4" t="n"/>
     </row>
     <row r="486">
       <c r="N486" s="4" t="n"/>
@@ -16352,6 +17822,9 @@
       <c r="AO486" s="4" t="n"/>
       <c r="AP486" s="4" t="n"/>
       <c r="AQ486" s="4" t="n"/>
+      <c r="AR486" s="4" t="n"/>
+      <c r="AS486" s="4" t="n"/>
+      <c r="AT486" s="4" t="n"/>
     </row>
     <row r="487">
       <c r="N487" s="4" t="n"/>
@@ -16384,6 +17857,9 @@
       <c r="AO487" s="4" t="n"/>
       <c r="AP487" s="4" t="n"/>
       <c r="AQ487" s="4" t="n"/>
+      <c r="AR487" s="4" t="n"/>
+      <c r="AS487" s="4" t="n"/>
+      <c r="AT487" s="4" t="n"/>
     </row>
     <row r="488">
       <c r="N488" s="4" t="n"/>
@@ -16416,6 +17892,9 @@
       <c r="AO488" s="4" t="n"/>
       <c r="AP488" s="4" t="n"/>
       <c r="AQ488" s="4" t="n"/>
+      <c r="AR488" s="4" t="n"/>
+      <c r="AS488" s="4" t="n"/>
+      <c r="AT488" s="4" t="n"/>
     </row>
     <row r="489">
       <c r="N489" s="4" t="n"/>
@@ -16448,6 +17927,9 @@
       <c r="AO489" s="4" t="n"/>
       <c r="AP489" s="4" t="n"/>
       <c r="AQ489" s="4" t="n"/>
+      <c r="AR489" s="4" t="n"/>
+      <c r="AS489" s="4" t="n"/>
+      <c r="AT489" s="4" t="n"/>
     </row>
     <row r="490">
       <c r="N490" s="4" t="n"/>
@@ -16480,6 +17962,9 @@
       <c r="AO490" s="4" t="n"/>
       <c r="AP490" s="4" t="n"/>
       <c r="AQ490" s="4" t="n"/>
+      <c r="AR490" s="4" t="n"/>
+      <c r="AS490" s="4" t="n"/>
+      <c r="AT490" s="4" t="n"/>
     </row>
     <row r="491">
       <c r="N491" s="4" t="n"/>
@@ -16512,6 +17997,9 @@
       <c r="AO491" s="4" t="n"/>
       <c r="AP491" s="4" t="n"/>
       <c r="AQ491" s="4" t="n"/>
+      <c r="AR491" s="4" t="n"/>
+      <c r="AS491" s="4" t="n"/>
+      <c r="AT491" s="4" t="n"/>
     </row>
     <row r="492">
       <c r="N492" s="4" t="n"/>
@@ -16544,6 +18032,9 @@
       <c r="AO492" s="4" t="n"/>
       <c r="AP492" s="4" t="n"/>
       <c r="AQ492" s="4" t="n"/>
+      <c r="AR492" s="4" t="n"/>
+      <c r="AS492" s="4" t="n"/>
+      <c r="AT492" s="4" t="n"/>
     </row>
     <row r="493">
       <c r="N493" s="4" t="n"/>
@@ -16576,6 +18067,9 @@
       <c r="AO493" s="4" t="n"/>
       <c r="AP493" s="4" t="n"/>
       <c r="AQ493" s="4" t="n"/>
+      <c r="AR493" s="4" t="n"/>
+      <c r="AS493" s="4" t="n"/>
+      <c r="AT493" s="4" t="n"/>
     </row>
     <row r="494">
       <c r="N494" s="4" t="n"/>
@@ -16608,6 +18102,9 @@
       <c r="AO494" s="4" t="n"/>
       <c r="AP494" s="4" t="n"/>
       <c r="AQ494" s="4" t="n"/>
+      <c r="AR494" s="4" t="n"/>
+      <c r="AS494" s="4" t="n"/>
+      <c r="AT494" s="4" t="n"/>
     </row>
     <row r="495">
       <c r="N495" s="4" t="n"/>
@@ -16640,6 +18137,9 @@
       <c r="AO495" s="4" t="n"/>
       <c r="AP495" s="4" t="n"/>
       <c r="AQ495" s="4" t="n"/>
+      <c r="AR495" s="4" t="n"/>
+      <c r="AS495" s="4" t="n"/>
+      <c r="AT495" s="4" t="n"/>
     </row>
     <row r="496">
       <c r="N496" s="4" t="n"/>
@@ -16672,6 +18172,9 @@
       <c r="AO496" s="4" t="n"/>
       <c r="AP496" s="4" t="n"/>
       <c r="AQ496" s="4" t="n"/>
+      <c r="AR496" s="4" t="n"/>
+      <c r="AS496" s="4" t="n"/>
+      <c r="AT496" s="4" t="n"/>
     </row>
     <row r="497">
       <c r="N497" s="4" t="n"/>
@@ -16704,6 +18207,9 @@
       <c r="AO497" s="4" t="n"/>
       <c r="AP497" s="4" t="n"/>
       <c r="AQ497" s="4" t="n"/>
+      <c r="AR497" s="4" t="n"/>
+      <c r="AS497" s="4" t="n"/>
+      <c r="AT497" s="4" t="n"/>
     </row>
     <row r="498">
       <c r="N498" s="4" t="n"/>
@@ -16736,6 +18242,9 @@
       <c r="AO498" s="4" t="n"/>
       <c r="AP498" s="4" t="n"/>
       <c r="AQ498" s="4" t="n"/>
+      <c r="AR498" s="4" t="n"/>
+      <c r="AS498" s="4" t="n"/>
+      <c r="AT498" s="4" t="n"/>
     </row>
     <row r="499">
       <c r="N499" s="4" t="n"/>
@@ -16768,6 +18277,9 @@
       <c r="AO499" s="4" t="n"/>
       <c r="AP499" s="4" t="n"/>
       <c r="AQ499" s="4" t="n"/>
+      <c r="AR499" s="4" t="n"/>
+      <c r="AS499" s="4" t="n"/>
+      <c r="AT499" s="4" t="n"/>
     </row>
     <row r="500">
       <c r="N500" s="4" t="n"/>
@@ -16800,6 +18312,9 @@
       <c r="AO500" s="4" t="n"/>
       <c r="AP500" s="4" t="n"/>
       <c r="AQ500" s="4" t="n"/>
+      <c r="AR500" s="4" t="n"/>
+      <c r="AS500" s="4" t="n"/>
+      <c r="AT500" s="4" t="n"/>
     </row>
     <row r="501">
       <c r="N501" s="4" t="n"/>
@@ -16832,6 +18347,9 @@
       <c r="AO501" s="4" t="n"/>
       <c r="AP501" s="4" t="n"/>
       <c r="AQ501" s="4" t="n"/>
+      <c r="AR501" s="4" t="n"/>
+      <c r="AS501" s="4" t="n"/>
+      <c r="AT501" s="4" t="n"/>
     </row>
     <row r="502">
       <c r="N502" s="4" t="n"/>
@@ -16864,6 +18382,9 @@
       <c r="AO502" s="4" t="n"/>
       <c r="AP502" s="4" t="n"/>
       <c r="AQ502" s="4" t="n"/>
+      <c r="AR502" s="4" t="n"/>
+      <c r="AS502" s="4" t="n"/>
+      <c r="AT502" s="4" t="n"/>
     </row>
     <row r="503">
       <c r="N503" s="4" t="n"/>
@@ -16896,6 +18417,9 @@
       <c r="AO503" s="4" t="n"/>
       <c r="AP503" s="4" t="n"/>
       <c r="AQ503" s="4" t="n"/>
+      <c r="AR503" s="4" t="n"/>
+      <c r="AS503" s="4" t="n"/>
+      <c r="AT503" s="4" t="n"/>
     </row>
     <row r="504">
       <c r="N504" s="4" t="n"/>
@@ -16928,6 +18452,9 @@
       <c r="AO504" s="4" t="n"/>
       <c r="AP504" s="4" t="n"/>
       <c r="AQ504" s="4" t="n"/>
+      <c r="AR504" s="4" t="n"/>
+      <c r="AS504" s="4" t="n"/>
+      <c r="AT504" s="4" t="n"/>
     </row>
     <row r="505">
       <c r="N505" s="4" t="n"/>
@@ -16960,6 +18487,9 @@
       <c r="AO505" s="4" t="n"/>
       <c r="AP505" s="4" t="n"/>
       <c r="AQ505" s="4" t="n"/>
+      <c r="AR505" s="4" t="n"/>
+      <c r="AS505" s="4" t="n"/>
+      <c r="AT505" s="4" t="n"/>
     </row>
     <row r="506">
       <c r="N506" s="4" t="n"/>
@@ -16992,6 +18522,9 @@
       <c r="AO506" s="4" t="n"/>
       <c r="AP506" s="4" t="n"/>
       <c r="AQ506" s="4" t="n"/>
+      <c r="AR506" s="4" t="n"/>
+      <c r="AS506" s="4" t="n"/>
+      <c r="AT506" s="4" t="n"/>
     </row>
     <row r="507">
       <c r="N507" s="4" t="n"/>
@@ -17024,6 +18557,9 @@
       <c r="AO507" s="4" t="n"/>
       <c r="AP507" s="4" t="n"/>
       <c r="AQ507" s="4" t="n"/>
+      <c r="AR507" s="4" t="n"/>
+      <c r="AS507" s="4" t="n"/>
+      <c r="AT507" s="4" t="n"/>
     </row>
     <row r="508">
       <c r="N508" s="4" t="n"/>
@@ -17056,6 +18592,9 @@
       <c r="AO508" s="4" t="n"/>
       <c r="AP508" s="4" t="n"/>
       <c r="AQ508" s="4" t="n"/>
+      <c r="AR508" s="4" t="n"/>
+      <c r="AS508" s="4" t="n"/>
+      <c r="AT508" s="4" t="n"/>
     </row>
     <row r="509">
       <c r="N509" s="4" t="n"/>
@@ -17088,6 +18627,9 @@
       <c r="AO509" s="4" t="n"/>
       <c r="AP509" s="4" t="n"/>
       <c r="AQ509" s="4" t="n"/>
+      <c r="AR509" s="4" t="n"/>
+      <c r="AS509" s="4" t="n"/>
+      <c r="AT509" s="4" t="n"/>
     </row>
     <row r="510">
       <c r="N510" s="4" t="n"/>
@@ -17120,6 +18662,9 @@
       <c r="AO510" s="4" t="n"/>
       <c r="AP510" s="4" t="n"/>
       <c r="AQ510" s="4" t="n"/>
+      <c r="AR510" s="4" t="n"/>
+      <c r="AS510" s="4" t="n"/>
+      <c r="AT510" s="4" t="n"/>
     </row>
     <row r="511">
       <c r="N511" s="4" t="n"/>
@@ -17152,6 +18697,9 @@
       <c r="AO511" s="4" t="n"/>
       <c r="AP511" s="4" t="n"/>
       <c r="AQ511" s="4" t="n"/>
+      <c r="AR511" s="4" t="n"/>
+      <c r="AS511" s="4" t="n"/>
+      <c r="AT511" s="4" t="n"/>
     </row>
     <row r="512">
       <c r="N512" s="4" t="n"/>
@@ -17184,6 +18732,9 @@
       <c r="AO512" s="4" t="n"/>
       <c r="AP512" s="4" t="n"/>
       <c r="AQ512" s="4" t="n"/>
+      <c r="AR512" s="4" t="n"/>
+      <c r="AS512" s="4" t="n"/>
+      <c r="AT512" s="4" t="n"/>
     </row>
     <row r="513">
       <c r="N513" s="4" t="n"/>
@@ -17216,6 +18767,9 @@
       <c r="AO513" s="4" t="n"/>
       <c r="AP513" s="4" t="n"/>
       <c r="AQ513" s="4" t="n"/>
+      <c r="AR513" s="4" t="n"/>
+      <c r="AS513" s="4" t="n"/>
+      <c r="AT513" s="4" t="n"/>
     </row>
     <row r="514">
       <c r="N514" s="4" t="n"/>
@@ -17248,6 +18802,9 @@
       <c r="AO514" s="4" t="n"/>
       <c r="AP514" s="4" t="n"/>
       <c r="AQ514" s="4" t="n"/>
+      <c r="AR514" s="4" t="n"/>
+      <c r="AS514" s="4" t="n"/>
+      <c r="AT514" s="4" t="n"/>
     </row>
     <row r="515">
       <c r="N515" s="4" t="n"/>
@@ -17280,6 +18837,9 @@
       <c r="AO515" s="4" t="n"/>
       <c r="AP515" s="4" t="n"/>
       <c r="AQ515" s="4" t="n"/>
+      <c r="AR515" s="4" t="n"/>
+      <c r="AS515" s="4" t="n"/>
+      <c r="AT515" s="4" t="n"/>
     </row>
     <row r="516">
       <c r="N516" s="4" t="n"/>
@@ -17312,6 +18872,9 @@
       <c r="AO516" s="4" t="n"/>
       <c r="AP516" s="4" t="n"/>
       <c r="AQ516" s="4" t="n"/>
+      <c r="AR516" s="4" t="n"/>
+      <c r="AS516" s="4" t="n"/>
+      <c r="AT516" s="4" t="n"/>
     </row>
     <row r="517">
       <c r="N517" s="4" t="n"/>
@@ -17344,6 +18907,9 @@
       <c r="AO517" s="4" t="n"/>
       <c r="AP517" s="4" t="n"/>
       <c r="AQ517" s="4" t="n"/>
+      <c r="AR517" s="4" t="n"/>
+      <c r="AS517" s="4" t="n"/>
+      <c r="AT517" s="4" t="n"/>
     </row>
     <row r="518">
       <c r="N518" s="4" t="n"/>
@@ -17376,6 +18942,9 @@
       <c r="AO518" s="4" t="n"/>
       <c r="AP518" s="4" t="n"/>
       <c r="AQ518" s="4" t="n"/>
+      <c r="AR518" s="4" t="n"/>
+      <c r="AS518" s="4" t="n"/>
+      <c r="AT518" s="4" t="n"/>
     </row>
     <row r="519">
       <c r="N519" s="4" t="n"/>
@@ -17408,6 +18977,9 @@
       <c r="AO519" s="4" t="n"/>
       <c r="AP519" s="4" t="n"/>
       <c r="AQ519" s="4" t="n"/>
+      <c r="AR519" s="4" t="n"/>
+      <c r="AS519" s="4" t="n"/>
+      <c r="AT519" s="4" t="n"/>
     </row>
     <row r="520">
       <c r="N520" s="4" t="n"/>
@@ -17440,6 +19012,9 @@
       <c r="AO520" s="4" t="n"/>
       <c r="AP520" s="4" t="n"/>
       <c r="AQ520" s="4" t="n"/>
+      <c r="AR520" s="4" t="n"/>
+      <c r="AS520" s="4" t="n"/>
+      <c r="AT520" s="4" t="n"/>
     </row>
     <row r="521">
       <c r="N521" s="4" t="n"/>
@@ -17472,6 +19047,9 @@
       <c r="AO521" s="4" t="n"/>
       <c r="AP521" s="4" t="n"/>
       <c r="AQ521" s="4" t="n"/>
+      <c r="AR521" s="4" t="n"/>
+      <c r="AS521" s="4" t="n"/>
+      <c r="AT521" s="4" t="n"/>
     </row>
     <row r="522">
       <c r="N522" s="4" t="n"/>
@@ -17504,6 +19082,9 @@
       <c r="AO522" s="4" t="n"/>
       <c r="AP522" s="4" t="n"/>
       <c r="AQ522" s="4" t="n"/>
+      <c r="AR522" s="4" t="n"/>
+      <c r="AS522" s="4" t="n"/>
+      <c r="AT522" s="4" t="n"/>
     </row>
     <row r="523">
       <c r="N523" s="4" t="n"/>
@@ -17536,6 +19117,9 @@
       <c r="AO523" s="4" t="n"/>
       <c r="AP523" s="4" t="n"/>
       <c r="AQ523" s="4" t="n"/>
+      <c r="AR523" s="4" t="n"/>
+      <c r="AS523" s="4" t="n"/>
+      <c r="AT523" s="4" t="n"/>
     </row>
     <row r="524">
       <c r="N524" s="4" t="n"/>
@@ -17568,6 +19152,9 @@
       <c r="AO524" s="4" t="n"/>
       <c r="AP524" s="4" t="n"/>
       <c r="AQ524" s="4" t="n"/>
+      <c r="AR524" s="4" t="n"/>
+      <c r="AS524" s="4" t="n"/>
+      <c r="AT524" s="4" t="n"/>
     </row>
     <row r="525">
       <c r="N525" s="4" t="n"/>
@@ -17600,6 +19187,9 @@
       <c r="AO525" s="4" t="n"/>
       <c r="AP525" s="4" t="n"/>
       <c r="AQ525" s="4" t="n"/>
+      <c r="AR525" s="4" t="n"/>
+      <c r="AS525" s="4" t="n"/>
+      <c r="AT525" s="4" t="n"/>
     </row>
     <row r="526">
       <c r="N526" s="4" t="n"/>
@@ -17632,6 +19222,9 @@
       <c r="AO526" s="4" t="n"/>
       <c r="AP526" s="4" t="n"/>
       <c r="AQ526" s="4" t="n"/>
+      <c r="AR526" s="4" t="n"/>
+      <c r="AS526" s="4" t="n"/>
+      <c r="AT526" s="4" t="n"/>
     </row>
     <row r="527">
       <c r="N527" s="4" t="n"/>
@@ -17664,6 +19257,9 @@
       <c r="AO527" s="4" t="n"/>
       <c r="AP527" s="4" t="n"/>
       <c r="AQ527" s="4" t="n"/>
+      <c r="AR527" s="4" t="n"/>
+      <c r="AS527" s="4" t="n"/>
+      <c r="AT527" s="4" t="n"/>
     </row>
     <row r="528">
       <c r="N528" s="4" t="n"/>
@@ -17696,6 +19292,9 @@
       <c r="AO528" s="4" t="n"/>
       <c r="AP528" s="4" t="n"/>
       <c r="AQ528" s="4" t="n"/>
+      <c r="AR528" s="4" t="n"/>
+      <c r="AS528" s="4" t="n"/>
+      <c r="AT528" s="4" t="n"/>
     </row>
     <row r="529">
       <c r="N529" s="4" t="n"/>
@@ -17728,6 +19327,9 @@
       <c r="AO529" s="4" t="n"/>
       <c r="AP529" s="4" t="n"/>
       <c r="AQ529" s="4" t="n"/>
+      <c r="AR529" s="4" t="n"/>
+      <c r="AS529" s="4" t="n"/>
+      <c r="AT529" s="4" t="n"/>
     </row>
     <row r="530">
       <c r="N530" s="4" t="n"/>
@@ -17760,6 +19362,9 @@
       <c r="AO530" s="4" t="n"/>
       <c r="AP530" s="4" t="n"/>
       <c r="AQ530" s="4" t="n"/>
+      <c r="AR530" s="4" t="n"/>
+      <c r="AS530" s="4" t="n"/>
+      <c r="AT530" s="4" t="n"/>
     </row>
     <row r="531">
       <c r="N531" s="4" t="n"/>
@@ -17792,6 +19397,9 @@
       <c r="AO531" s="4" t="n"/>
       <c r="AP531" s="4" t="n"/>
       <c r="AQ531" s="4" t="n"/>
+      <c r="AR531" s="4" t="n"/>
+      <c r="AS531" s="4" t="n"/>
+      <c r="AT531" s="4" t="n"/>
     </row>
     <row r="532">
       <c r="N532" s="4" t="n"/>
@@ -17824,6 +19432,9 @@
       <c r="AO532" s="4" t="n"/>
       <c r="AP532" s="4" t="n"/>
       <c r="AQ532" s="4" t="n"/>
+      <c r="AR532" s="4" t="n"/>
+      <c r="AS532" s="4" t="n"/>
+      <c r="AT532" s="4" t="n"/>
     </row>
     <row r="533">
       <c r="N533" s="4" t="n"/>
@@ -17856,6 +19467,9 @@
       <c r="AO533" s="4" t="n"/>
       <c r="AP533" s="4" t="n"/>
       <c r="AQ533" s="4" t="n"/>
+      <c r="AR533" s="4" t="n"/>
+      <c r="AS533" s="4" t="n"/>
+      <c r="AT533" s="4" t="n"/>
     </row>
     <row r="534">
       <c r="N534" s="4" t="n"/>
@@ -17888,6 +19502,9 @@
       <c r="AO534" s="4" t="n"/>
       <c r="AP534" s="4" t="n"/>
       <c r="AQ534" s="4" t="n"/>
+      <c r="AR534" s="4" t="n"/>
+      <c r="AS534" s="4" t="n"/>
+      <c r="AT534" s="4" t="n"/>
     </row>
     <row r="535">
       <c r="N535" s="4" t="n"/>
@@ -17920,6 +19537,9 @@
       <c r="AO535" s="4" t="n"/>
       <c r="AP535" s="4" t="n"/>
       <c r="AQ535" s="4" t="n"/>
+      <c r="AR535" s="4" t="n"/>
+      <c r="AS535" s="4" t="n"/>
+      <c r="AT535" s="4" t="n"/>
     </row>
     <row r="536">
       <c r="N536" s="4" t="n"/>
@@ -17952,6 +19572,9 @@
       <c r="AO536" s="4" t="n"/>
       <c r="AP536" s="4" t="n"/>
       <c r="AQ536" s="4" t="n"/>
+      <c r="AR536" s="4" t="n"/>
+      <c r="AS536" s="4" t="n"/>
+      <c r="AT536" s="4" t="n"/>
     </row>
     <row r="537">
       <c r="N537" s="4" t="n"/>
@@ -17984,6 +19607,9 @@
       <c r="AO537" s="4" t="n"/>
       <c r="AP537" s="4" t="n"/>
       <c r="AQ537" s="4" t="n"/>
+      <c r="AR537" s="4" t="n"/>
+      <c r="AS537" s="4" t="n"/>
+      <c r="AT537" s="4" t="n"/>
     </row>
     <row r="538">
       <c r="N538" s="4" t="n"/>
@@ -18016,6 +19642,9 @@
       <c r="AO538" s="4" t="n"/>
       <c r="AP538" s="4" t="n"/>
       <c r="AQ538" s="4" t="n"/>
+      <c r="AR538" s="4" t="n"/>
+      <c r="AS538" s="4" t="n"/>
+      <c r="AT538" s="4" t="n"/>
     </row>
     <row r="539">
       <c r="N539" s="4" t="n"/>
@@ -18048,6 +19677,9 @@
       <c r="AO539" s="4" t="n"/>
       <c r="AP539" s="4" t="n"/>
       <c r="AQ539" s="4" t="n"/>
+      <c r="AR539" s="4" t="n"/>
+      <c r="AS539" s="4" t="n"/>
+      <c r="AT539" s="4" t="n"/>
     </row>
     <row r="540">
       <c r="N540" s="4" t="n"/>
@@ -18080,6 +19712,9 @@
       <c r="AO540" s="4" t="n"/>
       <c r="AP540" s="4" t="n"/>
       <c r="AQ540" s="4" t="n"/>
+      <c r="AR540" s="4" t="n"/>
+      <c r="AS540" s="4" t="n"/>
+      <c r="AT540" s="4" t="n"/>
     </row>
     <row r="541">
       <c r="N541" s="4" t="n"/>
@@ -18112,6 +19747,9 @@
       <c r="AO541" s="4" t="n"/>
       <c r="AP541" s="4" t="n"/>
       <c r="AQ541" s="4" t="n"/>
+      <c r="AR541" s="4" t="n"/>
+      <c r="AS541" s="4" t="n"/>
+      <c r="AT541" s="4" t="n"/>
     </row>
     <row r="542">
       <c r="N542" s="4" t="n"/>
@@ -18144,6 +19782,9 @@
       <c r="AO542" s="4" t="n"/>
       <c r="AP542" s="4" t="n"/>
       <c r="AQ542" s="4" t="n"/>
+      <c r="AR542" s="4" t="n"/>
+      <c r="AS542" s="4" t="n"/>
+      <c r="AT542" s="4" t="n"/>
     </row>
     <row r="543">
       <c r="N543" s="4" t="n"/>
@@ -18176,6 +19817,9 @@
       <c r="AO543" s="4" t="n"/>
       <c r="AP543" s="4" t="n"/>
       <c r="AQ543" s="4" t="n"/>
+      <c r="AR543" s="4" t="n"/>
+      <c r="AS543" s="4" t="n"/>
+      <c r="AT543" s="4" t="n"/>
     </row>
     <row r="544">
       <c r="N544" s="4" t="n"/>
@@ -18208,6 +19852,9 @@
       <c r="AO544" s="4" t="n"/>
       <c r="AP544" s="4" t="n"/>
       <c r="AQ544" s="4" t="n"/>
+      <c r="AR544" s="4" t="n"/>
+      <c r="AS544" s="4" t="n"/>
+      <c r="AT544" s="4" t="n"/>
     </row>
     <row r="545">
       <c r="N545" s="4" t="n"/>
@@ -18240,6 +19887,9 @@
       <c r="AO545" s="4" t="n"/>
       <c r="AP545" s="4" t="n"/>
       <c r="AQ545" s="4" t="n"/>
+      <c r="AR545" s="4" t="n"/>
+      <c r="AS545" s="4" t="n"/>
+      <c r="AT545" s="4" t="n"/>
     </row>
     <row r="546">
       <c r="N546" s="4" t="n"/>
@@ -18272,6 +19922,9 @@
       <c r="AO546" s="4" t="n"/>
       <c r="AP546" s="4" t="n"/>
       <c r="AQ546" s="4" t="n"/>
+      <c r="AR546" s="4" t="n"/>
+      <c r="AS546" s="4" t="n"/>
+      <c r="AT546" s="4" t="n"/>
     </row>
     <row r="547">
       <c r="N547" s="4" t="n"/>
@@ -18304,6 +19957,9 @@
       <c r="AO547" s="4" t="n"/>
       <c r="AP547" s="4" t="n"/>
       <c r="AQ547" s="4" t="n"/>
+      <c r="AR547" s="4" t="n"/>
+      <c r="AS547" s="4" t="n"/>
+      <c r="AT547" s="4" t="n"/>
     </row>
     <row r="548">
       <c r="N548" s="4" t="n"/>
@@ -18336,6 +19992,9 @@
       <c r="AO548" s="4" t="n"/>
       <c r="AP548" s="4" t="n"/>
       <c r="AQ548" s="4" t="n"/>
+      <c r="AR548" s="4" t="n"/>
+      <c r="AS548" s="4" t="n"/>
+      <c r="AT548" s="4" t="n"/>
     </row>
     <row r="549">
       <c r="N549" s="4" t="n"/>
@@ -18368,6 +20027,9 @@
       <c r="AO549" s="4" t="n"/>
       <c r="AP549" s="4" t="n"/>
       <c r="AQ549" s="4" t="n"/>
+      <c r="AR549" s="4" t="n"/>
+      <c r="AS549" s="4" t="n"/>
+      <c r="AT549" s="4" t="n"/>
     </row>
     <row r="550">
       <c r="N550" s="4" t="n"/>
@@ -18400,6 +20062,9 @@
       <c r="AO550" s="4" t="n"/>
       <c r="AP550" s="4" t="n"/>
       <c r="AQ550" s="4" t="n"/>
+      <c r="AR550" s="4" t="n"/>
+      <c r="AS550" s="4" t="n"/>
+      <c r="AT550" s="4" t="n"/>
     </row>
     <row r="551">
       <c r="N551" s="4" t="n"/>
@@ -18432,6 +20097,9 @@
       <c r="AO551" s="4" t="n"/>
       <c r="AP551" s="4" t="n"/>
       <c r="AQ551" s="4" t="n"/>
+      <c r="AR551" s="4" t="n"/>
+      <c r="AS551" s="4" t="n"/>
+      <c r="AT551" s="4" t="n"/>
     </row>
     <row r="552">
       <c r="N552" s="4" t="n"/>
@@ -18464,6 +20132,9 @@
       <c r="AO552" s="4" t="n"/>
       <c r="AP552" s="4" t="n"/>
       <c r="AQ552" s="4" t="n"/>
+      <c r="AR552" s="4" t="n"/>
+      <c r="AS552" s="4" t="n"/>
+      <c r="AT552" s="4" t="n"/>
     </row>
     <row r="553">
       <c r="N553" s="4" t="n"/>
@@ -18496,6 +20167,9 @@
       <c r="AO553" s="4" t="n"/>
       <c r="AP553" s="4" t="n"/>
       <c r="AQ553" s="4" t="n"/>
+      <c r="AR553" s="4" t="n"/>
+      <c r="AS553" s="4" t="n"/>
+      <c r="AT553" s="4" t="n"/>
     </row>
     <row r="554">
       <c r="N554" s="4" t="n"/>
@@ -18528,6 +20202,9 @@
       <c r="AO554" s="4" t="n"/>
       <c r="AP554" s="4" t="n"/>
       <c r="AQ554" s="4" t="n"/>
+      <c r="AR554" s="4" t="n"/>
+      <c r="AS554" s="4" t="n"/>
+      <c r="AT554" s="4" t="n"/>
     </row>
     <row r="555">
       <c r="N555" s="4" t="n"/>
@@ -18560,6 +20237,9 @@
       <c r="AO555" s="4" t="n"/>
       <c r="AP555" s="4" t="n"/>
       <c r="AQ555" s="4" t="n"/>
+      <c r="AR555" s="4" t="n"/>
+      <c r="AS555" s="4" t="n"/>
+      <c r="AT555" s="4" t="n"/>
     </row>
     <row r="556">
       <c r="N556" s="4" t="n"/>
@@ -18592,6 +20272,9 @@
       <c r="AO556" s="4" t="n"/>
       <c r="AP556" s="4" t="n"/>
       <c r="AQ556" s="4" t="n"/>
+      <c r="AR556" s="4" t="n"/>
+      <c r="AS556" s="4" t="n"/>
+      <c r="AT556" s="4" t="n"/>
     </row>
     <row r="557">
       <c r="N557" s="4" t="n"/>
@@ -18624,6 +20307,9 @@
       <c r="AO557" s="4" t="n"/>
       <c r="AP557" s="4" t="n"/>
       <c r="AQ557" s="4" t="n"/>
+      <c r="AR557" s="4" t="n"/>
+      <c r="AS557" s="4" t="n"/>
+      <c r="AT557" s="4" t="n"/>
     </row>
     <row r="558">
       <c r="N558" s="4" t="n"/>
@@ -18656,6 +20342,9 @@
       <c r="AO558" s="4" t="n"/>
       <c r="AP558" s="4" t="n"/>
       <c r="AQ558" s="4" t="n"/>
+      <c r="AR558" s="4" t="n"/>
+      <c r="AS558" s="4" t="n"/>
+      <c r="AT558" s="4" t="n"/>
     </row>
     <row r="559">
       <c r="N559" s="4" t="n"/>
@@ -18688,6 +20377,9 @@
       <c r="AO559" s="4" t="n"/>
       <c r="AP559" s="4" t="n"/>
       <c r="AQ559" s="4" t="n"/>
+      <c r="AR559" s="4" t="n"/>
+      <c r="AS559" s="4" t="n"/>
+      <c r="AT559" s="4" t="n"/>
     </row>
     <row r="560">
       <c r="N560" s="4" t="n"/>
@@ -18720,6 +20412,9 @@
       <c r="AO560" s="4" t="n"/>
       <c r="AP560" s="4" t="n"/>
       <c r="AQ560" s="4" t="n"/>
+      <c r="AR560" s="4" t="n"/>
+      <c r="AS560" s="4" t="n"/>
+      <c r="AT560" s="4" t="n"/>
     </row>
     <row r="561">
       <c r="N561" s="4" t="n"/>
@@ -18752,6 +20447,9 @@
       <c r="AO561" s="4" t="n"/>
       <c r="AP561" s="4" t="n"/>
       <c r="AQ561" s="4" t="n"/>
+      <c r="AR561" s="4" t="n"/>
+      <c r="AS561" s="4" t="n"/>
+      <c r="AT561" s="4" t="n"/>
     </row>
     <row r="562">
       <c r="N562" s="4" t="n"/>
@@ -18784,6 +20482,9 @@
       <c r="AO562" s="4" t="n"/>
       <c r="AP562" s="4" t="n"/>
       <c r="AQ562" s="4" t="n"/>
+      <c r="AR562" s="4" t="n"/>
+      <c r="AS562" s="4" t="n"/>
+      <c r="AT562" s="4" t="n"/>
     </row>
     <row r="563">
       <c r="N563" s="4" t="n"/>
@@ -18816,6 +20517,9 @@
       <c r="AO563" s="4" t="n"/>
       <c r="AP563" s="4" t="n"/>
       <c r="AQ563" s="4" t="n"/>
+      <c r="AR563" s="4" t="n"/>
+      <c r="AS563" s="4" t="n"/>
+      <c r="AT563" s="4" t="n"/>
     </row>
     <row r="564">
       <c r="N564" s="4" t="n"/>
@@ -18848,6 +20552,9 @@
       <c r="AO564" s="4" t="n"/>
       <c r="AP564" s="4" t="n"/>
       <c r="AQ564" s="4" t="n"/>
+      <c r="AR564" s="4" t="n"/>
+      <c r="AS564" s="4" t="n"/>
+      <c r="AT564" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -820,6 +820,11 @@
       <c r="H3" t="n">
         <v>22</v>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>月明かりの冴え</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>【すべて】のト餓鬼を消去し、敵に【特小++】ダメージを与える</t>
@@ -1132,6 +1137,29 @@
           <t>太刀</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>兄弟</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>黄</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>22</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>水平一刀斬り</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える</t>
+        </is>
+      </c>
       <c r="O8" s="1" t="n"/>
       <c r="P8" s="1" t="n"/>
       <c r="Q8" s="1" t="n"/>
@@ -1142,7 +1170,11 @@
       <c r="V8" s="1" t="n"/>
       <c r="W8" s="1" t="n"/>
       <c r="X8" s="1" t="n"/>
-      <c r="Y8" s="1" t="n"/>
+      <c r="Y8" s="1" t="inlineStr">
+        <is>
+          <t>1050,108</t>
+        </is>
+      </c>
       <c r="Z8" s="1" t="n"/>
       <c r="AA8" s="1" t="n"/>
       <c r="AB8" s="1" t="n"/>
@@ -1320,6 +1352,29 @@
           <t>脇差</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>兄弟</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>黄</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>14</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>色変幻の術・青</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>青以外のト餓鬼を【最大10体】、青色に変換する</t>
+        </is>
+      </c>
       <c r="O11" s="1" t="n"/>
       <c r="P11" s="1" t="n"/>
       <c r="Q11" s="1" t="n"/>
@@ -1335,7 +1390,11 @@
       <c r="AA11" s="1" t="n"/>
       <c r="AB11" s="1" t="n"/>
       <c r="AC11" s="1" t="n"/>
-      <c r="AD11" s="1" t="n"/>
+      <c r="AD11" s="1" t="inlineStr">
+        <is>
+          <t>1024,163</t>
+        </is>
+      </c>
       <c r="AE11" s="1" t="n"/>
       <c r="AF11" s="1" t="n"/>
       <c r="AG11" s="1" t="n"/>
@@ -1506,6 +1565,29 @@
           <t>短刀</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>兄弟</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>黄</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>色変幻の術・乱</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ト餓鬼を【最大10体】、ランダムな色に変換する</t>
+        </is>
+      </c>
       <c r="O14" s="1" t="n"/>
       <c r="P14" s="1" t="n"/>
       <c r="Q14" s="1" t="n"/>
@@ -1515,7 +1597,11 @@
       <c r="U14" s="1" t="n"/>
       <c r="V14" s="1" t="n"/>
       <c r="W14" s="1" t="n"/>
-      <c r="X14" s="1" t="n"/>
+      <c r="X14" s="1" t="inlineStr">
+        <is>
+          <t>905,100</t>
+        </is>
+      </c>
       <c r="Y14" s="1" t="n"/>
       <c r="Z14" s="1" t="n"/>
       <c r="AA14" s="1" t="n"/>
@@ -1909,6 +1995,29 @@
           <t>打刀</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>兄弟</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>青</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>22</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>正円一刀斬り</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>【円型・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
+        </is>
+      </c>
       <c r="O23" s="1" t="n"/>
       <c r="P23" s="1" t="n"/>
       <c r="Q23" s="1" t="n"/>
@@ -1918,7 +2027,11 @@
       <c r="U23" s="1" t="n"/>
       <c r="V23" s="1" t="n"/>
       <c r="W23" s="1" t="n"/>
-      <c r="X23" s="1" t="n"/>
+      <c r="X23" s="1" t="inlineStr">
+        <is>
+          <t>850,107</t>
+        </is>
+      </c>
       <c r="Y23" s="1" t="n"/>
       <c r="Z23" s="1" t="n"/>
       <c r="AA23" s="1" t="n"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -900,6 +900,11 @@
       <c r="H4" t="n">
         <v>27</v>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ボム練成の術 三の火</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>ボムを【3個】生成する</t>
@@ -909,7 +914,7 @@
       <c r="P4" s="1" t="n"/>
       <c r="Q4" s="1" t="n"/>
       <c r="R4" s="1" t="n"/>
-      <c r="S4" s="6" t="inlineStr">
+      <c r="S4" s="1" t="inlineStr">
         <is>
           <t>740,77</t>
         </is>
@@ -1723,6 +1728,34 @@
           <t>大太刀</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>青</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>36</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>正円一刀斬り</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
+        <is>
+          <t>677,107</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1781,13 +1814,40 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>打刀</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>新選組</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>26</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>必中三段斬り</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>指定した【円型・特小範囲】のト餓鬼を3回消去し、敵に【小】ダメージを与える</t>
         </is>
       </c>
       <c r="O20" s="1" t="n"/>
       <c r="P20" s="1" t="n"/>
       <c r="Q20" s="1" t="n"/>
       <c r="R20" s="1" t="n"/>
-      <c r="S20" s="1" t="n"/>
+      <c r="S20" s="1" t="inlineStr">
+        <is>
+          <t>645,73</t>
+        </is>
+      </c>
       <c r="T20" s="1" t="n"/>
       <c r="U20" s="1" t="n"/>
       <c r="V20" s="1" t="n"/>
@@ -2128,11 +2188,38 @@
           <t>太刀</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>けもの</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>22</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>水平一刀斬り</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
+        </is>
+      </c>
       <c r="O25" s="1" t="n"/>
       <c r="P25" s="1" t="n"/>
       <c r="Q25" s="1" t="n"/>
       <c r="R25" s="1" t="n"/>
-      <c r="S25" s="1" t="n"/>
+      <c r="S25" s="1" t="inlineStr">
+        <is>
+          <t>771,74</t>
+        </is>
+      </c>
       <c r="T25" s="1" t="n"/>
       <c r="U25" s="1" t="n"/>
       <c r="V25" s="1" t="n"/>
@@ -2181,6 +2268,30 @@
           <t>太刀</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>鳥</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>24</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>水平斬り 攻勢の型</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>【横列・中範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える
+自身に攻撃力上昇【極小・1手】を付与する</t>
+        </is>
+      </c>
       <c r="O26" s="1" t="n"/>
       <c r="P26" s="1" t="n"/>
       <c r="Q26" s="1" t="n"/>
@@ -2190,7 +2301,11 @@
       <c r="U26" s="1" t="n"/>
       <c r="V26" s="1" t="n"/>
       <c r="W26" s="1" t="n"/>
-      <c r="X26" s="1" t="n"/>
+      <c r="X26" s="1" t="inlineStr">
+        <is>
+          <t>935,110</t>
+        </is>
+      </c>
       <c r="Y26" s="1" t="n"/>
       <c r="Z26" s="1" t="n"/>
       <c r="AA26" s="1" t="n"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -980,12 +980,18 @@
       <c r="H5" t="n">
         <v>22</v>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>逆さ扇斬り 守護の型</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>【扇型・中範囲】のト餓鬼を消去し、敵に【特小-】ダメージを与える。味方全体に被ダメージ軽減【極小+・3手】を付与する</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
+          <t>【扇型・中範囲】のト餓鬼を消去し、敵に【特小－】ダメージを与える。
+味方全員に被ダメージ軽減【極小＋・3手】を付与する</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
         <is>
           <t>561,61</t>
         </is>
@@ -1042,6 +1048,34 @@
           <t>薙刀</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>源氏</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>青</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>16</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>大薙ぎ払い・赤</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>【最大10体】の赤ト餓鬼を盤面の右下に集める</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>471,69</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1517,7 +1551,34 @@
           <t>短刀</t>
         </is>
       </c>
-      <c r="O13" s="1" t="n"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>兄弟</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>黄</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>14</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>色変幻の術・青</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>赤色のト餓鬼を【最大10体】、青色に変換する</t>
+        </is>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>440,77</t>
+        </is>
+      </c>
       <c r="P13" s="1" t="n"/>
       <c r="Q13" s="1" t="n"/>
       <c r="R13" s="1" t="n"/>
@@ -1675,7 +1736,34 @@
           <t>短刀</t>
         </is>
       </c>
-      <c r="O16" s="1" t="n"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>兄弟</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>13</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ボム練成の術 一の火</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ボムを【1個】生成する</t>
+        </is>
+      </c>
+      <c r="O16" s="1" t="inlineStr">
+        <is>
+          <t>477,56</t>
+        </is>
+      </c>
       <c r="P16" s="1" t="n"/>
       <c r="Q16" s="1" t="n"/>
       <c r="R16" s="1" t="n"/>
@@ -1774,6 +1862,34 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>槍</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>天下三名槍</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>黄</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>22</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>必中縦断突き</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>指定した【縦列・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>551,72</t>
         </is>
       </c>
     </row>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -1912,6 +1912,35 @@
           <t>太刀</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>雪</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>19</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>霧散斬り 先手の型</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ランダムなト餓鬼（攻撃指示優先）を最大5体消去し、敵に【特小＋＋】ダメージを与える
+消去時のブレイクゲージ減少量が【2倍】になる</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>507,74</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2251,7 +2280,35 @@
           <t>太刀</t>
         </is>
       </c>
-      <c r="O24" s="1" t="n"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>お山修行</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>22</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>逆さ扇斬り 守護の型</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>【扇型・特小範囲】のト餓鬼を消去し、敵に【極小＋】ダメージを与える
+味方全員に被ダメージ軽減【特小＋＋・3手】を付与する</t>
+        </is>
+      </c>
+      <c r="O24" s="1" t="inlineStr">
+        <is>
+          <t>584,70</t>
+        </is>
+      </c>
       <c r="P24" s="1" t="n"/>
       <c r="Q24" s="1" t="n"/>
       <c r="R24" s="1" t="n"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -2134,9 +2134,15 @@
       <c r="H22" t="n">
         <v>16</v>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>水平斬り 攻勢の型</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【極小】ダメージを与える味方全員に攻撃力上昇【極小++・3手】を付与する</t>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【極小】ダメージを与える
+味方全員に攻撃力上昇【極小＋＋・3手】を付与する</t>
         </is>
       </c>
       <c r="O22" s="1" t="n"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamasakoyuki/pazugiri-character-tracker/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C990C0D-ED7D-A14C-8CD5-DEAB7C10F4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729A3778-0439-2840-9CF6-8BAC9C03FD49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="キャラクター名" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="277">
   <si>
     <t>ステージ名</t>
   </si>
@@ -729,16 +729,6 @@
   </si>
   <si>
     <t>[紙,6][筆,6][鬼のツノ,4]</t>
-  </si>
-  <si>
-    <t>1lv[体力,攻撃,次レベル必要経験値]</t>
-    <rPh sb="10" eb="11">
-      <t>ジレベル</t>
-    </rPh>
-    <rPh sb="14" eb="19">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>2lv[体力,攻撃,次レベル必要経験値]</t>
@@ -1135,11 +1125,22 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>584,70,9</t>
+    <t>経験値</t>
+    <rPh sb="0" eb="3">
+      <t>ケイケンティ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>507,74,9</t>
+    <t>1lv[体力,攻撃]</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>507,74</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>584,70</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1607,124 +1608,124 @@
         <v>91</v>
       </c>
       <c r="O1" t="s">
+        <v>274</v>
+      </c>
+      <c r="P1" t="s">
         <v>233</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>234</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>235</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>236</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>237</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>238</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>239</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>240</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>241</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>242</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>243</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>244</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>245</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>246</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>247</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>248</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>249</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>250</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>251</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>252</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>253</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>254</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>255</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>256</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>257</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>258</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>259</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>260</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>261</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>262</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>263</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>264</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>265</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>266</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>267</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>268</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>269</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>270</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>271</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>272</v>
       </c>
       <c r="BC1" t="s">
         <v>92</v>
@@ -1737,51 +1738,12 @@
       </c>
     </row>
     <row r="2" spans="1:57">
-      <c r="A2">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" t="s">
-        <v>97</v>
-      </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="1"/>
-      <c r="AH2" s="1"/>
-      <c r="AI2" s="1"/>
-      <c r="AJ2" s="1"/>
-      <c r="AK2" s="1"/>
-      <c r="AL2" s="1"/>
-      <c r="AM2" s="1"/>
-      <c r="AN2" s="1"/>
-      <c r="AO2" s="1"/>
-      <c r="AP2" s="1"/>
-      <c r="AQ2" s="1"/>
-      <c r="AR2" s="1"/>
-      <c r="BC2" s="1"/>
-      <c r="BD2" s="1"/>
-      <c r="BE2" s="1"/>
+      <c r="A2" t="s">
+        <v>273</v>
+      </c>
+      <c r="O2">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" spans="1:57">
       <c r="A3">
@@ -1793,26 +1755,8 @@
       <c r="C3" t="s">
         <v>96</v>
       </c>
-      <c r="D3" t="s">
-        <v>98</v>
-      </c>
       <c r="E3" t="s">
         <v>97</v>
-      </c>
-      <c r="F3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G3" t="s">
-        <v>100</v>
-      </c>
-      <c r="H3">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>101</v>
-      </c>
-      <c r="J3" t="s">
-        <v>102</v>
       </c>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
@@ -1826,9 +1770,7 @@
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
-      <c r="AA3" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
@@ -1852,39 +1794,40 @@
     </row>
     <row r="4" spans="1:57">
       <c r="A4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
         <v>96</v>
       </c>
+      <c r="D4" t="s">
+        <v>98</v>
+      </c>
       <c r="E4" t="s">
         <v>97</v>
       </c>
       <c r="F4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G4" t="s">
         <v>100</v>
       </c>
       <c r="H4">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="J4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="1" t="s">
-        <v>108</v>
-      </c>
+      <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -1892,7 +1835,9 @@
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
+      <c r="AA4" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
@@ -1916,39 +1861,39 @@
     </row>
     <row r="5" spans="1:57">
       <c r="A5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
         <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="F5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G5" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J5" t="s">
-        <v>114</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
+      <c r="S5" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -1980,129 +1925,127 @@
     </row>
     <row r="6" spans="1:57">
       <c r="A6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s">
         <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F6" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G6" t="s">
         <v>112</v>
       </c>
       <c r="H6">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="J6" t="s">
-        <v>120</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>121</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="1"/>
+      <c r="AI6" s="1"/>
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="1"/>
+      <c r="AL6" s="1"/>
+      <c r="AM6" s="1"/>
+      <c r="AN6" s="1"/>
+      <c r="AO6" s="1"/>
+      <c r="AP6" s="1"/>
+      <c r="AQ6" s="1"/>
+      <c r="AR6" s="1"/>
+      <c r="BC6" s="1"/>
+      <c r="BD6" s="1"/>
+      <c r="BE6" s="1"/>
     </row>
     <row r="7" spans="1:57">
       <c r="A7">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
         <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F7" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="G7" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H7">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="J7" t="s">
-        <v>125</v>
-      </c>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="1"/>
-      <c r="AC7" s="1"/>
-      <c r="AD7" s="1"/>
-      <c r="AE7" s="1"/>
-      <c r="AF7" s="1"/>
-      <c r="AG7" s="1"/>
-      <c r="AH7" s="1"/>
-      <c r="AI7" s="1"/>
-      <c r="AJ7" s="1"/>
-      <c r="AK7" s="1"/>
-      <c r="AL7" s="1"/>
-      <c r="AM7" s="1"/>
-      <c r="AN7" s="1"/>
-      <c r="AO7" s="1"/>
-      <c r="AP7" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="AQ7" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="AR7" s="1"/>
-      <c r="BC7" s="1"/>
-      <c r="BD7" s="1"/>
-      <c r="BE7" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="8" spans="1:57">
       <c r="A8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C8" t="s">
         <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="F8" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="G8" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J8" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -2114,9 +2057,7 @@
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
-      <c r="Y8" s="1" t="s">
-        <v>132</v>
-      </c>
+      <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
@@ -2133,8 +2074,12 @@
       <c r="AM8" s="1"/>
       <c r="AN8" s="1"/>
       <c r="AO8" s="1"/>
-      <c r="AP8" s="1"/>
-      <c r="AQ8" s="1"/>
+      <c r="AP8" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AQ8" s="1" t="s">
+        <v>272</v>
+      </c>
       <c r="AR8" s="1"/>
       <c r="BC8" s="1"/>
       <c r="BD8" s="1"/>
@@ -2150,14 +2095,11 @@
       <c r="C9" t="s">
         <v>96</v>
       </c>
-      <c r="D9" t="s">
-        <v>98</v>
-      </c>
       <c r="E9" t="s">
         <v>97</v>
       </c>
       <c r="F9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G9" t="s">
         <v>129</v>
@@ -2166,85 +2108,88 @@
         <v>22</v>
       </c>
       <c r="I9" t="s">
-        <v>134</v>
-      </c>
-      <c r="K9" t="s">
-        <v>135</v>
-      </c>
-      <c r="AL9" s="5" t="s">
-        <v>136</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="J9" t="s">
+        <v>131</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+      <c r="AL9" s="1"/>
+      <c r="AM9" s="1"/>
+      <c r="AN9" s="1"/>
+      <c r="AO9" s="1"/>
+      <c r="AP9" s="1"/>
+      <c r="AQ9" s="1"/>
+      <c r="AR9" s="1"/>
+      <c r="BC9" s="1"/>
+      <c r="BD9" s="1"/>
+      <c r="BE9" s="1"/>
     </row>
     <row r="10" spans="1:57">
       <c r="A10">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
         <v>96</v>
       </c>
+      <c r="D10" t="s">
+        <v>98</v>
+      </c>
       <c r="E10" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="F10" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G10" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="H10">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>139</v>
-      </c>
-      <c r="J10" t="s">
-        <v>140</v>
-      </c>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-      <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="1"/>
-      <c r="AC10" s="1"/>
-      <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
-      <c r="AF10" s="1"/>
-      <c r="AG10" s="1"/>
-      <c r="AH10" s="1"/>
-      <c r="AI10" s="1"/>
-      <c r="AJ10" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="AK10" s="1"/>
-      <c r="AL10" s="1"/>
-      <c r="AM10" s="1"/>
-      <c r="AN10" s="1"/>
-      <c r="AO10" s="1"/>
-      <c r="AP10" s="1"/>
-      <c r="AQ10" s="1"/>
-      <c r="AR10" s="1"/>
-      <c r="BC10" s="1"/>
-      <c r="BD10" s="1"/>
-      <c r="BE10" s="1"/>
+        <v>134</v>
+      </c>
+      <c r="K10" t="s">
+        <v>135</v>
+      </c>
+      <c r="AL10" s="5" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="11" spans="1:57">
       <c r="A11">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s">
         <v>96</v>
@@ -2256,16 +2201,16 @@
         <v>128</v>
       </c>
       <c r="G11" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="J11" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
@@ -2282,15 +2227,15 @@
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
-      <c r="AD11" s="1" t="s">
-        <v>145</v>
-      </c>
+      <c r="AD11" s="1"/>
       <c r="AE11" s="1"/>
       <c r="AF11" s="1"/>
       <c r="AG11" s="1"/>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
-      <c r="AJ11" s="1"/>
+      <c r="AJ11" s="1" t="s">
+        <v>141</v>
+      </c>
       <c r="AK11" s="1"/>
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
@@ -2305,31 +2250,31 @@
     </row>
     <row r="12" spans="1:57">
       <c r="A12">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C12" t="s">
         <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="F12" t="s">
         <v>128</v>
       </c>
       <c r="G12" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="H12">
         <v>14</v>
       </c>
       <c r="I12" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="J12" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
@@ -2346,7 +2291,9 @@
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
-      <c r="AD12" s="1"/>
+      <c r="AD12" s="1" t="s">
+        <v>145</v>
+      </c>
       <c r="AE12" s="1"/>
       <c r="AF12" s="1"/>
       <c r="AG12" s="1"/>
@@ -2360,19 +2307,17 @@
       <c r="AO12" s="1"/>
       <c r="AP12" s="1"/>
       <c r="AQ12" s="1"/>
-      <c r="AR12" s="1" t="s">
-        <v>150</v>
-      </c>
+      <c r="AR12" s="1"/>
       <c r="BC12" s="1"/>
       <c r="BD12" s="1"/>
       <c r="BE12" s="1"/>
     </row>
     <row r="13" spans="1:57">
       <c r="A13">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C13" t="s">
         <v>96</v>
@@ -2384,20 +2329,18 @@
         <v>128</v>
       </c>
       <c r="G13" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="H13">
         <v>14</v>
       </c>
       <c r="I13" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J13" t="s">
-        <v>152</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>153</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
@@ -2426,17 +2369,19 @@
       <c r="AO13" s="1"/>
       <c r="AP13" s="1"/>
       <c r="AQ13" s="1"/>
-      <c r="AR13" s="1"/>
+      <c r="AR13" s="1" t="s">
+        <v>150</v>
+      </c>
       <c r="BC13" s="1"/>
       <c r="BD13" s="1"/>
       <c r="BE13" s="1"/>
     </row>
     <row r="14" spans="1:57">
       <c r="A14">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C14" t="s">
         <v>96</v>
@@ -2451,15 +2396,17 @@
         <v>129</v>
       </c>
       <c r="H14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I14" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J14" t="s">
-        <v>156</v>
-      </c>
-      <c r="O14" s="1"/>
+        <v>152</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>153</v>
+      </c>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
@@ -2468,9 +2415,7 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
-      <c r="X14" s="1" t="s">
-        <v>157</v>
-      </c>
+      <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1"/>
@@ -2505,243 +2450,243 @@
       <c r="C15" t="s">
         <v>96</v>
       </c>
-      <c r="D15" t="s">
-        <v>98</v>
-      </c>
       <c r="E15" t="s">
         <v>147</v>
       </c>
+      <c r="F15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H15">
+        <v>12</v>
+      </c>
+      <c r="I15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J15" t="s">
+        <v>156</v>
+      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="1"/>
+      <c r="AD15" s="1"/>
+      <c r="AE15" s="1"/>
+      <c r="AF15" s="1"/>
+      <c r="AG15" s="1"/>
+      <c r="AH15" s="1"/>
+      <c r="AI15" s="1"/>
+      <c r="AJ15" s="1"/>
+      <c r="AK15" s="1"/>
+      <c r="AL15" s="1"/>
+      <c r="AM15" s="1"/>
+      <c r="AN15" s="1"/>
+      <c r="AO15" s="1"/>
+      <c r="AP15" s="1"/>
+      <c r="AQ15" s="1"/>
+      <c r="AR15" s="1"/>
+      <c r="BC15" s="1"/>
+      <c r="BD15" s="1"/>
+      <c r="BE15" s="1"/>
     </row>
     <row r="16" spans="1:57">
       <c r="A16">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C16" t="s">
         <v>96</v>
       </c>
+      <c r="D16" t="s">
+        <v>98</v>
+      </c>
       <c r="E16" t="s">
         <v>147</v>
       </c>
-      <c r="F16" t="s">
-        <v>128</v>
-      </c>
-      <c r="G16" t="s">
-        <v>100</v>
-      </c>
-      <c r="H16">
-        <v>13</v>
-      </c>
-      <c r="I16" t="s">
-        <v>159</v>
-      </c>
-      <c r="J16" t="s">
-        <v>160</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-      <c r="Z16" s="1"/>
-      <c r="AA16" s="1"/>
-      <c r="AB16" s="1"/>
-      <c r="AC16" s="1"/>
-      <c r="AD16" s="1"/>
-      <c r="AE16" s="1"/>
-      <c r="AF16" s="1"/>
-      <c r="AG16" s="1"/>
-      <c r="AH16" s="1"/>
-      <c r="AI16" s="1"/>
-      <c r="AJ16" s="1"/>
-      <c r="AK16" s="1"/>
-      <c r="AL16" s="1"/>
-      <c r="AM16" s="1"/>
-      <c r="AN16" s="1"/>
-      <c r="AO16" s="1"/>
-      <c r="AP16" s="1"/>
-      <c r="AQ16" s="1"/>
-      <c r="AR16" s="1"/>
-      <c r="BC16" s="1"/>
-      <c r="BD16" s="1"/>
-      <c r="BE16" s="1"/>
     </row>
     <row r="17" spans="1:57">
       <c r="A17">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C17" t="s">
         <v>96</v>
       </c>
       <c r="E17" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="F17" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="G17" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="H17">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="I17" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="J17" t="s">
-        <v>165</v>
-      </c>
-      <c r="T17" s="5" t="s">
-        <v>166</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="1"/>
+      <c r="AC17" s="1"/>
+      <c r="AD17" s="1"/>
+      <c r="AE17" s="1"/>
+      <c r="AF17" s="1"/>
+      <c r="AG17" s="1"/>
+      <c r="AH17" s="1"/>
+      <c r="AI17" s="1"/>
+      <c r="AJ17" s="1"/>
+      <c r="AK17" s="1"/>
+      <c r="AL17" s="1"/>
+      <c r="AM17" s="1"/>
+      <c r="AN17" s="1"/>
+      <c r="AO17" s="1"/>
+      <c r="AP17" s="1"/>
+      <c r="AQ17" s="1"/>
+      <c r="AR17" s="1"/>
+      <c r="BC17" s="1"/>
+      <c r="BD17" s="1"/>
+      <c r="BE17" s="1"/>
     </row>
     <row r="18" spans="1:57">
       <c r="A18">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C18" t="s">
         <v>96</v>
       </c>
       <c r="E18" t="s">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="F18" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G18" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="H18">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I18" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="J18" t="s">
-        <v>171</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>172</v>
+        <v>165</v>
+      </c>
+      <c r="T18" s="5" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:57">
       <c r="A19">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C19" t="s">
         <v>96</v>
       </c>
       <c r="E19" t="s">
-        <v>97</v>
+        <v>168</v>
       </c>
       <c r="F19" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G19" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="H19">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="J19" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>275</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:57">
       <c r="A20">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C20" t="s">
         <v>96</v>
       </c>
       <c r="E20" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="F20" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G20" t="s">
         <v>100</v>
       </c>
       <c r="H20">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I20" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J20" t="s">
-        <v>180</v>
-      </c>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-      <c r="Z20" s="1"/>
-      <c r="AA20" s="1"/>
-      <c r="AB20" s="1"/>
-      <c r="AC20" s="1"/>
-      <c r="AD20" s="1"/>
-      <c r="AE20" s="1"/>
-      <c r="AF20" s="1"/>
-      <c r="AG20" s="1"/>
-      <c r="AH20" s="1"/>
-      <c r="AI20" s="1"/>
-      <c r="AJ20" s="1"/>
-      <c r="AK20" s="1"/>
-      <c r="AL20" s="1"/>
-      <c r="AM20" s="1"/>
-      <c r="AN20" s="1"/>
-      <c r="AO20" s="1"/>
-      <c r="AP20" s="1"/>
-      <c r="AQ20" s="1"/>
-      <c r="AR20" s="1"/>
-      <c r="BC20" s="1"/>
-      <c r="BD20" s="1"/>
-      <c r="BE20" s="1"/>
+        <v>176</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="21" spans="1:57">
       <c r="A21">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C21" t="s">
         <v>96</v>
@@ -2756,19 +2701,21 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="I21" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J21" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
+      <c r="S21" s="1" t="s">
+        <v>181</v>
+      </c>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
@@ -2783,9 +2730,7 @@
       <c r="AE21" s="1"/>
       <c r="AF21" s="1"/>
       <c r="AG21" s="1"/>
-      <c r="AH21" s="1" t="s">
-        <v>185</v>
-      </c>
+      <c r="AH21" s="1"/>
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
@@ -2802,10 +2747,10 @@
     </row>
     <row r="22" spans="1:57">
       <c r="A22">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C22" t="s">
         <v>96</v>
@@ -2814,19 +2759,19 @@
         <v>123</v>
       </c>
       <c r="F22" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="G22" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="H22">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I22" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="J22" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
@@ -2847,7 +2792,9 @@
       <c r="AE22" s="1"/>
       <c r="AF22" s="1"/>
       <c r="AG22" s="1"/>
-      <c r="AH22" s="1"/>
+      <c r="AH22" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
@@ -2857,21 +2804,17 @@
       <c r="AO22" s="1"/>
       <c r="AP22" s="1"/>
       <c r="AQ22" s="1"/>
-      <c r="AR22" s="1" t="s">
-        <v>190</v>
-      </c>
+      <c r="AR22" s="1"/>
       <c r="BC22" s="1"/>
       <c r="BD22" s="1"/>
-      <c r="BE22" s="1" t="s">
-        <v>191</v>
-      </c>
+      <c r="BE22" s="1"/>
     </row>
     <row r="23" spans="1:57">
       <c r="A23">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B23" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C23" t="s">
         <v>96</v>
@@ -2880,19 +2823,19 @@
         <v>123</v>
       </c>
       <c r="F23" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="G23" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="H23">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I23" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="J23" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -2903,9 +2846,7 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
-      <c r="X23" s="1" t="s">
-        <v>194</v>
-      </c>
+      <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
@@ -2925,42 +2866,44 @@
       <c r="AO23" s="1"/>
       <c r="AP23" s="1"/>
       <c r="AQ23" s="1"/>
-      <c r="AR23" s="1"/>
+      <c r="AR23" s="1" t="s">
+        <v>190</v>
+      </c>
       <c r="BC23" s="1"/>
       <c r="BD23" s="1"/>
-      <c r="BE23" s="1"/>
+      <c r="BE23" s="1" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="24" spans="1:57">
       <c r="A24">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B24" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C24" t="s">
         <v>96</v>
       </c>
       <c r="E24" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="F24" t="s">
-        <v>196</v>
+        <v>128</v>
       </c>
       <c r="G24" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H24">
         <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="J24" t="s">
-        <v>197</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>274</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
@@ -2969,7 +2912,9 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
+      <c r="X24" s="1" t="s">
+        <v>194</v>
+      </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
@@ -2996,10 +2941,10 @@
     </row>
     <row r="25" spans="1:57">
       <c r="A25">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="B25" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C25" t="s">
         <v>96</v>
@@ -3008,7 +2953,7 @@
         <v>97</v>
       </c>
       <c r="F25" t="s">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="G25" t="s">
         <v>100</v>
@@ -3017,18 +2962,18 @@
         <v>22</v>
       </c>
       <c r="I25" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="J25" t="s">
-        <v>199</v>
-      </c>
-      <c r="O25" s="1"/>
+        <v>197</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>276</v>
+      </c>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
-      <c r="S25" s="1" t="s">
-        <v>200</v>
-      </c>
+      <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
@@ -3060,10 +3005,10 @@
     </row>
     <row r="26" spans="1:57">
       <c r="A26">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B26" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C26" t="s">
         <v>96</v>
@@ -3072,32 +3017,32 @@
         <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>202</v>
+        <v>105</v>
       </c>
       <c r="G26" t="s">
         <v>100</v>
       </c>
       <c r="H26">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I26" t="s">
-        <v>188</v>
+        <v>130</v>
       </c>
       <c r="J26" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
+      <c r="S26" s="1" t="s">
+        <v>200</v>
+      </c>
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
-      <c r="X26" s="1" t="s">
-        <v>204</v>
-      </c>
+      <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
@@ -3123,6 +3068,33 @@
       <c r="BE26" s="1"/>
     </row>
     <row r="27" spans="1:57">
+      <c r="A27">
+        <v>130</v>
+      </c>
+      <c r="B27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27" t="s">
+        <v>202</v>
+      </c>
+      <c r="G27" t="s">
+        <v>100</v>
+      </c>
+      <c r="H27">
+        <v>24</v>
+      </c>
+      <c r="I27" t="s">
+        <v>188</v>
+      </c>
+      <c r="J27" t="s">
+        <v>203</v>
+      </c>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -3132,7 +3104,9 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
+      <c r="X27" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
@@ -21955,10 +21929,10 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D5 D7:D16 D20:D564" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D3:D6 D8:D17 D21:D564" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"○"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G5 G7:G8 G10:G14 G16 G20:G564" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G3:G6 G8:G9 G11:G15 G17 G21:G564" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"赤,黄,青"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -795,6 +795,15 @@
       <c r="O2" s="7" t="n">
         <v>9</v>
       </c>
+      <c r="S2" s="7" t="n">
+        <v>441</v>
+      </c>
+      <c r="T2" s="7" t="n">
+        <v>683</v>
+      </c>
+      <c r="Y2" s="7" t="n">
+        <v>2928</v>
+      </c>
       <c r="AA2" s="7" t="n">
         <v>4373</v>
       </c>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -795,11 +795,20 @@
       <c r="O2" s="7" t="n">
         <v>9</v>
       </c>
+      <c r="R2" s="7" t="n">
+        <v>258</v>
+      </c>
       <c r="S2" s="7" t="n">
         <v>441</v>
       </c>
       <c r="T2" s="7" t="n">
         <v>683</v>
+      </c>
+      <c r="V2" s="7" t="n">
+        <v>1363</v>
+      </c>
+      <c r="W2" s="7" t="n">
+        <v>1809</v>
       </c>
       <c r="Y2" s="7" t="n">
         <v>2928</v>
@@ -1088,13 +1097,25 @@
       </c>
       <c r="P6" s="1" t="n"/>
       <c r="Q6" s="1" t="n"/>
-      <c r="R6" s="1" t="n"/>
+      <c r="R6" s="1" t="inlineStr">
+        <is>
+          <t>700,76</t>
+        </is>
+      </c>
       <c r="S6" s="1" t="n"/>
       <c r="T6" s="1" t="n"/>
       <c r="U6" s="1" t="n"/>
-      <c r="V6" s="1" t="n"/>
+      <c r="V6" s="1" t="inlineStr">
+        <is>
+          <t>886,96</t>
+        </is>
+      </c>
       <c r="W6" s="1" t="n"/>
-      <c r="X6" s="1" t="n"/>
+      <c r="X6" s="1" t="inlineStr">
+        <is>
+          <t>979,106</t>
+        </is>
+      </c>
       <c r="Y6" s="1" t="n"/>
       <c r="Z6" s="1" t="n"/>
       <c r="AA6" s="1" t="n"/>
@@ -21418,7 +21439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="24"/>
@@ -22206,6 +22227,57 @@
       <c r="D45" t="inlineStr">
         <is>
           <t>強化素材</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>経験値の書</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>経験値の書・小</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>経験値+150</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>経験値の書</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>経験値の書・中</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>経験値+1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>経験値の書</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>経験値の書・大</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>経験値+6000</t>
         </is>
       </c>
     </row>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -1831,6 +1831,35 @@
           <t>短刀</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>兄弟,花</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>16</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>百花乱々みだれ咲き</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>味方全員に攻撃力上昇【極小＋＋・3手】を付与する
+敵に被ダメージ増加【極小＋・3手】を付与する</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>532,59</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1914,11 +1943,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>蛍丸</t>
+          <t>太郎太刀</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1926,6 +1955,11 @@
           <t>戦装束</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>大太刀</t>
@@ -1933,40 +1967,79 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>夜</t>
+          <t>ご神刀,兄弟</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>青</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>正円一刀斬り</t>
+          <t>天より墜つる暴威</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="T18" s="5" t="inlineStr">
-        <is>
-          <t>677,107</t>
-        </is>
-      </c>
+          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える。ボスが被ダメージ増加状態のとき、さらに威力が上昇する</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>613,67</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="5" t="n"/>
+      <c r="U18" s="5" t="n"/>
+      <c r="V18" s="5" t="n"/>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+      <c r="Y18" s="5" t="n"/>
+      <c r="Z18" s="5" t="n"/>
+      <c r="AA18" s="5" t="n"/>
+      <c r="AB18" s="5" t="n"/>
+      <c r="AC18" s="5" t="n"/>
+      <c r="AD18" s="5" t="n"/>
+      <c r="AE18" s="5" t="n"/>
+      <c r="AF18" s="5" t="n"/>
+      <c r="AG18" s="5" t="n"/>
+      <c r="AH18" s="5" t="n"/>
+      <c r="AI18" s="5" t="n"/>
+      <c r="AJ18" s="5" t="n"/>
+      <c r="AK18" s="5" t="n"/>
+      <c r="AL18" s="5" t="n"/>
+      <c r="AM18" s="5" t="n"/>
+      <c r="AN18" s="5" t="n"/>
+      <c r="AO18" s="5" t="n"/>
+      <c r="AP18" s="5" t="n"/>
+      <c r="AQ18" s="5" t="n"/>
+      <c r="AR18" s="5" t="n"/>
+      <c r="AS18" s="5" t="n"/>
+      <c r="AT18" s="5" t="n"/>
+      <c r="AU18" s="5" t="n"/>
+      <c r="AV18" s="5" t="n"/>
+      <c r="AW18" s="5" t="n"/>
+      <c r="AX18" s="5" t="n"/>
+      <c r="AY18" s="5" t="n"/>
+      <c r="AZ18" s="5" t="n"/>
+      <c r="BA18" s="5" t="n"/>
+      <c r="BB18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>蜻蛉切</t>
+          <t>蛍丸</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1976,174 +2049,174 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>槍</t>
+          <t>大太刀</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>天下三名槍</t>
+          <t>夜</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>黄</t>
+          <t>青</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>必中縦断突き</t>
+          <t>正円一刀斬り</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>指定した【縦列・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>551,72</t>
+          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>677,107</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>65</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>蜻蛉切</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>槍</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>天下三名槍</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>黄</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>22</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>必中縦断突き</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>指定した【縦列・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>551,72</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
         <v>79</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>江雪左文字</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>戦装束</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>太刀</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>雪</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>赤</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>19</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>霧散斬り 先手の型</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>ランダムなト餓鬼（攻撃指示優先）を最大5体消去し、敵に【特小＋＋】ダメージを与える
 消去時のブレイクゲージ減少量が【2倍】になる</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
+      <c r="O21" s="1" t="inlineStr">
         <is>
           <t>507,74</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>85</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>加州清光</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>戦装束</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>打刀</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>新選組</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>赤</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>26</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>必中三段斬り</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>指定した【円型・特小範囲】のト餓鬼を3回消去し、敵に【小】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O21" s="1" t="n"/>
-      <c r="P21" s="1" t="n"/>
-      <c r="Q21" s="1" t="n"/>
-      <c r="R21" s="1" t="n"/>
-      <c r="S21" s="1" t="inlineStr">
-        <is>
-          <t>645,73</t>
-        </is>
-      </c>
-      <c r="T21" s="1" t="n"/>
-      <c r="U21" s="1" t="n"/>
-      <c r="V21" s="1" t="n"/>
-      <c r="W21" s="1" t="n"/>
-      <c r="X21" s="1" t="n"/>
-      <c r="Y21" s="1" t="n"/>
-      <c r="Z21" s="1" t="n"/>
-      <c r="AA21" s="1" t="n"/>
-      <c r="AB21" s="1" t="n"/>
-      <c r="AC21" s="1" t="n"/>
-      <c r="AD21" s="1" t="n"/>
-      <c r="AE21" s="1" t="n"/>
-      <c r="AF21" s="1" t="n"/>
-      <c r="AG21" s="1" t="n"/>
-      <c r="AH21" s="1" t="n"/>
-      <c r="AI21" s="1" t="n"/>
-      <c r="AJ21" s="1" t="n"/>
-      <c r="AK21" s="1" t="n"/>
-      <c r="AL21" s="1" t="n"/>
-      <c r="AM21" s="1" t="n"/>
-      <c r="AN21" s="1" t="n"/>
-      <c r="AO21" s="1" t="n"/>
-      <c r="AP21" s="1" t="n"/>
-      <c r="AQ21" s="1" t="n"/>
-      <c r="AR21" s="1" t="n"/>
-      <c r="BC21" s="1" t="n"/>
-      <c r="BD21" s="1" t="n"/>
-      <c r="BE21" s="1" t="n"/>
+      <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="n"/>
+      <c r="T21" s="2" t="n"/>
+      <c r="U21" s="2" t="n"/>
+      <c r="V21" s="2" t="n"/>
+      <c r="W21" s="2" t="n"/>
+      <c r="X21" s="2" t="n"/>
+      <c r="Y21" s="2" t="n"/>
+      <c r="Z21" s="2" t="n"/>
+      <c r="AA21" s="2" t="n"/>
+      <c r="AB21" s="2" t="n"/>
+      <c r="AC21" s="2" t="n"/>
+      <c r="AD21" s="2" t="n"/>
+      <c r="AE21" s="2" t="n"/>
+      <c r="AF21" s="2" t="n"/>
+      <c r="AG21" s="2" t="n"/>
+      <c r="AH21" s="2" t="n"/>
+      <c r="AI21" s="2" t="n"/>
+      <c r="AJ21" s="2" t="n"/>
+      <c r="AK21" s="2" t="n"/>
+      <c r="AL21" s="2" t="n"/>
+      <c r="AM21" s="2" t="n"/>
+      <c r="AN21" s="2" t="n"/>
+      <c r="AO21" s="2" t="n"/>
+      <c r="AP21" s="2" t="n"/>
+      <c r="AQ21" s="2" t="n"/>
+      <c r="AR21" s="2" t="n"/>
+      <c r="BC21" s="2" t="n"/>
+      <c r="BD21" s="2" t="n"/>
+      <c r="BE21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>和泉守兼定</t>
+          <t>宗三左文字</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2158,7 +2231,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>新選組</t>
+          <t>蝶</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2167,19 +2240,23 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>正円二段斬り</t>
+          <t>攪乱戦術・黄</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>ランダムな場所の【円型・小範囲】のト餓鬼を2回消去し、敵に【中】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O22" s="1" t="n"/>
+          <t>【最大10体】の黄ト餓鬼を盤面の中央に集める</t>
+        </is>
+      </c>
+      <c r="O22" s="1" t="inlineStr">
+        <is>
+          <t>493,54</t>
+        </is>
+      </c>
       <c r="P22" s="1" t="n"/>
       <c r="Q22" s="1" t="n"/>
       <c r="R22" s="1" t="n"/>
@@ -2198,11 +2275,7 @@
       <c r="AE22" s="1" t="n"/>
       <c r="AF22" s="1" t="n"/>
       <c r="AG22" s="1" t="n"/>
-      <c r="AH22" s="1" t="inlineStr">
-        <is>
-          <t>1551,188</t>
-        </is>
-      </c>
+      <c r="AH22" s="1" t="n"/>
       <c r="AI22" s="1" t="n"/>
       <c r="AJ22" s="1" t="n"/>
       <c r="AK22" s="1" t="n"/>
@@ -2213,17 +2286,27 @@
       <c r="AP22" s="1" t="n"/>
       <c r="AQ22" s="1" t="n"/>
       <c r="AR22" s="1" t="n"/>
-      <c r="BC22" s="1" t="n"/>
-      <c r="BD22" s="1" t="n"/>
-      <c r="BE22" s="1" t="n"/>
+      <c r="AS22" s="5" t="n"/>
+      <c r="AT22" s="5" t="n"/>
+      <c r="AU22" s="5" t="n"/>
+      <c r="AV22" s="5" t="n"/>
+      <c r="AW22" s="5" t="n"/>
+      <c r="AX22" s="5" t="n"/>
+      <c r="AY22" s="5" t="n"/>
+      <c r="AZ22" s="5" t="n"/>
+      <c r="BA22" s="5" t="n"/>
+      <c r="BB22" s="5" t="n"/>
+      <c r="BC22" s="2" t="n"/>
+      <c r="BD22" s="2" t="n"/>
+      <c r="BE22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>陸奥守吉行</t>
+          <t>小夜左文字</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2233,34 +2316,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>短刀</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>海</t>
+          <t>夜</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>黄</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>水平斬り 攻勢の型</t>
+          <t>正円斬り 追撃の型</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【極小】ダメージを与える
-味方全員に攻撃力上昇【極小＋＋・3手】を付与する</t>
-        </is>
-      </c>
-      <c r="O23" s="1" t="n"/>
+          <t>【円型・特小範囲】のト餓鬼を消去し、敵に【中】ダメージを与える。乱舞ぎりタイム中はさらにダメージ上昇。</t>
+        </is>
+      </c>
+      <c r="O23" s="1" t="inlineStr">
+        <is>
+          <t>417,81</t>
+        </is>
+      </c>
       <c r="P23" s="1" t="n"/>
       <c r="Q23" s="1" t="n"/>
       <c r="R23" s="1" t="n"/>
@@ -2289,26 +2375,28 @@
       <c r="AO23" s="1" t="n"/>
       <c r="AP23" s="1" t="n"/>
       <c r="AQ23" s="1" t="n"/>
-      <c r="AR23" s="1" t="inlineStr">
-        <is>
-          <t>1575,228</t>
-        </is>
-      </c>
-      <c r="BC23" s="1" t="n"/>
-      <c r="BD23" s="1" t="n"/>
-      <c r="BE23" s="1" t="inlineStr">
-        <is>
-          <t>[黄の絵具,1][書き物道具,2][花札,2][天ぷら,2][そろばん,2][打刀の心得,1]</t>
-        </is>
-      </c>
+      <c r="AR23" s="1" t="n"/>
+      <c r="AS23" s="5" t="n"/>
+      <c r="AT23" s="5" t="n"/>
+      <c r="AU23" s="5" t="n"/>
+      <c r="AV23" s="5" t="n"/>
+      <c r="AW23" s="5" t="n"/>
+      <c r="AX23" s="5" t="n"/>
+      <c r="AY23" s="5" t="n"/>
+      <c r="AZ23" s="5" t="n"/>
+      <c r="BA23" s="5" t="n"/>
+      <c r="BB23" s="5" t="n"/>
+      <c r="BC23" s="2" t="n"/>
+      <c r="BD23" s="2" t="n"/>
+      <c r="BE23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>山姥切国広</t>
+          <t>加州清光</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2323,41 +2411,41 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>兄弟</t>
+          <t>新選組</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>青</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>正円一刀斬り</t>
+          <t>必中三段斬り</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>【円型・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
+          <t>指定した【円型・特小範囲】のト餓鬼を3回消去し、敵に【小】ダメージを与える</t>
         </is>
       </c>
       <c r="O24" s="1" t="n"/>
       <c r="P24" s="1" t="n"/>
       <c r="Q24" s="1" t="n"/>
       <c r="R24" s="1" t="n"/>
-      <c r="S24" s="1" t="n"/>
+      <c r="S24" s="1" t="inlineStr">
+        <is>
+          <t>645,73</t>
+        </is>
+      </c>
       <c r="T24" s="1" t="n"/>
       <c r="U24" s="1" t="n"/>
       <c r="V24" s="1" t="n"/>
       <c r="W24" s="1" t="n"/>
-      <c r="X24" s="1" t="inlineStr">
-        <is>
-          <t>850,107</t>
-        </is>
-      </c>
+      <c r="X24" s="1" t="n"/>
       <c r="Y24" s="1" t="n"/>
       <c r="Z24" s="1" t="n"/>
       <c r="AA24" s="1" t="n"/>
@@ -2384,11 +2472,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>山伏国広</t>
+          <t>歌仙兼定</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2396,14 +2484,19 @@
           <t>戦装束</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>お山修行</t>
+          <t>詠み人,花</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2412,22 +2505,21 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>逆さ扇斬り 守護の型</t>
+          <t>くちなしの挽歌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>【扇型・特小範囲】のト餓鬼を消去し、敵に【極小＋】ダメージを与える
-味方全員に被ダメージ軽減【特小＋＋・3手】を付与する</t>
+          <t>指定した【縦列・小範囲】のト餓鬼を、黄色に変化させる</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>584,70</t>
+          <t>492,74</t>
         </is>
       </c>
       <c r="P25" s="1" t="n"/>
@@ -2459,17 +2551,27 @@
       <c r="AP25" s="1" t="n"/>
       <c r="AQ25" s="1" t="n"/>
       <c r="AR25" s="1" t="n"/>
-      <c r="BC25" s="1" t="n"/>
-      <c r="BD25" s="1" t="n"/>
-      <c r="BE25" s="1" t="n"/>
+      <c r="AS25" s="5" t="n"/>
+      <c r="AT25" s="5" t="n"/>
+      <c r="AU25" s="5" t="n"/>
+      <c r="AV25" s="5" t="n"/>
+      <c r="AW25" s="5" t="n"/>
+      <c r="AX25" s="5" t="n"/>
+      <c r="AY25" s="5" t="n"/>
+      <c r="AZ25" s="5" t="n"/>
+      <c r="BA25" s="5" t="n"/>
+      <c r="BB25" s="5" t="n"/>
+      <c r="BC25" s="2" t="n"/>
+      <c r="BD25" s="2" t="n"/>
+      <c r="BE25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>獅子王</t>
+          <t>和泉守兼定</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2479,12 +2581,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>けもの</t>
+          <t>新選組</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2493,27 +2595,23 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>水平一刀斬り</t>
+          <t>正円二段斬り</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
+          <t>ランダムな場所の【円型・小範囲】のト餓鬼を2回消去し、敵に【中】ダメージを与える</t>
         </is>
       </c>
       <c r="O26" s="1" t="n"/>
       <c r="P26" s="1" t="n"/>
       <c r="Q26" s="1" t="n"/>
       <c r="R26" s="1" t="n"/>
-      <c r="S26" s="1" t="inlineStr">
-        <is>
-          <t>771,74</t>
-        </is>
-      </c>
+      <c r="S26" s="1" t="n"/>
       <c r="T26" s="1" t="n"/>
       <c r="U26" s="1" t="n"/>
       <c r="V26" s="1" t="n"/>
@@ -2528,7 +2626,11 @@
       <c r="AE26" s="1" t="n"/>
       <c r="AF26" s="1" t="n"/>
       <c r="AG26" s="1" t="n"/>
-      <c r="AH26" s="1" t="n"/>
+      <c r="AH26" s="1" t="inlineStr">
+        <is>
+          <t>1551,188</t>
+        </is>
+      </c>
       <c r="AI26" s="1" t="n"/>
       <c r="AJ26" s="1" t="n"/>
       <c r="AK26" s="1" t="n"/>
@@ -2545,11 +2647,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>鶴丸国永</t>
+          <t>陸奥守吉行</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2559,21 +2661,21 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>海</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>黄</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2582,8 +2684,8 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>【横列・中範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える
-自身に攻撃力上昇【極小・1手】を付与する</t>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【極小】ダメージを与える
+味方全員に攻撃力上昇【極小＋＋・3手】を付与する</t>
         </is>
       </c>
       <c r="O27" s="1" t="n"/>
@@ -2595,11 +2697,7 @@
       <c r="U27" s="1" t="n"/>
       <c r="V27" s="1" t="n"/>
       <c r="W27" s="1" t="n"/>
-      <c r="X27" s="1" t="inlineStr">
-        <is>
-          <t>935,110</t>
-        </is>
-      </c>
+      <c r="X27" s="1" t="n"/>
       <c r="Y27" s="1" t="n"/>
       <c r="Z27" s="1" t="n"/>
       <c r="AA27" s="1" t="n"/>
@@ -2619,12 +2717,61 @@
       <c r="AO27" s="1" t="n"/>
       <c r="AP27" s="1" t="n"/>
       <c r="AQ27" s="1" t="n"/>
-      <c r="AR27" s="1" t="n"/>
+      <c r="AR27" s="1" t="inlineStr">
+        <is>
+          <t>1575,228</t>
+        </is>
+      </c>
       <c r="BC27" s="1" t="n"/>
       <c r="BD27" s="1" t="n"/>
-      <c r="BE27" s="1" t="n"/>
+      <c r="BE27" s="1" t="inlineStr">
+        <is>
+          <t>[黄の絵具,1][書き物道具,2][花札,2][天ぷら,2][そろばん,2][打刀の心得,1]</t>
+        </is>
+      </c>
     </row>
     <row r="28">
+      <c r="A28" t="n">
+        <v>95</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>山姥切国広</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>打刀</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>兄弟</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>青</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>22</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>正円一刀斬り</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>【円型・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
+        </is>
+      </c>
       <c r="O28" s="1" t="n"/>
       <c r="P28" s="1" t="n"/>
       <c r="Q28" s="1" t="n"/>
@@ -2634,7 +2781,11 @@
       <c r="U28" s="1" t="n"/>
       <c r="V28" s="1" t="n"/>
       <c r="W28" s="1" t="n"/>
-      <c r="X28" s="1" t="n"/>
+      <c r="X28" s="1" t="inlineStr">
+        <is>
+          <t>850,107</t>
+        </is>
+      </c>
       <c r="Y28" s="1" t="n"/>
       <c r="Z28" s="1" t="n"/>
       <c r="AA28" s="1" t="n"/>
@@ -2660,7 +2811,53 @@
       <c r="BE28" s="1" t="n"/>
     </row>
     <row r="29">
-      <c r="O29" s="1" t="n"/>
+      <c r="A29" t="n">
+        <v>97</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>山伏国広</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>太刀</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>お山修行</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>22</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>逆さ扇斬り 守護の型</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>【扇型・特小範囲】のト餓鬼を消去し、敵に【極小＋】ダメージを与える
+味方全員に被ダメージ軽減【特小＋＋・3手】を付与する</t>
+        </is>
+      </c>
+      <c r="O29" s="1" t="inlineStr">
+        <is>
+          <t>584,70</t>
+        </is>
+      </c>
       <c r="P29" s="1" t="n"/>
       <c r="Q29" s="1" t="n"/>
       <c r="R29" s="1" t="n"/>
@@ -2695,11 +2892,56 @@
       <c r="BE29" s="1" t="n"/>
     </row>
     <row r="30">
+      <c r="A30" t="n">
+        <v>122</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>獅子王</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>太刀</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>けもの</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>22</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>水平一刀斬り</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
+        </is>
+      </c>
       <c r="O30" s="1" t="n"/>
       <c r="P30" s="1" t="n"/>
       <c r="Q30" s="1" t="n"/>
       <c r="R30" s="1" t="n"/>
-      <c r="S30" s="1" t="n"/>
+      <c r="S30" s="1" t="inlineStr">
+        <is>
+          <t>771,74</t>
+        </is>
+      </c>
       <c r="T30" s="1" t="n"/>
       <c r="U30" s="1" t="n"/>
       <c r="V30" s="1" t="n"/>
@@ -2730,6 +2972,48 @@
       <c r="BE30" s="1" t="n"/>
     </row>
     <row r="31">
+      <c r="A31" t="n">
+        <v>130</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>鶴丸国永</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>太刀</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>鳥</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>24</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>水平斬り 攻勢の型</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>【横列・中範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える
+自身に攻撃力上昇【極小・1手】を付与する</t>
+        </is>
+      </c>
       <c r="O31" s="1" t="n"/>
       <c r="P31" s="1" t="n"/>
       <c r="Q31" s="1" t="n"/>
@@ -2739,7 +3023,11 @@
       <c r="U31" s="1" t="n"/>
       <c r="V31" s="1" t="n"/>
       <c r="W31" s="1" t="n"/>
-      <c r="X31" s="1" t="n"/>
+      <c r="X31" s="1" t="inlineStr">
+        <is>
+          <t>935,110</t>
+        </is>
+      </c>
       <c r="Y31" s="1" t="n"/>
       <c r="Z31" s="1" t="n"/>
       <c r="AA31" s="1" t="n"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -2472,11 +2472,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>歌仙兼定</t>
+          <t>大和守安定</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2484,11 +2484,6 @@
           <t>戦装束</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>打刀</t>
@@ -2496,7 +2491,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>詠み人,花</t>
+          <t>新選組</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2505,21 +2500,22 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>くちなしの挽歌</t>
+          <t>霧散斬り ボムの型</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>指定した【縦列・小範囲】のト餓鬼を、黄色に変化させる</t>
+          <t>ランダムな孤立した青ト餓鬼を【最大3体】消去し、敵に【特小＋】ダメージを与える
+ボムを【1個】生成する</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>492,74</t>
+          <t>467,57</t>
         </is>
       </c>
       <c r="P25" s="1" t="n"/>
@@ -2567,11 +2563,11 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>和泉守兼定</t>
+          <t>歌仙兼定</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2586,7 +2582,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>新選組</t>
+          <t>花</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2595,19 +2591,23 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>正円二段斬り</t>
+          <t>水平一刀斬り</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>ランダムな場所の【円型・小範囲】のト餓鬼を2回消去し、敵に【中】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O26" s="1" t="n"/>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小－】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O26" s="1" t="inlineStr">
+        <is>
+          <t>475,70</t>
+        </is>
+      </c>
       <c r="P26" s="1" t="n"/>
       <c r="Q26" s="1" t="n"/>
       <c r="R26" s="1" t="n"/>
@@ -2626,11 +2626,7 @@
       <c r="AE26" s="1" t="n"/>
       <c r="AF26" s="1" t="n"/>
       <c r="AG26" s="1" t="n"/>
-      <c r="AH26" s="1" t="inlineStr">
-        <is>
-          <t>1551,188</t>
-        </is>
-      </c>
+      <c r="AH26" s="1" t="n"/>
       <c r="AI26" s="1" t="n"/>
       <c r="AJ26" s="1" t="n"/>
       <c r="AK26" s="1" t="n"/>
@@ -2641,17 +2637,27 @@
       <c r="AP26" s="1" t="n"/>
       <c r="AQ26" s="1" t="n"/>
       <c r="AR26" s="1" t="n"/>
-      <c r="BC26" s="1" t="n"/>
-      <c r="BD26" s="1" t="n"/>
-      <c r="BE26" s="1" t="n"/>
+      <c r="AS26" s="5" t="n"/>
+      <c r="AT26" s="5" t="n"/>
+      <c r="AU26" s="5" t="n"/>
+      <c r="AV26" s="5" t="n"/>
+      <c r="AW26" s="5" t="n"/>
+      <c r="AX26" s="5" t="n"/>
+      <c r="AY26" s="5" t="n"/>
+      <c r="AZ26" s="5" t="n"/>
+      <c r="BA26" s="5" t="n"/>
+      <c r="BB26" s="5" t="n"/>
+      <c r="BC26" s="2" t="n"/>
+      <c r="BD26" s="2" t="n"/>
+      <c r="BE26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>陸奥守吉行</t>
+          <t>歌仙兼定</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2659,6 +2665,11 @@
           <t>戦装束</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>打刀</t>
@@ -2666,12 +2677,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>海</t>
+          <t>詠み人,花</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>黄</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2679,16 +2690,19 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>水平斬り 攻勢の型</t>
+          <t>くちなしの挽歌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【極小】ダメージを与える
-味方全員に攻撃力上昇【極小＋＋・3手】を付与する</t>
-        </is>
-      </c>
-      <c r="O27" s="1" t="n"/>
+          <t>指定した【縦列・小範囲】のト餓鬼を、黄色に変化させる</t>
+        </is>
+      </c>
+      <c r="O27" s="1" t="inlineStr">
+        <is>
+          <t>492,74</t>
+        </is>
+      </c>
       <c r="P27" s="1" t="n"/>
       <c r="Q27" s="1" t="n"/>
       <c r="R27" s="1" t="n"/>
@@ -2717,26 +2731,28 @@
       <c r="AO27" s="1" t="n"/>
       <c r="AP27" s="1" t="n"/>
       <c r="AQ27" s="1" t="n"/>
-      <c r="AR27" s="1" t="inlineStr">
-        <is>
-          <t>1575,228</t>
-        </is>
-      </c>
-      <c r="BC27" s="1" t="n"/>
-      <c r="BD27" s="1" t="n"/>
-      <c r="BE27" s="1" t="inlineStr">
-        <is>
-          <t>[黄の絵具,1][書き物道具,2][花札,2][天ぷら,2][そろばん,2][打刀の心得,1]</t>
-        </is>
-      </c>
+      <c r="AR27" s="1" t="n"/>
+      <c r="AS27" s="5" t="n"/>
+      <c r="AT27" s="5" t="n"/>
+      <c r="AU27" s="5" t="n"/>
+      <c r="AV27" s="5" t="n"/>
+      <c r="AW27" s="5" t="n"/>
+      <c r="AX27" s="5" t="n"/>
+      <c r="AY27" s="5" t="n"/>
+      <c r="AZ27" s="5" t="n"/>
+      <c r="BA27" s="5" t="n"/>
+      <c r="BB27" s="5" t="n"/>
+      <c r="BC27" s="2" t="n"/>
+      <c r="BD27" s="2" t="n"/>
+      <c r="BE27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>山姥切国広</t>
+          <t>和泉守兼定</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2751,25 +2767,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>兄弟</t>
+          <t>新選組</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>青</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>正円一刀斬り</t>
+          <t>正円二段斬り</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>【円型・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
+          <t>ランダムな場所の【円型・小範囲】のト餓鬼を2回消去し、敵に【中】ダメージを与える</t>
         </is>
       </c>
       <c r="O28" s="1" t="n"/>
@@ -2781,11 +2797,7 @@
       <c r="U28" s="1" t="n"/>
       <c r="V28" s="1" t="n"/>
       <c r="W28" s="1" t="n"/>
-      <c r="X28" s="1" t="inlineStr">
-        <is>
-          <t>850,107</t>
-        </is>
-      </c>
+      <c r="X28" s="1" t="n"/>
       <c r="Y28" s="1" t="n"/>
       <c r="Z28" s="1" t="n"/>
       <c r="AA28" s="1" t="n"/>
@@ -2795,7 +2807,11 @@
       <c r="AE28" s="1" t="n"/>
       <c r="AF28" s="1" t="n"/>
       <c r="AG28" s="1" t="n"/>
-      <c r="AH28" s="1" t="n"/>
+      <c r="AH28" s="1" t="inlineStr">
+        <is>
+          <t>1551,188</t>
+        </is>
+      </c>
       <c r="AI28" s="1" t="n"/>
       <c r="AJ28" s="1" t="n"/>
       <c r="AK28" s="1" t="n"/>
@@ -2812,11 +2828,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>山伏国広</t>
+          <t>陸奥守吉行</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2826,38 +2842,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>お山修行</t>
+          <t>海</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>黄</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>逆さ扇斬り 守護の型</t>
+          <t>水平斬り 攻勢の型</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>【扇型・特小範囲】のト餓鬼を消去し、敵に【極小＋】ダメージを与える
-味方全員に被ダメージ軽減【特小＋＋・3手】を付与する</t>
-        </is>
-      </c>
-      <c r="O29" s="1" t="inlineStr">
-        <is>
-          <t>584,70</t>
-        </is>
-      </c>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【極小】ダメージを与える
+味方全員に攻撃力上昇【極小＋＋・3手】を付与する</t>
+        </is>
+      </c>
+      <c r="O29" s="1" t="n"/>
       <c r="P29" s="1" t="n"/>
       <c r="Q29" s="1" t="n"/>
       <c r="R29" s="1" t="n"/>
@@ -2886,18 +2898,26 @@
       <c r="AO29" s="1" t="n"/>
       <c r="AP29" s="1" t="n"/>
       <c r="AQ29" s="1" t="n"/>
-      <c r="AR29" s="1" t="n"/>
+      <c r="AR29" s="1" t="inlineStr">
+        <is>
+          <t>1575,228</t>
+        </is>
+      </c>
       <c r="BC29" s="1" t="n"/>
       <c r="BD29" s="1" t="n"/>
-      <c r="BE29" s="1" t="n"/>
+      <c r="BE29" s="1" t="inlineStr">
+        <is>
+          <t>[黄の絵具,1][書き物道具,2][花札,2][天ぷら,2][そろばん,2][打刀の心得,1]</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>獅子王</t>
+          <t>山姥切国広</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2907,17 +2927,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>けもの</t>
+          <t>兄弟</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>青</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -2925,28 +2945,28 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>水平一刀斬り</t>
+          <t>正円一刀斬り</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
+          <t>【円型・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
         </is>
       </c>
       <c r="O30" s="1" t="n"/>
       <c r="P30" s="1" t="n"/>
       <c r="Q30" s="1" t="n"/>
       <c r="R30" s="1" t="n"/>
-      <c r="S30" s="1" t="inlineStr">
-        <is>
-          <t>771,74</t>
-        </is>
-      </c>
+      <c r="S30" s="1" t="n"/>
       <c r="T30" s="1" t="n"/>
       <c r="U30" s="1" t="n"/>
       <c r="V30" s="1" t="n"/>
       <c r="W30" s="1" t="n"/>
-      <c r="X30" s="1" t="n"/>
+      <c r="X30" s="1" t="inlineStr">
+        <is>
+          <t>850,107</t>
+        </is>
+      </c>
       <c r="Y30" s="1" t="n"/>
       <c r="Z30" s="1" t="n"/>
       <c r="AA30" s="1" t="n"/>
@@ -2973,11 +2993,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>鶴丸国永</t>
+          <t>山伏国広</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2992,7 +3012,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>お山修行</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3001,20 +3021,24 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>水平斬り 攻勢の型</t>
+          <t>逆さ扇斬り 守護の型</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>【横列・中範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える
-自身に攻撃力上昇【極小・1手】を付与する</t>
-        </is>
-      </c>
-      <c r="O31" s="1" t="n"/>
+          <t>【扇型・特小範囲】のト餓鬼を消去し、敵に【極小＋】ダメージを与える
+味方全員に被ダメージ軽減【特小＋＋・3手】を付与する</t>
+        </is>
+      </c>
+      <c r="O31" s="1" t="inlineStr">
+        <is>
+          <t>584,70</t>
+        </is>
+      </c>
       <c r="P31" s="1" t="n"/>
       <c r="Q31" s="1" t="n"/>
       <c r="R31" s="1" t="n"/>
@@ -3023,11 +3047,7 @@
       <c r="U31" s="1" t="n"/>
       <c r="V31" s="1" t="n"/>
       <c r="W31" s="1" t="n"/>
-      <c r="X31" s="1" t="inlineStr">
-        <is>
-          <t>935,110</t>
-        </is>
-      </c>
+      <c r="X31" s="1" t="n"/>
       <c r="Y31" s="1" t="n"/>
       <c r="Z31" s="1" t="n"/>
       <c r="AA31" s="1" t="n"/>
@@ -3053,11 +3073,56 @@
       <c r="BE31" s="1" t="n"/>
     </row>
     <row r="32">
+      <c r="A32" t="n">
+        <v>122</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>獅子王</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>太刀</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>けもの</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>22</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>水平一刀斬り</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
+        </is>
+      </c>
       <c r="O32" s="1" t="n"/>
       <c r="P32" s="1" t="n"/>
       <c r="Q32" s="1" t="n"/>
       <c r="R32" s="1" t="n"/>
-      <c r="S32" s="1" t="n"/>
+      <c r="S32" s="1" t="inlineStr">
+        <is>
+          <t>771,74</t>
+        </is>
+      </c>
       <c r="T32" s="1" t="n"/>
       <c r="U32" s="1" t="n"/>
       <c r="V32" s="1" t="n"/>
@@ -3088,6 +3153,48 @@
       <c r="BE32" s="1" t="n"/>
     </row>
     <row r="33">
+      <c r="A33" t="n">
+        <v>130</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>鶴丸国永</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>太刀</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>鳥</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>24</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>水平斬り 攻勢の型</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>【横列・中範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える
+自身に攻撃力上昇【極小・1手】を付与する</t>
+        </is>
+      </c>
       <c r="O33" s="1" t="n"/>
       <c r="P33" s="1" t="n"/>
       <c r="Q33" s="1" t="n"/>
@@ -3097,7 +3204,11 @@
       <c r="U33" s="1" t="n"/>
       <c r="V33" s="1" t="n"/>
       <c r="W33" s="1" t="n"/>
-      <c r="X33" s="1" t="n"/>
+      <c r="X33" s="1" t="inlineStr">
+        <is>
+          <t>935,110</t>
+        </is>
+      </c>
       <c r="Y33" s="1" t="n"/>
       <c r="Z33" s="1" t="n"/>
       <c r="AA33" s="1" t="n"/>
@@ -3123,7 +3234,50 @@
       <c r="BE33" s="1" t="n"/>
     </row>
     <row r="34">
-      <c r="O34" s="1" t="n"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>大倶利伽羅</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>打刀</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>龍</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>24</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>三段斬り 攻勢の型</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ランダムな【円型・特小範囲】のト餓鬼を3回消去し、敵に【小－】ダメージを与える
+自身にクリティカル率上昇【極小＋＋・1手】を付与する</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>455,72</t>
+        </is>
+      </c>
       <c r="P34" s="1" t="n"/>
       <c r="Q34" s="1" t="n"/>
       <c r="R34" s="1" t="n"/>
@@ -3153,12 +3307,64 @@
       <c r="AP34" s="1" t="n"/>
       <c r="AQ34" s="1" t="n"/>
       <c r="AR34" s="1" t="n"/>
-      <c r="BC34" s="1" t="n"/>
-      <c r="BD34" s="1" t="n"/>
-      <c r="BE34" s="1" t="n"/>
+      <c r="AS34" s="5" t="n"/>
+      <c r="AT34" s="5" t="n"/>
+      <c r="AU34" s="5" t="n"/>
+      <c r="AV34" s="5" t="n"/>
+      <c r="AW34" s="5" t="n"/>
+      <c r="AX34" s="5" t="n"/>
+      <c r="AY34" s="5" t="n"/>
+      <c r="AZ34" s="5" t="n"/>
+      <c r="BA34" s="5" t="n"/>
+      <c r="BB34" s="5" t="n"/>
+      <c r="BC34" s="2" t="n"/>
+      <c r="BD34" s="2" t="n"/>
+      <c r="BE34" s="2" t="n"/>
     </row>
     <row r="35">
-      <c r="O35" s="1" t="n"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>へし切長谷部</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>打刀</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>もの斬り</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>27</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>必中二段斬り</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>指定した【縦列・小範囲】のト餓鬼を2回消去し、敵に【小＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O35" s="1" t="inlineStr">
+        <is>
+          <t>530,65</t>
+        </is>
+      </c>
       <c r="P35" s="1" t="n"/>
       <c r="Q35" s="1" t="n"/>
       <c r="R35" s="1" t="n"/>
@@ -3188,12 +3394,64 @@
       <c r="AP35" s="1" t="n"/>
       <c r="AQ35" s="1" t="n"/>
       <c r="AR35" s="1" t="n"/>
-      <c r="BC35" s="1" t="n"/>
-      <c r="BD35" s="1" t="n"/>
-      <c r="BE35" s="1" t="n"/>
+      <c r="AS35" s="5" t="n"/>
+      <c r="AT35" s="5" t="n"/>
+      <c r="AU35" s="5" t="n"/>
+      <c r="AV35" s="5" t="n"/>
+      <c r="AW35" s="5" t="n"/>
+      <c r="AX35" s="5" t="n"/>
+      <c r="AY35" s="5" t="n"/>
+      <c r="AZ35" s="5" t="n"/>
+      <c r="BA35" s="5" t="n"/>
+      <c r="BB35" s="5" t="n"/>
+      <c r="BC35" s="2" t="n"/>
+      <c r="BD35" s="2" t="n"/>
+      <c r="BE35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="O36" s="1" t="n"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>同田貫正国</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>打刀</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>もの斬り</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>22</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>真っ向一刀斬り</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>【縦列・小範囲】のト餓鬼を消去し、敵に【小＋＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>453,75</t>
+        </is>
+      </c>
       <c r="P36" s="1" t="n"/>
       <c r="Q36" s="1" t="n"/>
       <c r="R36" s="1" t="n"/>
@@ -3223,9 +3481,19 @@
       <c r="AP36" s="1" t="n"/>
       <c r="AQ36" s="1" t="n"/>
       <c r="AR36" s="1" t="n"/>
-      <c r="BC36" s="1" t="n"/>
-      <c r="BD36" s="1" t="n"/>
-      <c r="BE36" s="1" t="n"/>
+      <c r="AS36" s="5" t="n"/>
+      <c r="AT36" s="5" t="n"/>
+      <c r="AU36" s="5" t="n"/>
+      <c r="AV36" s="5" t="n"/>
+      <c r="AW36" s="5" t="n"/>
+      <c r="AX36" s="5" t="n"/>
+      <c r="AY36" s="5" t="n"/>
+      <c r="AZ36" s="5" t="n"/>
+      <c r="BA36" s="5" t="n"/>
+      <c r="BB36" s="5" t="n"/>
+      <c r="BC36" s="2" t="n"/>
+      <c r="BD36" s="2" t="n"/>
+      <c r="BE36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="O37" s="1" t="n"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -1955,11 +1955,6 @@
           <t>戦装束</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>大太刀</t>
@@ -1967,7 +1962,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ご神刀,兄弟</t>
+          <t>ご神刀</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1976,21 +1971,21 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>天より墜つる暴威</t>
+          <t>霧散斬り・黄</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える。ボスが被ダメージ増加状態のとき、さらに威力が上昇する</t>
+          <t>黄ト餓鬼をランダムに【最大10体】消去し、敵に【小＋】ダメージを与える</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>613,67</t>
+          <t>588,64</t>
         </is>
       </c>
       <c r="P18" s="5" t="n"/>
@@ -2035,11 +2030,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>蛍丸</t>
+          <t>太郎太刀</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2047,6 +2042,11 @@
           <t>戦装束</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>大太刀</t>
@@ -2054,40 +2054,79 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>夜</t>
+          <t>ご神刀,兄弟</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>青</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>正円一刀斬り</t>
+          <t>天より墜つる暴威</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="T19" s="5" t="inlineStr">
-        <is>
-          <t>677,107</t>
-        </is>
-      </c>
+          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える。ボスが被ダメージ増加状態のとき、さらに威力が上昇する</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>613,67</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="5" t="n"/>
+      <c r="U19" s="5" t="n"/>
+      <c r="V19" s="5" t="n"/>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+      <c r="Y19" s="5" t="n"/>
+      <c r="Z19" s="5" t="n"/>
+      <c r="AA19" s="5" t="n"/>
+      <c r="AB19" s="5" t="n"/>
+      <c r="AC19" s="5" t="n"/>
+      <c r="AD19" s="5" t="n"/>
+      <c r="AE19" s="5" t="n"/>
+      <c r="AF19" s="5" t="n"/>
+      <c r="AG19" s="5" t="n"/>
+      <c r="AH19" s="5" t="n"/>
+      <c r="AI19" s="5" t="n"/>
+      <c r="AJ19" s="5" t="n"/>
+      <c r="AK19" s="5" t="n"/>
+      <c r="AL19" s="5" t="n"/>
+      <c r="AM19" s="5" t="n"/>
+      <c r="AN19" s="5" t="n"/>
+      <c r="AO19" s="5" t="n"/>
+      <c r="AP19" s="5" t="n"/>
+      <c r="AQ19" s="5" t="n"/>
+      <c r="AR19" s="5" t="n"/>
+      <c r="AS19" s="5" t="n"/>
+      <c r="AT19" s="5" t="n"/>
+      <c r="AU19" s="5" t="n"/>
+      <c r="AV19" s="5" t="n"/>
+      <c r="AW19" s="5" t="n"/>
+      <c r="AX19" s="5" t="n"/>
+      <c r="AY19" s="5" t="n"/>
+      <c r="AZ19" s="5" t="n"/>
+      <c r="BA19" s="5" t="n"/>
+      <c r="BB19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>蜻蛉切</t>
+          <t>次郎太刀</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2097,45 +2136,84 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>槍</t>
+          <t>大太刀</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>天下三名槍</t>
+          <t>ご神刀</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>黄</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>必中縦断突き</t>
+          <t>正円一刀斬り</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>指定した【縦列・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
+          <t>【円型・大範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>551,72</t>
-        </is>
-      </c>
+          <t>501,71</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="5" t="n"/>
+      <c r="V20" s="5" t="n"/>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+      <c r="Y20" s="5" t="n"/>
+      <c r="Z20" s="5" t="n"/>
+      <c r="AA20" s="5" t="n"/>
+      <c r="AB20" s="5" t="n"/>
+      <c r="AC20" s="5" t="n"/>
+      <c r="AD20" s="5" t="n"/>
+      <c r="AE20" s="5" t="n"/>
+      <c r="AF20" s="5" t="n"/>
+      <c r="AG20" s="5" t="n"/>
+      <c r="AH20" s="5" t="n"/>
+      <c r="AI20" s="5" t="n"/>
+      <c r="AJ20" s="5" t="n"/>
+      <c r="AK20" s="5" t="n"/>
+      <c r="AL20" s="5" t="n"/>
+      <c r="AM20" s="5" t="n"/>
+      <c r="AN20" s="5" t="n"/>
+      <c r="AO20" s="5" t="n"/>
+      <c r="AP20" s="5" t="n"/>
+      <c r="AQ20" s="5" t="n"/>
+      <c r="AR20" s="5" t="n"/>
+      <c r="AS20" s="5" t="n"/>
+      <c r="AT20" s="5" t="n"/>
+      <c r="AU20" s="5" t="n"/>
+      <c r="AV20" s="5" t="n"/>
+      <c r="AW20" s="5" t="n"/>
+      <c r="AX20" s="5" t="n"/>
+      <c r="AY20" s="5" t="n"/>
+      <c r="AZ20" s="5" t="n"/>
+      <c r="BA20" s="5" t="n"/>
+      <c r="BB20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>江雪左文字</t>
+          <t>蛍丸</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2145,43 +2223,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>大太刀</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>雪</t>
+          <t>夜</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>青</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>霧散斬り 先手の型</t>
+          <t>正円一刀斬り</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>ランダムなト餓鬼（攻撃指示優先）を最大5体消去し、敵に【特小＋＋】ダメージを与える
-消去時のブレイクゲージ減少量が【2倍】になる</t>
-        </is>
-      </c>
-      <c r="O21" s="1" t="inlineStr">
-        <is>
-          <t>507,74</t>
-        </is>
-      </c>
+          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
       <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
-      <c r="T21" s="2" t="n"/>
+      <c r="T21" s="1" t="inlineStr">
+        <is>
+          <t>677,107</t>
+        </is>
+      </c>
       <c r="U21" s="2" t="n"/>
       <c r="V21" s="2" t="n"/>
       <c r="W21" s="2" t="n"/>
@@ -2212,11 +2289,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>宗三左文字</t>
+          <t>蜻蛉切</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2226,87 +2303,77 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>槍</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>蝶</t>
+          <t>天下三名槍</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>黄</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>攪乱戦術・黄</t>
+          <t>必中縦断突き</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>【最大10体】の黄ト餓鬼を盤面の中央に集める</t>
+          <t>指定した【縦列・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>493,54</t>
-        </is>
-      </c>
-      <c r="P22" s="1" t="n"/>
-      <c r="Q22" s="1" t="n"/>
-      <c r="R22" s="1" t="n"/>
-      <c r="S22" s="1" t="n"/>
-      <c r="T22" s="1" t="n"/>
-      <c r="U22" s="1" t="n"/>
-      <c r="V22" s="1" t="n"/>
-      <c r="W22" s="1" t="n"/>
-      <c r="X22" s="1" t="n"/>
-      <c r="Y22" s="1" t="n"/>
-      <c r="Z22" s="1" t="n"/>
-      <c r="AA22" s="1" t="n"/>
-      <c r="AB22" s="1" t="n"/>
-      <c r="AC22" s="1" t="n"/>
-      <c r="AD22" s="1" t="n"/>
-      <c r="AE22" s="1" t="n"/>
-      <c r="AF22" s="1" t="n"/>
-      <c r="AG22" s="1" t="n"/>
-      <c r="AH22" s="1" t="n"/>
-      <c r="AI22" s="1" t="n"/>
-      <c r="AJ22" s="1" t="n"/>
-      <c r="AK22" s="1" t="n"/>
-      <c r="AL22" s="1" t="n"/>
-      <c r="AM22" s="1" t="n"/>
-      <c r="AN22" s="1" t="n"/>
-      <c r="AO22" s="1" t="n"/>
-      <c r="AP22" s="1" t="n"/>
-      <c r="AQ22" s="1" t="n"/>
-      <c r="AR22" s="1" t="n"/>
-      <c r="AS22" s="5" t="n"/>
-      <c r="AT22" s="5" t="n"/>
-      <c r="AU22" s="5" t="n"/>
-      <c r="AV22" s="5" t="n"/>
-      <c r="AW22" s="5" t="n"/>
-      <c r="AX22" s="5" t="n"/>
-      <c r="AY22" s="5" t="n"/>
-      <c r="AZ22" s="5" t="n"/>
-      <c r="BA22" s="5" t="n"/>
-      <c r="BB22" s="5" t="n"/>
+          <t>551,72</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
+      <c r="T22" s="2" t="n"/>
+      <c r="U22" s="2" t="n"/>
+      <c r="V22" s="2" t="n"/>
+      <c r="W22" s="2" t="n"/>
+      <c r="X22" s="2" t="n"/>
+      <c r="Y22" s="2" t="n"/>
+      <c r="Z22" s="2" t="n"/>
+      <c r="AA22" s="2" t="n"/>
+      <c r="AB22" s="2" t="n"/>
+      <c r="AC22" s="2" t="n"/>
+      <c r="AD22" s="2" t="n"/>
+      <c r="AE22" s="2" t="n"/>
+      <c r="AF22" s="2" t="n"/>
+      <c r="AG22" s="2" t="n"/>
+      <c r="AH22" s="2" t="n"/>
+      <c r="AI22" s="2" t="n"/>
+      <c r="AJ22" s="2" t="n"/>
+      <c r="AK22" s="2" t="n"/>
+      <c r="AL22" s="2" t="n"/>
+      <c r="AM22" s="2" t="n"/>
+      <c r="AN22" s="2" t="n"/>
+      <c r="AO22" s="2" t="n"/>
+      <c r="AP22" s="2" t="n"/>
+      <c r="AQ22" s="2" t="n"/>
+      <c r="AR22" s="2" t="n"/>
       <c r="BC22" s="2" t="n"/>
       <c r="BD22" s="2" t="n"/>
       <c r="BE22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>小夜左文字</t>
+          <t>御手杵</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2316,12 +2383,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>短刀</t>
+          <t>槍</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>夜</t>
+          <t>天下三名槍</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2330,21 +2397,21 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>正円斬り 追撃の型</t>
+          <t>必中正円突き</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>【円型・特小範囲】のト餓鬼を消去し、敵に【中】ダメージを与える。乱舞ぎりタイム中はさらにダメージ上昇。</t>
+          <t>指定した1箇所【円型・特小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>417,81</t>
+          <t>461,60</t>
         </is>
       </c>
       <c r="P23" s="1" t="n"/>
@@ -2392,11 +2459,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>加州清光</t>
+          <t>江雪左文字</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2406,12 +2473,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>太刀</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>新選組</t>
+          <t>雪</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2420,63 +2487,64 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>必中三段斬り</t>
+          <t>霧散斬り 先手の型</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>指定した【円型・特小範囲】のト餓鬼を3回消去し、敵に【小】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O24" s="1" t="n"/>
-      <c r="P24" s="1" t="n"/>
-      <c r="Q24" s="1" t="n"/>
-      <c r="R24" s="1" t="n"/>
-      <c r="S24" s="1" t="inlineStr">
-        <is>
-          <t>645,73</t>
-        </is>
-      </c>
-      <c r="T24" s="1" t="n"/>
-      <c r="U24" s="1" t="n"/>
-      <c r="V24" s="1" t="n"/>
-      <c r="W24" s="1" t="n"/>
-      <c r="X24" s="1" t="n"/>
-      <c r="Y24" s="1" t="n"/>
-      <c r="Z24" s="1" t="n"/>
-      <c r="AA24" s="1" t="n"/>
-      <c r="AB24" s="1" t="n"/>
-      <c r="AC24" s="1" t="n"/>
-      <c r="AD24" s="1" t="n"/>
-      <c r="AE24" s="1" t="n"/>
-      <c r="AF24" s="1" t="n"/>
-      <c r="AG24" s="1" t="n"/>
-      <c r="AH24" s="1" t="n"/>
-      <c r="AI24" s="1" t="n"/>
-      <c r="AJ24" s="1" t="n"/>
-      <c r="AK24" s="1" t="n"/>
-      <c r="AL24" s="1" t="n"/>
-      <c r="AM24" s="1" t="n"/>
-      <c r="AN24" s="1" t="n"/>
-      <c r="AO24" s="1" t="n"/>
-      <c r="AP24" s="1" t="n"/>
-      <c r="AQ24" s="1" t="n"/>
-      <c r="AR24" s="1" t="n"/>
-      <c r="BC24" s="1" t="n"/>
-      <c r="BD24" s="1" t="n"/>
-      <c r="BE24" s="1" t="n"/>
+          <t>ランダムなト餓鬼（攻撃指示優先）を最大5体消去し、敵に【特小＋＋】ダメージを与える
+消去時のブレイクゲージ減少量が【2倍】になる</t>
+        </is>
+      </c>
+      <c r="O24" s="1" t="inlineStr">
+        <is>
+          <t>507,74</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
+      <c r="T24" s="2" t="n"/>
+      <c r="U24" s="2" t="n"/>
+      <c r="V24" s="2" t="n"/>
+      <c r="W24" s="2" t="n"/>
+      <c r="X24" s="2" t="n"/>
+      <c r="Y24" s="2" t="n"/>
+      <c r="Z24" s="2" t="n"/>
+      <c r="AA24" s="2" t="n"/>
+      <c r="AB24" s="2" t="n"/>
+      <c r="AC24" s="2" t="n"/>
+      <c r="AD24" s="2" t="n"/>
+      <c r="AE24" s="2" t="n"/>
+      <c r="AF24" s="2" t="n"/>
+      <c r="AG24" s="2" t="n"/>
+      <c r="AH24" s="2" t="n"/>
+      <c r="AI24" s="2" t="n"/>
+      <c r="AJ24" s="2" t="n"/>
+      <c r="AK24" s="2" t="n"/>
+      <c r="AL24" s="2" t="n"/>
+      <c r="AM24" s="2" t="n"/>
+      <c r="AN24" s="2" t="n"/>
+      <c r="AO24" s="2" t="n"/>
+      <c r="AP24" s="2" t="n"/>
+      <c r="AQ24" s="2" t="n"/>
+      <c r="AR24" s="2" t="n"/>
+      <c r="BC24" s="2" t="n"/>
+      <c r="BD24" s="2" t="n"/>
+      <c r="BE24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>大和守安定</t>
+          <t>宗三左文字</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2491,7 +2559,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>新選組</t>
+          <t>蝶</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2500,22 +2568,21 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>霧散斬り ボムの型</t>
+          <t>攪乱戦術・黄</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ランダムな孤立した青ト餓鬼を【最大3体】消去し、敵に【特小＋】ダメージを与える
-ボムを【1個】生成する</t>
+          <t>【最大10体】の黄ト餓鬼を盤面の中央に集める</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>467,57</t>
+          <t>493,54</t>
         </is>
       </c>
       <c r="P25" s="1" t="n"/>
@@ -2563,11 +2630,11 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>歌仙兼定</t>
+          <t>小夜左文字</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2577,12 +2644,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>短刀</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>花</t>
+          <t>夜</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2591,21 +2658,21 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>水平一刀斬り</t>
+          <t>正円斬り 追撃の型</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小－】ダメージを与える</t>
+          <t>【円型・特小範囲】のト餓鬼を消去し、敵に【中】ダメージを与える。乱舞ぎりタイム中はさらにダメージ上昇。</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>475,70</t>
+          <t>417,81</t>
         </is>
       </c>
       <c r="P26" s="1" t="n"/>
@@ -2653,11 +2720,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>歌仙兼定</t>
+          <t>加州清光</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2665,11 +2732,6 @@
           <t>戦装束</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>打刀</t>
@@ -2677,7 +2739,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>詠み人,花</t>
+          <t>新選組</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2686,27 +2748,27 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>くちなしの挽歌</t>
+          <t>必中三段斬り</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>指定した【縦列・小範囲】のト餓鬼を、黄色に変化させる</t>
-        </is>
-      </c>
-      <c r="O27" s="1" t="inlineStr">
-        <is>
-          <t>492,74</t>
-        </is>
-      </c>
+          <t>指定した【円型・特小範囲】のト餓鬼を3回消去し、敵に【小】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O27" s="1" t="n"/>
       <c r="P27" s="1" t="n"/>
       <c r="Q27" s="1" t="n"/>
       <c r="R27" s="1" t="n"/>
-      <c r="S27" s="1" t="n"/>
+      <c r="S27" s="1" t="inlineStr">
+        <is>
+          <t>645,73</t>
+        </is>
+      </c>
       <c r="T27" s="1" t="n"/>
       <c r="U27" s="1" t="n"/>
       <c r="V27" s="1" t="n"/>
@@ -2732,27 +2794,17 @@
       <c r="AP27" s="1" t="n"/>
       <c r="AQ27" s="1" t="n"/>
       <c r="AR27" s="1" t="n"/>
-      <c r="AS27" s="5" t="n"/>
-      <c r="AT27" s="5" t="n"/>
-      <c r="AU27" s="5" t="n"/>
-      <c r="AV27" s="5" t="n"/>
-      <c r="AW27" s="5" t="n"/>
-      <c r="AX27" s="5" t="n"/>
-      <c r="AY27" s="5" t="n"/>
-      <c r="AZ27" s="5" t="n"/>
-      <c r="BA27" s="5" t="n"/>
-      <c r="BB27" s="5" t="n"/>
-      <c r="BC27" s="2" t="n"/>
-      <c r="BD27" s="2" t="n"/>
-      <c r="BE27" s="2" t="n"/>
+      <c r="BC27" s="1" t="n"/>
+      <c r="BD27" s="1" t="n"/>
+      <c r="BE27" s="1" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>和泉守兼定</t>
+          <t>大和守安定</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2776,19 +2828,24 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>正円二段斬り</t>
+          <t>霧散斬り ボムの型</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>ランダムな場所の【円型・小範囲】のト餓鬼を2回消去し、敵に【中】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O28" s="1" t="n"/>
+          <t>ランダムな孤立した青ト餓鬼を【最大3体】消去し、敵に【特小＋】ダメージを与える
+ボムを【1個】生成する</t>
+        </is>
+      </c>
+      <c r="O28" s="1" t="inlineStr">
+        <is>
+          <t>467,57</t>
+        </is>
+      </c>
       <c r="P28" s="1" t="n"/>
       <c r="Q28" s="1" t="n"/>
       <c r="R28" s="1" t="n"/>
@@ -2807,11 +2864,7 @@
       <c r="AE28" s="1" t="n"/>
       <c r="AF28" s="1" t="n"/>
       <c r="AG28" s="1" t="n"/>
-      <c r="AH28" s="1" t="inlineStr">
-        <is>
-          <t>1551,188</t>
-        </is>
-      </c>
+      <c r="AH28" s="1" t="n"/>
       <c r="AI28" s="1" t="n"/>
       <c r="AJ28" s="1" t="n"/>
       <c r="AK28" s="1" t="n"/>
@@ -2822,17 +2875,27 @@
       <c r="AP28" s="1" t="n"/>
       <c r="AQ28" s="1" t="n"/>
       <c r="AR28" s="1" t="n"/>
-      <c r="BC28" s="1" t="n"/>
-      <c r="BD28" s="1" t="n"/>
-      <c r="BE28" s="1" t="n"/>
+      <c r="AS28" s="5" t="n"/>
+      <c r="AT28" s="5" t="n"/>
+      <c r="AU28" s="5" t="n"/>
+      <c r="AV28" s="5" t="n"/>
+      <c r="AW28" s="5" t="n"/>
+      <c r="AX28" s="5" t="n"/>
+      <c r="AY28" s="5" t="n"/>
+      <c r="AZ28" s="5" t="n"/>
+      <c r="BA28" s="5" t="n"/>
+      <c r="BB28" s="5" t="n"/>
+      <c r="BC28" s="2" t="n"/>
+      <c r="BD28" s="2" t="n"/>
+      <c r="BE28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>陸奥守吉行</t>
+          <t>歌仙兼定</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2847,29 +2910,32 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>海</t>
+          <t>花</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>黄</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>水平斬り 攻勢の型</t>
+          <t>水平一刀斬り</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【極小】ダメージを与える
-味方全員に攻撃力上昇【極小＋＋・3手】を付与する</t>
-        </is>
-      </c>
-      <c r="O29" s="1" t="n"/>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小－】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O29" s="1" t="inlineStr">
+        <is>
+          <t>475,70</t>
+        </is>
+      </c>
       <c r="P29" s="1" t="n"/>
       <c r="Q29" s="1" t="n"/>
       <c r="R29" s="1" t="n"/>
@@ -2898,26 +2964,28 @@
       <c r="AO29" s="1" t="n"/>
       <c r="AP29" s="1" t="n"/>
       <c r="AQ29" s="1" t="n"/>
-      <c r="AR29" s="1" t="inlineStr">
-        <is>
-          <t>1575,228</t>
-        </is>
-      </c>
-      <c r="BC29" s="1" t="n"/>
-      <c r="BD29" s="1" t="n"/>
-      <c r="BE29" s="1" t="inlineStr">
-        <is>
-          <t>[黄の絵具,1][書き物道具,2][花札,2][天ぷら,2][そろばん,2][打刀の心得,1]</t>
-        </is>
-      </c>
+      <c r="AR29" s="1" t="n"/>
+      <c r="AS29" s="5" t="n"/>
+      <c r="AT29" s="5" t="n"/>
+      <c r="AU29" s="5" t="n"/>
+      <c r="AV29" s="5" t="n"/>
+      <c r="AW29" s="5" t="n"/>
+      <c r="AX29" s="5" t="n"/>
+      <c r="AY29" s="5" t="n"/>
+      <c r="AZ29" s="5" t="n"/>
+      <c r="BA29" s="5" t="n"/>
+      <c r="BB29" s="5" t="n"/>
+      <c r="BC29" s="2" t="n"/>
+      <c r="BD29" s="2" t="n"/>
+      <c r="BE29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>山姥切国広</t>
+          <t>歌仙兼定</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2925,6 +2993,11 @@
           <t>戦装束</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>打刀</t>
@@ -2932,28 +3005,32 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>兄弟</t>
+          <t>詠み人,花</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>青</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>正円一刀斬り</t>
+          <t>くちなしの挽歌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>【円型・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O30" s="1" t="n"/>
+          <t>指定した【縦列・小範囲】のト餓鬼を、黄色に変化させる</t>
+        </is>
+      </c>
+      <c r="O30" s="1" t="inlineStr">
+        <is>
+          <t>492,74</t>
+        </is>
+      </c>
       <c r="P30" s="1" t="n"/>
       <c r="Q30" s="1" t="n"/>
       <c r="R30" s="1" t="n"/>
@@ -2962,11 +3039,7 @@
       <c r="U30" s="1" t="n"/>
       <c r="V30" s="1" t="n"/>
       <c r="W30" s="1" t="n"/>
-      <c r="X30" s="1" t="inlineStr">
-        <is>
-          <t>850,107</t>
-        </is>
-      </c>
+      <c r="X30" s="1" t="n"/>
       <c r="Y30" s="1" t="n"/>
       <c r="Z30" s="1" t="n"/>
       <c r="AA30" s="1" t="n"/>
@@ -2987,17 +3060,27 @@
       <c r="AP30" s="1" t="n"/>
       <c r="AQ30" s="1" t="n"/>
       <c r="AR30" s="1" t="n"/>
-      <c r="BC30" s="1" t="n"/>
-      <c r="BD30" s="1" t="n"/>
-      <c r="BE30" s="1" t="n"/>
+      <c r="AS30" s="5" t="n"/>
+      <c r="AT30" s="5" t="n"/>
+      <c r="AU30" s="5" t="n"/>
+      <c r="AV30" s="5" t="n"/>
+      <c r="AW30" s="5" t="n"/>
+      <c r="AX30" s="5" t="n"/>
+      <c r="AY30" s="5" t="n"/>
+      <c r="AZ30" s="5" t="n"/>
+      <c r="BA30" s="5" t="n"/>
+      <c r="BB30" s="5" t="n"/>
+      <c r="BC30" s="2" t="n"/>
+      <c r="BD30" s="2" t="n"/>
+      <c r="BE30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>山伏国広</t>
+          <t>和泉守兼定</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3007,12 +3090,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>お山修行</t>
+          <t>新選組</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3021,24 +3104,19 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>逆さ扇斬り 守護の型</t>
+          <t>正円二段斬り</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>【扇型・特小範囲】のト餓鬼を消去し、敵に【極小＋】ダメージを与える
-味方全員に被ダメージ軽減【特小＋＋・3手】を付与する</t>
-        </is>
-      </c>
-      <c r="O31" s="1" t="inlineStr">
-        <is>
-          <t>584,70</t>
-        </is>
-      </c>
+          <t>ランダムな場所の【円型・小範囲】のト餓鬼を2回消去し、敵に【中】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O31" s="1" t="n"/>
       <c r="P31" s="1" t="n"/>
       <c r="Q31" s="1" t="n"/>
       <c r="R31" s="1" t="n"/>
@@ -3057,7 +3135,11 @@
       <c r="AE31" s="1" t="n"/>
       <c r="AF31" s="1" t="n"/>
       <c r="AG31" s="1" t="n"/>
-      <c r="AH31" s="1" t="n"/>
+      <c r="AH31" s="1" t="inlineStr">
+        <is>
+          <t>1551,188</t>
+        </is>
+      </c>
       <c r="AI31" s="1" t="n"/>
       <c r="AJ31" s="1" t="n"/>
       <c r="AK31" s="1" t="n"/>
@@ -3074,11 +3156,11 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>獅子王</t>
+          <t>陸奥守吉行</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3088,41 +3170,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>けもの</t>
+          <t>海</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>黄</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>水平一刀斬り</t>
+          <t>水平斬り 攻勢の型</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【極小】ダメージを与える
+味方全員に攻撃力上昇【極小＋＋・3手】を付与する</t>
         </is>
       </c>
       <c r="O32" s="1" t="n"/>
       <c r="P32" s="1" t="n"/>
       <c r="Q32" s="1" t="n"/>
       <c r="R32" s="1" t="n"/>
-      <c r="S32" s="1" t="inlineStr">
-        <is>
-          <t>771,74</t>
-        </is>
-      </c>
+      <c r="S32" s="1" t="n"/>
       <c r="T32" s="1" t="n"/>
       <c r="U32" s="1" t="n"/>
       <c r="V32" s="1" t="n"/>
@@ -3147,18 +3226,26 @@
       <c r="AO32" s="1" t="n"/>
       <c r="AP32" s="1" t="n"/>
       <c r="AQ32" s="1" t="n"/>
-      <c r="AR32" s="1" t="n"/>
+      <c r="AR32" s="1" t="inlineStr">
+        <is>
+          <t>1575,228</t>
+        </is>
+      </c>
       <c r="BC32" s="1" t="n"/>
       <c r="BD32" s="1" t="n"/>
-      <c r="BE32" s="1" t="n"/>
+      <c r="BE32" s="1" t="inlineStr">
+        <is>
+          <t>[黄の絵具,1][書き物道具,2][花札,2][天ぷら,2][そろばん,2][打刀の心得,1]</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>鶴丸国永</t>
+          <t>山姥切国広</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3168,31 +3255,30 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>兄弟</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>青</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>水平斬り 攻勢の型</t>
+          <t>正円一刀斬り</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>【横列・中範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える
-自身に攻撃力上昇【極小・1手】を付与する</t>
+          <t>【円型・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
         </is>
       </c>
       <c r="O33" s="1" t="n"/>
@@ -3206,7 +3292,7 @@
       <c r="W33" s="1" t="n"/>
       <c r="X33" s="1" t="inlineStr">
         <is>
-          <t>935,110</t>
+          <t>850,107</t>
         </is>
       </c>
       <c r="Y33" s="1" t="n"/>
@@ -3234,9 +3320,12 @@
       <c r="BE33" s="1" t="n"/>
     </row>
     <row r="34">
+      <c r="A34" t="n">
+        <v>97</v>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>大倶利伽羅</t>
+          <t>山伏国広</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3246,12 +3335,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>太刀</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>龍</t>
+          <t>お山修行</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3260,22 +3349,22 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>三段斬り 攻勢の型</t>
+          <t>逆さ扇斬り 守護の型</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>ランダムな【円型・特小範囲】のト餓鬼を3回消去し、敵に【小－】ダメージを与える
-自身にクリティカル率上昇【極小＋＋・1手】を付与する</t>
+          <t>【扇型・特小範囲】のト餓鬼を消去し、敵に【極小＋】ダメージを与える
+味方全員に被ダメージ軽減【特小＋＋・3手】を付与する</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>455,72</t>
+          <t>584,70</t>
         </is>
       </c>
       <c r="P34" s="1" t="n"/>
@@ -3307,24 +3396,17 @@
       <c r="AP34" s="1" t="n"/>
       <c r="AQ34" s="1" t="n"/>
       <c r="AR34" s="1" t="n"/>
-      <c r="AS34" s="5" t="n"/>
-      <c r="AT34" s="5" t="n"/>
-      <c r="AU34" s="5" t="n"/>
-      <c r="AV34" s="5" t="n"/>
-      <c r="AW34" s="5" t="n"/>
-      <c r="AX34" s="5" t="n"/>
-      <c r="AY34" s="5" t="n"/>
-      <c r="AZ34" s="5" t="n"/>
-      <c r="BA34" s="5" t="n"/>
-      <c r="BB34" s="5" t="n"/>
-      <c r="BC34" s="2" t="n"/>
-      <c r="BD34" s="2" t="n"/>
-      <c r="BE34" s="2" t="n"/>
+      <c r="BC34" s="1" t="n"/>
+      <c r="BD34" s="1" t="n"/>
+      <c r="BE34" s="1" t="n"/>
     </row>
     <row r="35">
+      <c r="A35" t="n">
+        <v>122</v>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>へし切長谷部</t>
+          <t>獅子王</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3334,12 +3416,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>太刀</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>もの斬り</t>
+          <t>けもの</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3348,27 +3430,27 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>必中二段斬り</t>
+          <t>水平一刀斬り</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>指定した【縦列・小範囲】のト餓鬼を2回消去し、敵に【小＋】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O35" s="1" t="inlineStr">
-        <is>
-          <t>530,65</t>
-        </is>
-      </c>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O35" s="1" t="n"/>
       <c r="P35" s="1" t="n"/>
       <c r="Q35" s="1" t="n"/>
       <c r="R35" s="1" t="n"/>
-      <c r="S35" s="1" t="n"/>
+      <c r="S35" s="1" t="inlineStr">
+        <is>
+          <t>771,74</t>
+        </is>
+      </c>
       <c r="T35" s="1" t="n"/>
       <c r="U35" s="1" t="n"/>
       <c r="V35" s="1" t="n"/>
@@ -3394,24 +3476,17 @@
       <c r="AP35" s="1" t="n"/>
       <c r="AQ35" s="1" t="n"/>
       <c r="AR35" s="1" t="n"/>
-      <c r="AS35" s="5" t="n"/>
-      <c r="AT35" s="5" t="n"/>
-      <c r="AU35" s="5" t="n"/>
-      <c r="AV35" s="5" t="n"/>
-      <c r="AW35" s="5" t="n"/>
-      <c r="AX35" s="5" t="n"/>
-      <c r="AY35" s="5" t="n"/>
-      <c r="AZ35" s="5" t="n"/>
-      <c r="BA35" s="5" t="n"/>
-      <c r="BB35" s="5" t="n"/>
-      <c r="BC35" s="2" t="n"/>
-      <c r="BD35" s="2" t="n"/>
-      <c r="BE35" s="2" t="n"/>
+      <c r="BC35" s="1" t="n"/>
+      <c r="BD35" s="1" t="n"/>
+      <c r="BE35" s="1" t="n"/>
     </row>
     <row r="36">
+      <c r="A36" t="n">
+        <v>130</v>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>同田貫正国</t>
+          <t>鶴丸国永</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3421,12 +3496,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>太刀</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>もの斬り</t>
+          <t>鳥</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3435,23 +3510,20 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>真っ向一刀斬り</t>
+          <t>水平斬り 攻勢の型</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>【縦列・小範囲】のト餓鬼を消去し、敵に【小＋＋】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O36" s="1" t="inlineStr">
-        <is>
-          <t>453,75</t>
-        </is>
-      </c>
+          <t>【横列・中範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える
+自身に攻撃力上昇【極小・1手】を付与する</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="n"/>
       <c r="P36" s="1" t="n"/>
       <c r="Q36" s="1" t="n"/>
       <c r="R36" s="1" t="n"/>
@@ -3460,7 +3532,11 @@
       <c r="U36" s="1" t="n"/>
       <c r="V36" s="1" t="n"/>
       <c r="W36" s="1" t="n"/>
-      <c r="X36" s="1" t="n"/>
+      <c r="X36" s="1" t="inlineStr">
+        <is>
+          <t>935,110</t>
+        </is>
+      </c>
       <c r="Y36" s="1" t="n"/>
       <c r="Z36" s="1" t="n"/>
       <c r="AA36" s="1" t="n"/>
@@ -3481,22 +3557,55 @@
       <c r="AP36" s="1" t="n"/>
       <c r="AQ36" s="1" t="n"/>
       <c r="AR36" s="1" t="n"/>
-      <c r="AS36" s="5" t="n"/>
-      <c r="AT36" s="5" t="n"/>
-      <c r="AU36" s="5" t="n"/>
-      <c r="AV36" s="5" t="n"/>
-      <c r="AW36" s="5" t="n"/>
-      <c r="AX36" s="5" t="n"/>
-      <c r="AY36" s="5" t="n"/>
-      <c r="AZ36" s="5" t="n"/>
-      <c r="BA36" s="5" t="n"/>
-      <c r="BB36" s="5" t="n"/>
-      <c r="BC36" s="2" t="n"/>
-      <c r="BD36" s="2" t="n"/>
-      <c r="BE36" s="2" t="n"/>
+      <c r="BC36" s="1" t="n"/>
+      <c r="BD36" s="1" t="n"/>
+      <c r="BE36" s="1" t="n"/>
     </row>
     <row r="37">
-      <c r="O37" s="1" t="n"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>大倶利伽羅</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>打刀</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>龍</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>24</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>三段斬り 攻勢の型</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ランダムな【円型・特小範囲】のト餓鬼を3回消去し、敵に【小－】ダメージを与える
+自身にクリティカル率上昇【極小＋＋・1手】を付与する</t>
+        </is>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>455,72</t>
+        </is>
+      </c>
       <c r="P37" s="1" t="n"/>
       <c r="Q37" s="1" t="n"/>
       <c r="R37" s="1" t="n"/>
@@ -3526,12 +3635,64 @@
       <c r="AP37" s="1" t="n"/>
       <c r="AQ37" s="1" t="n"/>
       <c r="AR37" s="1" t="n"/>
-      <c r="BC37" s="1" t="n"/>
-      <c r="BD37" s="1" t="n"/>
-      <c r="BE37" s="1" t="n"/>
+      <c r="AS37" s="5" t="n"/>
+      <c r="AT37" s="5" t="n"/>
+      <c r="AU37" s="5" t="n"/>
+      <c r="AV37" s="5" t="n"/>
+      <c r="AW37" s="5" t="n"/>
+      <c r="AX37" s="5" t="n"/>
+      <c r="AY37" s="5" t="n"/>
+      <c r="AZ37" s="5" t="n"/>
+      <c r="BA37" s="5" t="n"/>
+      <c r="BB37" s="5" t="n"/>
+      <c r="BC37" s="2" t="n"/>
+      <c r="BD37" s="2" t="n"/>
+      <c r="BE37" s="2" t="n"/>
     </row>
     <row r="38">
-      <c r="O38" s="1" t="n"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>へし切長谷部</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>打刀</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>もの斬り</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>27</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>必中二段斬り</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>指定した【縦列・小範囲】のト餓鬼を2回消去し、敵に【小＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>530,65</t>
+        </is>
+      </c>
       <c r="P38" s="1" t="n"/>
       <c r="Q38" s="1" t="n"/>
       <c r="R38" s="1" t="n"/>
@@ -3561,12 +3722,64 @@
       <c r="AP38" s="1" t="n"/>
       <c r="AQ38" s="1" t="n"/>
       <c r="AR38" s="1" t="n"/>
-      <c r="BC38" s="1" t="n"/>
-      <c r="BD38" s="1" t="n"/>
-      <c r="BE38" s="1" t="n"/>
+      <c r="AS38" s="5" t="n"/>
+      <c r="AT38" s="5" t="n"/>
+      <c r="AU38" s="5" t="n"/>
+      <c r="AV38" s="5" t="n"/>
+      <c r="AW38" s="5" t="n"/>
+      <c r="AX38" s="5" t="n"/>
+      <c r="AY38" s="5" t="n"/>
+      <c r="AZ38" s="5" t="n"/>
+      <c r="BA38" s="5" t="n"/>
+      <c r="BB38" s="5" t="n"/>
+      <c r="BC38" s="2" t="n"/>
+      <c r="BD38" s="2" t="n"/>
+      <c r="BE38" s="2" t="n"/>
     </row>
     <row r="39">
-      <c r="O39" s="1" t="n"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>同田貫正国</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>打刀</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>もの斬り</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>22</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>真っ向一刀斬り</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>【縦列・小範囲】のト餓鬼を消去し、敵に【小＋＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t>453,75</t>
+        </is>
+      </c>
       <c r="P39" s="1" t="n"/>
       <c r="Q39" s="1" t="n"/>
       <c r="R39" s="1" t="n"/>
@@ -3596,12 +3809,64 @@
       <c r="AP39" s="1" t="n"/>
       <c r="AQ39" s="1" t="n"/>
       <c r="AR39" s="1" t="n"/>
-      <c r="BC39" s="1" t="n"/>
-      <c r="BD39" s="1" t="n"/>
-      <c r="BE39" s="1" t="n"/>
+      <c r="AS39" s="5" t="n"/>
+      <c r="AT39" s="5" t="n"/>
+      <c r="AU39" s="5" t="n"/>
+      <c r="AV39" s="5" t="n"/>
+      <c r="AW39" s="5" t="n"/>
+      <c r="AX39" s="5" t="n"/>
+      <c r="AY39" s="5" t="n"/>
+      <c r="AZ39" s="5" t="n"/>
+      <c r="BA39" s="5" t="n"/>
+      <c r="BB39" s="5" t="n"/>
+      <c r="BC39" s="2" t="n"/>
+      <c r="BD39" s="2" t="n"/>
+      <c r="BE39" s="2" t="n"/>
     </row>
     <row r="40">
-      <c r="O40" s="1" t="n"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>蜂須賀虎徹</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>打刀</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>兄弟</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>16</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>霧散斬り 掃討の型</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>孤立したト餓鬼をランダムに【最大5体】消去し、敵に【特小＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>481,71</t>
+        </is>
+      </c>
       <c r="P40" s="1" t="n"/>
       <c r="Q40" s="1" t="n"/>
       <c r="R40" s="1" t="n"/>
@@ -3631,12 +3896,65 @@
       <c r="AP40" s="1" t="n"/>
       <c r="AQ40" s="1" t="n"/>
       <c r="AR40" s="1" t="n"/>
-      <c r="BC40" s="1" t="n"/>
-      <c r="BD40" s="1" t="n"/>
-      <c r="BE40" s="1" t="n"/>
+      <c r="AS40" s="5" t="n"/>
+      <c r="AT40" s="5" t="n"/>
+      <c r="AU40" s="5" t="n"/>
+      <c r="AV40" s="5" t="n"/>
+      <c r="AW40" s="5" t="n"/>
+      <c r="AX40" s="5" t="n"/>
+      <c r="AY40" s="5" t="n"/>
+      <c r="AZ40" s="5" t="n"/>
+      <c r="BA40" s="5" t="n"/>
+      <c r="BB40" s="5" t="n"/>
+      <c r="BC40" s="2" t="n"/>
+      <c r="BD40" s="2" t="n"/>
+      <c r="BE40" s="2" t="n"/>
     </row>
     <row r="41">
-      <c r="O41" s="1" t="n"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>燭台切光忠</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>太刀</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>もの斬り</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>27</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>必中縦断斬り ボムの型</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>指定した【縦列・小範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える
+ボムを【1個】生成する</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>547,66</t>
+        </is>
+      </c>
       <c r="P41" s="1" t="n"/>
       <c r="Q41" s="1" t="n"/>
       <c r="R41" s="1" t="n"/>
@@ -3666,9 +3984,19 @@
       <c r="AP41" s="1" t="n"/>
       <c r="AQ41" s="1" t="n"/>
       <c r="AR41" s="1" t="n"/>
-      <c r="BC41" s="1" t="n"/>
-      <c r="BD41" s="1" t="n"/>
-      <c r="BE41" s="1" t="n"/>
+      <c r="AS41" s="5" t="n"/>
+      <c r="AT41" s="5" t="n"/>
+      <c r="AU41" s="5" t="n"/>
+      <c r="AV41" s="5" t="n"/>
+      <c r="AW41" s="5" t="n"/>
+      <c r="AX41" s="5" t="n"/>
+      <c r="AY41" s="5" t="n"/>
+      <c r="AZ41" s="5" t="n"/>
+      <c r="BA41" s="5" t="n"/>
+      <c r="BB41" s="5" t="n"/>
+      <c r="BC41" s="2" t="n"/>
+      <c r="BD41" s="2" t="n"/>
+      <c r="BE41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="O42" s="1" t="n"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -831,11 +831,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>三日月宗近</t>
+          <t>今剣</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -845,10 +845,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>太刀</t>
-        </is>
-      </c>
-      <c r="O3" s="1" t="n"/>
+          <t>短刀</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>源氏</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>色変幻の術・赤</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>赤以外のト餓鬼を【最大10体】、赤色に変換する</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>459,74</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="n"/>
       <c r="Q3" s="1" t="n"/>
       <c r="R3" s="1" t="n"/>
@@ -878,9 +905,19 @@
       <c r="AP3" s="1" t="n"/>
       <c r="AQ3" s="1" t="n"/>
       <c r="AR3" s="1" t="n"/>
-      <c r="BC3" s="1" t="n"/>
-      <c r="BD3" s="1" t="n"/>
-      <c r="BE3" s="1" t="n"/>
+      <c r="AS3" s="5" t="n"/>
+      <c r="AT3" s="5" t="n"/>
+      <c r="AU3" s="5" t="n"/>
+      <c r="AV3" s="5" t="n"/>
+      <c r="AW3" s="5" t="n"/>
+      <c r="AX3" s="5" t="n"/>
+      <c r="AY3" s="5" t="n"/>
+      <c r="AZ3" s="5" t="n"/>
+      <c r="BA3" s="5" t="n"/>
+      <c r="BB3" s="5" t="n"/>
+      <c r="BC3" s="2" t="n"/>
+      <c r="BD3" s="2" t="n"/>
+      <c r="BE3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -896,37 +933,9 @@
           <t>戦装束</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>太刀</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>夜,天下五剣</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>赤</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>月明かりの冴え</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>【すべて】のト餓鬼を消去し、敵に【特小++】ダメージを与える</t>
         </is>
       </c>
       <c r="O4" s="1" t="n"/>
@@ -941,11 +950,7 @@
       <c r="X4" s="1" t="n"/>
       <c r="Y4" s="1" t="n"/>
       <c r="Z4" s="1" t="n"/>
-      <c r="AA4" s="1" t="inlineStr">
-        <is>
-          <t>1060,140</t>
-        </is>
-      </c>
+      <c r="AA4" s="1" t="n"/>
       <c r="AB4" s="1" t="n"/>
       <c r="AC4" s="1" t="n"/>
       <c r="AD4" s="1" t="n"/>
@@ -969,11 +974,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>小狐丸</t>
+          <t>三日月宗近</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,6 +986,11 @@
           <t>戦装束</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>太刀</t>
@@ -988,7 +998,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>けもの</t>
+          <t>夜,天下五剣</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -997,27 +1007,23 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ボム練成の術 三の火</t>
+          <t>月明かりの冴え</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ボムを【3個】生成する</t>
+          <t>【すべて】のト餓鬼を消去し、敵に【特小++】ダメージを与える</t>
         </is>
       </c>
       <c r="O5" s="1" t="n"/>
       <c r="P5" s="1" t="n"/>
       <c r="Q5" s="1" t="n"/>
       <c r="R5" s="1" t="n"/>
-      <c r="S5" s="1" t="inlineStr">
-        <is>
-          <t>740,77</t>
-        </is>
-      </c>
+      <c r="S5" s="1" t="n"/>
       <c r="T5" s="1" t="n"/>
       <c r="U5" s="1" t="n"/>
       <c r="V5" s="1" t="n"/>
@@ -1025,7 +1031,11 @@
       <c r="X5" s="1" t="n"/>
       <c r="Y5" s="1" t="n"/>
       <c r="Z5" s="1" t="n"/>
-      <c r="AA5" s="1" t="n"/>
+      <c r="AA5" s="1" t="inlineStr">
+        <is>
+          <t>1060,140</t>
+        </is>
+      </c>
       <c r="AB5" s="1" t="n"/>
       <c r="AC5" s="1" t="n"/>
       <c r="AD5" s="1" t="n"/>
@@ -1049,11 +1059,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>石切丸</t>
+          <t>小狐丸</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1063,59 +1073,50 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>大太刀</t>
+          <t>太刀</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ご神刀</t>
+          <t>けもの</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>青</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>逆さ扇斬り 守護の型</t>
+          <t>ボム練成の術 三の火</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>【扇型・中範囲】のト餓鬼を消去し、敵に【特小－】ダメージを与える。
-味方全員に被ダメージ軽減【極小＋・3手】を付与する</t>
+          <t>ボムを【3個】生成する</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>561,61</t>
+          <t>556,58</t>
         </is>
       </c>
       <c r="P6" s="1" t="n"/>
       <c r="Q6" s="1" t="n"/>
-      <c r="R6" s="1" t="inlineStr">
-        <is>
-          <t>700,76</t>
-        </is>
-      </c>
-      <c r="S6" s="1" t="n"/>
+      <c r="R6" s="1" t="n"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>740,77</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="n"/>
       <c r="U6" s="1" t="n"/>
-      <c r="V6" s="1" t="inlineStr">
-        <is>
-          <t>886,96</t>
-        </is>
-      </c>
+      <c r="V6" s="1" t="n"/>
       <c r="W6" s="1" t="n"/>
-      <c r="X6" s="1" t="inlineStr">
-        <is>
-          <t>979,106</t>
-        </is>
-      </c>
+      <c r="X6" s="1" t="n"/>
       <c r="Y6" s="1" t="n"/>
       <c r="Z6" s="1" t="n"/>
       <c r="AA6" s="1" t="n"/>
@@ -1142,11 +1143,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>岩融</t>
+          <t>石切丸</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1156,12 +1157,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>薙刀</t>
+          <t>大太刀</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>源氏</t>
+          <t>ご神刀</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1170,31 +1171,76 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>大薙ぎ払い・赤</t>
+          <t>逆さ扇斬り 守護の型</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>【最大10体】の赤ト餓鬼を盤面の右下に集める</t>
+          <t>【扇型・中範囲】のト餓鬼を消去し、敵に【特小－】ダメージを与える。
+味方全員に被ダメージ軽減【極小＋・3手】を付与する</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>471,69</t>
-        </is>
-      </c>
+          <t>561,61</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>700,76</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>886,96</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="inlineStr">
+        <is>
+          <t>979,106</t>
+        </is>
+      </c>
+      <c r="Y7" s="5" t="n"/>
+      <c r="Z7" s="5" t="n"/>
+      <c r="AA7" s="5" t="n"/>
+      <c r="AB7" s="5" t="n"/>
+      <c r="AC7" s="5" t="n"/>
+      <c r="AD7" s="5" t="n"/>
+      <c r="AE7" s="5" t="n"/>
+      <c r="AF7" s="5" t="n"/>
+      <c r="AG7" s="5" t="n"/>
+      <c r="AH7" s="5" t="n"/>
+      <c r="AI7" s="5" t="n"/>
+      <c r="AJ7" s="5" t="n"/>
+      <c r="AK7" s="5" t="n"/>
+      <c r="AL7" s="5" t="n"/>
+      <c r="AM7" s="5" t="n"/>
+      <c r="AN7" s="5" t="n"/>
+      <c r="AO7" s="5" t="n"/>
+      <c r="AP7" s="5" t="n"/>
+      <c r="AQ7" s="5" t="n"/>
+      <c r="AR7" s="5" t="n"/>
+      <c r="BC7" s="5" t="n"/>
+      <c r="BD7" s="5" t="n"/>
+      <c r="BE7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>鳴狐</t>
+          <t>岩融</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1204,81 +1250,77 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>薙刀</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>けもの</t>
+          <t>源氏</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>青</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ボム練成の術 二の火</t>
+          <t>大薙ぎ払い・赤</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ボムを【2個】生成する</t>
-        </is>
-      </c>
-      <c r="O8" s="1" t="n"/>
-      <c r="P8" s="1" t="n"/>
-      <c r="Q8" s="1" t="n"/>
-      <c r="R8" s="1" t="n"/>
-      <c r="S8" s="1" t="n"/>
-      <c r="T8" s="1" t="n"/>
-      <c r="U8" s="1" t="n"/>
-      <c r="V8" s="1" t="n"/>
-      <c r="W8" s="1" t="n"/>
-      <c r="X8" s="1" t="n"/>
-      <c r="Y8" s="1" t="n"/>
-      <c r="Z8" s="1" t="n"/>
-      <c r="AA8" s="1" t="n"/>
-      <c r="AB8" s="1" t="n"/>
-      <c r="AC8" s="1" t="n"/>
-      <c r="AD8" s="1" t="n"/>
-      <c r="AE8" s="1" t="n"/>
-      <c r="AF8" s="1" t="n"/>
-      <c r="AG8" s="1" t="n"/>
-      <c r="AH8" s="1" t="n"/>
-      <c r="AI8" s="1" t="n"/>
-      <c r="AJ8" s="1" t="n"/>
-      <c r="AK8" s="1" t="n"/>
-      <c r="AL8" s="1" t="n"/>
-      <c r="AM8" s="1" t="n"/>
-      <c r="AN8" s="1" t="n"/>
-      <c r="AO8" s="1" t="n"/>
-      <c r="AP8" s="1" t="inlineStr">
-        <is>
-          <t>1505,223</t>
-        </is>
-      </c>
-      <c r="AQ8" s="1" t="inlineStr">
-        <is>
-          <t>1543,229</t>
-        </is>
-      </c>
-      <c r="AR8" s="1" t="n"/>
-      <c r="BC8" s="1" t="n"/>
-      <c r="BD8" s="1" t="n"/>
-      <c r="BE8" s="1" t="n"/>
+          <t>【最大10体】の赤ト餓鬼を盤面の右下に集める</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>471,69</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n"/>
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="n"/>
+      <c r="U8" s="2" t="n"/>
+      <c r="V8" s="2" t="n"/>
+      <c r="W8" s="2" t="n"/>
+      <c r="X8" s="2" t="n"/>
+      <c r="Y8" s="2" t="n"/>
+      <c r="Z8" s="2" t="n"/>
+      <c r="AA8" s="2" t="n"/>
+      <c r="AB8" s="2" t="n"/>
+      <c r="AC8" s="2" t="n"/>
+      <c r="AD8" s="2" t="n"/>
+      <c r="AE8" s="2" t="n"/>
+      <c r="AF8" s="2" t="n"/>
+      <c r="AG8" s="2" t="n"/>
+      <c r="AH8" s="2" t="n"/>
+      <c r="AI8" s="2" t="n"/>
+      <c r="AJ8" s="2" t="n"/>
+      <c r="AK8" s="2" t="n"/>
+      <c r="AL8" s="2" t="n"/>
+      <c r="AM8" s="2" t="n"/>
+      <c r="AN8" s="2" t="n"/>
+      <c r="AO8" s="2" t="n"/>
+      <c r="AP8" s="2" t="n"/>
+      <c r="AQ8" s="2" t="n"/>
+      <c r="AR8" s="2" t="n"/>
+      <c r="BC8" s="2" t="n"/>
+      <c r="BD8" s="2" t="n"/>
+      <c r="BE8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>一期一振</t>
+          <t>鳴狐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1288,30 +1330,30 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>兄弟</t>
+          <t>けもの</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>黄</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>水平一刀斬り</t>
+          <t>ボム練成の術 二の火</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える</t>
+          <t>ボムを【2個】生成する</t>
         </is>
       </c>
       <c r="O9" s="1" t="n"/>
@@ -1324,11 +1366,7 @@
       <c r="V9" s="1" t="n"/>
       <c r="W9" s="1" t="n"/>
       <c r="X9" s="1" t="n"/>
-      <c r="Y9" s="1" t="inlineStr">
-        <is>
-          <t>1050,108</t>
-        </is>
-      </c>
+      <c r="Y9" s="1" t="n"/>
       <c r="Z9" s="1" t="n"/>
       <c r="AA9" s="1" t="n"/>
       <c r="AB9" s="1" t="n"/>
@@ -1345,8 +1383,16 @@
       <c r="AM9" s="1" t="n"/>
       <c r="AN9" s="1" t="n"/>
       <c r="AO9" s="1" t="n"/>
-      <c r="AP9" s="1" t="n"/>
-      <c r="AQ9" s="1" t="n"/>
+      <c r="AP9" s="1" t="inlineStr">
+        <is>
+          <t>1505,223</t>
+        </is>
+      </c>
+      <c r="AQ9" s="1" t="inlineStr">
+        <is>
+          <t>1543,229</t>
+        </is>
+      </c>
       <c r="AR9" s="1" t="n"/>
       <c r="BC9" s="1" t="n"/>
       <c r="BD9" s="1" t="n"/>
@@ -1366,11 +1412,6 @@
           <t>戦装束</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>太刀</t>
@@ -1378,7 +1419,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>兄弟,炎</t>
+          <t>兄弟</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1391,109 +1432,146 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>水平一刀斬り</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="5" t="n"/>
+      <c r="V10" s="5" t="n"/>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="5" t="n"/>
+      <c r="Y10" s="5" t="inlineStr">
+        <is>
+          <t>1050,108</t>
+        </is>
+      </c>
+      <c r="Z10" s="5" t="n"/>
+      <c r="AA10" s="5" t="n"/>
+      <c r="AB10" s="5" t="n"/>
+      <c r="AC10" s="5" t="n"/>
+      <c r="AD10" s="5" t="n"/>
+      <c r="AE10" s="5" t="n"/>
+      <c r="AF10" s="5" t="n"/>
+      <c r="AG10" s="5" t="n"/>
+      <c r="AH10" s="5" t="n"/>
+      <c r="AI10" s="5" t="n"/>
+      <c r="AJ10" s="5" t="n"/>
+      <c r="AK10" s="5" t="n"/>
+      <c r="AL10" s="5" t="n"/>
+      <c r="AM10" s="5" t="n"/>
+      <c r="AN10" s="5" t="n"/>
+      <c r="AO10" s="5" t="n"/>
+      <c r="AP10" s="5" t="n"/>
+      <c r="AQ10" s="5" t="n"/>
+      <c r="AR10" s="5" t="n"/>
+      <c r="BC10" s="5" t="n"/>
+      <c r="BD10" s="5" t="n"/>
+      <c r="BE10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>一期一振</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>太刀</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>兄弟,炎</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>黄</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>22</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>華々しき雄飛への導き</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>自身・脇差・短刀にブレイク力上昇【大・6手】を付与する
 自身・脇差・短刀に攻撃力上昇【特小＋・6手】を付与する
 バリア【1回】を付与する</t>
         </is>
       </c>
-      <c r="AL10" s="5" t="inlineStr">
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n"/>
+      <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="n"/>
+      <c r="S11" s="2" t="n"/>
+      <c r="T11" s="2" t="n"/>
+      <c r="U11" s="2" t="n"/>
+      <c r="V11" s="2" t="n"/>
+      <c r="W11" s="2" t="n"/>
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="2" t="n"/>
+      <c r="Z11" s="2" t="n"/>
+      <c r="AA11" s="2" t="n"/>
+      <c r="AB11" s="2" t="n"/>
+      <c r="AC11" s="2" t="n"/>
+      <c r="AD11" s="2" t="n"/>
+      <c r="AE11" s="2" t="n"/>
+      <c r="AF11" s="2" t="n"/>
+      <c r="AG11" s="2" t="n"/>
+      <c r="AH11" s="2" t="n"/>
+      <c r="AI11" s="2" t="n"/>
+      <c r="AJ11" s="2" t="n"/>
+      <c r="AK11" s="2" t="n"/>
+      <c r="AL11" s="1" t="inlineStr">
         <is>
           <t>1673,173</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>27</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>鯰尾藤四郎</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>戦装束</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>脇差</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>兄弟</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>赤</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>15</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>大薙ぎ払い・青</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>【最大10体】の青ト餓鬼を盤面の下に集める</t>
-        </is>
-      </c>
-      <c r="O11" s="1" t="n"/>
-      <c r="P11" s="1" t="n"/>
-      <c r="Q11" s="1" t="n"/>
-      <c r="R11" s="1" t="n"/>
-      <c r="S11" s="1" t="n"/>
-      <c r="T11" s="1" t="n"/>
-      <c r="U11" s="1" t="n"/>
-      <c r="V11" s="1" t="n"/>
-      <c r="W11" s="1" t="n"/>
-      <c r="X11" s="1" t="n"/>
-      <c r="Y11" s="1" t="n"/>
-      <c r="Z11" s="1" t="n"/>
-      <c r="AA11" s="1" t="n"/>
-      <c r="AB11" s="1" t="n"/>
-      <c r="AC11" s="1" t="n"/>
-      <c r="AD11" s="1" t="n"/>
-      <c r="AE11" s="1" t="n"/>
-      <c r="AF11" s="1" t="n"/>
-      <c r="AG11" s="1" t="n"/>
-      <c r="AH11" s="1" t="n"/>
-      <c r="AI11" s="1" t="n"/>
-      <c r="AJ11" s="1" t="inlineStr">
-        <is>
-          <t>1357,188</t>
-        </is>
-      </c>
-      <c r="AK11" s="1" t="n"/>
-      <c r="AL11" s="1" t="n"/>
-      <c r="AM11" s="1" t="n"/>
-      <c r="AN11" s="1" t="n"/>
-      <c r="AO11" s="1" t="n"/>
-      <c r="AP11" s="1" t="n"/>
-      <c r="AQ11" s="1" t="n"/>
-      <c r="AR11" s="1" t="n"/>
-      <c r="BC11" s="1" t="n"/>
-      <c r="BD11" s="1" t="n"/>
-      <c r="BE11" s="1" t="n"/>
+      <c r="AM11" s="2" t="n"/>
+      <c r="AN11" s="2" t="n"/>
+      <c r="AO11" s="2" t="n"/>
+      <c r="AP11" s="2" t="n"/>
+      <c r="AQ11" s="2" t="n"/>
+      <c r="AR11" s="2" t="n"/>
+      <c r="BC11" s="2" t="n"/>
+      <c r="BD11" s="2" t="n"/>
+      <c r="BE11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>骨喰藤四郎</t>
+          <t>鯰尾藤四郎</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1513,20 +1591,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>黄</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>色変幻の術・青</t>
+          <t>大薙ぎ払い・青</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>青以外のト餓鬼を【最大10体】、青色に変換する</t>
+          <t>【最大10体】の青ト餓鬼を盤面の下に集める</t>
         </is>
       </c>
       <c r="O12" s="1" t="n"/>
@@ -1544,17 +1622,17 @@
       <c r="AA12" s="1" t="n"/>
       <c r="AB12" s="1" t="n"/>
       <c r="AC12" s="1" t="n"/>
-      <c r="AD12" s="1" t="inlineStr">
-        <is>
-          <t>1024,163</t>
-        </is>
-      </c>
+      <c r="AD12" s="1" t="n"/>
       <c r="AE12" s="1" t="n"/>
       <c r="AF12" s="1" t="n"/>
       <c r="AG12" s="1" t="n"/>
       <c r="AH12" s="1" t="n"/>
       <c r="AI12" s="1" t="n"/>
-      <c r="AJ12" s="1" t="n"/>
+      <c r="AJ12" s="1" t="inlineStr">
+        <is>
+          <t>1357,188</t>
+        </is>
+      </c>
       <c r="AK12" s="1" t="n"/>
       <c r="AL12" s="1" t="n"/>
       <c r="AM12" s="1" t="n"/>
@@ -1569,11 +1647,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>平野藤四郎</t>
+          <t>骨喰藤四郎</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1583,7 +1661,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>短刀</t>
+          <t>脇差</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1593,7 +1671,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>青</t>
+          <t>黄</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1601,12 +1679,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>色変幻の術・赤</t>
+          <t>色変幻の術・青</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>黄色のト餓鬼を【最大10体】、赤色に変換する</t>
+          <t>青以外のト餓鬼を【最大10体】、青色に変換する</t>
         </is>
       </c>
       <c r="O13" s="1" t="n"/>
@@ -1624,7 +1702,11 @@
       <c r="AA13" s="1" t="n"/>
       <c r="AB13" s="1" t="n"/>
       <c r="AC13" s="1" t="n"/>
-      <c r="AD13" s="1" t="n"/>
+      <c r="AD13" s="1" t="inlineStr">
+        <is>
+          <t>1024,163</t>
+        </is>
+      </c>
       <c r="AE13" s="1" t="n"/>
       <c r="AF13" s="1" t="n"/>
       <c r="AG13" s="1" t="n"/>
@@ -1638,22 +1720,18 @@
       <c r="AO13" s="1" t="n"/>
       <c r="AP13" s="1" t="n"/>
       <c r="AQ13" s="1" t="n"/>
-      <c r="AR13" s="1" t="inlineStr">
-        <is>
-          <t>1691,232</t>
-        </is>
-      </c>
+      <c r="AR13" s="1" t="n"/>
       <c r="BC13" s="1" t="n"/>
       <c r="BD13" s="1" t="n"/>
       <c r="BE13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>厚藤四郎</t>
+          <t>平野藤四郎</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1673,7 +1751,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>黄</t>
+          <t>青</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1681,19 +1759,15 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>色変幻の術・青</t>
+          <t>色変幻の術・赤</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>赤色のト餓鬼を【最大10体】、青色に変換する</t>
-        </is>
-      </c>
-      <c r="O14" s="1" t="inlineStr">
-        <is>
-          <t>440,77</t>
-        </is>
-      </c>
+          <t>黄色のト餓鬼を【最大10体】、赤色に変換する</t>
+        </is>
+      </c>
+      <c r="O14" s="1" t="n"/>
       <c r="P14" s="1" t="n"/>
       <c r="Q14" s="1" t="n"/>
       <c r="R14" s="1" t="n"/>
@@ -1722,18 +1796,22 @@
       <c r="AO14" s="1" t="n"/>
       <c r="AP14" s="1" t="n"/>
       <c r="AQ14" s="1" t="n"/>
-      <c r="AR14" s="1" t="n"/>
+      <c r="AR14" s="1" t="inlineStr">
+        <is>
+          <t>1691,232</t>
+        </is>
+      </c>
       <c r="BC14" s="1" t="n"/>
       <c r="BD14" s="1" t="n"/>
       <c r="BE14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>乱藤四郎</t>
+          <t>厚藤四郎</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1757,19 +1835,23 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>色変幻の術・乱</t>
+          <t>色変幻の術・青</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>ト餓鬼を【最大10体】、ランダムな色に変換する</t>
-        </is>
-      </c>
-      <c r="O15" s="1" t="n"/>
+          <t>赤色のト餓鬼を【最大10体】、青色に変換する</t>
+        </is>
+      </c>
+      <c r="O15" s="1" t="inlineStr">
+        <is>
+          <t>440,77</t>
+        </is>
+      </c>
       <c r="P15" s="1" t="n"/>
       <c r="Q15" s="1" t="n"/>
       <c r="R15" s="1" t="n"/>
@@ -1778,11 +1860,7 @@
       <c r="U15" s="1" t="n"/>
       <c r="V15" s="1" t="n"/>
       <c r="W15" s="1" t="n"/>
-      <c r="X15" s="1" t="inlineStr">
-        <is>
-          <t>905,100</t>
-        </is>
-      </c>
+      <c r="X15" s="1" t="n"/>
       <c r="Y15" s="1" t="n"/>
       <c r="Z15" s="1" t="n"/>
       <c r="AA15" s="1" t="n"/>
@@ -1821,133 +1899,165 @@
           <t>戦装束</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>短刀</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>兄弟</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>黄</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>色変幻の術・乱</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ト餓鬼を【最大10体】、ランダムな色に変換する</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+      <c r="Q16" s="5" t="n"/>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" s="5" t="n"/>
+      <c r="T16" s="5" t="n"/>
+      <c r="U16" s="5" t="n"/>
+      <c r="V16" s="5" t="n"/>
+      <c r="W16" s="5" t="n"/>
+      <c r="X16" s="5" t="inlineStr">
+        <is>
+          <t>905,100</t>
+        </is>
+      </c>
+      <c r="Y16" s="5" t="n"/>
+      <c r="Z16" s="5" t="n"/>
+      <c r="AA16" s="5" t="n"/>
+      <c r="AB16" s="5" t="n"/>
+      <c r="AC16" s="5" t="n"/>
+      <c r="AD16" s="5" t="n"/>
+      <c r="AE16" s="5" t="n"/>
+      <c r="AF16" s="5" t="n"/>
+      <c r="AG16" s="5" t="n"/>
+      <c r="AH16" s="5" t="n"/>
+      <c r="AI16" s="5" t="n"/>
+      <c r="AJ16" s="5" t="n"/>
+      <c r="AK16" s="5" t="n"/>
+      <c r="AL16" s="5" t="n"/>
+      <c r="AM16" s="5" t="n"/>
+      <c r="AN16" s="5" t="n"/>
+      <c r="AO16" s="5" t="n"/>
+      <c r="AP16" s="5" t="n"/>
+      <c r="AQ16" s="5" t="n"/>
+      <c r="AR16" s="5" t="n"/>
+      <c r="BC16" s="5" t="n"/>
+      <c r="BD16" s="5" t="n"/>
+      <c r="BE16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>45</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>乱藤四郎</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>短刀</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>兄弟,花</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>赤</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="H17" t="n">
         <v>16</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>百花乱々みだれ咲き</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>味方全員に攻撃力上昇【極小＋＋・3手】を付与する
 敵に被ダメージ増加【極小＋・3手】を付与する</t>
         </is>
       </c>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="O17" s="1" t="inlineStr">
         <is>
           <t>532,59</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>47</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>五虎退</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>戦装束</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>短刀</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>兄弟</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>赤</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>13</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>ボム練成の術 一の火</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ボムを【1個】生成する</t>
-        </is>
-      </c>
-      <c r="O17" s="1" t="inlineStr">
-        <is>
-          <t>477,56</t>
-        </is>
-      </c>
-      <c r="P17" s="1" t="n"/>
-      <c r="Q17" s="1" t="n"/>
-      <c r="R17" s="1" t="n"/>
-      <c r="S17" s="1" t="n"/>
-      <c r="T17" s="1" t="n"/>
-      <c r="U17" s="1" t="n"/>
-      <c r="V17" s="1" t="n"/>
-      <c r="W17" s="1" t="n"/>
-      <c r="X17" s="1" t="n"/>
-      <c r="Y17" s="1" t="n"/>
-      <c r="Z17" s="1" t="n"/>
-      <c r="AA17" s="1" t="n"/>
-      <c r="AB17" s="1" t="n"/>
-      <c r="AC17" s="1" t="n"/>
-      <c r="AD17" s="1" t="n"/>
-      <c r="AE17" s="1" t="n"/>
-      <c r="AF17" s="1" t="n"/>
-      <c r="AG17" s="1" t="n"/>
-      <c r="AH17" s="1" t="n"/>
-      <c r="AI17" s="1" t="n"/>
-      <c r="AJ17" s="1" t="n"/>
-      <c r="AK17" s="1" t="n"/>
-      <c r="AL17" s="1" t="n"/>
-      <c r="AM17" s="1" t="n"/>
-      <c r="AN17" s="1" t="n"/>
-      <c r="AO17" s="1" t="n"/>
-      <c r="AP17" s="1" t="n"/>
-      <c r="AQ17" s="1" t="n"/>
-      <c r="AR17" s="1" t="n"/>
-      <c r="BC17" s="1" t="n"/>
-      <c r="BD17" s="1" t="n"/>
-      <c r="BE17" s="1" t="n"/>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="n"/>
+      <c r="T17" s="2" t="n"/>
+      <c r="U17" s="2" t="n"/>
+      <c r="V17" s="2" t="n"/>
+      <c r="W17" s="2" t="n"/>
+      <c r="X17" s="2" t="n"/>
+      <c r="Y17" s="2" t="n"/>
+      <c r="Z17" s="2" t="n"/>
+      <c r="AA17" s="2" t="n"/>
+      <c r="AB17" s="2" t="n"/>
+      <c r="AC17" s="2" t="n"/>
+      <c r="AD17" s="2" t="n"/>
+      <c r="AE17" s="2" t="n"/>
+      <c r="AF17" s="2" t="n"/>
+      <c r="AG17" s="2" t="n"/>
+      <c r="AH17" s="2" t="n"/>
+      <c r="AI17" s="2" t="n"/>
+      <c r="AJ17" s="2" t="n"/>
+      <c r="AK17" s="2" t="n"/>
+      <c r="AL17" s="2" t="n"/>
+      <c r="AM17" s="2" t="n"/>
+      <c r="AN17" s="2" t="n"/>
+      <c r="AO17" s="2" t="n"/>
+      <c r="AP17" s="2" t="n"/>
+      <c r="AQ17" s="2" t="n"/>
+      <c r="AR17" s="2" t="n"/>
+      <c r="BC17" s="2" t="n"/>
+      <c r="BD17" s="2" t="n"/>
+      <c r="BE17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>太郎太刀</t>
+          <t>五虎退</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1957,12 +2067,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>大太刀</t>
+          <t>短刀</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ご神刀</t>
+          <t>兄弟</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1971,21 +2081,21 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>霧散斬り・黄</t>
+          <t>ボム練成の術 一の火</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>黄ト餓鬼をランダムに【最大10体】消去し、敵に【小＋】ダメージを与える</t>
+          <t>ボムを【1個】生成する</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>588,64</t>
+          <t>477,56</t>
         </is>
       </c>
       <c r="P18" s="5" t="n"/>
@@ -2017,16 +2127,9 @@
       <c r="AP18" s="5" t="n"/>
       <c r="AQ18" s="5" t="n"/>
       <c r="AR18" s="5" t="n"/>
-      <c r="AS18" s="5" t="n"/>
-      <c r="AT18" s="5" t="n"/>
-      <c r="AU18" s="5" t="n"/>
-      <c r="AV18" s="5" t="n"/>
-      <c r="AW18" s="5" t="n"/>
-      <c r="AX18" s="5" t="n"/>
-      <c r="AY18" s="5" t="n"/>
-      <c r="AZ18" s="5" t="n"/>
-      <c r="BA18" s="5" t="n"/>
-      <c r="BB18" s="5" t="n"/>
+      <c r="BC18" s="5" t="n"/>
+      <c r="BD18" s="5" t="n"/>
+      <c r="BE18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2042,11 +2145,6 @@
           <t>戦装束</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>大太刀</t>
@@ -2054,7 +2152,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ご神刀,兄弟</t>
+          <t>ご神刀</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2063,21 +2161,21 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>天より墜つる暴威</t>
+          <t>霧散斬り・黄</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える。ボスが被ダメージ増加状態のとき、さらに威力が上昇する</t>
+          <t>黄ト餓鬼をランダムに【最大10体】消去し、敵に【小＋】ダメージを与える</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>613,67</t>
+          <t>588,64</t>
         </is>
       </c>
       <c r="P19" s="5" t="n"/>
@@ -2122,11 +2220,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>次郎太刀</t>
+          <t>太郎太刀</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2134,6 +2232,11 @@
           <t>戦装束</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>大太刀</t>
@@ -2141,7 +2244,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ご神刀</t>
+          <t>ご神刀,兄弟</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2150,21 +2253,21 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>正円一刀斬り</t>
+          <t>天より墜つる暴威</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>【円型・大範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える</t>
+          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える。ボスが被ダメージ増加状態のとき、さらに威力が上昇する</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>501,71</t>
+          <t>613,67</t>
         </is>
       </c>
       <c r="P20" s="5" t="n"/>
@@ -2209,11 +2312,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>蛍丸</t>
+          <t>次郎太刀</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2228,16 +2331,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>夜</t>
+          <t>ご神刀</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>青</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2246,54 +2349,64 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="n"/>
-      <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="n"/>
-      <c r="R21" s="2" t="n"/>
-      <c r="S21" s="2" t="n"/>
-      <c r="T21" s="1" t="inlineStr">
-        <is>
-          <t>677,107</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="n"/>
-      <c r="V21" s="2" t="n"/>
-      <c r="W21" s="2" t="n"/>
-      <c r="X21" s="2" t="n"/>
-      <c r="Y21" s="2" t="n"/>
-      <c r="Z21" s="2" t="n"/>
-      <c r="AA21" s="2" t="n"/>
-      <c r="AB21" s="2" t="n"/>
-      <c r="AC21" s="2" t="n"/>
-      <c r="AD21" s="2" t="n"/>
-      <c r="AE21" s="2" t="n"/>
-      <c r="AF21" s="2" t="n"/>
-      <c r="AG21" s="2" t="n"/>
-      <c r="AH21" s="2" t="n"/>
-      <c r="AI21" s="2" t="n"/>
-      <c r="AJ21" s="2" t="n"/>
-      <c r="AK21" s="2" t="n"/>
-      <c r="AL21" s="2" t="n"/>
-      <c r="AM21" s="2" t="n"/>
-      <c r="AN21" s="2" t="n"/>
-      <c r="AO21" s="2" t="n"/>
-      <c r="AP21" s="2" t="n"/>
-      <c r="AQ21" s="2" t="n"/>
-      <c r="AR21" s="2" t="n"/>
+          <t>【円型・大範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O21" s="1" t="inlineStr">
+        <is>
+          <t>501,71</t>
+        </is>
+      </c>
+      <c r="P21" s="1" t="n"/>
+      <c r="Q21" s="1" t="n"/>
+      <c r="R21" s="1" t="n"/>
+      <c r="S21" s="1" t="n"/>
+      <c r="T21" s="1" t="n"/>
+      <c r="U21" s="1" t="n"/>
+      <c r="V21" s="1" t="n"/>
+      <c r="W21" s="1" t="n"/>
+      <c r="X21" s="1" t="n"/>
+      <c r="Y21" s="1" t="n"/>
+      <c r="Z21" s="1" t="n"/>
+      <c r="AA21" s="1" t="n"/>
+      <c r="AB21" s="1" t="n"/>
+      <c r="AC21" s="1" t="n"/>
+      <c r="AD21" s="1" t="n"/>
+      <c r="AE21" s="1" t="n"/>
+      <c r="AF21" s="1" t="n"/>
+      <c r="AG21" s="1" t="n"/>
+      <c r="AH21" s="1" t="n"/>
+      <c r="AI21" s="1" t="n"/>
+      <c r="AJ21" s="1" t="n"/>
+      <c r="AK21" s="1" t="n"/>
+      <c r="AL21" s="1" t="n"/>
+      <c r="AM21" s="1" t="n"/>
+      <c r="AN21" s="1" t="n"/>
+      <c r="AO21" s="1" t="n"/>
+      <c r="AP21" s="1" t="n"/>
+      <c r="AQ21" s="1" t="n"/>
+      <c r="AR21" s="1" t="n"/>
+      <c r="AS21" s="5" t="n"/>
+      <c r="AT21" s="5" t="n"/>
+      <c r="AU21" s="5" t="n"/>
+      <c r="AV21" s="5" t="n"/>
+      <c r="AW21" s="5" t="n"/>
+      <c r="AX21" s="5" t="n"/>
+      <c r="AY21" s="5" t="n"/>
+      <c r="AZ21" s="5" t="n"/>
+      <c r="BA21" s="5" t="n"/>
+      <c r="BB21" s="5" t="n"/>
       <c r="BC21" s="2" t="n"/>
       <c r="BD21" s="2" t="n"/>
       <c r="BE21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>蜻蛉切</t>
+          <t>蛍丸</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2303,42 +2416,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>槍</t>
+          <t>大太刀</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>天下三名槍</t>
+          <t>夜</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>黄</t>
+          <t>青</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>必中縦断突き</t>
+          <t>正円一刀斬り</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>指定した【縦列・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O22" s="1" t="inlineStr">
-        <is>
-          <t>551,72</t>
-        </is>
-      </c>
+          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="n"/>
       <c r="R22" s="2" t="n"/>
       <c r="S22" s="2" t="n"/>
-      <c r="T22" s="2" t="n"/>
+      <c r="T22" s="1" t="inlineStr">
+        <is>
+          <t>677,107</t>
+        </is>
+      </c>
       <c r="U22" s="2" t="n"/>
       <c r="V22" s="2" t="n"/>
       <c r="W22" s="2" t="n"/>
@@ -2369,11 +2482,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>御手杵</t>
+          <t>蜻蛉切</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2393,7 +2506,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>黄</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2401,69 +2514,59 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>必中正円突き</t>
+          <t>必中縦断突き</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>指定した1箇所【円型・特小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
+          <t>指定した【縦列・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>461,60</t>
-        </is>
-      </c>
-      <c r="P23" s="1" t="n"/>
-      <c r="Q23" s="1" t="n"/>
-      <c r="R23" s="1" t="n"/>
-      <c r="S23" s="1" t="n"/>
-      <c r="T23" s="1" t="n"/>
-      <c r="U23" s="1" t="n"/>
-      <c r="V23" s="1" t="n"/>
-      <c r="W23" s="1" t="n"/>
-      <c r="X23" s="1" t="n"/>
-      <c r="Y23" s="1" t="n"/>
-      <c r="Z23" s="1" t="n"/>
-      <c r="AA23" s="1" t="n"/>
-      <c r="AB23" s="1" t="n"/>
-      <c r="AC23" s="1" t="n"/>
-      <c r="AD23" s="1" t="n"/>
-      <c r="AE23" s="1" t="n"/>
-      <c r="AF23" s="1" t="n"/>
-      <c r="AG23" s="1" t="n"/>
-      <c r="AH23" s="1" t="n"/>
-      <c r="AI23" s="1" t="n"/>
-      <c r="AJ23" s="1" t="n"/>
-      <c r="AK23" s="1" t="n"/>
-      <c r="AL23" s="1" t="n"/>
-      <c r="AM23" s="1" t="n"/>
-      <c r="AN23" s="1" t="n"/>
-      <c r="AO23" s="1" t="n"/>
-      <c r="AP23" s="1" t="n"/>
-      <c r="AQ23" s="1" t="n"/>
-      <c r="AR23" s="1" t="n"/>
-      <c r="AS23" s="5" t="n"/>
-      <c r="AT23" s="5" t="n"/>
-      <c r="AU23" s="5" t="n"/>
-      <c r="AV23" s="5" t="n"/>
-      <c r="AW23" s="5" t="n"/>
-      <c r="AX23" s="5" t="n"/>
-      <c r="AY23" s="5" t="n"/>
-      <c r="AZ23" s="5" t="n"/>
-      <c r="BA23" s="5" t="n"/>
-      <c r="BB23" s="5" t="n"/>
+          <t>551,72</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="n"/>
+      <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
+      <c r="T23" s="2" t="n"/>
+      <c r="U23" s="2" t="n"/>
+      <c r="V23" s="2" t="n"/>
+      <c r="W23" s="2" t="n"/>
+      <c r="X23" s="2" t="n"/>
+      <c r="Y23" s="2" t="n"/>
+      <c r="Z23" s="2" t="n"/>
+      <c r="AA23" s="2" t="n"/>
+      <c r="AB23" s="2" t="n"/>
+      <c r="AC23" s="2" t="n"/>
+      <c r="AD23" s="2" t="n"/>
+      <c r="AE23" s="2" t="n"/>
+      <c r="AF23" s="2" t="n"/>
+      <c r="AG23" s="2" t="n"/>
+      <c r="AH23" s="2" t="n"/>
+      <c r="AI23" s="2" t="n"/>
+      <c r="AJ23" s="2" t="n"/>
+      <c r="AK23" s="2" t="n"/>
+      <c r="AL23" s="2" t="n"/>
+      <c r="AM23" s="2" t="n"/>
+      <c r="AN23" s="2" t="n"/>
+      <c r="AO23" s="2" t="n"/>
+      <c r="AP23" s="2" t="n"/>
+      <c r="AQ23" s="2" t="n"/>
+      <c r="AR23" s="2" t="n"/>
       <c r="BC23" s="2" t="n"/>
       <c r="BD23" s="2" t="n"/>
       <c r="BE23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>江雪左文字</t>
+          <t>御手杵</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2473,12 +2576,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>槍</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>雪</t>
+          <t>天下三名槍</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2487,64 +2590,73 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>霧散斬り 先手の型</t>
+          <t>必中正円突き</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>ランダムなト餓鬼（攻撃指示優先）を最大5体消去し、敵に【特小＋＋】ダメージを与える
-消去時のブレイクゲージ減少量が【2倍】になる</t>
+          <t>指定した1箇所【円型・特小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>507,74</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="n"/>
-      <c r="Q24" s="2" t="n"/>
-      <c r="R24" s="2" t="n"/>
-      <c r="S24" s="2" t="n"/>
-      <c r="T24" s="2" t="n"/>
-      <c r="U24" s="2" t="n"/>
-      <c r="V24" s="2" t="n"/>
-      <c r="W24" s="2" t="n"/>
-      <c r="X24" s="2" t="n"/>
-      <c r="Y24" s="2" t="n"/>
-      <c r="Z24" s="2" t="n"/>
-      <c r="AA24" s="2" t="n"/>
-      <c r="AB24" s="2" t="n"/>
-      <c r="AC24" s="2" t="n"/>
-      <c r="AD24" s="2" t="n"/>
-      <c r="AE24" s="2" t="n"/>
-      <c r="AF24" s="2" t="n"/>
-      <c r="AG24" s="2" t="n"/>
-      <c r="AH24" s="2" t="n"/>
-      <c r="AI24" s="2" t="n"/>
-      <c r="AJ24" s="2" t="n"/>
-      <c r="AK24" s="2" t="n"/>
-      <c r="AL24" s="2" t="n"/>
-      <c r="AM24" s="2" t="n"/>
-      <c r="AN24" s="2" t="n"/>
-      <c r="AO24" s="2" t="n"/>
-      <c r="AP24" s="2" t="n"/>
-      <c r="AQ24" s="2" t="n"/>
-      <c r="AR24" s="2" t="n"/>
+          <t>461,60</t>
+        </is>
+      </c>
+      <c r="P24" s="1" t="n"/>
+      <c r="Q24" s="1" t="n"/>
+      <c r="R24" s="1" t="n"/>
+      <c r="S24" s="1" t="n"/>
+      <c r="T24" s="1" t="n"/>
+      <c r="U24" s="1" t="n"/>
+      <c r="V24" s="1" t="n"/>
+      <c r="W24" s="1" t="n"/>
+      <c r="X24" s="1" t="n"/>
+      <c r="Y24" s="1" t="n"/>
+      <c r="Z24" s="1" t="n"/>
+      <c r="AA24" s="1" t="n"/>
+      <c r="AB24" s="1" t="n"/>
+      <c r="AC24" s="1" t="n"/>
+      <c r="AD24" s="1" t="n"/>
+      <c r="AE24" s="1" t="n"/>
+      <c r="AF24" s="1" t="n"/>
+      <c r="AG24" s="1" t="n"/>
+      <c r="AH24" s="1" t="n"/>
+      <c r="AI24" s="1" t="n"/>
+      <c r="AJ24" s="1" t="n"/>
+      <c r="AK24" s="1" t="n"/>
+      <c r="AL24" s="1" t="n"/>
+      <c r="AM24" s="1" t="n"/>
+      <c r="AN24" s="1" t="n"/>
+      <c r="AO24" s="1" t="n"/>
+      <c r="AP24" s="1" t="n"/>
+      <c r="AQ24" s="1" t="n"/>
+      <c r="AR24" s="1" t="n"/>
+      <c r="AS24" s="5" t="n"/>
+      <c r="AT24" s="5" t="n"/>
+      <c r="AU24" s="5" t="n"/>
+      <c r="AV24" s="5" t="n"/>
+      <c r="AW24" s="5" t="n"/>
+      <c r="AX24" s="5" t="n"/>
+      <c r="AY24" s="5" t="n"/>
+      <c r="AZ24" s="5" t="n"/>
+      <c r="BA24" s="5" t="n"/>
+      <c r="BB24" s="5" t="n"/>
       <c r="BC24" s="2" t="n"/>
       <c r="BD24" s="2" t="n"/>
       <c r="BE24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>宗三左文字</t>
+          <t>江雪左文字</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2554,12 +2666,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>太刀</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>蝶</t>
+          <t>雪</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2568,73 +2680,64 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>攪乱戦術・黄</t>
+          <t>霧散斬り 先手の型</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>【最大10体】の黄ト餓鬼を盤面の中央に集める</t>
+          <t>ランダムなト餓鬼（攻撃指示優先）を最大5体消去し、敵に【特小＋＋】ダメージを与える
+消去時のブレイクゲージ減少量が【2倍】になる</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>493,54</t>
-        </is>
-      </c>
-      <c r="P25" s="1" t="n"/>
-      <c r="Q25" s="1" t="n"/>
-      <c r="R25" s="1" t="n"/>
-      <c r="S25" s="1" t="n"/>
-      <c r="T25" s="1" t="n"/>
-      <c r="U25" s="1" t="n"/>
-      <c r="V25" s="1" t="n"/>
-      <c r="W25" s="1" t="n"/>
-      <c r="X25" s="1" t="n"/>
-      <c r="Y25" s="1" t="n"/>
-      <c r="Z25" s="1" t="n"/>
-      <c r="AA25" s="1" t="n"/>
-      <c r="AB25" s="1" t="n"/>
-      <c r="AC25" s="1" t="n"/>
-      <c r="AD25" s="1" t="n"/>
-      <c r="AE25" s="1" t="n"/>
-      <c r="AF25" s="1" t="n"/>
-      <c r="AG25" s="1" t="n"/>
-      <c r="AH25" s="1" t="n"/>
-      <c r="AI25" s="1" t="n"/>
-      <c r="AJ25" s="1" t="n"/>
-      <c r="AK25" s="1" t="n"/>
-      <c r="AL25" s="1" t="n"/>
-      <c r="AM25" s="1" t="n"/>
-      <c r="AN25" s="1" t="n"/>
-      <c r="AO25" s="1" t="n"/>
-      <c r="AP25" s="1" t="n"/>
-      <c r="AQ25" s="1" t="n"/>
-      <c r="AR25" s="1" t="n"/>
-      <c r="AS25" s="5" t="n"/>
-      <c r="AT25" s="5" t="n"/>
-      <c r="AU25" s="5" t="n"/>
-      <c r="AV25" s="5" t="n"/>
-      <c r="AW25" s="5" t="n"/>
-      <c r="AX25" s="5" t="n"/>
-      <c r="AY25" s="5" t="n"/>
-      <c r="AZ25" s="5" t="n"/>
-      <c r="BA25" s="5" t="n"/>
-      <c r="BB25" s="5" t="n"/>
+          <t>507,74</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="n"/>
+      <c r="Q25" s="2" t="n"/>
+      <c r="R25" s="2" t="n"/>
+      <c r="S25" s="2" t="n"/>
+      <c r="T25" s="2" t="n"/>
+      <c r="U25" s="2" t="n"/>
+      <c r="V25" s="2" t="n"/>
+      <c r="W25" s="2" t="n"/>
+      <c r="X25" s="2" t="n"/>
+      <c r="Y25" s="2" t="n"/>
+      <c r="Z25" s="2" t="n"/>
+      <c r="AA25" s="2" t="n"/>
+      <c r="AB25" s="2" t="n"/>
+      <c r="AC25" s="2" t="n"/>
+      <c r="AD25" s="2" t="n"/>
+      <c r="AE25" s="2" t="n"/>
+      <c r="AF25" s="2" t="n"/>
+      <c r="AG25" s="2" t="n"/>
+      <c r="AH25" s="2" t="n"/>
+      <c r="AI25" s="2" t="n"/>
+      <c r="AJ25" s="2" t="n"/>
+      <c r="AK25" s="2" t="n"/>
+      <c r="AL25" s="2" t="n"/>
+      <c r="AM25" s="2" t="n"/>
+      <c r="AN25" s="2" t="n"/>
+      <c r="AO25" s="2" t="n"/>
+      <c r="AP25" s="2" t="n"/>
+      <c r="AQ25" s="2" t="n"/>
+      <c r="AR25" s="2" t="n"/>
       <c r="BC25" s="2" t="n"/>
       <c r="BD25" s="2" t="n"/>
       <c r="BE25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>小夜左文字</t>
+          <t>宗三左文字</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2644,12 +2747,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>短刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>夜</t>
+          <t>蝶</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2658,21 +2761,21 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>正円斬り 追撃の型</t>
+          <t>攪乱戦術・黄</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>【円型・特小範囲】のト餓鬼を消去し、敵に【中】ダメージを与える。乱舞ぎりタイム中はさらにダメージ上昇。</t>
+          <t>【最大10体】の黄ト餓鬼を盤面の中央に集める</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>417,81</t>
+          <t>493,54</t>
         </is>
       </c>
       <c r="P26" s="1" t="n"/>
@@ -2720,11 +2823,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>加州清光</t>
+          <t>小夜左文字</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2734,12 +2837,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>短刀</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>新選組</t>
+          <t>夜</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2748,27 +2851,27 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>必中三段斬り</t>
+          <t>正円斬り 追撃の型</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>指定した【円型・特小範囲】のト餓鬼を3回消去し、敵に【小】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O27" s="1" t="n"/>
+          <t>【円型・特小範囲】のト餓鬼を消去し、敵に【中】ダメージを与える。乱舞ぎりタイム中はさらにダメージ上昇。</t>
+        </is>
+      </c>
+      <c r="O27" s="1" t="inlineStr">
+        <is>
+          <t>417,81</t>
+        </is>
+      </c>
       <c r="P27" s="1" t="n"/>
       <c r="Q27" s="1" t="n"/>
       <c r="R27" s="1" t="n"/>
-      <c r="S27" s="1" t="inlineStr">
-        <is>
-          <t>645,73</t>
-        </is>
-      </c>
+      <c r="S27" s="1" t="n"/>
       <c r="T27" s="1" t="n"/>
       <c r="U27" s="1" t="n"/>
       <c r="V27" s="1" t="n"/>
@@ -2794,17 +2897,27 @@
       <c r="AP27" s="1" t="n"/>
       <c r="AQ27" s="1" t="n"/>
       <c r="AR27" s="1" t="n"/>
-      <c r="BC27" s="1" t="n"/>
-      <c r="BD27" s="1" t="n"/>
-      <c r="BE27" s="1" t="n"/>
+      <c r="AS27" s="5" t="n"/>
+      <c r="AT27" s="5" t="n"/>
+      <c r="AU27" s="5" t="n"/>
+      <c r="AV27" s="5" t="n"/>
+      <c r="AW27" s="5" t="n"/>
+      <c r="AX27" s="5" t="n"/>
+      <c r="AY27" s="5" t="n"/>
+      <c r="AZ27" s="5" t="n"/>
+      <c r="BA27" s="5" t="n"/>
+      <c r="BB27" s="5" t="n"/>
+      <c r="BC27" s="2" t="n"/>
+      <c r="BD27" s="2" t="n"/>
+      <c r="BE27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>大和守安定</t>
+          <t>加州清光</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2828,28 +2941,27 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>霧散斬り ボムの型</t>
+          <t>必中三段斬り</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>ランダムな孤立した青ト餓鬼を【最大3体】消去し、敵に【特小＋】ダメージを与える
-ボムを【1個】生成する</t>
-        </is>
-      </c>
-      <c r="O28" s="1" t="inlineStr">
-        <is>
-          <t>467,57</t>
-        </is>
-      </c>
+          <t>指定した【円型・特小範囲】のト餓鬼を3回消去し、敵に【小】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O28" s="1" t="n"/>
       <c r="P28" s="1" t="n"/>
       <c r="Q28" s="1" t="n"/>
       <c r="R28" s="1" t="n"/>
-      <c r="S28" s="1" t="n"/>
+      <c r="S28" s="1" t="inlineStr">
+        <is>
+          <t>645,73</t>
+        </is>
+      </c>
       <c r="T28" s="1" t="n"/>
       <c r="U28" s="1" t="n"/>
       <c r="V28" s="1" t="n"/>
@@ -2875,27 +2987,17 @@
       <c r="AP28" s="1" t="n"/>
       <c r="AQ28" s="1" t="n"/>
       <c r="AR28" s="1" t="n"/>
-      <c r="AS28" s="5" t="n"/>
-      <c r="AT28" s="5" t="n"/>
-      <c r="AU28" s="5" t="n"/>
-      <c r="AV28" s="5" t="n"/>
-      <c r="AW28" s="5" t="n"/>
-      <c r="AX28" s="5" t="n"/>
-      <c r="AY28" s="5" t="n"/>
-      <c r="AZ28" s="5" t="n"/>
-      <c r="BA28" s="5" t="n"/>
-      <c r="BB28" s="5" t="n"/>
-      <c r="BC28" s="2" t="n"/>
-      <c r="BD28" s="2" t="n"/>
-      <c r="BE28" s="2" t="n"/>
+      <c r="BC28" s="1" t="n"/>
+      <c r="BD28" s="1" t="n"/>
+      <c r="BE28" s="1" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>歌仙兼定</t>
+          <t>大和守安定</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2910,7 +3012,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>花</t>
+          <t>新選組</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2923,17 +3025,18 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>水平一刀斬り</t>
+          <t>霧散斬り ボムの型</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小－】ダメージを与える</t>
+          <t>ランダムな孤立した青ト餓鬼を【最大3体】消去し、敵に【特小＋】ダメージを与える
+ボムを【1個】生成する</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>475,70</t>
+          <t>467,57</t>
         </is>
       </c>
       <c r="P29" s="1" t="n"/>
@@ -2993,11 +3096,6 @@
           <t>戦装束</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>打刀</t>
@@ -3005,7 +3103,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>詠み人,花</t>
+          <t>花</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3014,21 +3112,21 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>くちなしの挽歌</t>
+          <t>水平一刀斬り</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>指定した【縦列・小範囲】のト餓鬼を、黄色に変化させる</t>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小－】ダメージを与える</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>492,74</t>
+          <t>475,70</t>
         </is>
       </c>
       <c r="P30" s="1" t="n"/>
@@ -3076,11 +3174,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>和泉守兼定</t>
+          <t>歌仙兼定</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3088,6 +3186,11 @@
           <t>戦装束</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>打刀</t>
@@ -3095,7 +3198,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>新選組</t>
+          <t>詠み人,花</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3104,19 +3207,23 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>正円二段斬り</t>
+          <t>くちなしの挽歌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ランダムな場所の【円型・小範囲】のト餓鬼を2回消去し、敵に【中】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O31" s="1" t="n"/>
+          <t>指定した【縦列・小範囲】のト餓鬼を、黄色に変化させる</t>
+        </is>
+      </c>
+      <c r="O31" s="1" t="inlineStr">
+        <is>
+          <t>492,74</t>
+        </is>
+      </c>
       <c r="P31" s="1" t="n"/>
       <c r="Q31" s="1" t="n"/>
       <c r="R31" s="1" t="n"/>
@@ -3135,11 +3242,7 @@
       <c r="AE31" s="1" t="n"/>
       <c r="AF31" s="1" t="n"/>
       <c r="AG31" s="1" t="n"/>
-      <c r="AH31" s="1" t="inlineStr">
-        <is>
-          <t>1551,188</t>
-        </is>
-      </c>
+      <c r="AH31" s="1" t="n"/>
       <c r="AI31" s="1" t="n"/>
       <c r="AJ31" s="1" t="n"/>
       <c r="AK31" s="1" t="n"/>
@@ -3150,17 +3253,27 @@
       <c r="AP31" s="1" t="n"/>
       <c r="AQ31" s="1" t="n"/>
       <c r="AR31" s="1" t="n"/>
-      <c r="BC31" s="1" t="n"/>
-      <c r="BD31" s="1" t="n"/>
-      <c r="BE31" s="1" t="n"/>
+      <c r="AS31" s="5" t="n"/>
+      <c r="AT31" s="5" t="n"/>
+      <c r="AU31" s="5" t="n"/>
+      <c r="AV31" s="5" t="n"/>
+      <c r="AW31" s="5" t="n"/>
+      <c r="AX31" s="5" t="n"/>
+      <c r="AY31" s="5" t="n"/>
+      <c r="AZ31" s="5" t="n"/>
+      <c r="BA31" s="5" t="n"/>
+      <c r="BB31" s="5" t="n"/>
+      <c r="BC31" s="2" t="n"/>
+      <c r="BD31" s="2" t="n"/>
+      <c r="BE31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>陸奥守吉行</t>
+          <t>和泉守兼定</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3175,26 +3288,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>海</t>
+          <t>新選組</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>黄</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>水平斬り 攻勢の型</t>
+          <t>正円二段斬り</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【極小】ダメージを与える
-味方全員に攻撃力上昇【極小＋＋・3手】を付与する</t>
+          <t>ランダムな場所の【円型・小範囲】のト餓鬼を2回消去し、敵に【中】ダメージを与える</t>
         </is>
       </c>
       <c r="O32" s="1" t="n"/>
@@ -3216,7 +3328,11 @@
       <c r="AE32" s="1" t="n"/>
       <c r="AF32" s="1" t="n"/>
       <c r="AG32" s="1" t="n"/>
-      <c r="AH32" s="1" t="n"/>
+      <c r="AH32" s="1" t="inlineStr">
+        <is>
+          <t>1551,188</t>
+        </is>
+      </c>
       <c r="AI32" s="1" t="n"/>
       <c r="AJ32" s="1" t="n"/>
       <c r="AK32" s="1" t="n"/>
@@ -3226,26 +3342,18 @@
       <c r="AO32" s="1" t="n"/>
       <c r="AP32" s="1" t="n"/>
       <c r="AQ32" s="1" t="n"/>
-      <c r="AR32" s="1" t="inlineStr">
-        <is>
-          <t>1575,228</t>
-        </is>
-      </c>
+      <c r="AR32" s="1" t="n"/>
       <c r="BC32" s="1" t="n"/>
       <c r="BD32" s="1" t="n"/>
-      <c r="BE32" s="1" t="inlineStr">
-        <is>
-          <t>[黄の絵具,1][書き物道具,2][花札,2][天ぷら,2][そろばん,2][打刀の心得,1]</t>
-        </is>
-      </c>
+      <c r="BE32" s="1" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>山姥切国広</t>
+          <t>陸奥守吉行</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3260,25 +3368,26 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>兄弟</t>
+          <t>海</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>青</t>
+          <t>黄</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>正円一刀斬り</t>
+          <t>水平斬り 攻勢の型</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>【円型・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【極小】ダメージを与える
+味方全員に攻撃力上昇【極小＋＋・3手】を付与する</t>
         </is>
       </c>
       <c r="O33" s="1" t="n"/>
@@ -3290,11 +3399,7 @@
       <c r="U33" s="1" t="n"/>
       <c r="V33" s="1" t="n"/>
       <c r="W33" s="1" t="n"/>
-      <c r="X33" s="1" t="inlineStr">
-        <is>
-          <t>850,107</t>
-        </is>
-      </c>
+      <c r="X33" s="1" t="n"/>
       <c r="Y33" s="1" t="n"/>
       <c r="Z33" s="1" t="n"/>
       <c r="AA33" s="1" t="n"/>
@@ -3314,18 +3419,26 @@
       <c r="AO33" s="1" t="n"/>
       <c r="AP33" s="1" t="n"/>
       <c r="AQ33" s="1" t="n"/>
-      <c r="AR33" s="1" t="n"/>
+      <c r="AR33" s="1" t="inlineStr">
+        <is>
+          <t>1575,228</t>
+        </is>
+      </c>
       <c r="BC33" s="1" t="n"/>
       <c r="BD33" s="1" t="n"/>
-      <c r="BE33" s="1" t="n"/>
+      <c r="BE33" s="1" t="inlineStr">
+        <is>
+          <t>[黄の絵具,1][書き物道具,2][花札,2][天ぷら,2][そろばん,2][打刀の心得,1]</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>山伏国広</t>
+          <t>山姥切国広</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3335,17 +3448,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>お山修行</t>
+          <t>兄弟</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>青</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3353,20 +3466,15 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>逆さ扇斬り 守護の型</t>
+          <t>正円一刀斬り</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>【扇型・特小範囲】のト餓鬼を消去し、敵に【極小＋】ダメージを与える
-味方全員に被ダメージ軽減【特小＋＋・3手】を付与する</t>
-        </is>
-      </c>
-      <c r="O34" s="1" t="inlineStr">
-        <is>
-          <t>584,70</t>
-        </is>
-      </c>
+          <t>【円型・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="n"/>
       <c r="P34" s="1" t="n"/>
       <c r="Q34" s="1" t="n"/>
       <c r="R34" s="1" t="n"/>
@@ -3375,7 +3483,11 @@
       <c r="U34" s="1" t="n"/>
       <c r="V34" s="1" t="n"/>
       <c r="W34" s="1" t="n"/>
-      <c r="X34" s="1" t="n"/>
+      <c r="X34" s="1" t="inlineStr">
+        <is>
+          <t>850,107</t>
+        </is>
+      </c>
       <c r="Y34" s="1" t="n"/>
       <c r="Z34" s="1" t="n"/>
       <c r="AA34" s="1" t="n"/>
@@ -3402,11 +3514,11 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>獅子王</t>
+          <t>山伏国広</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3421,7 +3533,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>けもの</t>
+          <t>お山修行</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3434,23 +3546,24 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>水平一刀斬り</t>
+          <t>逆さ扇斬り 守護の型</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O35" s="1" t="n"/>
+          <t>【扇型・特小範囲】のト餓鬼を消去し、敵に【極小＋】ダメージを与える
+味方全員に被ダメージ軽減【特小＋＋・3手】を付与する</t>
+        </is>
+      </c>
+      <c r="O35" s="1" t="inlineStr">
+        <is>
+          <t>584,70</t>
+        </is>
+      </c>
       <c r="P35" s="1" t="n"/>
       <c r="Q35" s="1" t="n"/>
       <c r="R35" s="1" t="n"/>
-      <c r="S35" s="1" t="inlineStr">
-        <is>
-          <t>771,74</t>
-        </is>
-      </c>
+      <c r="S35" s="1" t="n"/>
       <c r="T35" s="1" t="n"/>
       <c r="U35" s="1" t="n"/>
       <c r="V35" s="1" t="n"/>
@@ -3482,11 +3595,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>鶴丸国永</t>
+          <t>堀川国広</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3496,12 +3609,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>脇差</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>新選組</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3510,20 +3623,24 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>水平斬り 攻勢の型</t>
+          <t>会心猛攻の法</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>【横列・中範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える
-自身に攻撃力上昇【極小・1手】を付与する</t>
-        </is>
-      </c>
-      <c r="O36" s="1" t="n"/>
+          <t>味方全員に攻撃力上昇【極小＋＋・3手】を付与する
+味方全員にクリティカル率上昇【特小＋＋・9手】を付与する</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>491,63</t>
+        </is>
+      </c>
       <c r="P36" s="1" t="n"/>
       <c r="Q36" s="1" t="n"/>
       <c r="R36" s="1" t="n"/>
@@ -3532,11 +3649,7 @@
       <c r="U36" s="1" t="n"/>
       <c r="V36" s="1" t="n"/>
       <c r="W36" s="1" t="n"/>
-      <c r="X36" s="1" t="inlineStr">
-        <is>
-          <t>935,110</t>
-        </is>
-      </c>
+      <c r="X36" s="1" t="n"/>
       <c r="Y36" s="1" t="n"/>
       <c r="Z36" s="1" t="n"/>
       <c r="AA36" s="1" t="n"/>
@@ -3557,14 +3670,27 @@
       <c r="AP36" s="1" t="n"/>
       <c r="AQ36" s="1" t="n"/>
       <c r="AR36" s="1" t="n"/>
-      <c r="BC36" s="1" t="n"/>
-      <c r="BD36" s="1" t="n"/>
-      <c r="BE36" s="1" t="n"/>
+      <c r="AS36" s="5" t="n"/>
+      <c r="AT36" s="5" t="n"/>
+      <c r="AU36" s="5" t="n"/>
+      <c r="AV36" s="5" t="n"/>
+      <c r="AW36" s="5" t="n"/>
+      <c r="AX36" s="5" t="n"/>
+      <c r="AY36" s="5" t="n"/>
+      <c r="AZ36" s="5" t="n"/>
+      <c r="BA36" s="5" t="n"/>
+      <c r="BB36" s="5" t="n"/>
+      <c r="BC36" s="2" t="n"/>
+      <c r="BD36" s="2" t="n"/>
+      <c r="BE36" s="2" t="n"/>
     </row>
     <row r="37">
+      <c r="A37" t="n">
+        <v>122</v>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>大倶利伽羅</t>
+          <t>獅子王</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3574,12 +3700,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>太刀</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>龍</t>
+          <t>けもの</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3588,28 +3714,27 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>三段斬り 攻勢の型</t>
+          <t>水平一刀斬り</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>ランダムな【円型・特小範囲】のト餓鬼を3回消去し、敵に【小－】ダメージを与える
-自身にクリティカル率上昇【極小＋＋・1手】を付与する</t>
-        </is>
-      </c>
-      <c r="O37" s="1" t="inlineStr">
-        <is>
-          <t>455,72</t>
-        </is>
-      </c>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O37" s="1" t="n"/>
       <c r="P37" s="1" t="n"/>
       <c r="Q37" s="1" t="n"/>
       <c r="R37" s="1" t="n"/>
-      <c r="S37" s="1" t="n"/>
+      <c r="S37" s="1" t="inlineStr">
+        <is>
+          <t>771,74</t>
+        </is>
+      </c>
       <c r="T37" s="1" t="n"/>
       <c r="U37" s="1" t="n"/>
       <c r="V37" s="1" t="n"/>
@@ -3635,24 +3760,17 @@
       <c r="AP37" s="1" t="n"/>
       <c r="AQ37" s="1" t="n"/>
       <c r="AR37" s="1" t="n"/>
-      <c r="AS37" s="5" t="n"/>
-      <c r="AT37" s="5" t="n"/>
-      <c r="AU37" s="5" t="n"/>
-      <c r="AV37" s="5" t="n"/>
-      <c r="AW37" s="5" t="n"/>
-      <c r="AX37" s="5" t="n"/>
-      <c r="AY37" s="5" t="n"/>
-      <c r="AZ37" s="5" t="n"/>
-      <c r="BA37" s="5" t="n"/>
-      <c r="BB37" s="5" t="n"/>
-      <c r="BC37" s="2" t="n"/>
-      <c r="BD37" s="2" t="n"/>
-      <c r="BE37" s="2" t="n"/>
+      <c r="BC37" s="1" t="n"/>
+      <c r="BD37" s="1" t="n"/>
+      <c r="BE37" s="1" t="n"/>
     </row>
     <row r="38">
+      <c r="A38" t="n">
+        <v>130</v>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>へし切長谷部</t>
+          <t>鶴丸国永</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3662,12 +3780,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>太刀</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>もの斬り</t>
+          <t>鳥</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3676,23 +3794,20 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>必中二段斬り</t>
+          <t>水平斬り 攻勢の型</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>指定した【縦列・小範囲】のト餓鬼を2回消去し、敵に【小＋】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O38" s="1" t="inlineStr">
-        <is>
-          <t>530,65</t>
-        </is>
-      </c>
+          <t>【横列・中範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える
+自身に攻撃力上昇【極小・1手】を付与する</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="n"/>
       <c r="P38" s="1" t="n"/>
       <c r="Q38" s="1" t="n"/>
       <c r="R38" s="1" t="n"/>
@@ -3701,7 +3816,11 @@
       <c r="U38" s="1" t="n"/>
       <c r="V38" s="1" t="n"/>
       <c r="W38" s="1" t="n"/>
-      <c r="X38" s="1" t="n"/>
+      <c r="X38" s="1" t="inlineStr">
+        <is>
+          <t>935,110</t>
+        </is>
+      </c>
       <c r="Y38" s="1" t="n"/>
       <c r="Z38" s="1" t="n"/>
       <c r="AA38" s="1" t="n"/>
@@ -3722,24 +3841,14 @@
       <c r="AP38" s="1" t="n"/>
       <c r="AQ38" s="1" t="n"/>
       <c r="AR38" s="1" t="n"/>
-      <c r="AS38" s="5" t="n"/>
-      <c r="AT38" s="5" t="n"/>
-      <c r="AU38" s="5" t="n"/>
-      <c r="AV38" s="5" t="n"/>
-      <c r="AW38" s="5" t="n"/>
-      <c r="AX38" s="5" t="n"/>
-      <c r="AY38" s="5" t="n"/>
-      <c r="AZ38" s="5" t="n"/>
-      <c r="BA38" s="5" t="n"/>
-      <c r="BB38" s="5" t="n"/>
-      <c r="BC38" s="2" t="n"/>
-      <c r="BD38" s="2" t="n"/>
-      <c r="BE38" s="2" t="n"/>
+      <c r="BC38" s="1" t="n"/>
+      <c r="BD38" s="1" t="n"/>
+      <c r="BE38" s="1" t="n"/>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>同田貫正国</t>
+          <t>大倶利伽羅</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3754,7 +3863,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>もの斬り</t>
+          <t>龍</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3763,21 +3872,22 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>真っ向一刀斬り</t>
+          <t>三段斬り 攻勢の型</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>【縦列・小範囲】のト餓鬼を消去し、敵に【小＋＋】ダメージを与える</t>
+          <t>ランダムな【円型・特小範囲】のト餓鬼を3回消去し、敵に【小－】ダメージを与える
+自身にクリティカル率上昇【極小＋＋・1手】を付与する</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>453,75</t>
+          <t>455,72</t>
         </is>
       </c>
       <c r="P39" s="1" t="n"/>
@@ -3826,7 +3936,7 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>蜂須賀虎徹</t>
+          <t>へし切長谷部</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3841,7 +3951,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>兄弟</t>
+          <t>もの斬り</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3850,21 +3960,21 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>霧散斬り 掃討の型</t>
+          <t>必中二段斬り</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>孤立したト餓鬼をランダムに【最大5体】消去し、敵に【特小＋】ダメージを与える</t>
+          <t>指定した【縦列・小範囲】のト餓鬼を2回消去し、敵に【小＋】ダメージを与える</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>481,71</t>
+          <t>530,65</t>
         </is>
       </c>
       <c r="P40" s="1" t="n"/>
@@ -3913,7 +4023,7 @@
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>燭台切光忠</t>
+          <t>同田貫正国</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3923,7 +4033,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3937,22 +4047,21 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>必中縦断斬り ボムの型</t>
+          <t>真っ向一刀斬り</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>指定した【縦列・小範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える
-ボムを【1個】生成する</t>
+          <t>【縦列・小範囲】のト餓鬼を消去し、敵に【小＋＋】ダメージを与える</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>547,66</t>
+          <t>453,75</t>
         </is>
       </c>
       <c r="P41" s="1" t="n"/>
@@ -3999,7 +4108,49 @@
       <c r="BE41" s="2" t="n"/>
     </row>
     <row r="42">
-      <c r="O42" s="1" t="n"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>蜂須賀虎徹</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>打刀</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>兄弟</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>16</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>霧散斬り 掃討の型</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>孤立したト餓鬼をランダムに【最大5体】消去し、敵に【特小＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>481,71</t>
+        </is>
+      </c>
       <c r="P42" s="1" t="n"/>
       <c r="Q42" s="1" t="n"/>
       <c r="R42" s="1" t="n"/>
@@ -4029,12 +4180,65 @@
       <c r="AP42" s="1" t="n"/>
       <c r="AQ42" s="1" t="n"/>
       <c r="AR42" s="1" t="n"/>
-      <c r="BC42" s="1" t="n"/>
-      <c r="BD42" s="1" t="n"/>
-      <c r="BE42" s="1" t="n"/>
+      <c r="AS42" s="5" t="n"/>
+      <c r="AT42" s="5" t="n"/>
+      <c r="AU42" s="5" t="n"/>
+      <c r="AV42" s="5" t="n"/>
+      <c r="AW42" s="5" t="n"/>
+      <c r="AX42" s="5" t="n"/>
+      <c r="AY42" s="5" t="n"/>
+      <c r="AZ42" s="5" t="n"/>
+      <c r="BA42" s="5" t="n"/>
+      <c r="BB42" s="5" t="n"/>
+      <c r="BC42" s="2" t="n"/>
+      <c r="BD42" s="2" t="n"/>
+      <c r="BE42" s="2" t="n"/>
     </row>
     <row r="43">
-      <c r="O43" s="1" t="n"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>燭台切光忠</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>太刀</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>もの斬り</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>27</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>必中縦断斬り ボムの型</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>指定した【縦列・小範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える
+ボムを【1個】生成する</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>547,66</t>
+        </is>
+      </c>
       <c r="P43" s="1" t="n"/>
       <c r="Q43" s="1" t="n"/>
       <c r="R43" s="1" t="n"/>
@@ -4064,12 +4268,65 @@
       <c r="AP43" s="1" t="n"/>
       <c r="AQ43" s="1" t="n"/>
       <c r="AR43" s="1" t="n"/>
-      <c r="BC43" s="1" t="n"/>
-      <c r="BD43" s="1" t="n"/>
-      <c r="BE43" s="1" t="n"/>
+      <c r="AS43" s="5" t="n"/>
+      <c r="AT43" s="5" t="n"/>
+      <c r="AU43" s="5" t="n"/>
+      <c r="AV43" s="5" t="n"/>
+      <c r="AW43" s="5" t="n"/>
+      <c r="AX43" s="5" t="n"/>
+      <c r="AY43" s="5" t="n"/>
+      <c r="AZ43" s="5" t="n"/>
+      <c r="BA43" s="5" t="n"/>
+      <c r="BB43" s="5" t="n"/>
+      <c r="BC43" s="2" t="n"/>
+      <c r="BD43" s="2" t="n"/>
+      <c r="BE43" s="2" t="n"/>
     </row>
     <row r="44">
-      <c r="O44" s="1" t="n"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>愛染国俊</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>短刀</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>炎</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>17</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>強攻の法</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>自身に攻撃力上昇【特小・1手】を付与する
+自身に攻撃力上昇【極小＋・1手】を付与する</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>483,62</t>
+        </is>
+      </c>
       <c r="P44" s="1" t="n"/>
       <c r="Q44" s="1" t="n"/>
       <c r="R44" s="1" t="n"/>
@@ -4099,12 +4356,64 @@
       <c r="AP44" s="1" t="n"/>
       <c r="AQ44" s="1" t="n"/>
       <c r="AR44" s="1" t="n"/>
-      <c r="BC44" s="1" t="n"/>
-      <c r="BD44" s="1" t="n"/>
-      <c r="BE44" s="1" t="n"/>
+      <c r="AS44" s="5" t="n"/>
+      <c r="AT44" s="5" t="n"/>
+      <c r="AU44" s="5" t="n"/>
+      <c r="AV44" s="5" t="n"/>
+      <c r="AW44" s="5" t="n"/>
+      <c r="AX44" s="5" t="n"/>
+      <c r="AY44" s="5" t="n"/>
+      <c r="AZ44" s="5" t="n"/>
+      <c r="BA44" s="5" t="n"/>
+      <c r="BB44" s="5" t="n"/>
+      <c r="BC44" s="2" t="n"/>
+      <c r="BD44" s="2" t="n"/>
+      <c r="BE44" s="2" t="n"/>
     </row>
     <row r="45">
-      <c r="O45" s="1" t="n"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>にっかり青江</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>脇差</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>15</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>守備制約の計</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>敵に被ダメージ増加【極小＋・1手】を付与する</t>
+        </is>
+      </c>
+      <c r="O45" s="1" t="inlineStr">
+        <is>
+          <t>524,65</t>
+        </is>
+      </c>
       <c r="P45" s="1" t="n"/>
       <c r="Q45" s="1" t="n"/>
       <c r="R45" s="1" t="n"/>
@@ -4134,9 +4443,19 @@
       <c r="AP45" s="1" t="n"/>
       <c r="AQ45" s="1" t="n"/>
       <c r="AR45" s="1" t="n"/>
-      <c r="BC45" s="1" t="n"/>
-      <c r="BD45" s="1" t="n"/>
-      <c r="BE45" s="1" t="n"/>
+      <c r="AS45" s="5" t="n"/>
+      <c r="AT45" s="5" t="n"/>
+      <c r="AU45" s="5" t="n"/>
+      <c r="AV45" s="5" t="n"/>
+      <c r="AW45" s="5" t="n"/>
+      <c r="AX45" s="5" t="n"/>
+      <c r="AY45" s="5" t="n"/>
+      <c r="AZ45" s="5" t="n"/>
+      <c r="BA45" s="5" t="n"/>
+      <c r="BB45" s="5" t="n"/>
+      <c r="BC45" s="2" t="n"/>
+      <c r="BD45" s="2" t="n"/>
+      <c r="BE45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="O46" s="1" t="n"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -938,7 +938,34 @@
           <t>太刀</t>
         </is>
       </c>
-      <c r="O4" s="1" t="n"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>正円白刃斬り</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>【円型・小範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>513,67</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="n"/>
       <c r="Q4" s="1" t="n"/>
       <c r="R4" s="1" t="n"/>
@@ -4458,7 +4485,49 @@
       <c r="BE45" s="2" t="n"/>
     </row>
     <row r="46">
-      <c r="O46" s="1" t="n"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>秋田藤四郎</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>短刀</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>兄弟</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>15</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>受け流しの法</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>味方全員にガード率上昇【中－・5手】を付与する</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t>473,60</t>
+        </is>
+      </c>
       <c r="P46" s="1" t="n"/>
       <c r="Q46" s="1" t="n"/>
       <c r="R46" s="1" t="n"/>
@@ -4488,12 +4557,65 @@
       <c r="AP46" s="1" t="n"/>
       <c r="AQ46" s="1" t="n"/>
       <c r="AR46" s="1" t="n"/>
-      <c r="BC46" s="1" t="n"/>
-      <c r="BD46" s="1" t="n"/>
-      <c r="BE46" s="1" t="n"/>
+      <c r="AS46" s="5" t="n"/>
+      <c r="AT46" s="5" t="n"/>
+      <c r="AU46" s="5" t="n"/>
+      <c r="AV46" s="5" t="n"/>
+      <c r="AW46" s="5" t="n"/>
+      <c r="AX46" s="5" t="n"/>
+      <c r="AY46" s="5" t="n"/>
+      <c r="AZ46" s="5" t="n"/>
+      <c r="BA46" s="5" t="n"/>
+      <c r="BB46" s="5" t="n"/>
+      <c r="BC46" s="2" t="n"/>
+      <c r="BD46" s="2" t="n"/>
+      <c r="BE46" s="2" t="n"/>
     </row>
     <row r="47">
-      <c r="O47" s="1" t="n"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>薬研藤四郎</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>短刀</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>兄弟</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>16</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>真っ向斬り 攻勢の型</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>【縦列・特小範囲】のト餓鬼を消去し、敵に【極小】ダメージを与える
+味方全員にクリティカル率上昇【小・3手】を付与する</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>542,55</t>
+        </is>
+      </c>
       <c r="P47" s="1" t="n"/>
       <c r="Q47" s="1" t="n"/>
       <c r="R47" s="1" t="n"/>
@@ -4523,12 +4645,64 @@
       <c r="AP47" s="1" t="n"/>
       <c r="AQ47" s="1" t="n"/>
       <c r="AR47" s="1" t="n"/>
-      <c r="BC47" s="1" t="n"/>
-      <c r="BD47" s="1" t="n"/>
-      <c r="BE47" s="1" t="n"/>
+      <c r="AS47" s="5" t="n"/>
+      <c r="AT47" s="5" t="n"/>
+      <c r="AU47" s="5" t="n"/>
+      <c r="AV47" s="5" t="n"/>
+      <c r="AW47" s="5" t="n"/>
+      <c r="AX47" s="5" t="n"/>
+      <c r="AY47" s="5" t="n"/>
+      <c r="AZ47" s="5" t="n"/>
+      <c r="BA47" s="5" t="n"/>
+      <c r="BB47" s="5" t="n"/>
+      <c r="BC47" s="2" t="n"/>
+      <c r="BD47" s="2" t="n"/>
+      <c r="BE47" s="2" t="n"/>
     </row>
     <row r="48">
-      <c r="O48" s="1" t="n"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>前田藤四郎</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>短刀</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>兄弟</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>14</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>色変幻の術・黄</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>青色のト餓鬼を【最大10体】、黄色に変換する</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="inlineStr">
+        <is>
+          <t>565,58</t>
+        </is>
+      </c>
       <c r="P48" s="1" t="n"/>
       <c r="Q48" s="1" t="n"/>
       <c r="R48" s="1" t="n"/>
@@ -4558,12 +4732,64 @@
       <c r="AP48" s="1" t="n"/>
       <c r="AQ48" s="1" t="n"/>
       <c r="AR48" s="1" t="n"/>
-      <c r="BC48" s="1" t="n"/>
-      <c r="BD48" s="1" t="n"/>
-      <c r="BE48" s="1" t="n"/>
+      <c r="AS48" s="5" t="n"/>
+      <c r="AT48" s="5" t="n"/>
+      <c r="AU48" s="5" t="n"/>
+      <c r="AV48" s="5" t="n"/>
+      <c r="AW48" s="5" t="n"/>
+      <c r="AX48" s="5" t="n"/>
+      <c r="AY48" s="5" t="n"/>
+      <c r="AZ48" s="5" t="n"/>
+      <c r="BA48" s="5" t="n"/>
+      <c r="BB48" s="5" t="n"/>
+      <c r="BC48" s="2" t="n"/>
+      <c r="BD48" s="2" t="n"/>
+      <c r="BE48" s="2" t="n"/>
     </row>
     <row r="49">
-      <c r="O49" s="1" t="n"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>鶯丸</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>太刀</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>鳥</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>赤</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>22</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>霧散斬り・青</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>ランダムな青ト餓鬼を【最大8体】消去し、敵に【小＋＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="inlineStr">
+        <is>
+          <t>626,54</t>
+        </is>
+      </c>
       <c r="P49" s="1" t="n"/>
       <c r="Q49" s="1" t="n"/>
       <c r="R49" s="1" t="n"/>
@@ -4593,9 +4819,19 @@
       <c r="AP49" s="1" t="n"/>
       <c r="AQ49" s="1" t="n"/>
       <c r="AR49" s="1" t="n"/>
-      <c r="BC49" s="1" t="n"/>
-      <c r="BD49" s="1" t="n"/>
-      <c r="BE49" s="1" t="n"/>
+      <c r="AS49" s="5" t="n"/>
+      <c r="AT49" s="5" t="n"/>
+      <c r="AU49" s="5" t="n"/>
+      <c r="AV49" s="5" t="n"/>
+      <c r="AW49" s="5" t="n"/>
+      <c r="AX49" s="5" t="n"/>
+      <c r="AY49" s="5" t="n"/>
+      <c r="AZ49" s="5" t="n"/>
+      <c r="BA49" s="5" t="n"/>
+      <c r="BB49" s="5" t="n"/>
+      <c r="BC49" s="2" t="n"/>
+      <c r="BD49" s="2" t="n"/>
+      <c r="BE49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="O50" s="1" t="n"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -831,11 +831,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>今剣</t>
+          <t>三日月宗近</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>短刀</t>
+          <t>太刀</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>源氏</t>
+          <t>夜</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -859,21 +859,21 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>色変幻の術・赤</t>
+          <t>正円白刃斬り</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>赤以外のト餓鬼を【最大10体】、赤色に変換する</t>
+          <t>【円型・小範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>459,74</t>
+          <t>513,67</t>
         </is>
       </c>
       <c r="P3" s="1" t="n"/>
@@ -905,19 +905,9 @@
       <c r="AP3" s="1" t="n"/>
       <c r="AQ3" s="1" t="n"/>
       <c r="AR3" s="1" t="n"/>
-      <c r="AS3" s="5" t="n"/>
-      <c r="AT3" s="5" t="n"/>
-      <c r="AU3" s="5" t="n"/>
-      <c r="AV3" s="5" t="n"/>
-      <c r="AW3" s="5" t="n"/>
-      <c r="AX3" s="5" t="n"/>
-      <c r="AY3" s="5" t="n"/>
-      <c r="AZ3" s="5" t="n"/>
-      <c r="BA3" s="5" t="n"/>
-      <c r="BB3" s="5" t="n"/>
-      <c r="BC3" s="2" t="n"/>
-      <c r="BD3" s="2" t="n"/>
-      <c r="BE3" s="2" t="n"/>
+      <c r="BC3" s="1" t="n"/>
+      <c r="BD3" s="1" t="n"/>
+      <c r="BE3" s="1" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -933,6 +923,11 @@
           <t>戦装束</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>太刀</t>
@@ -940,7 +935,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>夜</t>
+          <t>夜,天下五剣</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -953,19 +948,15 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>正円白刃斬り</t>
+          <t>月明かりの冴え</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>【円型・小範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O4" s="1" t="inlineStr">
-        <is>
-          <t>513,67</t>
-        </is>
-      </c>
+          <t>【すべて】のト餓鬼を消去し、敵に【特小++】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="n"/>
       <c r="P4" s="1" t="n"/>
       <c r="Q4" s="1" t="n"/>
       <c r="R4" s="1" t="n"/>
@@ -977,7 +968,11 @@
       <c r="X4" s="1" t="n"/>
       <c r="Y4" s="1" t="n"/>
       <c r="Z4" s="1" t="n"/>
-      <c r="AA4" s="1" t="n"/>
+      <c r="AA4" s="1" t="inlineStr">
+        <is>
+          <t>1060,140</t>
+        </is>
+      </c>
       <c r="AB4" s="1" t="n"/>
       <c r="AC4" s="1" t="n"/>
       <c r="AD4" s="1" t="n"/>
@@ -1001,11 +996,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>三日月宗近</t>
+          <t>小狐丸</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1013,11 +1008,6 @@
           <t>戦装束</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>太刀</t>
@@ -1025,7 +1015,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>夜,天下五剣</t>
+          <t>けもの</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1034,23 +1024,31 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>月明かりの冴え</t>
+          <t>ボム練成の術 三の火</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>【すべて】のト餓鬼を消去し、敵に【特小++】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O5" s="1" t="n"/>
+          <t>ボムを【3個】生成する</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>556,58</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="n"/>
       <c r="Q5" s="1" t="n"/>
       <c r="R5" s="1" t="n"/>
-      <c r="S5" s="1" t="n"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>740,77</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="n"/>
       <c r="U5" s="1" t="n"/>
       <c r="V5" s="1" t="n"/>
@@ -1058,11 +1056,7 @@
       <c r="X5" s="1" t="n"/>
       <c r="Y5" s="1" t="n"/>
       <c r="Z5" s="1" t="n"/>
-      <c r="AA5" s="1" t="inlineStr">
-        <is>
-          <t>1060,140</t>
-        </is>
-      </c>
+      <c r="AA5" s="1" t="n"/>
       <c r="AB5" s="1" t="n"/>
       <c r="AC5" s="1" t="n"/>
       <c r="AD5" s="1" t="n"/>
@@ -1086,11 +1080,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小狐丸</t>
+          <t>石切丸</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1100,50 +1094,59 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>大太刀</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>けもの</t>
+          <t>ご神刀</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>青</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ボム練成の術 三の火</t>
+          <t>逆さ扇斬り 守護の型</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ボムを【3個】生成する</t>
+          <t>【扇型・中範囲】のト餓鬼を消去し、敵に【特小－】ダメージを与える。
+味方全員に被ダメージ軽減【極小＋・3手】を付与する</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>556,58</t>
+          <t>561,61</t>
         </is>
       </c>
       <c r="P6" s="1" t="n"/>
       <c r="Q6" s="1" t="n"/>
-      <c r="R6" s="1" t="n"/>
-      <c r="S6" s="1" t="inlineStr">
-        <is>
-          <t>740,77</t>
-        </is>
-      </c>
+      <c r="R6" s="1" t="inlineStr">
+        <is>
+          <t>700,76</t>
+        </is>
+      </c>
+      <c r="S6" s="1" t="n"/>
       <c r="T6" s="1" t="n"/>
       <c r="U6" s="1" t="n"/>
-      <c r="V6" s="1" t="n"/>
+      <c r="V6" s="1" t="inlineStr">
+        <is>
+          <t>886,96</t>
+        </is>
+      </c>
       <c r="W6" s="1" t="n"/>
-      <c r="X6" s="1" t="n"/>
+      <c r="X6" s="1" t="inlineStr">
+        <is>
+          <t>979,106</t>
+        </is>
+      </c>
       <c r="Y6" s="1" t="n"/>
       <c r="Z6" s="1" t="n"/>
       <c r="AA6" s="1" t="n"/>
@@ -1170,11 +1173,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>石切丸</t>
+          <t>岩融</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1184,12 +1187,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>大太刀</t>
+          <t>薙刀</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ご神刀</t>
+          <t>源氏</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1198,76 +1201,31 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>逆さ扇斬り 守護の型</t>
+          <t>大薙ぎ払い・赤</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>【扇型・中範囲】のト餓鬼を消去し、敵に【特小－】ダメージを与える。
-味方全員に被ダメージ軽減【極小＋・3手】を付与する</t>
+          <t>【最大10体】の赤ト餓鬼を盤面の右下に集める</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>561,61</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>700,76</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>886,96</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="inlineStr">
-        <is>
-          <t>979,106</t>
-        </is>
-      </c>
-      <c r="Y7" s="5" t="n"/>
-      <c r="Z7" s="5" t="n"/>
-      <c r="AA7" s="5" t="n"/>
-      <c r="AB7" s="5" t="n"/>
-      <c r="AC7" s="5" t="n"/>
-      <c r="AD7" s="5" t="n"/>
-      <c r="AE7" s="5" t="n"/>
-      <c r="AF7" s="5" t="n"/>
-      <c r="AG7" s="5" t="n"/>
-      <c r="AH7" s="5" t="n"/>
-      <c r="AI7" s="5" t="n"/>
-      <c r="AJ7" s="5" t="n"/>
-      <c r="AK7" s="5" t="n"/>
-      <c r="AL7" s="5" t="n"/>
-      <c r="AM7" s="5" t="n"/>
-      <c r="AN7" s="5" t="n"/>
-      <c r="AO7" s="5" t="n"/>
-      <c r="AP7" s="5" t="n"/>
-      <c r="AQ7" s="5" t="n"/>
-      <c r="AR7" s="5" t="n"/>
-      <c r="BC7" s="5" t="n"/>
-      <c r="BD7" s="5" t="n"/>
-      <c r="BE7" s="5" t="n"/>
+          <t>471,69</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>岩融</t>
+          <t>今剣</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1277,7 +1235,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>薙刀</t>
+          <t>短刀</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1287,67 +1245,77 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>青</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>大薙ぎ払い・赤</t>
+          <t>色変幻の術・赤</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>【最大10体】の赤ト餓鬼を盤面の右下に集める</t>
+          <t>赤以外のト餓鬼を【最大10体】、赤色に変換する</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>471,69</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2" t="n"/>
-      <c r="R8" s="2" t="n"/>
-      <c r="S8" s="2" t="n"/>
-      <c r="T8" s="2" t="n"/>
-      <c r="U8" s="2" t="n"/>
-      <c r="V8" s="2" t="n"/>
-      <c r="W8" s="2" t="n"/>
-      <c r="X8" s="2" t="n"/>
-      <c r="Y8" s="2" t="n"/>
-      <c r="Z8" s="2" t="n"/>
-      <c r="AA8" s="2" t="n"/>
-      <c r="AB8" s="2" t="n"/>
-      <c r="AC8" s="2" t="n"/>
-      <c r="AD8" s="2" t="n"/>
-      <c r="AE8" s="2" t="n"/>
-      <c r="AF8" s="2" t="n"/>
-      <c r="AG8" s="2" t="n"/>
-      <c r="AH8" s="2" t="n"/>
-      <c r="AI8" s="2" t="n"/>
-      <c r="AJ8" s="2" t="n"/>
-      <c r="AK8" s="2" t="n"/>
-      <c r="AL8" s="2" t="n"/>
-      <c r="AM8" s="2" t="n"/>
-      <c r="AN8" s="2" t="n"/>
-      <c r="AO8" s="2" t="n"/>
-      <c r="AP8" s="2" t="n"/>
-      <c r="AQ8" s="2" t="n"/>
-      <c r="AR8" s="2" t="n"/>
+          <t>459,74</t>
+        </is>
+      </c>
+      <c r="P8" s="1" t="n"/>
+      <c r="Q8" s="1" t="n"/>
+      <c r="R8" s="1" t="n"/>
+      <c r="S8" s="1" t="n"/>
+      <c r="T8" s="1" t="n"/>
+      <c r="U8" s="1" t="n"/>
+      <c r="V8" s="1" t="n"/>
+      <c r="W8" s="1" t="n"/>
+      <c r="X8" s="1" t="n"/>
+      <c r="Y8" s="1" t="n"/>
+      <c r="Z8" s="1" t="n"/>
+      <c r="AA8" s="1" t="n"/>
+      <c r="AB8" s="1" t="n"/>
+      <c r="AC8" s="1" t="n"/>
+      <c r="AD8" s="1" t="n"/>
+      <c r="AE8" s="1" t="n"/>
+      <c r="AF8" s="1" t="n"/>
+      <c r="AG8" s="1" t="n"/>
+      <c r="AH8" s="1" t="n"/>
+      <c r="AI8" s="1" t="n"/>
+      <c r="AJ8" s="1" t="n"/>
+      <c r="AK8" s="1" t="n"/>
+      <c r="AL8" s="1" t="n"/>
+      <c r="AM8" s="1" t="n"/>
+      <c r="AN8" s="1" t="n"/>
+      <c r="AO8" s="1" t="n"/>
+      <c r="AP8" s="1" t="n"/>
+      <c r="AQ8" s="1" t="n"/>
+      <c r="AR8" s="1" t="n"/>
+      <c r="AS8" s="5" t="n"/>
+      <c r="AT8" s="5" t="n"/>
+      <c r="AU8" s="5" t="n"/>
+      <c r="AV8" s="5" t="n"/>
+      <c r="AW8" s="5" t="n"/>
+      <c r="AX8" s="5" t="n"/>
+      <c r="AY8" s="5" t="n"/>
+      <c r="AZ8" s="5" t="n"/>
+      <c r="BA8" s="5" t="n"/>
+      <c r="BB8" s="5" t="n"/>
       <c r="BC8" s="2" t="n"/>
       <c r="BD8" s="2" t="n"/>
       <c r="BE8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>鳴狐</t>
+          <t>にっかり青江</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1357,12 +1325,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>脇差</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>けもの</t>
+          <t>夜</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1371,19 +1339,23 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ボム練成の術 二の火</t>
+          <t>守備制約の計</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ボムを【2個】生成する</t>
-        </is>
-      </c>
-      <c r="O9" s="1" t="n"/>
+          <t>敵に被ダメージ増加【極小＋・1手】を付与する</t>
+        </is>
+      </c>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>524,65</t>
+        </is>
+      </c>
       <c r="P9" s="1" t="n"/>
       <c r="Q9" s="1" t="n"/>
       <c r="R9" s="1" t="n"/>
@@ -1410,28 +1382,30 @@
       <c r="AM9" s="1" t="n"/>
       <c r="AN9" s="1" t="n"/>
       <c r="AO9" s="1" t="n"/>
-      <c r="AP9" s="1" t="inlineStr">
-        <is>
-          <t>1505,223</t>
-        </is>
-      </c>
-      <c r="AQ9" s="1" t="inlineStr">
-        <is>
-          <t>1543,229</t>
-        </is>
-      </c>
+      <c r="AP9" s="1" t="n"/>
+      <c r="AQ9" s="1" t="n"/>
       <c r="AR9" s="1" t="n"/>
-      <c r="BC9" s="1" t="n"/>
-      <c r="BD9" s="1" t="n"/>
-      <c r="BE9" s="1" t="n"/>
+      <c r="AS9" s="5" t="n"/>
+      <c r="AT9" s="5" t="n"/>
+      <c r="AU9" s="5" t="n"/>
+      <c r="AV9" s="5" t="n"/>
+      <c r="AW9" s="5" t="n"/>
+      <c r="AX9" s="5" t="n"/>
+      <c r="AY9" s="5" t="n"/>
+      <c r="AZ9" s="5" t="n"/>
+      <c r="BA9" s="5" t="n"/>
+      <c r="BB9" s="5" t="n"/>
+      <c r="BC9" s="2" t="n"/>
+      <c r="BD9" s="2" t="n"/>
+      <c r="BE9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>一期一振</t>
+          <t>鳴狐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1441,30 +1415,30 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>兄弟</t>
+          <t>けもの</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>黄</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>水平一刀斬り</t>
+          <t>ボム練成の術 二の火</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える</t>
+          <t>ボムを【2個】生成する</t>
         </is>
       </c>
       <c r="O10" s="5" t="n"/>
@@ -1477,11 +1451,7 @@
       <c r="V10" s="5" t="n"/>
       <c r="W10" s="5" t="n"/>
       <c r="X10" s="5" t="n"/>
-      <c r="Y10" s="5" t="inlineStr">
-        <is>
-          <t>1050,108</t>
-        </is>
-      </c>
+      <c r="Y10" s="5" t="n"/>
       <c r="Z10" s="5" t="n"/>
       <c r="AA10" s="5" t="n"/>
       <c r="AB10" s="5" t="n"/>
@@ -1498,8 +1468,16 @@
       <c r="AM10" s="5" t="n"/>
       <c r="AN10" s="5" t="n"/>
       <c r="AO10" s="5" t="n"/>
-      <c r="AP10" s="5" t="n"/>
-      <c r="AQ10" s="5" t="n"/>
+      <c r="AP10" s="5" t="inlineStr">
+        <is>
+          <t>1505,223</t>
+        </is>
+      </c>
+      <c r="AQ10" s="5" t="inlineStr">
+        <is>
+          <t>1543,229</t>
+        </is>
+      </c>
       <c r="AR10" s="5" t="n"/>
       <c r="BC10" s="5" t="n"/>
       <c r="BD10" s="5" t="n"/>
@@ -1519,11 +1497,6 @@
           <t>戦装束</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>太刀</t>
@@ -1531,7 +1504,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>兄弟,炎</t>
+          <t>兄弟</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1544,141 +1517,146 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>水平一刀斬り</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O11" s="1" t="n"/>
+      <c r="P11" s="1" t="n"/>
+      <c r="Q11" s="1" t="n"/>
+      <c r="R11" s="1" t="n"/>
+      <c r="S11" s="1" t="n"/>
+      <c r="T11" s="1" t="n"/>
+      <c r="U11" s="1" t="n"/>
+      <c r="V11" s="1" t="n"/>
+      <c r="W11" s="1" t="n"/>
+      <c r="X11" s="1" t="n"/>
+      <c r="Y11" s="1" t="inlineStr">
+        <is>
+          <t>1050,108</t>
+        </is>
+      </c>
+      <c r="Z11" s="1" t="n"/>
+      <c r="AA11" s="1" t="n"/>
+      <c r="AB11" s="1" t="n"/>
+      <c r="AC11" s="1" t="n"/>
+      <c r="AD11" s="1" t="n"/>
+      <c r="AE11" s="1" t="n"/>
+      <c r="AF11" s="1" t="n"/>
+      <c r="AG11" s="1" t="n"/>
+      <c r="AH11" s="1" t="n"/>
+      <c r="AI11" s="1" t="n"/>
+      <c r="AJ11" s="1" t="n"/>
+      <c r="AK11" s="1" t="n"/>
+      <c r="AL11" s="1" t="n"/>
+      <c r="AM11" s="1" t="n"/>
+      <c r="AN11" s="1" t="n"/>
+      <c r="AO11" s="1" t="n"/>
+      <c r="AP11" s="1" t="n"/>
+      <c r="AQ11" s="1" t="n"/>
+      <c r="AR11" s="1" t="n"/>
+      <c r="BC11" s="1" t="n"/>
+      <c r="BD11" s="1" t="n"/>
+      <c r="BE11" s="1" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>一期一振</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>戦装束</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>太刀</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>兄弟,炎</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>黄</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>華々しき雄飛への導き</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>自身・脇差・短刀にブレイク力上昇【大・6手】を付与する
 自身・脇差・短刀に攻撃力上昇【特小＋・6手】を付与する
 バリア【1回】を付与する</t>
         </is>
       </c>
-      <c r="O11" s="2" t="n"/>
-      <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="n"/>
-      <c r="R11" s="2" t="n"/>
-      <c r="S11" s="2" t="n"/>
-      <c r="T11" s="2" t="n"/>
-      <c r="U11" s="2" t="n"/>
-      <c r="V11" s="2" t="n"/>
-      <c r="W11" s="2" t="n"/>
-      <c r="X11" s="2" t="n"/>
-      <c r="Y11" s="2" t="n"/>
-      <c r="Z11" s="2" t="n"/>
-      <c r="AA11" s="2" t="n"/>
-      <c r="AB11" s="2" t="n"/>
-      <c r="AC11" s="2" t="n"/>
-      <c r="AD11" s="2" t="n"/>
-      <c r="AE11" s="2" t="n"/>
-      <c r="AF11" s="2" t="n"/>
-      <c r="AG11" s="2" t="n"/>
-      <c r="AH11" s="2" t="n"/>
-      <c r="AI11" s="2" t="n"/>
-      <c r="AJ11" s="2" t="n"/>
-      <c r="AK11" s="2" t="n"/>
-      <c r="AL11" s="1" t="inlineStr">
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2" t="n"/>
+      <c r="T12" s="2" t="n"/>
+      <c r="U12" s="2" t="n"/>
+      <c r="V12" s="2" t="n"/>
+      <c r="W12" s="2" t="n"/>
+      <c r="X12" s="2" t="n"/>
+      <c r="Y12" s="2" t="n"/>
+      <c r="Z12" s="2" t="n"/>
+      <c r="AA12" s="2" t="n"/>
+      <c r="AB12" s="2" t="n"/>
+      <c r="AC12" s="2" t="n"/>
+      <c r="AD12" s="2" t="n"/>
+      <c r="AE12" s="2" t="n"/>
+      <c r="AF12" s="2" t="n"/>
+      <c r="AG12" s="2" t="n"/>
+      <c r="AH12" s="2" t="n"/>
+      <c r="AI12" s="2" t="n"/>
+      <c r="AJ12" s="2" t="n"/>
+      <c r="AK12" s="2" t="n"/>
+      <c r="AL12" s="1" t="inlineStr">
         <is>
           <t>1673,173</t>
         </is>
       </c>
-      <c r="AM11" s="2" t="n"/>
-      <c r="AN11" s="2" t="n"/>
-      <c r="AO11" s="2" t="n"/>
-      <c r="AP11" s="2" t="n"/>
-      <c r="AQ11" s="2" t="n"/>
-      <c r="AR11" s="2" t="n"/>
-      <c r="BC11" s="2" t="n"/>
-      <c r="BD11" s="2" t="n"/>
-      <c r="BE11" s="2" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>27</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>鯰尾藤四郎</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>戦装束</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>脇差</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>兄弟</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>赤</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>大薙ぎ払い・青</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>【最大10体】の青ト餓鬼を盤面の下に集める</t>
-        </is>
-      </c>
-      <c r="O12" s="1" t="n"/>
-      <c r="P12" s="1" t="n"/>
-      <c r="Q12" s="1" t="n"/>
-      <c r="R12" s="1" t="n"/>
-      <c r="S12" s="1" t="n"/>
-      <c r="T12" s="1" t="n"/>
-      <c r="U12" s="1" t="n"/>
-      <c r="V12" s="1" t="n"/>
-      <c r="W12" s="1" t="n"/>
-      <c r="X12" s="1" t="n"/>
-      <c r="Y12" s="1" t="n"/>
-      <c r="Z12" s="1" t="n"/>
-      <c r="AA12" s="1" t="n"/>
-      <c r="AB12" s="1" t="n"/>
-      <c r="AC12" s="1" t="n"/>
-      <c r="AD12" s="1" t="n"/>
-      <c r="AE12" s="1" t="n"/>
-      <c r="AF12" s="1" t="n"/>
-      <c r="AG12" s="1" t="n"/>
-      <c r="AH12" s="1" t="n"/>
-      <c r="AI12" s="1" t="n"/>
-      <c r="AJ12" s="1" t="inlineStr">
-        <is>
-          <t>1357,188</t>
-        </is>
-      </c>
-      <c r="AK12" s="1" t="n"/>
-      <c r="AL12" s="1" t="n"/>
-      <c r="AM12" s="1" t="n"/>
-      <c r="AN12" s="1" t="n"/>
-      <c r="AO12" s="1" t="n"/>
-      <c r="AP12" s="1" t="n"/>
-      <c r="AQ12" s="1" t="n"/>
-      <c r="AR12" s="1" t="n"/>
-      <c r="BC12" s="1" t="n"/>
-      <c r="BD12" s="1" t="n"/>
-      <c r="BE12" s="1" t="n"/>
+      <c r="AM12" s="2" t="n"/>
+      <c r="AN12" s="2" t="n"/>
+      <c r="AO12" s="2" t="n"/>
+      <c r="AP12" s="2" t="n"/>
+      <c r="AQ12" s="2" t="n"/>
+      <c r="AR12" s="2" t="n"/>
+      <c r="BC12" s="2" t="n"/>
+      <c r="BD12" s="2" t="n"/>
+      <c r="BE12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>骨喰藤四郎</t>
+          <t>鯰尾藤四郎</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1698,20 +1676,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>黄</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>色変幻の術・青</t>
+          <t>大薙ぎ払い・青</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>青以外のト餓鬼を【最大10体】、青色に変換する</t>
+          <t>【最大10体】の青ト餓鬼を盤面の下に集める</t>
         </is>
       </c>
       <c r="O13" s="1" t="n"/>
@@ -1729,17 +1707,17 @@
       <c r="AA13" s="1" t="n"/>
       <c r="AB13" s="1" t="n"/>
       <c r="AC13" s="1" t="n"/>
-      <c r="AD13" s="1" t="inlineStr">
-        <is>
-          <t>1024,163</t>
-        </is>
-      </c>
+      <c r="AD13" s="1" t="n"/>
       <c r="AE13" s="1" t="n"/>
       <c r="AF13" s="1" t="n"/>
       <c r="AG13" s="1" t="n"/>
       <c r="AH13" s="1" t="n"/>
       <c r="AI13" s="1" t="n"/>
-      <c r="AJ13" s="1" t="n"/>
+      <c r="AJ13" s="1" t="inlineStr">
+        <is>
+          <t>1357,188</t>
+        </is>
+      </c>
       <c r="AK13" s="1" t="n"/>
       <c r="AL13" s="1" t="n"/>
       <c r="AM13" s="1" t="n"/>
@@ -1754,11 +1732,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>平野藤四郎</t>
+          <t>骨喰藤四郎</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1768,7 +1746,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>短刀</t>
+          <t>脇差</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1778,7 +1756,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>青</t>
+          <t>黄</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1786,12 +1764,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>色変幻の術・赤</t>
+          <t>色変幻の術・青</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>黄色のト餓鬼を【最大10体】、赤色に変換する</t>
+          <t>青以外のト餓鬼を【最大10体】、青色に変換する</t>
         </is>
       </c>
       <c r="O14" s="1" t="n"/>
@@ -1809,7 +1787,11 @@
       <c r="AA14" s="1" t="n"/>
       <c r="AB14" s="1" t="n"/>
       <c r="AC14" s="1" t="n"/>
-      <c r="AD14" s="1" t="n"/>
+      <c r="AD14" s="1" t="inlineStr">
+        <is>
+          <t>1024,163</t>
+        </is>
+      </c>
       <c r="AE14" s="1" t="n"/>
       <c r="AF14" s="1" t="n"/>
       <c r="AG14" s="1" t="n"/>
@@ -1823,22 +1805,18 @@
       <c r="AO14" s="1" t="n"/>
       <c r="AP14" s="1" t="n"/>
       <c r="AQ14" s="1" t="n"/>
-      <c r="AR14" s="1" t="inlineStr">
-        <is>
-          <t>1691,232</t>
-        </is>
-      </c>
+      <c r="AR14" s="1" t="n"/>
       <c r="BC14" s="1" t="n"/>
       <c r="BD14" s="1" t="n"/>
       <c r="BE14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>厚藤四郎</t>
+          <t>平野藤四郎</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1858,7 +1836,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>黄</t>
+          <t>青</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1866,19 +1844,15 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>色変幻の術・青</t>
+          <t>色変幻の術・赤</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>赤色のト餓鬼を【最大10体】、青色に変換する</t>
-        </is>
-      </c>
-      <c r="O15" s="1" t="inlineStr">
-        <is>
-          <t>440,77</t>
-        </is>
-      </c>
+          <t>黄色のト餓鬼を【最大10体】、赤色に変換する</t>
+        </is>
+      </c>
+      <c r="O15" s="1" t="n"/>
       <c r="P15" s="1" t="n"/>
       <c r="Q15" s="1" t="n"/>
       <c r="R15" s="1" t="n"/>
@@ -1907,18 +1881,22 @@
       <c r="AO15" s="1" t="n"/>
       <c r="AP15" s="1" t="n"/>
       <c r="AQ15" s="1" t="n"/>
-      <c r="AR15" s="1" t="n"/>
+      <c r="AR15" s="1" t="inlineStr">
+        <is>
+          <t>1691,232</t>
+        </is>
+      </c>
       <c r="BC15" s="1" t="n"/>
       <c r="BD15" s="1" t="n"/>
       <c r="BE15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>乱藤四郎</t>
+          <t>厚藤四郎</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1942,19 +1920,23 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>色変幻の術・乱</t>
+          <t>色変幻の術・青</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ト餓鬼を【最大10体】、ランダムな色に変換する</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="n"/>
+          <t>赤色のト餓鬼を【最大10体】、青色に変換する</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>440,77</t>
+        </is>
+      </c>
       <c r="P16" s="5" t="n"/>
       <c r="Q16" s="5" t="n"/>
       <c r="R16" s="5" t="n"/>
@@ -1963,11 +1945,7 @@
       <c r="U16" s="5" t="n"/>
       <c r="V16" s="5" t="n"/>
       <c r="W16" s="5" t="n"/>
-      <c r="X16" s="5" t="inlineStr">
-        <is>
-          <t>905,100</t>
-        </is>
-      </c>
+      <c r="X16" s="5" t="n"/>
       <c r="Y16" s="5" t="n"/>
       <c r="Z16" s="5" t="n"/>
       <c r="AA16" s="5" t="n"/>
@@ -1994,11 +1972,11 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>乱藤四郎</t>
+          <t>前田藤四郎</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2006,11 +1984,6 @@
           <t>戦装束</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>短刀</t>
@@ -2018,7 +1991,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>兄弟,花</t>
+          <t>兄弟</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2027,64 +2000,73 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>百花乱々みだれ咲き</t>
+          <t>色変幻の術・黄</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>味方全員に攻撃力上昇【極小＋＋・3手】を付与する
-敵に被ダメージ増加【極小＋・3手】を付与する</t>
+          <t>青色のト餓鬼を【最大10体】、黄色に変換する</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>532,59</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="n"/>
-      <c r="Q17" s="2" t="n"/>
-      <c r="R17" s="2" t="n"/>
-      <c r="S17" s="2" t="n"/>
-      <c r="T17" s="2" t="n"/>
-      <c r="U17" s="2" t="n"/>
-      <c r="V17" s="2" t="n"/>
-      <c r="W17" s="2" t="n"/>
-      <c r="X17" s="2" t="n"/>
-      <c r="Y17" s="2" t="n"/>
-      <c r="Z17" s="2" t="n"/>
-      <c r="AA17" s="2" t="n"/>
-      <c r="AB17" s="2" t="n"/>
-      <c r="AC17" s="2" t="n"/>
-      <c r="AD17" s="2" t="n"/>
-      <c r="AE17" s="2" t="n"/>
-      <c r="AF17" s="2" t="n"/>
-      <c r="AG17" s="2" t="n"/>
-      <c r="AH17" s="2" t="n"/>
-      <c r="AI17" s="2" t="n"/>
-      <c r="AJ17" s="2" t="n"/>
-      <c r="AK17" s="2" t="n"/>
-      <c r="AL17" s="2" t="n"/>
-      <c r="AM17" s="2" t="n"/>
-      <c r="AN17" s="2" t="n"/>
-      <c r="AO17" s="2" t="n"/>
-      <c r="AP17" s="2" t="n"/>
-      <c r="AQ17" s="2" t="n"/>
-      <c r="AR17" s="2" t="n"/>
+          <t>565,58</t>
+        </is>
+      </c>
+      <c r="P17" s="1" t="n"/>
+      <c r="Q17" s="1" t="n"/>
+      <c r="R17" s="1" t="n"/>
+      <c r="S17" s="1" t="n"/>
+      <c r="T17" s="1" t="n"/>
+      <c r="U17" s="1" t="n"/>
+      <c r="V17" s="1" t="n"/>
+      <c r="W17" s="1" t="n"/>
+      <c r="X17" s="1" t="n"/>
+      <c r="Y17" s="1" t="n"/>
+      <c r="Z17" s="1" t="n"/>
+      <c r="AA17" s="1" t="n"/>
+      <c r="AB17" s="1" t="n"/>
+      <c r="AC17" s="1" t="n"/>
+      <c r="AD17" s="1" t="n"/>
+      <c r="AE17" s="1" t="n"/>
+      <c r="AF17" s="1" t="n"/>
+      <c r="AG17" s="1" t="n"/>
+      <c r="AH17" s="1" t="n"/>
+      <c r="AI17" s="1" t="n"/>
+      <c r="AJ17" s="1" t="n"/>
+      <c r="AK17" s="1" t="n"/>
+      <c r="AL17" s="1" t="n"/>
+      <c r="AM17" s="1" t="n"/>
+      <c r="AN17" s="1" t="n"/>
+      <c r="AO17" s="1" t="n"/>
+      <c r="AP17" s="1" t="n"/>
+      <c r="AQ17" s="1" t="n"/>
+      <c r="AR17" s="1" t="n"/>
+      <c r="AS17" s="5" t="n"/>
+      <c r="AT17" s="5" t="n"/>
+      <c r="AU17" s="5" t="n"/>
+      <c r="AV17" s="5" t="n"/>
+      <c r="AW17" s="5" t="n"/>
+      <c r="AX17" s="5" t="n"/>
+      <c r="AY17" s="5" t="n"/>
+      <c r="AZ17" s="5" t="n"/>
+      <c r="BA17" s="5" t="n"/>
+      <c r="BB17" s="5" t="n"/>
       <c r="BC17" s="2" t="n"/>
       <c r="BD17" s="2" t="n"/>
       <c r="BE17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>五虎退</t>
+          <t>秋田藤四郎</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2108,21 +2090,21 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ボム練成の術 一の火</t>
+          <t>受け流しの法</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>ボムを【1個】生成する</t>
+          <t>味方全員にガード率上昇【中－・5手】を付与する</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>477,56</t>
+          <t>473,60</t>
         </is>
       </c>
       <c r="P18" s="5" t="n"/>
@@ -2154,17 +2136,24 @@
       <c r="AP18" s="5" t="n"/>
       <c r="AQ18" s="5" t="n"/>
       <c r="AR18" s="5" t="n"/>
-      <c r="BC18" s="5" t="n"/>
-      <c r="BD18" s="5" t="n"/>
-      <c r="BE18" s="5" t="n"/>
+      <c r="AS18" s="5" t="n"/>
+      <c r="AT18" s="5" t="n"/>
+      <c r="AU18" s="5" t="n"/>
+      <c r="AV18" s="5" t="n"/>
+      <c r="AW18" s="5" t="n"/>
+      <c r="AX18" s="5" t="n"/>
+      <c r="AY18" s="5" t="n"/>
+      <c r="AZ18" s="5" t="n"/>
+      <c r="BA18" s="5" t="n"/>
+      <c r="BB18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>太郎太刀</t>
+          <t>乱藤四郎</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2174,37 +2163,33 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>大太刀</t>
+          <t>短刀</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ご神刀</t>
+          <t>兄弟</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>黄</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>霧散斬り・黄</t>
+          <t>色変幻の術・乱</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>黄ト餓鬼をランダムに【最大10体】消去し、敵に【小＋】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>588,64</t>
-        </is>
-      </c>
+          <t>ト餓鬼を【最大10体】、ランダムな色に変換する</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="n"/>
       <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="n"/>
       <c r="R19" s="5" t="n"/>
@@ -2213,7 +2198,11 @@
       <c r="U19" s="5" t="n"/>
       <c r="V19" s="5" t="n"/>
       <c r="W19" s="5" t="n"/>
-      <c r="X19" s="5" t="n"/>
+      <c r="X19" s="5" t="inlineStr">
+        <is>
+          <t>905,100</t>
+        </is>
+      </c>
       <c r="Y19" s="5" t="n"/>
       <c r="Z19" s="5" t="n"/>
       <c r="AA19" s="5" t="n"/>
@@ -2234,24 +2223,17 @@
       <c r="AP19" s="5" t="n"/>
       <c r="AQ19" s="5" t="n"/>
       <c r="AR19" s="5" t="n"/>
-      <c r="AS19" s="5" t="n"/>
-      <c r="AT19" s="5" t="n"/>
-      <c r="AU19" s="5" t="n"/>
-      <c r="AV19" s="5" t="n"/>
-      <c r="AW19" s="5" t="n"/>
-      <c r="AX19" s="5" t="n"/>
-      <c r="AY19" s="5" t="n"/>
-      <c r="AZ19" s="5" t="n"/>
-      <c r="BA19" s="5" t="n"/>
-      <c r="BB19" s="5" t="n"/>
+      <c r="BC19" s="5" t="n"/>
+      <c r="BD19" s="5" t="n"/>
+      <c r="BE19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>太郎太刀</t>
+          <t>乱藤四郎</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2266,12 +2248,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>大太刀</t>
+          <t>短刀</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ご神刀,兄弟</t>
+          <t>兄弟,花</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2280,70 +2262,32 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>天より墜つる暴威</t>
+          <t>百花乱々みだれ咲き</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える。ボスが被ダメージ増加状態のとき、さらに威力が上昇する</t>
+          <t>味方全員に攻撃力上昇【極小＋＋・3手】を付与する
+敵に被ダメージ増加【極小＋・3手】を付与する</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>613,67</t>
-        </is>
-      </c>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="5" t="n"/>
-      <c r="T20" s="5" t="n"/>
-      <c r="U20" s="5" t="n"/>
-      <c r="V20" s="5" t="n"/>
-      <c r="W20" s="5" t="n"/>
-      <c r="X20" s="5" t="n"/>
-      <c r="Y20" s="5" t="n"/>
-      <c r="Z20" s="5" t="n"/>
-      <c r="AA20" s="5" t="n"/>
-      <c r="AB20" s="5" t="n"/>
-      <c r="AC20" s="5" t="n"/>
-      <c r="AD20" s="5" t="n"/>
-      <c r="AE20" s="5" t="n"/>
-      <c r="AF20" s="5" t="n"/>
-      <c r="AG20" s="5" t="n"/>
-      <c r="AH20" s="5" t="n"/>
-      <c r="AI20" s="5" t="n"/>
-      <c r="AJ20" s="5" t="n"/>
-      <c r="AK20" s="5" t="n"/>
-      <c r="AL20" s="5" t="n"/>
-      <c r="AM20" s="5" t="n"/>
-      <c r="AN20" s="5" t="n"/>
-      <c r="AO20" s="5" t="n"/>
-      <c r="AP20" s="5" t="n"/>
-      <c r="AQ20" s="5" t="n"/>
-      <c r="AR20" s="5" t="n"/>
-      <c r="AS20" s="5" t="n"/>
-      <c r="AT20" s="5" t="n"/>
-      <c r="AU20" s="5" t="n"/>
-      <c r="AV20" s="5" t="n"/>
-      <c r="AW20" s="5" t="n"/>
-      <c r="AX20" s="5" t="n"/>
-      <c r="AY20" s="5" t="n"/>
-      <c r="AZ20" s="5" t="n"/>
-      <c r="BA20" s="5" t="n"/>
-      <c r="BB20" s="5" t="n"/>
+          <t>532,59</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>次郎太刀</t>
+          <t>五虎退</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2353,12 +2297,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>大太刀</t>
+          <t>短刀</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ご神刀</t>
+          <t>兄弟</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2367,21 +2311,21 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>正円一刀斬り</t>
+          <t>ボム練成の術 一の火</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>【円型・大範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える</t>
+          <t>ボムを【1個】生成する</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>501,71</t>
+          <t>477,56</t>
         </is>
       </c>
       <c r="P21" s="1" t="n"/>
@@ -2413,27 +2357,17 @@
       <c r="AP21" s="1" t="n"/>
       <c r="AQ21" s="1" t="n"/>
       <c r="AR21" s="1" t="n"/>
-      <c r="AS21" s="5" t="n"/>
-      <c r="AT21" s="5" t="n"/>
-      <c r="AU21" s="5" t="n"/>
-      <c r="AV21" s="5" t="n"/>
-      <c r="AW21" s="5" t="n"/>
-      <c r="AX21" s="5" t="n"/>
-      <c r="AY21" s="5" t="n"/>
-      <c r="AZ21" s="5" t="n"/>
-      <c r="BA21" s="5" t="n"/>
-      <c r="BB21" s="5" t="n"/>
-      <c r="BC21" s="2" t="n"/>
-      <c r="BD21" s="2" t="n"/>
-      <c r="BE21" s="2" t="n"/>
+      <c r="BC21" s="1" t="n"/>
+      <c r="BD21" s="1" t="n"/>
+      <c r="BE21" s="1" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>蛍丸</t>
+          <t>薬研藤四郎</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2443,77 +2377,88 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>大太刀</t>
+          <t>短刀</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>夜</t>
+          <t>兄弟</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>青</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>正円一刀斬り</t>
+          <t>真っ向斬り 攻勢の型</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="n"/>
-      <c r="P22" s="2" t="n"/>
-      <c r="Q22" s="2" t="n"/>
-      <c r="R22" s="2" t="n"/>
-      <c r="S22" s="2" t="n"/>
-      <c r="T22" s="1" t="inlineStr">
-        <is>
-          <t>677,107</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="n"/>
-      <c r="V22" s="2" t="n"/>
-      <c r="W22" s="2" t="n"/>
-      <c r="X22" s="2" t="n"/>
-      <c r="Y22" s="2" t="n"/>
-      <c r="Z22" s="2" t="n"/>
-      <c r="AA22" s="2" t="n"/>
-      <c r="AB22" s="2" t="n"/>
-      <c r="AC22" s="2" t="n"/>
-      <c r="AD22" s="2" t="n"/>
-      <c r="AE22" s="2" t="n"/>
-      <c r="AF22" s="2" t="n"/>
-      <c r="AG22" s="2" t="n"/>
-      <c r="AH22" s="2" t="n"/>
-      <c r="AI22" s="2" t="n"/>
-      <c r="AJ22" s="2" t="n"/>
-      <c r="AK22" s="2" t="n"/>
-      <c r="AL22" s="2" t="n"/>
-      <c r="AM22" s="2" t="n"/>
-      <c r="AN22" s="2" t="n"/>
-      <c r="AO22" s="2" t="n"/>
-      <c r="AP22" s="2" t="n"/>
-      <c r="AQ22" s="2" t="n"/>
-      <c r="AR22" s="2" t="n"/>
+          <t>【縦列・特小範囲】のト餓鬼を消去し、敵に【極小】ダメージを与える
+味方全員にクリティカル率上昇【小・3手】を付与する</t>
+        </is>
+      </c>
+      <c r="O22" s="1" t="inlineStr">
+        <is>
+          <t>542,55</t>
+        </is>
+      </c>
+      <c r="P22" s="1" t="n"/>
+      <c r="Q22" s="1" t="n"/>
+      <c r="R22" s="1" t="n"/>
+      <c r="S22" s="1" t="n"/>
+      <c r="T22" s="1" t="n"/>
+      <c r="U22" s="1" t="n"/>
+      <c r="V22" s="1" t="n"/>
+      <c r="W22" s="1" t="n"/>
+      <c r="X22" s="1" t="n"/>
+      <c r="Y22" s="1" t="n"/>
+      <c r="Z22" s="1" t="n"/>
+      <c r="AA22" s="1" t="n"/>
+      <c r="AB22" s="1" t="n"/>
+      <c r="AC22" s="1" t="n"/>
+      <c r="AD22" s="1" t="n"/>
+      <c r="AE22" s="1" t="n"/>
+      <c r="AF22" s="1" t="n"/>
+      <c r="AG22" s="1" t="n"/>
+      <c r="AH22" s="1" t="n"/>
+      <c r="AI22" s="1" t="n"/>
+      <c r="AJ22" s="1" t="n"/>
+      <c r="AK22" s="1" t="n"/>
+      <c r="AL22" s="1" t="n"/>
+      <c r="AM22" s="1" t="n"/>
+      <c r="AN22" s="1" t="n"/>
+      <c r="AO22" s="1" t="n"/>
+      <c r="AP22" s="1" t="n"/>
+      <c r="AQ22" s="1" t="n"/>
+      <c r="AR22" s="1" t="n"/>
+      <c r="AS22" s="5" t="n"/>
+      <c r="AT22" s="5" t="n"/>
+      <c r="AU22" s="5" t="n"/>
+      <c r="AV22" s="5" t="n"/>
+      <c r="AW22" s="5" t="n"/>
+      <c r="AX22" s="5" t="n"/>
+      <c r="AY22" s="5" t="n"/>
+      <c r="AZ22" s="5" t="n"/>
+      <c r="BA22" s="5" t="n"/>
+      <c r="BB22" s="5" t="n"/>
       <c r="BC22" s="2" t="n"/>
       <c r="BD22" s="2" t="n"/>
       <c r="BE22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>蜻蛉切</t>
+          <t>鶯丸</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2523,17 +2468,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>槍</t>
+          <t>太刀</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>天下三名槍</t>
+          <t>鳥</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>黄</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2541,59 +2486,69 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>必中縦断突き</t>
+          <t>霧散斬り・青</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>指定した【縦列・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
+          <t>ランダムな青ト餓鬼を【最大8体】消去し、敵に【小＋＋】ダメージを与える</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>551,72</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="n"/>
-      <c r="Q23" s="2" t="n"/>
-      <c r="R23" s="2" t="n"/>
-      <c r="S23" s="2" t="n"/>
-      <c r="T23" s="2" t="n"/>
-      <c r="U23" s="2" t="n"/>
-      <c r="V23" s="2" t="n"/>
-      <c r="W23" s="2" t="n"/>
-      <c r="X23" s="2" t="n"/>
-      <c r="Y23" s="2" t="n"/>
-      <c r="Z23" s="2" t="n"/>
-      <c r="AA23" s="2" t="n"/>
-      <c r="AB23" s="2" t="n"/>
-      <c r="AC23" s="2" t="n"/>
-      <c r="AD23" s="2" t="n"/>
-      <c r="AE23" s="2" t="n"/>
-      <c r="AF23" s="2" t="n"/>
-      <c r="AG23" s="2" t="n"/>
-      <c r="AH23" s="2" t="n"/>
-      <c r="AI23" s="2" t="n"/>
-      <c r="AJ23" s="2" t="n"/>
-      <c r="AK23" s="2" t="n"/>
-      <c r="AL23" s="2" t="n"/>
-      <c r="AM23" s="2" t="n"/>
-      <c r="AN23" s="2" t="n"/>
-      <c r="AO23" s="2" t="n"/>
-      <c r="AP23" s="2" t="n"/>
-      <c r="AQ23" s="2" t="n"/>
-      <c r="AR23" s="2" t="n"/>
+          <t>626,54</t>
+        </is>
+      </c>
+      <c r="P23" s="1" t="n"/>
+      <c r="Q23" s="1" t="n"/>
+      <c r="R23" s="1" t="n"/>
+      <c r="S23" s="1" t="n"/>
+      <c r="T23" s="1" t="n"/>
+      <c r="U23" s="1" t="n"/>
+      <c r="V23" s="1" t="n"/>
+      <c r="W23" s="1" t="n"/>
+      <c r="X23" s="1" t="n"/>
+      <c r="Y23" s="1" t="n"/>
+      <c r="Z23" s="1" t="n"/>
+      <c r="AA23" s="1" t="n"/>
+      <c r="AB23" s="1" t="n"/>
+      <c r="AC23" s="1" t="n"/>
+      <c r="AD23" s="1" t="n"/>
+      <c r="AE23" s="1" t="n"/>
+      <c r="AF23" s="1" t="n"/>
+      <c r="AG23" s="1" t="n"/>
+      <c r="AH23" s="1" t="n"/>
+      <c r="AI23" s="1" t="n"/>
+      <c r="AJ23" s="1" t="n"/>
+      <c r="AK23" s="1" t="n"/>
+      <c r="AL23" s="1" t="n"/>
+      <c r="AM23" s="1" t="n"/>
+      <c r="AN23" s="1" t="n"/>
+      <c r="AO23" s="1" t="n"/>
+      <c r="AP23" s="1" t="n"/>
+      <c r="AQ23" s="1" t="n"/>
+      <c r="AR23" s="1" t="n"/>
+      <c r="AS23" s="5" t="n"/>
+      <c r="AT23" s="5" t="n"/>
+      <c r="AU23" s="5" t="n"/>
+      <c r="AV23" s="5" t="n"/>
+      <c r="AW23" s="5" t="n"/>
+      <c r="AX23" s="5" t="n"/>
+      <c r="AY23" s="5" t="n"/>
+      <c r="AZ23" s="5" t="n"/>
+      <c r="BA23" s="5" t="n"/>
+      <c r="BB23" s="5" t="n"/>
       <c r="BC23" s="2" t="n"/>
       <c r="BD23" s="2" t="n"/>
       <c r="BE23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>御手杵</t>
+          <t>蛍丸</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2603,87 +2558,77 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>槍</t>
+          <t>大太刀</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>天下三名槍</t>
+          <t>夜</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>青</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>必中正円突き</t>
+          <t>正円一刀斬り</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>指定した1箇所【円型・特小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O24" s="1" t="inlineStr">
-        <is>
-          <t>461,60</t>
-        </is>
-      </c>
-      <c r="P24" s="1" t="n"/>
-      <c r="Q24" s="1" t="n"/>
-      <c r="R24" s="1" t="n"/>
-      <c r="S24" s="1" t="n"/>
-      <c r="T24" s="1" t="n"/>
-      <c r="U24" s="1" t="n"/>
-      <c r="V24" s="1" t="n"/>
-      <c r="W24" s="1" t="n"/>
-      <c r="X24" s="1" t="n"/>
-      <c r="Y24" s="1" t="n"/>
-      <c r="Z24" s="1" t="n"/>
-      <c r="AA24" s="1" t="n"/>
-      <c r="AB24" s="1" t="n"/>
-      <c r="AC24" s="1" t="n"/>
-      <c r="AD24" s="1" t="n"/>
-      <c r="AE24" s="1" t="n"/>
-      <c r="AF24" s="1" t="n"/>
-      <c r="AG24" s="1" t="n"/>
-      <c r="AH24" s="1" t="n"/>
-      <c r="AI24" s="1" t="n"/>
-      <c r="AJ24" s="1" t="n"/>
-      <c r="AK24" s="1" t="n"/>
-      <c r="AL24" s="1" t="n"/>
-      <c r="AM24" s="1" t="n"/>
-      <c r="AN24" s="1" t="n"/>
-      <c r="AO24" s="1" t="n"/>
-      <c r="AP24" s="1" t="n"/>
-      <c r="AQ24" s="1" t="n"/>
-      <c r="AR24" s="1" t="n"/>
-      <c r="AS24" s="5" t="n"/>
-      <c r="AT24" s="5" t="n"/>
-      <c r="AU24" s="5" t="n"/>
-      <c r="AV24" s="5" t="n"/>
-      <c r="AW24" s="5" t="n"/>
-      <c r="AX24" s="5" t="n"/>
-      <c r="AY24" s="5" t="n"/>
-      <c r="AZ24" s="5" t="n"/>
-      <c r="BA24" s="5" t="n"/>
-      <c r="BB24" s="5" t="n"/>
+          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
+      <c r="T24" s="1" t="inlineStr">
+        <is>
+          <t>677,107</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="n"/>
+      <c r="V24" s="2" t="n"/>
+      <c r="W24" s="2" t="n"/>
+      <c r="X24" s="2" t="n"/>
+      <c r="Y24" s="2" t="n"/>
+      <c r="Z24" s="2" t="n"/>
+      <c r="AA24" s="2" t="n"/>
+      <c r="AB24" s="2" t="n"/>
+      <c r="AC24" s="2" t="n"/>
+      <c r="AD24" s="2" t="n"/>
+      <c r="AE24" s="2" t="n"/>
+      <c r="AF24" s="2" t="n"/>
+      <c r="AG24" s="2" t="n"/>
+      <c r="AH24" s="2" t="n"/>
+      <c r="AI24" s="2" t="n"/>
+      <c r="AJ24" s="2" t="n"/>
+      <c r="AK24" s="2" t="n"/>
+      <c r="AL24" s="2" t="n"/>
+      <c r="AM24" s="2" t="n"/>
+      <c r="AN24" s="2" t="n"/>
+      <c r="AO24" s="2" t="n"/>
+      <c r="AP24" s="2" t="n"/>
+      <c r="AQ24" s="2" t="n"/>
+      <c r="AR24" s="2" t="n"/>
       <c r="BC24" s="2" t="n"/>
       <c r="BD24" s="2" t="n"/>
       <c r="BE24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>江雪左文字</t>
+          <t>愛染国俊</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2693,12 +2638,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>短刀</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>雪</t>
+          <t>炎</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2707,64 +2652,74 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>霧散斬り 先手の型</t>
+          <t>強攻の法</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ランダムなト餓鬼（攻撃指示優先）を最大5体消去し、敵に【特小＋＋】ダメージを与える
-消去時のブレイクゲージ減少量が【2倍】になる</t>
+          <t>自身に攻撃力上昇【特小・1手】を付与する
+自身に攻撃力上昇【極小＋・1手】を付与する</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>507,74</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="n"/>
-      <c r="Q25" s="2" t="n"/>
-      <c r="R25" s="2" t="n"/>
-      <c r="S25" s="2" t="n"/>
-      <c r="T25" s="2" t="n"/>
-      <c r="U25" s="2" t="n"/>
-      <c r="V25" s="2" t="n"/>
-      <c r="W25" s="2" t="n"/>
-      <c r="X25" s="2" t="n"/>
-      <c r="Y25" s="2" t="n"/>
-      <c r="Z25" s="2" t="n"/>
-      <c r="AA25" s="2" t="n"/>
-      <c r="AB25" s="2" t="n"/>
-      <c r="AC25" s="2" t="n"/>
-      <c r="AD25" s="2" t="n"/>
-      <c r="AE25" s="2" t="n"/>
-      <c r="AF25" s="2" t="n"/>
-      <c r="AG25" s="2" t="n"/>
-      <c r="AH25" s="2" t="n"/>
-      <c r="AI25" s="2" t="n"/>
-      <c r="AJ25" s="2" t="n"/>
-      <c r="AK25" s="2" t="n"/>
-      <c r="AL25" s="2" t="n"/>
-      <c r="AM25" s="2" t="n"/>
-      <c r="AN25" s="2" t="n"/>
-      <c r="AO25" s="2" t="n"/>
-      <c r="AP25" s="2" t="n"/>
-      <c r="AQ25" s="2" t="n"/>
-      <c r="AR25" s="2" t="n"/>
+          <t>483,62</t>
+        </is>
+      </c>
+      <c r="P25" s="1" t="n"/>
+      <c r="Q25" s="1" t="n"/>
+      <c r="R25" s="1" t="n"/>
+      <c r="S25" s="1" t="n"/>
+      <c r="T25" s="1" t="n"/>
+      <c r="U25" s="1" t="n"/>
+      <c r="V25" s="1" t="n"/>
+      <c r="W25" s="1" t="n"/>
+      <c r="X25" s="1" t="n"/>
+      <c r="Y25" s="1" t="n"/>
+      <c r="Z25" s="1" t="n"/>
+      <c r="AA25" s="1" t="n"/>
+      <c r="AB25" s="1" t="n"/>
+      <c r="AC25" s="1" t="n"/>
+      <c r="AD25" s="1" t="n"/>
+      <c r="AE25" s="1" t="n"/>
+      <c r="AF25" s="1" t="n"/>
+      <c r="AG25" s="1" t="n"/>
+      <c r="AH25" s="1" t="n"/>
+      <c r="AI25" s="1" t="n"/>
+      <c r="AJ25" s="1" t="n"/>
+      <c r="AK25" s="1" t="n"/>
+      <c r="AL25" s="1" t="n"/>
+      <c r="AM25" s="1" t="n"/>
+      <c r="AN25" s="1" t="n"/>
+      <c r="AO25" s="1" t="n"/>
+      <c r="AP25" s="1" t="n"/>
+      <c r="AQ25" s="1" t="n"/>
+      <c r="AR25" s="1" t="n"/>
+      <c r="AS25" s="5" t="n"/>
+      <c r="AT25" s="5" t="n"/>
+      <c r="AU25" s="5" t="n"/>
+      <c r="AV25" s="5" t="n"/>
+      <c r="AW25" s="5" t="n"/>
+      <c r="AX25" s="5" t="n"/>
+      <c r="AY25" s="5" t="n"/>
+      <c r="AZ25" s="5" t="n"/>
+      <c r="BA25" s="5" t="n"/>
+      <c r="BB25" s="5" t="n"/>
       <c r="BC25" s="2" t="n"/>
       <c r="BD25" s="2" t="n"/>
       <c r="BE25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>宗三左文字</t>
+          <t>蜻蛉切</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2774,87 +2729,77 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>槍</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>蝶</t>
+          <t>天下三名槍</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>黄</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>攪乱戦術・黄</t>
+          <t>必中縦断突き</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>【最大10体】の黄ト餓鬼を盤面の中央に集める</t>
+          <t>指定した【縦列・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>493,54</t>
-        </is>
-      </c>
-      <c r="P26" s="1" t="n"/>
-      <c r="Q26" s="1" t="n"/>
-      <c r="R26" s="1" t="n"/>
-      <c r="S26" s="1" t="n"/>
-      <c r="T26" s="1" t="n"/>
-      <c r="U26" s="1" t="n"/>
-      <c r="V26" s="1" t="n"/>
-      <c r="W26" s="1" t="n"/>
-      <c r="X26" s="1" t="n"/>
-      <c r="Y26" s="1" t="n"/>
-      <c r="Z26" s="1" t="n"/>
-      <c r="AA26" s="1" t="n"/>
-      <c r="AB26" s="1" t="n"/>
-      <c r="AC26" s="1" t="n"/>
-      <c r="AD26" s="1" t="n"/>
-      <c r="AE26" s="1" t="n"/>
-      <c r="AF26" s="1" t="n"/>
-      <c r="AG26" s="1" t="n"/>
-      <c r="AH26" s="1" t="n"/>
-      <c r="AI26" s="1" t="n"/>
-      <c r="AJ26" s="1" t="n"/>
-      <c r="AK26" s="1" t="n"/>
-      <c r="AL26" s="1" t="n"/>
-      <c r="AM26" s="1" t="n"/>
-      <c r="AN26" s="1" t="n"/>
-      <c r="AO26" s="1" t="n"/>
-      <c r="AP26" s="1" t="n"/>
-      <c r="AQ26" s="1" t="n"/>
-      <c r="AR26" s="1" t="n"/>
-      <c r="AS26" s="5" t="n"/>
-      <c r="AT26" s="5" t="n"/>
-      <c r="AU26" s="5" t="n"/>
-      <c r="AV26" s="5" t="n"/>
-      <c r="AW26" s="5" t="n"/>
-      <c r="AX26" s="5" t="n"/>
-      <c r="AY26" s="5" t="n"/>
-      <c r="AZ26" s="5" t="n"/>
-      <c r="BA26" s="5" t="n"/>
-      <c r="BB26" s="5" t="n"/>
+          <t>551,72</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="n"/>
+      <c r="Q26" s="2" t="n"/>
+      <c r="R26" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="n"/>
+      <c r="U26" s="2" t="n"/>
+      <c r="V26" s="2" t="n"/>
+      <c r="W26" s="2" t="n"/>
+      <c r="X26" s="2" t="n"/>
+      <c r="Y26" s="2" t="n"/>
+      <c r="Z26" s="2" t="n"/>
+      <c r="AA26" s="2" t="n"/>
+      <c r="AB26" s="2" t="n"/>
+      <c r="AC26" s="2" t="n"/>
+      <c r="AD26" s="2" t="n"/>
+      <c r="AE26" s="2" t="n"/>
+      <c r="AF26" s="2" t="n"/>
+      <c r="AG26" s="2" t="n"/>
+      <c r="AH26" s="2" t="n"/>
+      <c r="AI26" s="2" t="n"/>
+      <c r="AJ26" s="2" t="n"/>
+      <c r="AK26" s="2" t="n"/>
+      <c r="AL26" s="2" t="n"/>
+      <c r="AM26" s="2" t="n"/>
+      <c r="AN26" s="2" t="n"/>
+      <c r="AO26" s="2" t="n"/>
+      <c r="AP26" s="2" t="n"/>
+      <c r="AQ26" s="2" t="n"/>
+      <c r="AR26" s="2" t="n"/>
       <c r="BC26" s="2" t="n"/>
       <c r="BD26" s="2" t="n"/>
       <c r="BE26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>小夜左文字</t>
+          <t>燭台切光忠</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2864,12 +2809,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>短刀</t>
+          <t>太刀</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>夜</t>
+          <t>もの斬り</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2882,17 +2827,18 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>正円斬り 追撃の型</t>
+          <t>必中縦断斬り ボムの型</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>【円型・特小範囲】のト餓鬼を消去し、敵に【中】ダメージを与える。乱舞ぎりタイム中はさらにダメージ上昇。</t>
+          <t>指定した【縦列・小範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える
+ボムを【1個】生成する</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>417,81</t>
+          <t>547,66</t>
         </is>
       </c>
       <c r="P27" s="1" t="n"/>
@@ -2940,11 +2886,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>加州清光</t>
+          <t>江雪左文字</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2954,12 +2900,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>太刀</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>新選組</t>
+          <t>雪</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2968,63 +2914,64 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>必中三段斬り</t>
+          <t>霧散斬り 先手の型</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>指定した【円型・特小範囲】のト餓鬼を3回消去し、敵に【小】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O28" s="1" t="n"/>
-      <c r="P28" s="1" t="n"/>
-      <c r="Q28" s="1" t="n"/>
-      <c r="R28" s="1" t="n"/>
-      <c r="S28" s="1" t="inlineStr">
-        <is>
-          <t>645,73</t>
-        </is>
-      </c>
-      <c r="T28" s="1" t="n"/>
-      <c r="U28" s="1" t="n"/>
-      <c r="V28" s="1" t="n"/>
-      <c r="W28" s="1" t="n"/>
-      <c r="X28" s="1" t="n"/>
-      <c r="Y28" s="1" t="n"/>
-      <c r="Z28" s="1" t="n"/>
-      <c r="AA28" s="1" t="n"/>
-      <c r="AB28" s="1" t="n"/>
-      <c r="AC28" s="1" t="n"/>
-      <c r="AD28" s="1" t="n"/>
-      <c r="AE28" s="1" t="n"/>
-      <c r="AF28" s="1" t="n"/>
-      <c r="AG28" s="1" t="n"/>
-      <c r="AH28" s="1" t="n"/>
-      <c r="AI28" s="1" t="n"/>
-      <c r="AJ28" s="1" t="n"/>
-      <c r="AK28" s="1" t="n"/>
-      <c r="AL28" s="1" t="n"/>
-      <c r="AM28" s="1" t="n"/>
-      <c r="AN28" s="1" t="n"/>
-      <c r="AO28" s="1" t="n"/>
-      <c r="AP28" s="1" t="n"/>
-      <c r="AQ28" s="1" t="n"/>
-      <c r="AR28" s="1" t="n"/>
-      <c r="BC28" s="1" t="n"/>
-      <c r="BD28" s="1" t="n"/>
-      <c r="BE28" s="1" t="n"/>
+          <t>ランダムなト餓鬼（攻撃指示優先）を最大5体消去し、敵に【特小＋＋】ダメージを与える
+消去時のブレイクゲージ減少量が【2倍】になる</t>
+        </is>
+      </c>
+      <c r="O28" s="1" t="inlineStr">
+        <is>
+          <t>507,74</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="n"/>
+      <c r="R28" s="2" t="n"/>
+      <c r="S28" s="2" t="n"/>
+      <c r="T28" s="2" t="n"/>
+      <c r="U28" s="2" t="n"/>
+      <c r="V28" s="2" t="n"/>
+      <c r="W28" s="2" t="n"/>
+      <c r="X28" s="2" t="n"/>
+      <c r="Y28" s="2" t="n"/>
+      <c r="Z28" s="2" t="n"/>
+      <c r="AA28" s="2" t="n"/>
+      <c r="AB28" s="2" t="n"/>
+      <c r="AC28" s="2" t="n"/>
+      <c r="AD28" s="2" t="n"/>
+      <c r="AE28" s="2" t="n"/>
+      <c r="AF28" s="2" t="n"/>
+      <c r="AG28" s="2" t="n"/>
+      <c r="AH28" s="2" t="n"/>
+      <c r="AI28" s="2" t="n"/>
+      <c r="AJ28" s="2" t="n"/>
+      <c r="AK28" s="2" t="n"/>
+      <c r="AL28" s="2" t="n"/>
+      <c r="AM28" s="2" t="n"/>
+      <c r="AN28" s="2" t="n"/>
+      <c r="AO28" s="2" t="n"/>
+      <c r="AP28" s="2" t="n"/>
+      <c r="AQ28" s="2" t="n"/>
+      <c r="AR28" s="2" t="n"/>
+      <c r="BC28" s="2" t="n"/>
+      <c r="BD28" s="2" t="n"/>
+      <c r="BE28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>大和守安定</t>
+          <t>宗三左文字</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3039,7 +2986,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>新選組</t>
+          <t>蝶</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3048,22 +2995,21 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>霧散斬り ボムの型</t>
+          <t>攪乱戦術・黄</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>ランダムな孤立した青ト餓鬼を【最大3体】消去し、敵に【特小＋】ダメージを与える
-ボムを【1個】生成する</t>
+          <t>【最大10体】の黄ト餓鬼を盤面の中央に集める</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>467,57</t>
+          <t>493,54</t>
         </is>
       </c>
       <c r="P29" s="1" t="n"/>
@@ -3111,11 +3057,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>歌仙兼定</t>
+          <t>小夜左文字</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3125,12 +3071,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>短刀</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>花</t>
+          <t>夜</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3139,21 +3085,21 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>水平一刀斬り</t>
+          <t>正円斬り 追撃の型</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小－】ダメージを与える</t>
+          <t>【円型・特小範囲】のト餓鬼を消去し、敵に【中】ダメージを与える。乱舞ぎりタイム中はさらにダメージ上昇。</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>475,70</t>
+          <t>417,81</t>
         </is>
       </c>
       <c r="P30" s="1" t="n"/>
@@ -3201,11 +3147,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>歌仙兼定</t>
+          <t>加州清光</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3213,11 +3159,6 @@
           <t>戦装束</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>打刀</t>
@@ -3225,7 +3166,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>詠み人,花</t>
+          <t>新選組</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3234,27 +3175,27 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>くちなしの挽歌</t>
+          <t>必中三段斬り</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>指定した【縦列・小範囲】のト餓鬼を、黄色に変化させる</t>
-        </is>
-      </c>
-      <c r="O31" s="1" t="inlineStr">
-        <is>
-          <t>492,74</t>
-        </is>
-      </c>
+          <t>指定した【円型・特小範囲】のト餓鬼を3回消去し、敵に【小】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O31" s="1" t="n"/>
       <c r="P31" s="1" t="n"/>
       <c r="Q31" s="1" t="n"/>
       <c r="R31" s="1" t="n"/>
-      <c r="S31" s="1" t="n"/>
+      <c r="S31" s="1" t="inlineStr">
+        <is>
+          <t>645,73</t>
+        </is>
+      </c>
       <c r="T31" s="1" t="n"/>
       <c r="U31" s="1" t="n"/>
       <c r="V31" s="1" t="n"/>
@@ -3280,27 +3221,17 @@
       <c r="AP31" s="1" t="n"/>
       <c r="AQ31" s="1" t="n"/>
       <c r="AR31" s="1" t="n"/>
-      <c r="AS31" s="5" t="n"/>
-      <c r="AT31" s="5" t="n"/>
-      <c r="AU31" s="5" t="n"/>
-      <c r="AV31" s="5" t="n"/>
-      <c r="AW31" s="5" t="n"/>
-      <c r="AX31" s="5" t="n"/>
-      <c r="AY31" s="5" t="n"/>
-      <c r="AZ31" s="5" t="n"/>
-      <c r="BA31" s="5" t="n"/>
-      <c r="BB31" s="5" t="n"/>
-      <c r="BC31" s="2" t="n"/>
-      <c r="BD31" s="2" t="n"/>
-      <c r="BE31" s="2" t="n"/>
+      <c r="BC31" s="1" t="n"/>
+      <c r="BD31" s="1" t="n"/>
+      <c r="BE31" s="1" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>和泉守兼定</t>
+          <t>大和守安定</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3324,19 +3255,24 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>正円二段斬り</t>
+          <t>霧散斬り ボムの型</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>ランダムな場所の【円型・小範囲】のト餓鬼を2回消去し、敵に【中】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O32" s="1" t="n"/>
+          <t>ランダムな孤立した青ト餓鬼を【最大3体】消去し、敵に【特小＋】ダメージを与える
+ボムを【1個】生成する</t>
+        </is>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t>467,57</t>
+        </is>
+      </c>
       <c r="P32" s="1" t="n"/>
       <c r="Q32" s="1" t="n"/>
       <c r="R32" s="1" t="n"/>
@@ -3355,11 +3291,7 @@
       <c r="AE32" s="1" t="n"/>
       <c r="AF32" s="1" t="n"/>
       <c r="AG32" s="1" t="n"/>
-      <c r="AH32" s="1" t="inlineStr">
-        <is>
-          <t>1551,188</t>
-        </is>
-      </c>
+      <c r="AH32" s="1" t="n"/>
       <c r="AI32" s="1" t="n"/>
       <c r="AJ32" s="1" t="n"/>
       <c r="AK32" s="1" t="n"/>
@@ -3370,17 +3302,27 @@
       <c r="AP32" s="1" t="n"/>
       <c r="AQ32" s="1" t="n"/>
       <c r="AR32" s="1" t="n"/>
-      <c r="BC32" s="1" t="n"/>
-      <c r="BD32" s="1" t="n"/>
-      <c r="BE32" s="1" t="n"/>
+      <c r="AS32" s="5" t="n"/>
+      <c r="AT32" s="5" t="n"/>
+      <c r="AU32" s="5" t="n"/>
+      <c r="AV32" s="5" t="n"/>
+      <c r="AW32" s="5" t="n"/>
+      <c r="AX32" s="5" t="n"/>
+      <c r="AY32" s="5" t="n"/>
+      <c r="AZ32" s="5" t="n"/>
+      <c r="BA32" s="5" t="n"/>
+      <c r="BB32" s="5" t="n"/>
+      <c r="BC32" s="2" t="n"/>
+      <c r="BD32" s="2" t="n"/>
+      <c r="BE32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>陸奥守吉行</t>
+          <t>歌仙兼定</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3395,29 +3337,32 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>海</t>
+          <t>花</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>黄</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>水平斬り 攻勢の型</t>
+          <t>水平一刀斬り</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【極小】ダメージを与える
-味方全員に攻撃力上昇【極小＋＋・3手】を付与する</t>
-        </is>
-      </c>
-      <c r="O33" s="1" t="n"/>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小－】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O33" s="1" t="inlineStr">
+        <is>
+          <t>475,70</t>
+        </is>
+      </c>
       <c r="P33" s="1" t="n"/>
       <c r="Q33" s="1" t="n"/>
       <c r="R33" s="1" t="n"/>
@@ -3446,26 +3391,28 @@
       <c r="AO33" s="1" t="n"/>
       <c r="AP33" s="1" t="n"/>
       <c r="AQ33" s="1" t="n"/>
-      <c r="AR33" s="1" t="inlineStr">
-        <is>
-          <t>1575,228</t>
-        </is>
-      </c>
-      <c r="BC33" s="1" t="n"/>
-      <c r="BD33" s="1" t="n"/>
-      <c r="BE33" s="1" t="inlineStr">
-        <is>
-          <t>[黄の絵具,1][書き物道具,2][花札,2][天ぷら,2][そろばん,2][打刀の心得,1]</t>
-        </is>
-      </c>
+      <c r="AR33" s="1" t="n"/>
+      <c r="AS33" s="5" t="n"/>
+      <c r="AT33" s="5" t="n"/>
+      <c r="AU33" s="5" t="n"/>
+      <c r="AV33" s="5" t="n"/>
+      <c r="AW33" s="5" t="n"/>
+      <c r="AX33" s="5" t="n"/>
+      <c r="AY33" s="5" t="n"/>
+      <c r="AZ33" s="5" t="n"/>
+      <c r="BA33" s="5" t="n"/>
+      <c r="BB33" s="5" t="n"/>
+      <c r="BC33" s="2" t="n"/>
+      <c r="BD33" s="2" t="n"/>
+      <c r="BE33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>山姥切国広</t>
+          <t>歌仙兼定</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3473,6 +3420,11 @@
           <t>戦装束</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>打刀</t>
@@ -3480,28 +3432,32 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>兄弟</t>
+          <t>詠み人,花</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>青</t>
+          <t>赤</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>正円一刀斬り</t>
+          <t>くちなしの挽歌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>【円型・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
-        </is>
-      </c>
-      <c r="O34" s="1" t="n"/>
+          <t>指定した【縦列・小範囲】のト餓鬼を、黄色に変化させる</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>492,74</t>
+        </is>
+      </c>
       <c r="P34" s="1" t="n"/>
       <c r="Q34" s="1" t="n"/>
       <c r="R34" s="1" t="n"/>
@@ -3510,11 +3466,7 @@
       <c r="U34" s="1" t="n"/>
       <c r="V34" s="1" t="n"/>
       <c r="W34" s="1" t="n"/>
-      <c r="X34" s="1" t="inlineStr">
-        <is>
-          <t>850,107</t>
-        </is>
-      </c>
+      <c r="X34" s="1" t="n"/>
       <c r="Y34" s="1" t="n"/>
       <c r="Z34" s="1" t="n"/>
       <c r="AA34" s="1" t="n"/>
@@ -3535,17 +3487,27 @@
       <c r="AP34" s="1" t="n"/>
       <c r="AQ34" s="1" t="n"/>
       <c r="AR34" s="1" t="n"/>
-      <c r="BC34" s="1" t="n"/>
-      <c r="BD34" s="1" t="n"/>
-      <c r="BE34" s="1" t="n"/>
+      <c r="AS34" s="5" t="n"/>
+      <c r="AT34" s="5" t="n"/>
+      <c r="AU34" s="5" t="n"/>
+      <c r="AV34" s="5" t="n"/>
+      <c r="AW34" s="5" t="n"/>
+      <c r="AX34" s="5" t="n"/>
+      <c r="AY34" s="5" t="n"/>
+      <c r="AZ34" s="5" t="n"/>
+      <c r="BA34" s="5" t="n"/>
+      <c r="BB34" s="5" t="n"/>
+      <c r="BC34" s="2" t="n"/>
+      <c r="BD34" s="2" t="n"/>
+      <c r="BE34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>山伏国広</t>
+          <t>和泉守兼定</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3555,12 +3517,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>お山修行</t>
+          <t>新選組</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3569,24 +3531,19 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>逆さ扇斬り 守護の型</t>
+          <t>正円二段斬り</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>【扇型・特小範囲】のト餓鬼を消去し、敵に【極小＋】ダメージを与える
-味方全員に被ダメージ軽減【特小＋＋・3手】を付与する</t>
-        </is>
-      </c>
-      <c r="O35" s="1" t="inlineStr">
-        <is>
-          <t>584,70</t>
-        </is>
-      </c>
+          <t>ランダムな場所の【円型・小範囲】のト餓鬼を2回消去し、敵に【中】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O35" s="1" t="n"/>
       <c r="P35" s="1" t="n"/>
       <c r="Q35" s="1" t="n"/>
       <c r="R35" s="1" t="n"/>
@@ -3605,7 +3562,11 @@
       <c r="AE35" s="1" t="n"/>
       <c r="AF35" s="1" t="n"/>
       <c r="AG35" s="1" t="n"/>
-      <c r="AH35" s="1" t="n"/>
+      <c r="AH35" s="1" t="inlineStr">
+        <is>
+          <t>1551,188</t>
+        </is>
+      </c>
       <c r="AI35" s="1" t="n"/>
       <c r="AJ35" s="1" t="n"/>
       <c r="AK35" s="1" t="n"/>
@@ -3622,11 +3583,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>堀川国広</t>
+          <t>陸奥守吉行</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3636,17 +3597,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>脇差</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>新選組</t>
+          <t>海</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>黄</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -3654,20 +3615,16 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>会心猛攻の法</t>
+          <t>水平斬り 攻勢の型</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>味方全員に攻撃力上昇【極小＋＋・3手】を付与する
-味方全員にクリティカル率上昇【特小＋＋・9手】を付与する</t>
-        </is>
-      </c>
-      <c r="O36" s="1" t="inlineStr">
-        <is>
-          <t>491,63</t>
-        </is>
-      </c>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【極小】ダメージを与える
+味方全員に攻撃力上昇【極小＋＋・3手】を付与する</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="n"/>
       <c r="P36" s="1" t="n"/>
       <c r="Q36" s="1" t="n"/>
       <c r="R36" s="1" t="n"/>
@@ -3696,28 +3653,26 @@
       <c r="AO36" s="1" t="n"/>
       <c r="AP36" s="1" t="n"/>
       <c r="AQ36" s="1" t="n"/>
-      <c r="AR36" s="1" t="n"/>
-      <c r="AS36" s="5" t="n"/>
-      <c r="AT36" s="5" t="n"/>
-      <c r="AU36" s="5" t="n"/>
-      <c r="AV36" s="5" t="n"/>
-      <c r="AW36" s="5" t="n"/>
-      <c r="AX36" s="5" t="n"/>
-      <c r="AY36" s="5" t="n"/>
-      <c r="AZ36" s="5" t="n"/>
-      <c r="BA36" s="5" t="n"/>
-      <c r="BB36" s="5" t="n"/>
-      <c r="BC36" s="2" t="n"/>
-      <c r="BD36" s="2" t="n"/>
-      <c r="BE36" s="2" t="n"/>
+      <c r="AR36" s="1" t="inlineStr">
+        <is>
+          <t>1575,228</t>
+        </is>
+      </c>
+      <c r="BC36" s="1" t="n"/>
+      <c r="BD36" s="1" t="n"/>
+      <c r="BE36" s="1" t="inlineStr">
+        <is>
+          <t>[黄の絵具,1][書き物道具,2][花札,2][天ぷら,2][そろばん,2][打刀の心得,1]</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>獅子王</t>
+          <t>山姥切国広</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3727,17 +3682,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>けもの</t>
+          <t>兄弟</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>赤</t>
+          <t>青</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -3745,28 +3700,28 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>水平一刀斬り</t>
+          <t>正円一刀斬り</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
+          <t>【円型・小範囲】のト餓鬼を消去し、敵に【小】ダメージを与える</t>
         </is>
       </c>
       <c r="O37" s="1" t="n"/>
       <c r="P37" s="1" t="n"/>
       <c r="Q37" s="1" t="n"/>
       <c r="R37" s="1" t="n"/>
-      <c r="S37" s="1" t="inlineStr">
-        <is>
-          <t>771,74</t>
-        </is>
-      </c>
+      <c r="S37" s="1" t="n"/>
       <c r="T37" s="1" t="n"/>
       <c r="U37" s="1" t="n"/>
       <c r="V37" s="1" t="n"/>
       <c r="W37" s="1" t="n"/>
-      <c r="X37" s="1" t="n"/>
+      <c r="X37" s="1" t="inlineStr">
+        <is>
+          <t>850,107</t>
+        </is>
+      </c>
       <c r="Y37" s="1" t="n"/>
       <c r="Z37" s="1" t="n"/>
       <c r="AA37" s="1" t="n"/>
@@ -3793,11 +3748,11 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>鶴丸国永</t>
+          <t>山伏国広</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3812,7 +3767,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>お山修行</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3821,20 +3776,24 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>水平斬り 攻勢の型</t>
+          <t>逆さ扇斬り 守護の型</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>【横列・中範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える
-自身に攻撃力上昇【極小・1手】を付与する</t>
-        </is>
-      </c>
-      <c r="O38" s="1" t="n"/>
+          <t>【扇型・特小範囲】のト餓鬼を消去し、敵に【極小＋】ダメージを与える
+味方全員に被ダメージ軽減【特小＋＋・3手】を付与する</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>584,70</t>
+        </is>
+      </c>
       <c r="P38" s="1" t="n"/>
       <c r="Q38" s="1" t="n"/>
       <c r="R38" s="1" t="n"/>
@@ -3843,11 +3802,7 @@
       <c r="U38" s="1" t="n"/>
       <c r="V38" s="1" t="n"/>
       <c r="W38" s="1" t="n"/>
-      <c r="X38" s="1" t="inlineStr">
-        <is>
-          <t>935,110</t>
-        </is>
-      </c>
+      <c r="X38" s="1" t="n"/>
       <c r="Y38" s="1" t="n"/>
       <c r="Z38" s="1" t="n"/>
       <c r="AA38" s="1" t="n"/>
@@ -3873,9 +3828,12 @@
       <c r="BE38" s="1" t="n"/>
     </row>
     <row r="39">
+      <c r="A39" t="n">
+        <v>99</v>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>大倶利伽羅</t>
+          <t>堀川国広</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3885,12 +3843,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>打刀</t>
+          <t>脇差</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>龍</t>
+          <t>新選組</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3899,22 +3857,22 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>三段斬り 攻勢の型</t>
+          <t>会心猛攻の法</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>ランダムな【円型・特小範囲】のト餓鬼を3回消去し、敵に【小－】ダメージを与える
-自身にクリティカル率上昇【極小＋＋・1手】を付与する</t>
+          <t>味方全員に攻撃力上昇【極小＋＋・3手】を付与する
+味方全員にクリティカル率上昇【特小＋＋・9手】を付与する</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>455,72</t>
+          <t>491,63</t>
         </is>
       </c>
       <c r="P39" s="1" t="n"/>
@@ -3961,9 +3919,12 @@
       <c r="BE39" s="2" t="n"/>
     </row>
     <row r="40">
+      <c r="A40" t="n">
+        <v>101</v>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>へし切長谷部</t>
+          <t>蜂須賀虎徹</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3978,7 +3939,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>もの斬り</t>
+          <t>兄弟</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3987,21 +3948,21 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>必中二段斬り</t>
+          <t>霧散斬り 掃討の型</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>指定した【縦列・小範囲】のト餓鬼を2回消去し、敵に【小＋】ダメージを与える</t>
+          <t>孤立したト餓鬼をランダムに【最大5体】消去し、敵に【特小＋】ダメージを与える</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>530,65</t>
+          <t>481,71</t>
         </is>
       </c>
       <c r="P40" s="1" t="n"/>
@@ -4048,9 +4009,12 @@
       <c r="BE40" s="2" t="n"/>
     </row>
     <row r="41">
+      <c r="A41" t="n">
+        <v>116</v>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>同田貫正国</t>
+          <t>大倶利伽羅</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4065,7 +4029,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>もの斬り</t>
+          <t>龍</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4074,21 +4038,22 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>真っ向一刀斬り</t>
+          <t>三段斬り 攻勢の型</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>【縦列・小範囲】のト餓鬼を消去し、敵に【小＋＋】ダメージを与える</t>
+          <t>ランダムな【円型・特小範囲】のト餓鬼を3回消去し、敵に【小－】ダメージを与える
+自身にクリティカル率上昇【極小＋＋・1手】を付与する</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>453,75</t>
+          <t>455,72</t>
         </is>
       </c>
       <c r="P41" s="1" t="n"/>
@@ -4135,9 +4100,12 @@
       <c r="BE41" s="2" t="n"/>
     </row>
     <row r="42">
+      <c r="A42" t="n">
+        <v>118</v>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>蜂須賀虎徹</t>
+          <t>へし切長谷部</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4152,7 +4120,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>兄弟</t>
+          <t>もの斬り</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4161,21 +4129,21 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>霧散斬り 掃討の型</t>
+          <t>必中二段斬り</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>孤立したト餓鬼をランダムに【最大5体】消去し、敵に【特小＋】ダメージを与える</t>
+          <t>指定した【縦列・小範囲】のト餓鬼を2回消去し、敵に【小＋】ダメージを与える</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>481,71</t>
+          <t>530,65</t>
         </is>
       </c>
       <c r="P42" s="1" t="n"/>
@@ -4222,9 +4190,12 @@
       <c r="BE42" s="2" t="n"/>
     </row>
     <row r="43">
+      <c r="A43" t="n">
+        <v>122</v>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>燭台切光忠</t>
+          <t>獅子王</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4239,7 +4210,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>もの斬り</t>
+          <t>けもの</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4248,28 +4219,27 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>必中縦断斬り ボムの型</t>
+          <t>水平一刀斬り</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>指定した【縦列・小範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える
-ボムを【1個】生成する</t>
-        </is>
-      </c>
-      <c r="O43" s="1" t="inlineStr">
-        <is>
-          <t>547,66</t>
-        </is>
-      </c>
+          <t>【横列・小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="n"/>
       <c r="P43" s="1" t="n"/>
       <c r="Q43" s="1" t="n"/>
       <c r="R43" s="1" t="n"/>
-      <c r="S43" s="1" t="n"/>
+      <c r="S43" s="1" t="inlineStr">
+        <is>
+          <t>771,74</t>
+        </is>
+      </c>
       <c r="T43" s="1" t="n"/>
       <c r="U43" s="1" t="n"/>
       <c r="V43" s="1" t="n"/>
@@ -4295,24 +4265,17 @@
       <c r="AP43" s="1" t="n"/>
       <c r="AQ43" s="1" t="n"/>
       <c r="AR43" s="1" t="n"/>
-      <c r="AS43" s="5" t="n"/>
-      <c r="AT43" s="5" t="n"/>
-      <c r="AU43" s="5" t="n"/>
-      <c r="AV43" s="5" t="n"/>
-      <c r="AW43" s="5" t="n"/>
-      <c r="AX43" s="5" t="n"/>
-      <c r="AY43" s="5" t="n"/>
-      <c r="AZ43" s="5" t="n"/>
-      <c r="BA43" s="5" t="n"/>
-      <c r="BB43" s="5" t="n"/>
-      <c r="BC43" s="2" t="n"/>
-      <c r="BD43" s="2" t="n"/>
-      <c r="BE43" s="2" t="n"/>
+      <c r="BC43" s="1" t="n"/>
+      <c r="BD43" s="1" t="n"/>
+      <c r="BE43" s="1" t="n"/>
     </row>
     <row r="44">
+      <c r="A44" t="n">
+        <v>128</v>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>愛染国俊</t>
+          <t>同田貫正国</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4322,12 +4285,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>短刀</t>
+          <t>打刀</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>炎</t>
+          <t>もの斬り</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4336,22 +4299,21 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>強攻の法</t>
+          <t>真っ向一刀斬り</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>自身に攻撃力上昇【特小・1手】を付与する
-自身に攻撃力上昇【極小＋・1手】を付与する</t>
+          <t>【縦列・小範囲】のト餓鬼を消去し、敵に【小＋＋】ダメージを与える</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>483,62</t>
+          <t>453,75</t>
         </is>
       </c>
       <c r="P44" s="1" t="n"/>
@@ -4398,9 +4360,12 @@
       <c r="BE44" s="2" t="n"/>
     </row>
     <row r="45">
+      <c r="A45" t="n">
+        <v>130</v>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>にっかり青江</t>
+          <t>鶴丸国永</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4410,12 +4375,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>脇差</t>
+          <t>太刀</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>夜</t>
+          <t>鳥</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4424,23 +4389,20 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>守備制約の計</t>
+          <t>水平斬り 攻勢の型</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>敵に被ダメージ増加【極小＋・1手】を付与する</t>
-        </is>
-      </c>
-      <c r="O45" s="1" t="inlineStr">
-        <is>
-          <t>524,65</t>
-        </is>
-      </c>
+          <t>【横列・中範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える
+自身に攻撃力上昇【極小・1手】を付与する</t>
+        </is>
+      </c>
+      <c r="O45" s="1" t="n"/>
       <c r="P45" s="1" t="n"/>
       <c r="Q45" s="1" t="n"/>
       <c r="R45" s="1" t="n"/>
@@ -4449,7 +4411,11 @@
       <c r="U45" s="1" t="n"/>
       <c r="V45" s="1" t="n"/>
       <c r="W45" s="1" t="n"/>
-      <c r="X45" s="1" t="n"/>
+      <c r="X45" s="1" t="inlineStr">
+        <is>
+          <t>935,110</t>
+        </is>
+      </c>
       <c r="Y45" s="1" t="n"/>
       <c r="Z45" s="1" t="n"/>
       <c r="AA45" s="1" t="n"/>
@@ -4470,24 +4436,17 @@
       <c r="AP45" s="1" t="n"/>
       <c r="AQ45" s="1" t="n"/>
       <c r="AR45" s="1" t="n"/>
-      <c r="AS45" s="5" t="n"/>
-      <c r="AT45" s="5" t="n"/>
-      <c r="AU45" s="5" t="n"/>
-      <c r="AV45" s="5" t="n"/>
-      <c r="AW45" s="5" t="n"/>
-      <c r="AX45" s="5" t="n"/>
-      <c r="AY45" s="5" t="n"/>
-      <c r="AZ45" s="5" t="n"/>
-      <c r="BA45" s="5" t="n"/>
-      <c r="BB45" s="5" t="n"/>
-      <c r="BC45" s="2" t="n"/>
-      <c r="BD45" s="2" t="n"/>
-      <c r="BE45" s="2" t="n"/>
+      <c r="BC45" s="1" t="n"/>
+      <c r="BD45" s="1" t="n"/>
+      <c r="BE45" s="1" t="n"/>
     </row>
     <row r="46">
+      <c r="A46" t="n">
+        <v>132</v>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>秋田藤四郎</t>
+          <t>太郎太刀</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4497,12 +4456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>短刀</t>
+          <t>大太刀</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>兄弟</t>
+          <t>ご神刀</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4511,21 +4470,21 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>受け流しの法</t>
+          <t>霧散斬り・黄</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>味方全員にガード率上昇【中－・5手】を付与する</t>
+          <t>黄ト餓鬼をランダムに【最大10体】消去し、敵に【小＋】ダメージを与える</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>473,60</t>
+          <t>588,64</t>
         </is>
       </c>
       <c r="P46" s="1" t="n"/>
@@ -4572,9 +4531,12 @@
       <c r="BE46" s="2" t="n"/>
     </row>
     <row r="47">
+      <c r="A47" t="n">
+        <v>132</v>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>薬研藤四郎</t>
+          <t>太郎太刀</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4582,14 +4544,19 @@
           <t>戦装束</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>短刀</t>
+          <t>大太刀</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>兄弟</t>
+          <t>ご神刀,兄弟</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4598,22 +4565,21 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>真っ向斬り 攻勢の型</t>
+          <t>天より墜つる暴威</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>【縦列・特小範囲】のト餓鬼を消去し、敵に【極小】ダメージを与える
-味方全員にクリティカル率上昇【小・3手】を付与する</t>
+          <t>【円型・大範囲】のト餓鬼を消去し、敵に【中＋】ダメージを与える。ボスが被ダメージ増加状態のとき、さらに威力が上昇する</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>542,55</t>
+          <t>613,67</t>
         </is>
       </c>
       <c r="P47" s="1" t="n"/>
@@ -4660,9 +4626,12 @@
       <c r="BE47" s="2" t="n"/>
     </row>
     <row r="48">
+      <c r="A48" t="n">
+        <v>134</v>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>前田藤四郎</t>
+          <t>次郎太刀</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4672,12 +4641,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>短刀</t>
+          <t>大太刀</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>兄弟</t>
+          <t>ご神刀</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4686,21 +4655,21 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>色変幻の術・黄</t>
+          <t>正円一刀斬り</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>青色のト餓鬼を【最大10体】、黄色に変換する</t>
+          <t>【円型・大範囲】のト餓鬼を消去し、敵に【特小＋＋】ダメージを与える</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>565,58</t>
+          <t>501,71</t>
         </is>
       </c>
       <c r="P48" s="1" t="n"/>
@@ -4747,9 +4716,12 @@
       <c r="BE48" s="2" t="n"/>
     </row>
     <row r="49">
+      <c r="A49" t="n">
+        <v>138</v>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>鶯丸</t>
+          <t>御手杵</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4759,12 +4731,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>太刀</t>
+          <t>槍</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>天下三名槍</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4777,17 +4749,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>霧散斬り・青</t>
+          <t>必中正円突き</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>ランダムな青ト餓鬼を【最大8体】消去し、敵に【小＋＋】ダメージを与える</t>
+          <t>指定した1箇所【円型・特小範囲】のト餓鬼を消去し、敵に【小＋】ダメージを与える</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>626,54</t>
+          <t>461,60</t>
         </is>
       </c>
       <c r="P49" s="1" t="n"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -819,11 +819,17 @@
       <c r="AD2" s="7" t="n">
         <v>7198</v>
       </c>
+      <c r="AH2" s="7" t="n">
+        <v>12298</v>
+      </c>
       <c r="AK2" s="7" t="n">
         <v>17199</v>
       </c>
       <c r="AL2" s="7" t="n">
         <v>19049</v>
+      </c>
+      <c r="AM2" s="7" t="n">
+        <v>21009</v>
       </c>
       <c r="AQ2" s="7" t="n">
         <v>30000</v>
@@ -954,6 +960,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>【すべて】のト餓鬼を消去し、敵に【特小++】ダメージを与える</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>【すべて】のト餓鬼を消去し、敵に【中－】ダメージを与える</t>
         </is>
       </c>
       <c r="O4" s="1" t="n"/>
@@ -1640,7 +1651,11 @@
           <t>1673,173</t>
         </is>
       </c>
-      <c r="AM12" s="2" t="n"/>
+      <c r="AM12" s="1" t="inlineStr">
+        <is>
+          <t>1720,178</t>
+        </is>
+      </c>
       <c r="AN12" s="2" t="n"/>
       <c r="AO12" s="2" t="n"/>
       <c r="AP12" s="2" t="n"/>
@@ -2595,7 +2610,11 @@
         </is>
       </c>
       <c r="U24" s="2" t="n"/>
-      <c r="V24" s="2" t="n"/>
+      <c r="V24" s="1" t="inlineStr">
+        <is>
+          <t>756,119</t>
+        </is>
+      </c>
       <c r="W24" s="2" t="n"/>
       <c r="X24" s="2" t="n"/>
       <c r="Y24" s="2" t="n"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -22869,7 +22869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="24"/>
@@ -23602,17 +23602,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>赤の絵具</t>
+          <t>囲碁</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>イベント</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>強化素材</t>
+          <t>合成</t>
         </is>
       </c>
     </row>
@@ -23624,17 +23619,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>青の絵具</t>
+          <t>お椀</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>イベント</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>強化素材</t>
+          <t>合成</t>
         </is>
       </c>
     </row>
@@ -23646,66 +23636,161 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>黄の絵具</t>
+          <t>お味噌汁</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>イベント</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>強化素材</t>
+          <t>合成</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>経験値の書</t>
+          <t>贈物</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>経験値の書・小</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>経験値+150</t>
+          <t>味噌</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>合成</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>経験値の書</t>
+          <t>贈物</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>経験値の書・中</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>経験値+1200</t>
+          <t>短刀の心得</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>合成</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>贈物</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>赤の絵具</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>イベント</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>強化素材</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>贈物</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>青の絵具</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>イベント</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>強化素材</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>贈物</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>黄の絵具</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>イベント</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>強化素材</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>経験値の書</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>経験値の書・小</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>経験値+150</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>経験値の書</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>経験値の書・中</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>経験値+1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>経験値の書</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>経験値の書・大</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>経験値+6000</t>
         </is>
@@ -23723,7 +23808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -23824,6 +23909,42 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>[紙,6][筆,6][鬼のツノ,4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>囲碁</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[丸太,2][獣の牙,2][お椀,2][ウロコ,2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>お味噌汁</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[味噌,4][葉っぱ,2][水,2][昆布,2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>短刀の心得</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[紙,6][筆,6][粘土,12]</t>
         </is>
       </c>
     </row>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -2073,7 +2073,11 @@
       <c r="BB17" s="5" t="n"/>
       <c r="BC17" s="2" t="n"/>
       <c r="BD17" s="2" t="n"/>
-      <c r="BE17" s="2" t="n"/>
+      <c r="BE17" s="2" t="inlineStr">
+        <is>
+          <t>青の絵具1,書き物道具2,囲碁2,お味噌汁2,そろばん2,短刀の心得1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2238,7 +2242,11 @@
       <c r="AP19" s="5" t="n"/>
       <c r="AQ19" s="5" t="n"/>
       <c r="AR19" s="5" t="n"/>
-      <c r="BC19" s="5" t="n"/>
+      <c r="BC19" s="5" t="inlineStr">
+        <is>
+          <t>葉っぱ2,大豆2</t>
+        </is>
+      </c>
       <c r="BD19" s="5" t="n"/>
       <c r="BE19" s="5" t="n"/>
     </row>
@@ -3597,7 +3605,11 @@
       <c r="AQ35" s="1" t="n"/>
       <c r="AR35" s="1" t="n"/>
       <c r="BC35" s="1" t="n"/>
-      <c r="BD35" s="1" t="n"/>
+      <c r="BD35" s="1" t="inlineStr">
+        <is>
+          <t>紙2,水2,大豆2,お花4</t>
+        </is>
+      </c>
       <c r="BE35" s="1" t="n"/>
     </row>
     <row r="36">
@@ -3761,7 +3773,11 @@
       <c r="AP37" s="1" t="n"/>
       <c r="AQ37" s="1" t="n"/>
       <c r="AR37" s="1" t="n"/>
-      <c r="BC37" s="1" t="n"/>
+      <c r="BC37" s="1" t="inlineStr">
+        <is>
+          <t>ふさふさの毛2,麦2</t>
+        </is>
+      </c>
       <c r="BD37" s="1" t="n"/>
       <c r="BE37" s="1" t="n"/>
     </row>
@@ -4455,7 +4471,11 @@
       <c r="AP45" s="1" t="n"/>
       <c r="AQ45" s="1" t="n"/>
       <c r="AR45" s="1" t="n"/>
-      <c r="BC45" s="1" t="n"/>
+      <c r="BC45" s="1" t="inlineStr">
+        <is>
+          <t>水2,ふさふさの毛2</t>
+        </is>
+      </c>
       <c r="BD45" s="1" t="n"/>
       <c r="BE45" s="1" t="n"/>
     </row>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -1903,7 +1903,11 @@
       </c>
       <c r="BC15" s="1" t="n"/>
       <c r="BD15" s="1" t="n"/>
-      <c r="BE15" s="1" t="n"/>
+      <c r="BE15" s="1" t="inlineStr">
+        <is>
+          <t>青の絵具1,書き物道具2,囲碁2,お味噌汁2,そろばん2,短刀の心得1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2073,11 +2077,7 @@
       <c r="BB17" s="5" t="n"/>
       <c r="BC17" s="2" t="n"/>
       <c r="BD17" s="2" t="n"/>
-      <c r="BE17" s="2" t="inlineStr">
-        <is>
-          <t>青の絵具1,書き物道具2,囲碁2,お味噌汁2,そろばん2,短刀の心得1</t>
-        </is>
-      </c>
+      <c r="BE17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -23828,7 +23828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -23940,7 +23940,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[丸太,2][獣の牙,2][お椀,2][ウロコ,2]</t>
+          <t>[丸太,1][獣の牙,1][お椀,1][ウロコ,1]</t>
         </is>
       </c>
     </row>
@@ -23952,7 +23952,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[味噌,4][葉っぱ,2][水,2][昆布,2]</t>
+          <t>[味噌,2][葉っぱ,1][水,1][昆布,1]</t>
         </is>
       </c>
     </row>
@@ -23965,6 +23965,30 @@
       <c r="B11" t="inlineStr">
         <is>
           <t>[紙,6][筆,6][粘土,12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>味噌</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[お米,1][大豆,1][塩,1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>お椀</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[粘土,1][火打ち石,1]</t>
         </is>
       </c>
     </row>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -804,6 +804,9 @@
       <c r="T2" s="7" t="n">
         <v>683</v>
       </c>
+      <c r="U2" s="7" t="n">
+        <v>989</v>
+      </c>
       <c r="V2" s="7" t="n">
         <v>1363</v>
       </c>
@@ -1060,11 +1063,27 @@
           <t>740,77</t>
         </is>
       </c>
-      <c r="T5" s="1" t="n"/>
-      <c r="U5" s="1" t="n"/>
+      <c r="T5" s="1" t="inlineStr">
+        <is>
+          <t>786,82</t>
+        </is>
+      </c>
+      <c r="U5" s="1" t="inlineStr">
+        <is>
+          <t>832,87</t>
+        </is>
+      </c>
       <c r="V5" s="1" t="n"/>
-      <c r="W5" s="1" t="n"/>
-      <c r="X5" s="1" t="n"/>
+      <c r="W5" s="1" t="inlineStr">
+        <is>
+          <t>924,97</t>
+        </is>
+      </c>
+      <c r="X5" s="1" t="inlineStr">
+        <is>
+          <t>971,102</t>
+        </is>
+      </c>
       <c r="Y5" s="1" t="n"/>
       <c r="Z5" s="1" t="n"/>
       <c r="AA5" s="1" t="n"/>
@@ -1144,7 +1163,11 @@
           <t>700,76</t>
         </is>
       </c>
-      <c r="S6" s="1" t="n"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>746,81</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="n"/>
       <c r="U6" s="1" t="n"/>
       <c r="V6" s="1" t="inlineStr">
@@ -1227,6 +1250,16 @@
       <c r="O7" s="5" t="inlineStr">
         <is>
           <t>471,69</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>588,86</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>627,92</t>
         </is>
       </c>
     </row>
@@ -1960,8 +1993,16 @@
       <c r="Q16" s="5" t="n"/>
       <c r="R16" s="5" t="n"/>
       <c r="S16" s="5" t="n"/>
-      <c r="T16" s="5" t="n"/>
-      <c r="U16" s="5" t="n"/>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>622,109</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>658,115</t>
+        </is>
+      </c>
       <c r="V16" s="5" t="n"/>
       <c r="W16" s="5" t="n"/>
       <c r="X16" s="5" t="n"/>
@@ -2353,8 +2394,16 @@
       </c>
       <c r="P21" s="1" t="n"/>
       <c r="Q21" s="1" t="n"/>
-      <c r="R21" s="1" t="n"/>
-      <c r="S21" s="1" t="n"/>
+      <c r="R21" s="1" t="inlineStr">
+        <is>
+          <t>595,70</t>
+        </is>
+      </c>
+      <c r="S21" s="1" t="inlineStr">
+        <is>
+          <t>635,74</t>
+        </is>
+      </c>
       <c r="T21" s="1" t="n"/>
       <c r="U21" s="1" t="n"/>
       <c r="V21" s="1" t="n"/>
@@ -2789,8 +2838,16 @@
       </c>
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
-      <c r="R26" s="2" t="n"/>
-      <c r="S26" s="2" t="n"/>
+      <c r="R26" s="1" t="inlineStr">
+        <is>
+          <t>688,90</t>
+        </is>
+      </c>
+      <c r="S26" s="1" t="inlineStr">
+        <is>
+          <t>733,96</t>
+        </is>
+      </c>
       <c r="T26" s="2" t="n"/>
       <c r="U26" s="2" t="n"/>
       <c r="V26" s="2" t="n"/>
@@ -2961,8 +3018,16 @@
       </c>
       <c r="P28" s="2" t="n"/>
       <c r="Q28" s="2" t="n"/>
-      <c r="R28" s="2" t="n"/>
-      <c r="S28" s="2" t="n"/>
+      <c r="R28" s="1" t="inlineStr">
+        <is>
+          <t>633,92</t>
+        </is>
+      </c>
+      <c r="S28" s="1" t="inlineStr">
+        <is>
+          <t>675,98</t>
+        </is>
+      </c>
       <c r="T28" s="2" t="n"/>
       <c r="U28" s="2" t="n"/>
       <c r="V28" s="2" t="n"/>
@@ -3223,11 +3288,27 @@
           <t>645,73</t>
         </is>
       </c>
-      <c r="T31" s="1" t="n"/>
-      <c r="U31" s="1" t="n"/>
+      <c r="T31" s="1" t="inlineStr">
+        <is>
+          <t>686,77</t>
+        </is>
+      </c>
+      <c r="U31" s="1" t="inlineStr">
+        <is>
+          <t>726,82</t>
+        </is>
+      </c>
       <c r="V31" s="1" t="n"/>
-      <c r="W31" s="1" t="n"/>
-      <c r="X31" s="1" t="n"/>
+      <c r="W31" s="1" t="inlineStr">
+        <is>
+          <t>806,91</t>
+        </is>
+      </c>
+      <c r="X31" s="1" t="inlineStr">
+        <is>
+          <t>847,96</t>
+        </is>
+      </c>
       <c r="Y31" s="1" t="n"/>
       <c r="Z31" s="1" t="n"/>
       <c r="AA31" s="1" t="n"/>
@@ -3831,8 +3912,16 @@
       </c>
       <c r="P38" s="1" t="n"/>
       <c r="Q38" s="1" t="n"/>
-      <c r="R38" s="1" t="n"/>
-      <c r="S38" s="1" t="n"/>
+      <c r="R38" s="1" t="inlineStr">
+        <is>
+          <t>729,87</t>
+        </is>
+      </c>
+      <c r="S38" s="1" t="inlineStr">
+        <is>
+          <t>777,93</t>
+        </is>
+      </c>
       <c r="T38" s="1" t="n"/>
       <c r="U38" s="1" t="n"/>
       <c r="V38" s="1" t="n"/>
@@ -4275,8 +4364,16 @@
           <t>771,74</t>
         </is>
       </c>
-      <c r="T43" s="1" t="n"/>
-      <c r="U43" s="1" t="n"/>
+      <c r="T43" s="1" t="inlineStr">
+        <is>
+          <t>819,79</t>
+        </is>
+      </c>
+      <c r="U43" s="1" t="inlineStr">
+        <is>
+          <t>867,84</t>
+        </is>
+      </c>
       <c r="V43" s="1" t="n"/>
       <c r="W43" s="1" t="n"/>
       <c r="X43" s="1" t="n"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -813,18 +813,36 @@
       <c r="W2" s="7" t="n">
         <v>1809</v>
       </c>
+      <c r="X2" s="7" t="n">
+        <v>2330</v>
+      </c>
       <c r="Y2" s="7" t="n">
         <v>2928</v>
       </c>
+      <c r="Z2" s="7" t="n">
+        <v>3609</v>
+      </c>
       <c r="AA2" s="7" t="n">
         <v>4373</v>
       </c>
+      <c r="AB2" s="7" t="n">
+        <v>5224</v>
+      </c>
       <c r="AD2" s="7" t="n">
         <v>7198</v>
       </c>
+      <c r="AE2" s="7" t="n">
+        <v>8326</v>
+      </c>
+      <c r="AF2" s="7" t="n">
+        <v>9550</v>
+      </c>
       <c r="AH2" s="7" t="n">
         <v>12298</v>
       </c>
+      <c r="AJ2" s="7" t="n">
+        <v>15458</v>
+      </c>
       <c r="AK2" s="7" t="n">
         <v>17199</v>
       </c>
@@ -833,6 +851,12 @@
       </c>
       <c r="AM2" s="7" t="n">
         <v>21009</v>
+      </c>
+      <c r="AN2" s="7" t="n">
+        <v>23083</v>
+      </c>
+      <c r="AP2" s="7" t="n">
+        <v>27576</v>
       </c>
       <c r="AQ2" s="7" t="n">
         <v>30000</v>
@@ -1691,8 +1715,16 @@
       </c>
       <c r="AN12" s="2" t="n"/>
       <c r="AO12" s="2" t="n"/>
-      <c r="AP12" s="2" t="n"/>
-      <c r="AQ12" s="2" t="n"/>
+      <c r="AP12" s="1" t="inlineStr">
+        <is>
+          <t>1861,192</t>
+        </is>
+      </c>
+      <c r="AQ12" s="1" t="inlineStr">
+        <is>
+          <t>1908,197</t>
+        </is>
+      </c>
       <c r="AR12" s="2" t="n"/>
       <c r="BC12" s="2" t="n"/>
       <c r="BD12" s="2" t="n"/>
@@ -1840,8 +1872,16 @@
           <t>1024,163</t>
         </is>
       </c>
-      <c r="AE14" s="1" t="n"/>
-      <c r="AF14" s="1" t="n"/>
+      <c r="AE14" s="1" t="inlineStr">
+        <is>
+          <t>1062,169</t>
+        </is>
+      </c>
+      <c r="AF14" s="1" t="inlineStr">
+        <is>
+          <t>1100,175</t>
+        </is>
+      </c>
       <c r="AG14" s="1" t="n"/>
       <c r="AH14" s="1" t="n"/>
       <c r="AI14" s="1" t="n"/>
@@ -3675,12 +3715,24 @@
           <t>1551,188</t>
         </is>
       </c>
-      <c r="AI35" s="1" t="n"/>
-      <c r="AJ35" s="1" t="n"/>
+      <c r="AI35" s="1" t="inlineStr">
+        <is>
+          <t>1600,194</t>
+        </is>
+      </c>
+      <c r="AJ35" s="1" t="inlineStr">
+        <is>
+          <t>1650,200</t>
+        </is>
+      </c>
       <c r="AK35" s="1" t="n"/>
       <c r="AL35" s="1" t="n"/>
       <c r="AM35" s="1" t="n"/>
-      <c r="AN35" s="1" t="n"/>
+      <c r="AN35" s="1" t="inlineStr">
+        <is>
+          <t>1850,224</t>
+        </is>
+      </c>
       <c r="AO35" s="1" t="n"/>
       <c r="AP35" s="1" t="n"/>
       <c r="AQ35" s="1" t="n"/>
@@ -4549,9 +4601,17 @@
         </is>
       </c>
       <c r="Y45" s="1" t="n"/>
-      <c r="Z45" s="1" t="n"/>
+      <c r="Z45" s="1" t="inlineStr">
+        <is>
+          <t>1023,120</t>
+        </is>
+      </c>
       <c r="AA45" s="1" t="n"/>
-      <c r="AB45" s="1" t="n"/>
+      <c r="AB45" s="1" t="inlineStr">
+        <is>
+          <t>1112,130</t>
+        </is>
+      </c>
       <c r="AC45" s="1" t="n"/>
       <c r="AD45" s="1" t="n"/>
       <c r="AE45" s="1" t="n"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -828,6 +828,9 @@
       <c r="AB2" s="7" t="n">
         <v>5224</v>
       </c>
+      <c r="AC2" s="7" t="n">
+        <v>6165</v>
+      </c>
       <c r="AD2" s="7" t="n">
         <v>7198</v>
       </c>
@@ -836,6 +839,9 @@
       </c>
       <c r="AF2" s="7" t="n">
         <v>9550</v>
+      </c>
+      <c r="AG2" s="7" t="n">
+        <v>10873</v>
       </c>
       <c r="AH2" s="7" t="n">
         <v>12298</v>
@@ -2305,13 +2311,25 @@
       </c>
       <c r="Y19" s="5" t="n"/>
       <c r="Z19" s="5" t="n"/>
-      <c r="AA19" s="5" t="n"/>
+      <c r="AA19" s="5" t="inlineStr">
+        <is>
+          <t>1033,114</t>
+        </is>
+      </c>
       <c r="AB19" s="5" t="n"/>
-      <c r="AC19" s="5" t="n"/>
+      <c r="AC19" s="5" t="inlineStr">
+        <is>
+          <t>1119,123</t>
+        </is>
+      </c>
       <c r="AD19" s="5" t="n"/>
       <c r="AE19" s="5" t="n"/>
       <c r="AF19" s="5" t="n"/>
-      <c r="AG19" s="5" t="n"/>
+      <c r="AG19" s="5" t="inlineStr">
+        <is>
+          <t>1291,142</t>
+        </is>
+      </c>
       <c r="AH19" s="5" t="n"/>
       <c r="AI19" s="5" t="n"/>
       <c r="AJ19" s="5" t="n"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamasakoyuki/Desktop/pazugiri-clean/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B32027E-937F-C444-B89A-B25699586A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025A2920-7BDE-2C48-87C5-6802247CF774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="468">
   <si>
     <t>刀剣男士番号</t>
   </si>
@@ -813,9 +813,6 @@
   </si>
   <si>
     <t>850,107</t>
-  </si>
-  <si>
-    <t>ふさふさの毛2,麦2</t>
   </si>
   <si>
     <t>山伏国広</t>
@@ -1431,6 +1428,65 @@
     <rPh sb="5" eb="7">
       <t>ダイズ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ふさふさの毛2,麦2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>水2,ふさふさの毛2</t>
+    <rPh sb="0" eb="1">
+      <t>ミズ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1398,194</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1076,118</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>971,122</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1019,122</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1068,125</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>565,93</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>955,150</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>615,67</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>682,82</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>603,99</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>656,72</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>727,87</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1468,12 +1524,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1488,7 +1550,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1496,7 +1558,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1852,8 +1915,7 @@
     <col min="11" max="11" width="2.33203125" hidden="1" customWidth="1"/>
     <col min="12" max="13" width="2.1640625" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="2.5" hidden="1" customWidth="1"/>
-    <col min="15" max="17" width="6.83203125" hidden="1" customWidth="1"/>
-    <col min="18" max="48" width="6.83203125" customWidth="1"/>
+    <col min="15" max="48" width="6.83203125" customWidth="1"/>
     <col min="49" max="54" width="1.1640625" customWidth="1"/>
     <col min="55" max="55" width="28" customWidth="1"/>
     <col min="56" max="56" width="16.5" customWidth="1"/>
@@ -2037,81 +2099,96 @@
       <c r="A2" t="s">
         <v>57</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="5">
         <v>9</v>
       </c>
-      <c r="R2" s="7">
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5">
         <v>258</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="5">
         <v>441</v>
       </c>
-      <c r="T2" s="7">
+      <c r="T2" s="5">
         <v>683</v>
       </c>
-      <c r="U2" s="7">
+      <c r="U2" s="5">
         <v>989</v>
       </c>
-      <c r="V2" s="7">
+      <c r="V2" s="5">
         <v>1363</v>
       </c>
-      <c r="W2" s="7">
+      <c r="W2" s="5">
         <v>1809</v>
       </c>
-      <c r="X2" s="7">
+      <c r="X2" s="5">
         <v>2330</v>
       </c>
-      <c r="Y2" s="7">
+      <c r="Y2" s="5">
         <v>2928</v>
       </c>
-      <c r="Z2" s="7">
+      <c r="Z2" s="5">
         <v>3609</v>
       </c>
-      <c r="AA2" s="7">
+      <c r="AA2" s="5">
         <v>4373</v>
       </c>
-      <c r="AB2" s="7">
+      <c r="AB2" s="5">
         <v>5224</v>
       </c>
-      <c r="AC2" s="7">
+      <c r="AC2" s="5">
         <v>6165</v>
       </c>
-      <c r="AD2" s="7">
+      <c r="AD2" s="5">
         <v>7198</v>
       </c>
-      <c r="AE2" s="7">
+      <c r="AE2" s="5">
         <v>8326</v>
       </c>
-      <c r="AF2" s="7">
+      <c r="AF2" s="5">
         <v>9550</v>
       </c>
-      <c r="AG2" s="7">
+      <c r="AG2" s="5">
         <v>10873</v>
       </c>
-      <c r="AH2" s="7">
+      <c r="AH2" s="5">
         <v>12298</v>
       </c>
-      <c r="AJ2" s="7">
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5">
         <v>15458</v>
       </c>
-      <c r="AK2" s="7">
+      <c r="AK2" s="5">
         <v>17199</v>
       </c>
-      <c r="AL2" s="7">
+      <c r="AL2" s="5">
         <v>19049</v>
       </c>
-      <c r="AM2" s="7">
+      <c r="AM2" s="5">
         <v>21009</v>
       </c>
-      <c r="AN2" s="7">
+      <c r="AN2" s="5">
         <v>23083</v>
       </c>
-      <c r="AP2" s="7">
+      <c r="AO2" s="5"/>
+      <c r="AP2" s="5">
         <v>27576</v>
       </c>
-      <c r="AQ2" s="7">
+      <c r="AQ2" s="5">
         <v>30000</v>
       </c>
+      <c r="AR2" s="5"/>
+      <c r="AS2" s="5"/>
+      <c r="AT2" s="5"/>
+      <c r="AU2" s="5"/>
+      <c r="AV2" s="5"/>
+      <c r="AW2" s="5"/>
+      <c r="AX2" s="5"/>
+      <c r="AY2" s="5"/>
+      <c r="AZ2" s="5"/>
+      <c r="BA2" s="5"/>
+      <c r="BB2" s="5"/>
     </row>
     <row r="3" spans="1:57">
       <c r="A3">
@@ -2173,6 +2250,16 @@
       <c r="AP3" s="1"/>
       <c r="AQ3" s="1"/>
       <c r="AR3" s="1"/>
+      <c r="AS3" s="5"/>
+      <c r="AT3" s="5"/>
+      <c r="AU3" s="5"/>
+      <c r="AV3" s="5"/>
+      <c r="AW3" s="5"/>
+      <c r="AX3" s="5"/>
+      <c r="AY3" s="5"/>
+      <c r="AZ3" s="5"/>
+      <c r="BA3" s="5"/>
+      <c r="BB3" s="5"/>
       <c r="BC3" s="1"/>
       <c r="BD3" s="1"/>
       <c r="BE3" s="1"/>
@@ -2211,21 +2298,21 @@
       <c r="K4" t="s">
         <v>70</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1" t="s">
+      <c r="O4" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="7" t="s">
         <v>71</v>
       </c>
       <c r="AB4" s="1"/>
@@ -2245,6 +2332,16 @@
       <c r="AP4" s="1"/>
       <c r="AQ4" s="1"/>
       <c r="AR4" s="1"/>
+      <c r="AS4" s="5"/>
+      <c r="AT4" s="5"/>
+      <c r="AU4" s="5"/>
+      <c r="AV4" s="5"/>
+      <c r="AW4" s="5"/>
+      <c r="AX4" s="5"/>
+      <c r="AY4" s="5"/>
+      <c r="AZ4" s="5"/>
+      <c r="BA4" s="5"/>
+      <c r="BB4" s="5"/>
       <c r="BC4" s="1"/>
       <c r="BD4" s="1"/>
       <c r="BE4" s="1"/>
@@ -2277,26 +2374,26 @@
       <c r="J5" t="s">
         <v>75</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="O5" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1" t="s">
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="T5" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="U5" s="1" t="s">
+      <c r="U5" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1" t="s">
+      <c r="V5" s="7"/>
+      <c r="W5" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="X5" s="1" t="s">
+      <c r="X5" s="7" t="s">
         <v>81</v>
       </c>
       <c r="Y5" s="1"/>
@@ -2319,7 +2416,19 @@
       <c r="AP5" s="1"/>
       <c r="AQ5" s="1"/>
       <c r="AR5" s="1"/>
-      <c r="BC5" s="1"/>
+      <c r="AS5" s="5"/>
+      <c r="AT5" s="5"/>
+      <c r="AU5" s="5"/>
+      <c r="AV5" s="5"/>
+      <c r="AW5" s="5"/>
+      <c r="AX5" s="5"/>
+      <c r="AY5" s="5"/>
+      <c r="AZ5" s="5"/>
+      <c r="BA5" s="5"/>
+      <c r="BB5" s="5"/>
+      <c r="BC5" s="1" t="s">
+        <v>455</v>
+      </c>
       <c r="BD5" s="1"/>
       <c r="BE5" s="1"/>
     </row>
@@ -2351,12 +2460,12 @@
       <c r="J6" t="s">
         <v>87</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="O6" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1" t="s">
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7" t="s">
         <v>89</v>
       </c>
       <c r="S6" s="1" t="s">
@@ -2391,6 +2500,16 @@
       <c r="AP6" s="1"/>
       <c r="AQ6" s="1"/>
       <c r="AR6" s="1"/>
+      <c r="AS6" s="5"/>
+      <c r="AT6" s="5"/>
+      <c r="AU6" s="5"/>
+      <c r="AV6" s="5"/>
+      <c r="AW6" s="5"/>
+      <c r="AX6" s="5"/>
+      <c r="AY6" s="5"/>
+      <c r="AZ6" s="5"/>
+      <c r="BA6" s="5"/>
+      <c r="BB6" s="5"/>
       <c r="BC6" s="1"/>
       <c r="BD6" s="1"/>
       <c r="BE6" s="1"/>
@@ -2423,15 +2542,52 @@
       <c r="J7" t="s">
         <v>97</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="R7" s="5" t="s">
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8" t="s">
         <v>99</v>
       </c>
       <c r="S7" s="5" t="s">
         <v>100</v>
       </c>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5"/>
+      <c r="AA7" s="5"/>
+      <c r="AB7" s="5"/>
+      <c r="AC7" s="5"/>
+      <c r="AD7" s="5"/>
+      <c r="AE7" s="5"/>
+      <c r="AF7" s="5"/>
+      <c r="AG7" s="5"/>
+      <c r="AH7" s="5"/>
+      <c r="AI7" s="5"/>
+      <c r="AJ7" s="5"/>
+      <c r="AK7" s="5"/>
+      <c r="AL7" s="5"/>
+      <c r="AM7" s="5"/>
+      <c r="AN7" s="5"/>
+      <c r="AO7" s="5"/>
+      <c r="AP7" s="5"/>
+      <c r="AQ7" s="5"/>
+      <c r="AR7" s="5"/>
+      <c r="AS7" s="5"/>
+      <c r="AT7" s="5"/>
+      <c r="AU7" s="5"/>
+      <c r="AV7" s="5"/>
+      <c r="AW7" s="5"/>
+      <c r="AX7" s="5"/>
+      <c r="AY7" s="5"/>
+      <c r="AZ7" s="5"/>
+      <c r="BA7" s="5"/>
+      <c r="BB7" s="5"/>
     </row>
     <row r="8" spans="1:57">
       <c r="A8">
@@ -2461,7 +2617,7 @@
       <c r="J8" t="s">
         <v>104</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="O8" s="7" t="s">
         <v>105</v>
       </c>
       <c r="P8" s="1"/>
@@ -2609,42 +2765,52 @@
       <c r="J10" t="s">
         <v>114</v>
       </c>
-      <c r="O10" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
-      <c r="AB10" s="5"/>
-      <c r="AC10" s="5"/>
-      <c r="AD10" s="5"/>
-      <c r="AE10" s="5"/>
-      <c r="AF10" s="5"/>
-      <c r="AG10" s="5"/>
-      <c r="AH10" s="5"/>
-      <c r="AI10" s="5"/>
-      <c r="AJ10" s="5"/>
-      <c r="AK10" s="5"/>
-      <c r="AL10" s="5"/>
-      <c r="AM10" s="5"/>
-      <c r="AN10" s="5"/>
-      <c r="AO10" s="5"/>
-      <c r="AP10" s="5" t="s">
+      <c r="O10" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+      <c r="AA10" s="8"/>
+      <c r="AB10" s="8"/>
+      <c r="AC10" s="8"/>
+      <c r="AD10" s="8"/>
+      <c r="AE10" s="8"/>
+      <c r="AF10" s="8"/>
+      <c r="AG10" s="8"/>
+      <c r="AH10" s="8"/>
+      <c r="AI10" s="8"/>
+      <c r="AJ10" s="8"/>
+      <c r="AK10" s="8"/>
+      <c r="AL10" s="8"/>
+      <c r="AM10" s="8"/>
+      <c r="AN10" s="8"/>
+      <c r="AO10" s="8"/>
+      <c r="AP10" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="AQ10" s="5" t="s">
+      <c r="AQ10" s="8" t="s">
         <v>116</v>
       </c>
       <c r="AR10" s="5"/>
+      <c r="AS10" s="5"/>
+      <c r="AT10" s="5"/>
+      <c r="AU10" s="5"/>
+      <c r="AV10" s="5"/>
+      <c r="AW10" s="5"/>
+      <c r="AX10" s="5"/>
+      <c r="AY10" s="5"/>
+      <c r="AZ10" s="5"/>
+      <c r="BA10" s="5"/>
+      <c r="BB10" s="5"/>
       <c r="BC10" s="5"/>
       <c r="BD10" s="5"/>
       <c r="BE10" s="5"/>
@@ -2677,19 +2843,19 @@
       <c r="J11" t="s">
         <v>121</v>
       </c>
-      <c r="O11" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1" t="s">
+      <c r="O11" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7" t="s">
         <v>122</v>
       </c>
       <c r="Z11" s="1"/>
@@ -2711,6 +2877,16 @@
       <c r="AP11" s="1"/>
       <c r="AQ11" s="1"/>
       <c r="AR11" s="1"/>
+      <c r="AS11" s="5"/>
+      <c r="AT11" s="5"/>
+      <c r="AU11" s="5"/>
+      <c r="AV11" s="5"/>
+      <c r="AW11" s="5"/>
+      <c r="AX11" s="5"/>
+      <c r="AY11" s="5"/>
+      <c r="AZ11" s="5"/>
+      <c r="BA11" s="5"/>
+      <c r="BB11" s="5"/>
       <c r="BC11" s="1"/>
       <c r="BD11" s="1"/>
       <c r="BE11" s="1"/>
@@ -2746,46 +2922,56 @@
       <c r="K12" t="s">
         <v>125</v>
       </c>
-      <c r="O12" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Y12" s="2"/>
-      <c r="Z12" s="2"/>
-      <c r="AA12" s="2"/>
-      <c r="AB12" s="2"/>
-      <c r="AC12" s="2"/>
-      <c r="AD12" s="2"/>
-      <c r="AE12" s="2"/>
-      <c r="AF12" s="2"/>
-      <c r="AG12" s="2"/>
-      <c r="AH12" s="2"/>
-      <c r="AI12" s="2"/>
-      <c r="AJ12" s="2"/>
-      <c r="AK12" s="2"/>
-      <c r="AL12" s="1" t="s">
+      <c r="O12" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="7"/>
+      <c r="AC12" s="7"/>
+      <c r="AD12" s="7"/>
+      <c r="AE12" s="7"/>
+      <c r="AF12" s="7"/>
+      <c r="AG12" s="7"/>
+      <c r="AH12" s="7"/>
+      <c r="AI12" s="7"/>
+      <c r="AJ12" s="7"/>
+      <c r="AK12" s="7"/>
+      <c r="AL12" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="AM12" s="1" t="s">
+      <c r="AM12" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="AN12" s="2"/>
-      <c r="AO12" s="2"/>
+      <c r="AN12" s="1"/>
+      <c r="AO12" s="1"/>
       <c r="AP12" s="1" t="s">
         <v>128</v>
       </c>
       <c r="AQ12" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="AR12" s="2"/>
+      <c r="AR12" s="1"/>
+      <c r="AS12" s="5"/>
+      <c r="AT12" s="5"/>
+      <c r="AU12" s="5"/>
+      <c r="AV12" s="5"/>
+      <c r="AW12" s="5"/>
+      <c r="AX12" s="5"/>
+      <c r="AY12" s="5"/>
+      <c r="AZ12" s="5"/>
+      <c r="BA12" s="5"/>
+      <c r="BB12" s="5"/>
       <c r="BC12" s="2"/>
       <c r="BD12" s="2"/>
       <c r="BE12" s="2"/>
@@ -2818,33 +3004,35 @@
       <c r="J13" t="s">
         <v>132</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="1"/>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="1"/>
-      <c r="Z13" s="1"/>
-      <c r="AA13" s="1"/>
-      <c r="AB13" s="1"/>
-      <c r="AC13" s="1"/>
-      <c r="AD13" s="1"/>
-      <c r="AE13" s="1"/>
-      <c r="AF13" s="1"/>
-      <c r="AG13" s="1"/>
-      <c r="AH13" s="1"/>
-      <c r="AI13" s="1"/>
-      <c r="AJ13" s="1" t="s">
+      <c r="O13" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
+      <c r="AA13" s="7"/>
+      <c r="AB13" s="7"/>
+      <c r="AC13" s="7"/>
+      <c r="AD13" s="7"/>
+      <c r="AE13" s="7"/>
+      <c r="AF13" s="7"/>
+      <c r="AG13" s="7"/>
+      <c r="AH13" s="7"/>
+      <c r="AI13" s="7"/>
+      <c r="AJ13" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="AK13" s="1"/>
+      <c r="AK13" s="7" t="s">
+        <v>456</v>
+      </c>
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
       <c r="AN13" s="1"/>
@@ -2852,6 +3040,16 @@
       <c r="AP13" s="1"/>
       <c r="AQ13" s="1"/>
       <c r="AR13" s="1"/>
+      <c r="AS13" s="5"/>
+      <c r="AT13" s="5"/>
+      <c r="AU13" s="5"/>
+      <c r="AV13" s="5"/>
+      <c r="AW13" s="5"/>
+      <c r="AX13" s="5"/>
+      <c r="AY13" s="5"/>
+      <c r="AZ13" s="5"/>
+      <c r="BA13" s="5"/>
+      <c r="BB13" s="5"/>
       <c r="BC13" s="1"/>
       <c r="BD13" s="1"/>
       <c r="BE13" s="1"/>
@@ -2884,30 +3082,30 @@
       <c r="J14" t="s">
         <v>136</v>
       </c>
-      <c r="O14" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
-      <c r="AD14" s="1" t="s">
+      <c r="O14" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="7"/>
+      <c r="AB14" s="7"/>
+      <c r="AC14" s="7"/>
+      <c r="AD14" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="AE14" s="1" t="s">
+      <c r="AE14" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="AF14" s="1" t="s">
+      <c r="AF14" s="7" t="s">
         <v>139</v>
       </c>
       <c r="AG14" s="1"/>
@@ -2922,6 +3120,16 @@
       <c r="AP14" s="1"/>
       <c r="AQ14" s="1"/>
       <c r="AR14" s="1"/>
+      <c r="AS14" s="5"/>
+      <c r="AT14" s="5"/>
+      <c r="AU14" s="5"/>
+      <c r="AV14" s="5"/>
+      <c r="AW14" s="5"/>
+      <c r="AX14" s="5"/>
+      <c r="AY14" s="5"/>
+      <c r="AZ14" s="5"/>
+      <c r="BA14" s="5"/>
+      <c r="BB14" s="5"/>
       <c r="BC14" s="1"/>
       <c r="BD14" s="1"/>
       <c r="BE14" s="1"/>
@@ -2954,40 +3162,50 @@
       <c r="J15" t="s">
         <v>141</v>
       </c>
-      <c r="O15" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-      <c r="Z15" s="1"/>
-      <c r="AA15" s="1"/>
-      <c r="AB15" s="1"/>
-      <c r="AC15" s="1"/>
-      <c r="AD15" s="1"/>
-      <c r="AE15" s="1"/>
-      <c r="AF15" s="1"/>
-      <c r="AG15" s="1"/>
-      <c r="AH15" s="1"/>
-      <c r="AI15" s="1"/>
-      <c r="AJ15" s="1"/>
-      <c r="AK15" s="1"/>
-      <c r="AL15" s="1"/>
-      <c r="AM15" s="1"/>
-      <c r="AN15" s="1"/>
-      <c r="AO15" s="1"/>
-      <c r="AP15" s="1"/>
-      <c r="AQ15" s="1"/>
-      <c r="AR15" s="1" t="s">
+      <c r="O15" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7"/>
+      <c r="AC15" s="7"/>
+      <c r="AD15" s="7"/>
+      <c r="AE15" s="7"/>
+      <c r="AF15" s="7"/>
+      <c r="AG15" s="7"/>
+      <c r="AH15" s="7"/>
+      <c r="AI15" s="7"/>
+      <c r="AJ15" s="7"/>
+      <c r="AK15" s="7"/>
+      <c r="AL15" s="7"/>
+      <c r="AM15" s="7"/>
+      <c r="AN15" s="7"/>
+      <c r="AO15" s="7"/>
+      <c r="AP15" s="7"/>
+      <c r="AQ15" s="7"/>
+      <c r="AR15" s="7" t="s">
         <v>142</v>
       </c>
+      <c r="AS15" s="5"/>
+      <c r="AT15" s="5"/>
+      <c r="AU15" s="5"/>
+      <c r="AV15" s="5"/>
+      <c r="AW15" s="5"/>
+      <c r="AX15" s="5"/>
+      <c r="AY15" s="5"/>
+      <c r="AZ15" s="5"/>
+      <c r="BA15" s="5"/>
+      <c r="BB15" s="5"/>
       <c r="BC15" s="1"/>
       <c r="BD15" s="1"/>
       <c r="BE15" s="1" t="s">
@@ -3022,22 +3240,22 @@
       <c r="J16" t="s">
         <v>145</v>
       </c>
-      <c r="O16" s="5" t="s">
+      <c r="O16" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5" t="s">
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="U16" s="5" t="s">
+      <c r="U16" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
       <c r="AA16" s="5"/>
@@ -3058,6 +3276,16 @@
       <c r="AP16" s="5"/>
       <c r="AQ16" s="5"/>
       <c r="AR16" s="5"/>
+      <c r="AS16" s="5"/>
+      <c r="AT16" s="5"/>
+      <c r="AU16" s="5"/>
+      <c r="AV16" s="5"/>
+      <c r="AW16" s="5"/>
+      <c r="AX16" s="5"/>
+      <c r="AY16" s="5"/>
+      <c r="AZ16" s="5"/>
+      <c r="BA16" s="5"/>
+      <c r="BB16" s="5"/>
       <c r="BC16" s="5"/>
       <c r="BD16" s="5"/>
       <c r="BE16" s="5"/>
@@ -3235,26 +3463,28 @@
       <c r="J19" t="s">
         <v>159</v>
       </c>
-      <c r="O19" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
-      <c r="V19" s="5"/>
-      <c r="W19" s="5"/>
-      <c r="X19" s="5" t="s">
+      <c r="O19" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="8"/>
+      <c r="X19" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="Y19" s="5"/>
-      <c r="Z19" s="5"/>
-      <c r="AA19" s="5" t="s">
+      <c r="Y19" s="8"/>
+      <c r="Z19" s="8"/>
+      <c r="AA19" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="AB19" s="5"/>
+      <c r="AB19" s="8" t="s">
+        <v>457</v>
+      </c>
       <c r="AC19" s="5" t="s">
         <v>162</v>
       </c>
@@ -3275,6 +3505,16 @@
       <c r="AP19" s="5"/>
       <c r="AQ19" s="5"/>
       <c r="AR19" s="5"/>
+      <c r="AS19" s="5"/>
+      <c r="AT19" s="5"/>
+      <c r="AU19" s="5"/>
+      <c r="AV19" s="5"/>
+      <c r="AW19" s="5"/>
+      <c r="AX19" s="5"/>
+      <c r="AY19" s="5"/>
+      <c r="AZ19" s="5"/>
+      <c r="BA19" s="5"/>
+      <c r="BB19" s="5"/>
       <c r="BC19" s="5" t="s">
         <v>164</v>
       </c>
@@ -3315,6 +3555,45 @@
       <c r="O20" s="5" t="s">
         <v>168</v>
       </c>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="5"/>
+      <c r="Z20" s="5"/>
+      <c r="AA20" s="5"/>
+      <c r="AB20" s="5"/>
+      <c r="AC20" s="5"/>
+      <c r="AD20" s="5"/>
+      <c r="AE20" s="5"/>
+      <c r="AF20" s="5"/>
+      <c r="AG20" s="5"/>
+      <c r="AH20" s="5"/>
+      <c r="AI20" s="5"/>
+      <c r="AJ20" s="5"/>
+      <c r="AK20" s="5"/>
+      <c r="AL20" s="5"/>
+      <c r="AM20" s="5"/>
+      <c r="AN20" s="5"/>
+      <c r="AO20" s="5"/>
+      <c r="AP20" s="5"/>
+      <c r="AQ20" s="5"/>
+      <c r="AR20" s="5"/>
+      <c r="AS20" s="5"/>
+      <c r="AT20" s="5"/>
+      <c r="AU20" s="5"/>
+      <c r="AV20" s="5"/>
+      <c r="AW20" s="5"/>
+      <c r="AX20" s="5"/>
+      <c r="AY20" s="5"/>
+      <c r="AZ20" s="5"/>
+      <c r="BA20" s="5"/>
+      <c r="BB20" s="5"/>
     </row>
     <row r="21" spans="1:57">
       <c r="A21">
@@ -3344,12 +3623,12 @@
       <c r="J21" t="s">
         <v>171</v>
       </c>
-      <c r="O21" s="1" t="s">
+      <c r="O21" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1" t="s">
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7" t="s">
         <v>173</v>
       </c>
       <c r="S21" s="1" t="s">
@@ -3380,6 +3659,16 @@
       <c r="AP21" s="1"/>
       <c r="AQ21" s="1"/>
       <c r="AR21" s="1"/>
+      <c r="AS21" s="5"/>
+      <c r="AT21" s="5"/>
+      <c r="AU21" s="5"/>
+      <c r="AV21" s="5"/>
+      <c r="AW21" s="5"/>
+      <c r="AX21" s="5"/>
+      <c r="AY21" s="5"/>
+      <c r="AZ21" s="5"/>
+      <c r="BA21" s="5"/>
+      <c r="BB21" s="5"/>
       <c r="BC21" s="1"/>
       <c r="BD21" s="1"/>
       <c r="BE21" s="1"/>
@@ -3560,44 +3849,56 @@
       <c r="J24" t="s">
         <v>186</v>
       </c>
-      <c r="O24" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="1" t="s">
+      <c r="O24" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="U24" s="2"/>
-      <c r="V24" s="1" t="s">
+      <c r="U24" s="7"/>
+      <c r="V24" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-      <c r="Z24" s="2"/>
-      <c r="AA24" s="2"/>
-      <c r="AB24" s="2"/>
-      <c r="AC24" s="2"/>
-      <c r="AD24" s="2"/>
-      <c r="AE24" s="2"/>
-      <c r="AF24" s="2"/>
-      <c r="AG24" s="2"/>
-      <c r="AH24" s="2"/>
-      <c r="AI24" s="2"/>
-      <c r="AJ24" s="2"/>
-      <c r="AK24" s="2"/>
-      <c r="AL24" s="2"/>
-      <c r="AM24" s="2"/>
-      <c r="AN24" s="2"/>
-      <c r="AO24" s="2"/>
-      <c r="AP24" s="2"/>
-      <c r="AQ24" s="2"/>
-      <c r="AR24" s="2"/>
+      <c r="W24" s="7"/>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="7"/>
+      <c r="AA24" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1"/>
+      <c r="AD24" s="1"/>
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="1"/>
+      <c r="AG24" s="1"/>
+      <c r="AH24" s="1"/>
+      <c r="AI24" s="1"/>
+      <c r="AJ24" s="1"/>
+      <c r="AK24" s="1"/>
+      <c r="AL24" s="1"/>
+      <c r="AM24" s="1"/>
+      <c r="AN24" s="1"/>
+      <c r="AO24" s="1"/>
+      <c r="AP24" s="1"/>
+      <c r="AQ24" s="1"/>
+      <c r="AR24" s="1"/>
+      <c r="AS24" s="5"/>
+      <c r="AT24" s="5"/>
+      <c r="AU24" s="5"/>
+      <c r="AV24" s="5"/>
+      <c r="AW24" s="5"/>
+      <c r="AX24" s="5"/>
+      <c r="AY24" s="5"/>
+      <c r="AZ24" s="5"/>
+      <c r="BA24" s="5"/>
+      <c r="BB24" s="5"/>
       <c r="BC24" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="BD24" s="2"/>
       <c r="BE24" s="2"/>
@@ -3704,42 +4005,52 @@
       <c r="J26" t="s">
         <v>198</v>
       </c>
-      <c r="O26" s="1" t="s">
+      <c r="O26" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="1" t="s">
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7" t="s">
         <v>200</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
-      <c r="Y26" s="2"/>
-      <c r="Z26" s="2"/>
-      <c r="AA26" s="2"/>
-      <c r="AB26" s="2"/>
-      <c r="AC26" s="2"/>
-      <c r="AD26" s="2"/>
-      <c r="AE26" s="2"/>
-      <c r="AF26" s="2"/>
-      <c r="AG26" s="2"/>
-      <c r="AH26" s="2"/>
-      <c r="AI26" s="2"/>
-      <c r="AJ26" s="2"/>
-      <c r="AK26" s="2"/>
-      <c r="AL26" s="2"/>
-      <c r="AM26" s="2"/>
-      <c r="AN26" s="2"/>
-      <c r="AO26" s="2"/>
-      <c r="AP26" s="2"/>
-      <c r="AQ26" s="2"/>
-      <c r="AR26" s="2"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1"/>
+      <c r="AF26" s="1"/>
+      <c r="AG26" s="1"/>
+      <c r="AH26" s="1"/>
+      <c r="AI26" s="1"/>
+      <c r="AJ26" s="1"/>
+      <c r="AK26" s="1"/>
+      <c r="AL26" s="1"/>
+      <c r="AM26" s="1"/>
+      <c r="AN26" s="1"/>
+      <c r="AO26" s="1"/>
+      <c r="AP26" s="1"/>
+      <c r="AQ26" s="1"/>
+      <c r="AR26" s="1"/>
+      <c r="AS26" s="5"/>
+      <c r="AT26" s="5"/>
+      <c r="AU26" s="5"/>
+      <c r="AV26" s="5"/>
+      <c r="AW26" s="5"/>
+      <c r="AX26" s="5"/>
+      <c r="AY26" s="5"/>
+      <c r="AZ26" s="5"/>
+      <c r="BA26" s="5"/>
+      <c r="BB26" s="5"/>
       <c r="BC26" s="2"/>
       <c r="BD26" s="2"/>
       <c r="BE26" s="2"/>
@@ -3772,13 +4083,17 @@
       <c r="J27" t="s">
         <v>205</v>
       </c>
-      <c r="O27" s="1" t="s">
+      <c r="O27" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="S27" s="7" t="s">
+        <v>467</v>
+      </c>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
@@ -3846,42 +4161,52 @@
       <c r="J28" t="s">
         <v>210</v>
       </c>
-      <c r="O28" s="1" t="s">
+      <c r="O28" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="1" t="s">
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7" t="s">
         <v>212</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="T28" s="2"/>
-      <c r="U28" s="2"/>
-      <c r="V28" s="2"/>
-      <c r="W28" s="2"/>
-      <c r="X28" s="2"/>
-      <c r="Y28" s="2"/>
-      <c r="Z28" s="2"/>
-      <c r="AA28" s="2"/>
-      <c r="AB28" s="2"/>
-      <c r="AC28" s="2"/>
-      <c r="AD28" s="2"/>
-      <c r="AE28" s="2"/>
-      <c r="AF28" s="2"/>
-      <c r="AG28" s="2"/>
-      <c r="AH28" s="2"/>
-      <c r="AI28" s="2"/>
-      <c r="AJ28" s="2"/>
-      <c r="AK28" s="2"/>
-      <c r="AL28" s="2"/>
-      <c r="AM28" s="2"/>
-      <c r="AN28" s="2"/>
-      <c r="AO28" s="2"/>
-      <c r="AP28" s="2"/>
-      <c r="AQ28" s="2"/>
-      <c r="AR28" s="2"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="1"/>
+      <c r="AD28" s="1"/>
+      <c r="AE28" s="1"/>
+      <c r="AF28" s="1"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="1"/>
+      <c r="AI28" s="1"/>
+      <c r="AJ28" s="1"/>
+      <c r="AK28" s="1"/>
+      <c r="AL28" s="1"/>
+      <c r="AM28" s="1"/>
+      <c r="AN28" s="1"/>
+      <c r="AO28" s="1"/>
+      <c r="AP28" s="1"/>
+      <c r="AQ28" s="1"/>
+      <c r="AR28" s="1"/>
+      <c r="AS28" s="5"/>
+      <c r="AT28" s="5"/>
+      <c r="AU28" s="5"/>
+      <c r="AV28" s="5"/>
+      <c r="AW28" s="5"/>
+      <c r="AX28" s="5"/>
+      <c r="AY28" s="5"/>
+      <c r="AZ28" s="5"/>
+      <c r="BA28" s="5"/>
+      <c r="BB28" s="5"/>
       <c r="BC28" s="2"/>
       <c r="BD28" s="2"/>
       <c r="BE28" s="2"/>
@@ -3914,13 +4239,17 @@
       <c r="J29" t="s">
         <v>217</v>
       </c>
-      <c r="O29" s="1" t="s">
+      <c r="O29" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="S29" s="7" t="s">
+        <v>466</v>
+      </c>
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
@@ -4062,19 +4391,19 @@
       <c r="J31" t="s">
         <v>226</v>
       </c>
-      <c r="O31" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1" t="s">
+      <c r="O31" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="T31" s="1" t="s">
+      <c r="T31" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="U31" s="1" t="s">
+      <c r="U31" s="7" t="s">
         <v>229</v>
       </c>
       <c r="V31" s="1"/>
@@ -4104,6 +4433,16 @@
       <c r="AP31" s="1"/>
       <c r="AQ31" s="1"/>
       <c r="AR31" s="1"/>
+      <c r="AS31" s="5"/>
+      <c r="AT31" s="5"/>
+      <c r="AU31" s="5"/>
+      <c r="AV31" s="5"/>
+      <c r="AW31" s="5"/>
+      <c r="AX31" s="5"/>
+      <c r="AY31" s="5"/>
+      <c r="AZ31" s="5"/>
+      <c r="BA31" s="5"/>
+      <c r="BB31" s="5"/>
       <c r="BC31" s="1"/>
       <c r="BD31" s="1"/>
       <c r="BE31" s="1"/>
@@ -4361,34 +4700,34 @@
       <c r="J35" t="s">
         <v>246</v>
       </c>
-      <c r="O35" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
-      <c r="Z35" s="1"/>
-      <c r="AA35" s="1"/>
-      <c r="AB35" s="1"/>
-      <c r="AC35" s="1"/>
-      <c r="AD35" s="1"/>
-      <c r="AE35" s="1"/>
-      <c r="AF35" s="1"/>
-      <c r="AG35" s="1"/>
-      <c r="AH35" s="1" t="s">
+      <c r="O35" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
+      <c r="Y35" s="7"/>
+      <c r="Z35" s="7"/>
+      <c r="AA35" s="7"/>
+      <c r="AB35" s="7"/>
+      <c r="AC35" s="7"/>
+      <c r="AD35" s="7"/>
+      <c r="AE35" s="7"/>
+      <c r="AF35" s="7"/>
+      <c r="AG35" s="7"/>
+      <c r="AH35" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="AI35" s="1" t="s">
+      <c r="AI35" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="AJ35" s="1" t="s">
+      <c r="AJ35" s="7" t="s">
         <v>249</v>
       </c>
       <c r="AK35" s="1"/>
@@ -4401,6 +4740,16 @@
       <c r="AP35" s="1"/>
       <c r="AQ35" s="1"/>
       <c r="AR35" s="1"/>
+      <c r="AS35" s="5"/>
+      <c r="AT35" s="5"/>
+      <c r="AU35" s="5"/>
+      <c r="AV35" s="5"/>
+      <c r="AW35" s="5"/>
+      <c r="AX35" s="5"/>
+      <c r="AY35" s="5"/>
+      <c r="AZ35" s="5"/>
+      <c r="BA35" s="5"/>
+      <c r="BB35" s="5"/>
       <c r="BC35" s="1"/>
       <c r="BD35" s="1" t="s">
         <v>251</v>
@@ -4435,44 +4784,54 @@
       <c r="J36" t="s">
         <v>255</v>
       </c>
-      <c r="O36" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
-      <c r="W36" s="1"/>
-      <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
-      <c r="Z36" s="1"/>
-      <c r="AA36" s="1"/>
-      <c r="AB36" s="1"/>
-      <c r="AC36" s="1"/>
-      <c r="AD36" s="1"/>
-      <c r="AE36" s="1"/>
-      <c r="AF36" s="1"/>
-      <c r="AG36" s="1"/>
-      <c r="AH36" s="1"/>
-      <c r="AI36" s="1"/>
-      <c r="AJ36" s="1"/>
-      <c r="AK36" s="1"/>
-      <c r="AL36" s="1"/>
-      <c r="AM36" s="1"/>
-      <c r="AN36" s="1"/>
-      <c r="AO36" s="1"/>
-      <c r="AP36" s="1"/>
-      <c r="AQ36" s="1"/>
-      <c r="AR36" s="1" t="s">
+      <c r="O36" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="7"/>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
+      <c r="U36" s="7"/>
+      <c r="V36" s="7"/>
+      <c r="W36" s="7"/>
+      <c r="X36" s="7"/>
+      <c r="Y36" s="7"/>
+      <c r="Z36" s="7"/>
+      <c r="AA36" s="7"/>
+      <c r="AB36" s="7"/>
+      <c r="AC36" s="7"/>
+      <c r="AD36" s="7"/>
+      <c r="AE36" s="7"/>
+      <c r="AF36" s="7"/>
+      <c r="AG36" s="7"/>
+      <c r="AH36" s="7"/>
+      <c r="AI36" s="7"/>
+      <c r="AJ36" s="7"/>
+      <c r="AK36" s="7"/>
+      <c r="AL36" s="7"/>
+      <c r="AM36" s="7"/>
+      <c r="AN36" s="7"/>
+      <c r="AO36" s="7"/>
+      <c r="AP36" s="7"/>
+      <c r="AQ36" s="7"/>
+      <c r="AR36" s="7" t="s">
         <v>256</v>
       </c>
+      <c r="AS36" s="5"/>
+      <c r="AT36" s="5"/>
+      <c r="AU36" s="5"/>
+      <c r="AV36" s="5"/>
+      <c r="AW36" s="5"/>
+      <c r="AX36" s="5"/>
+      <c r="AY36" s="5"/>
+      <c r="AZ36" s="5"/>
+      <c r="BA36" s="5"/>
+      <c r="BB36" s="5"/>
       <c r="BC36" s="1"/>
       <c r="BD36" s="1"/>
       <c r="BE36" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="37" spans="1:57">
@@ -4503,23 +4862,25 @@
       <c r="J37" t="s">
         <v>258</v>
       </c>
-      <c r="O37" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="1"/>
-      <c r="X37" s="1" t="s">
+      <c r="O37" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="Y37" s="1"/>
-      <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="7"/>
+      <c r="AA37" s="7" t="s">
+        <v>458</v>
+      </c>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
@@ -4537,8 +4898,18 @@
       <c r="AP37" s="1"/>
       <c r="AQ37" s="1"/>
       <c r="AR37" s="1"/>
+      <c r="AS37" s="5"/>
+      <c r="AT37" s="5"/>
+      <c r="AU37" s="5"/>
+      <c r="AV37" s="5"/>
+      <c r="AW37" s="5"/>
+      <c r="AX37" s="5"/>
+      <c r="AY37" s="5"/>
+      <c r="AZ37" s="5"/>
+      <c r="BA37" s="5"/>
+      <c r="BB37" s="5"/>
       <c r="BC37" s="1" t="s">
-        <v>260</v>
+        <v>454</v>
       </c>
       <c r="BD37" s="1"/>
       <c r="BE37" s="1"/>
@@ -4548,7 +4919,7 @@
         <v>97</v>
       </c>
       <c r="B38" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C38" t="s">
         <v>59</v>
@@ -4557,7 +4928,7 @@
         <v>60</v>
       </c>
       <c r="F38" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G38" t="s">
         <v>62</v>
@@ -4569,27 +4940,29 @@
         <v>86</v>
       </c>
       <c r="J38" t="s">
+        <v>262</v>
+      </c>
+      <c r="O38" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="O38" s="1" t="s">
+      <c r="P38" s="7"/>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1" t="s">
+      <c r="S38" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="S38" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
-      <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="7"/>
+      <c r="W38" s="7"/>
+      <c r="X38" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="Y38" s="5"/>
+      <c r="Z38" s="5"/>
+      <c r="AA38" s="5"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
@@ -4607,8 +4980,18 @@
       <c r="AP38" s="1"/>
       <c r="AQ38" s="1"/>
       <c r="AR38" s="1"/>
+      <c r="AS38" s="5"/>
+      <c r="AT38" s="5"/>
+      <c r="AU38" s="5"/>
+      <c r="AV38" s="5"/>
+      <c r="AW38" s="5"/>
+      <c r="AX38" s="5"/>
+      <c r="AY38" s="5"/>
+      <c r="AZ38" s="5"/>
+      <c r="BA38" s="5"/>
+      <c r="BB38" s="5"/>
       <c r="BC38" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="BD38" s="1"/>
       <c r="BE38" s="1"/>
@@ -4618,7 +5001,7 @@
         <v>99</v>
       </c>
       <c r="B39" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C39" t="s">
         <v>59</v>
@@ -4636,13 +5019,13 @@
         <v>16</v>
       </c>
       <c r="I39" t="s">
+        <v>267</v>
+      </c>
+      <c r="J39" t="s">
         <v>268</v>
       </c>
-      <c r="J39" t="s">
+      <c r="O39" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="O39" s="1" t="s">
-        <v>270</v>
       </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
@@ -4692,7 +5075,7 @@
         <v>101</v>
       </c>
       <c r="B40" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C40" t="s">
         <v>59</v>
@@ -4710,13 +5093,13 @@
         <v>16</v>
       </c>
       <c r="I40" t="s">
+        <v>271</v>
+      </c>
+      <c r="J40" t="s">
         <v>272</v>
       </c>
-      <c r="J40" t="s">
+      <c r="O40" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>274</v>
       </c>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
@@ -4766,7 +5149,7 @@
         <v>116</v>
       </c>
       <c r="B41" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C41" t="s">
         <v>59</v>
@@ -4775,7 +5158,7 @@
         <v>112</v>
       </c>
       <c r="F41" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G41" t="s">
         <v>62</v>
@@ -4784,13 +5167,13 @@
         <v>24</v>
       </c>
       <c r="I41" t="s">
+        <v>276</v>
+      </c>
+      <c r="J41" t="s">
         <v>277</v>
       </c>
-      <c r="J41" t="s">
+      <c r="O41" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
@@ -4840,7 +5223,7 @@
         <v>118</v>
       </c>
       <c r="B42" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C42" t="s">
         <v>59</v>
@@ -4858,13 +5241,13 @@
         <v>27</v>
       </c>
       <c r="I42" t="s">
+        <v>280</v>
+      </c>
+      <c r="J42" t="s">
         <v>281</v>
       </c>
-      <c r="J42" t="s">
+      <c r="O42" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
@@ -4914,7 +5297,7 @@
         <v>122</v>
       </c>
       <c r="B43" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C43" t="s">
         <v>59</v>
@@ -4935,22 +5318,22 @@
         <v>120</v>
       </c>
       <c r="J43" t="s">
+        <v>284</v>
+      </c>
+      <c r="O43" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="7"/>
+      <c r="S43" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="O43" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
-      <c r="S43" s="1" t="s">
+      <c r="T43" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="T43" s="1" t="s">
+      <c r="U43" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
@@ -4975,6 +5358,16 @@
       <c r="AP43" s="1"/>
       <c r="AQ43" s="1"/>
       <c r="AR43" s="1"/>
+      <c r="AS43" s="5"/>
+      <c r="AT43" s="5"/>
+      <c r="AU43" s="5"/>
+      <c r="AV43" s="5"/>
+      <c r="AW43" s="5"/>
+      <c r="AX43" s="5"/>
+      <c r="AY43" s="5"/>
+      <c r="AZ43" s="5"/>
+      <c r="BA43" s="5"/>
+      <c r="BB43" s="5"/>
       <c r="BC43" s="1"/>
       <c r="BD43" s="1"/>
       <c r="BE43" s="1"/>
@@ -4984,7 +5377,7 @@
         <v>128</v>
       </c>
       <c r="B44" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C44" t="s">
         <v>59</v>
@@ -5002,18 +5395,22 @@
         <v>22</v>
       </c>
       <c r="I44" t="s">
+        <v>289</v>
+      </c>
+      <c r="J44" t="s">
         <v>290</v>
       </c>
-      <c r="J44" t="s">
+      <c r="O44" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="O44" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
+      <c r="P44" s="7"/>
+      <c r="Q44" s="7"/>
+      <c r="R44" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="S44" s="7" t="s">
+        <v>465</v>
+      </c>
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
@@ -5058,7 +5455,7 @@
         <v>130</v>
       </c>
       <c r="B45" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C45" t="s">
         <v>59</v>
@@ -5079,29 +5476,31 @@
         <v>254</v>
       </c>
       <c r="J45" t="s">
+        <v>293</v>
+      </c>
+      <c r="O45" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
+      <c r="R45" s="7"/>
+      <c r="S45" s="7"/>
+      <c r="T45" s="7"/>
+      <c r="U45" s="7"/>
+      <c r="V45" s="7"/>
+      <c r="W45" s="7"/>
+      <c r="X45" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="O45" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="P45" s="1"/>
-      <c r="Q45" s="1"/>
-      <c r="R45" s="1"/>
-      <c r="S45" s="1"/>
-      <c r="T45" s="1"/>
-      <c r="U45" s="1"/>
-      <c r="V45" s="1"/>
-      <c r="W45" s="1"/>
-      <c r="X45" s="1" t="s">
+      <c r="Y45" s="7"/>
+      <c r="Z45" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="Y45" s="1"/>
-      <c r="Z45" s="1" t="s">
+      <c r="AA45" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="AB45" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="AA45" s="1"/>
-      <c r="AB45" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
@@ -5119,8 +5518,18 @@
       <c r="AP45" s="1"/>
       <c r="AQ45" s="1"/>
       <c r="AR45" s="1"/>
+      <c r="AS45" s="5"/>
+      <c r="AT45" s="5"/>
+      <c r="AU45" s="5"/>
+      <c r="AV45" s="5"/>
+      <c r="AW45" s="5"/>
+      <c r="AX45" s="5"/>
+      <c r="AY45" s="5"/>
+      <c r="AZ45" s="5"/>
+      <c r="BA45" s="5"/>
+      <c r="BB45" s="5"/>
       <c r="BC45" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="BD45" s="1"/>
       <c r="BE45" s="1"/>
@@ -5130,7 +5539,7 @@
         <v>132</v>
       </c>
       <c r="B46" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C46" t="s">
         <v>59</v>
@@ -5148,13 +5557,13 @@
         <v>36</v>
       </c>
       <c r="I46" t="s">
+        <v>299</v>
+      </c>
+      <c r="J46" t="s">
         <v>300</v>
       </c>
-      <c r="J46" t="s">
+      <c r="O46" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="O46" s="1" t="s">
-        <v>302</v>
       </c>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
@@ -5204,7 +5613,7 @@
         <v>132</v>
       </c>
       <c r="B47" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C47" t="s">
         <v>59</v>
@@ -5216,7 +5625,7 @@
         <v>83</v>
       </c>
       <c r="F47" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G47" t="s">
         <v>62</v>
@@ -5225,13 +5634,13 @@
         <v>33</v>
       </c>
       <c r="I47" t="s">
+        <v>303</v>
+      </c>
+      <c r="J47" t="s">
         <v>304</v>
       </c>
-      <c r="J47" t="s">
+      <c r="O47" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -5281,7 +5690,7 @@
         <v>134</v>
       </c>
       <c r="B48" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C48" t="s">
         <v>59</v>
@@ -5302,10 +5711,10 @@
         <v>185</v>
       </c>
       <c r="J48" t="s">
+        <v>307</v>
+      </c>
+      <c r="O48" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="O48" s="1" t="s">
-        <v>309</v>
       </c>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
@@ -5355,7 +5764,7 @@
         <v>138</v>
       </c>
       <c r="B49" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C49" t="s">
         <v>59</v>
@@ -5373,13 +5782,13 @@
         <v>22</v>
       </c>
       <c r="I49" t="s">
+        <v>310</v>
+      </c>
+      <c r="J49" t="s">
         <v>311</v>
       </c>
-      <c r="J49" t="s">
+      <c r="O49" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="O49" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
@@ -23474,597 +23883,597 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1" t="s">
         <v>314</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>315</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>316</v>
-      </c>
-      <c r="D1" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B2" t="s">
         <v>318</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>319</v>
-      </c>
-      <c r="C2" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B14" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C14" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B16" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C16" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C18" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B19" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C19" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B20" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C21" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C22" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B23" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C23" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B24" t="s">
+        <v>341</v>
+      </c>
+      <c r="C24" t="s">
         <v>342</v>
-      </c>
-      <c r="C24" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B25" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C25" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B26" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B27" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C27" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B28" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C28" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B29" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C29" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B30" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C30" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B31" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C31" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B32" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C32" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C33" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C35" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C36" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B37" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C37" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C38" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B39" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C39" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C40" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B41" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C41" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B42" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C42" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C43" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B44" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C44" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C45" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B46" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C46" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B47" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C47" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B48" t="s">
+        <v>366</v>
+      </c>
+      <c r="C48" t="s">
         <v>367</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>368</v>
-      </c>
-      <c r="D48" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B49" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C49" t="s">
+        <v>367</v>
+      </c>
+      <c r="D49" t="s">
         <v>368</v>
-      </c>
-      <c r="D49" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B50" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C50" t="s">
+        <v>367</v>
+      </c>
+      <c r="D50" t="s">
         <v>368</v>
-      </c>
-      <c r="D50" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
+        <v>371</v>
+      </c>
+      <c r="B51" t="s">
         <v>372</v>
       </c>
-      <c r="B51" t="s">
+      <c r="D51" t="s">
         <v>373</v>
-      </c>
-      <c r="D51" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B52" t="s">
+        <v>374</v>
+      </c>
+      <c r="D52" t="s">
         <v>375</v>
-      </c>
-      <c r="D52" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B53" t="s">
+        <v>376</v>
+      </c>
+      <c r="D53" t="s">
         <v>377</v>
-      </c>
-      <c r="D53" t="s">
-        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -24086,106 +24495,106 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B8" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B11" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B13" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -24207,823 +24616,823 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B1" t="s">
         <v>392</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>393</v>
-      </c>
-      <c r="C1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B2" t="s">
         <v>395</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F2" t="s">
         <v>396</v>
-      </c>
-      <c r="C2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E2" t="s">
-        <v>324</v>
-      </c>
-      <c r="F2" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D3" t="s">
+        <v>328</v>
+      </c>
+      <c r="E3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F3" t="s">
+        <v>329</v>
+      </c>
+      <c r="G3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H3" t="s">
         <v>396</v>
-      </c>
-      <c r="C3" t="s">
-        <v>335</v>
-      </c>
-      <c r="D3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E3" t="s">
-        <v>336</v>
-      </c>
-      <c r="F3" t="s">
-        <v>330</v>
-      </c>
-      <c r="G3" t="s">
-        <v>326</v>
-      </c>
-      <c r="H3" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C4" t="s">
+        <v>336</v>
+      </c>
+      <c r="D4" t="s">
+        <v>328</v>
+      </c>
+      <c r="E4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F4" t="s">
         <v>396</v>
-      </c>
-      <c r="C4" t="s">
-        <v>337</v>
-      </c>
-      <c r="D4" t="s">
-        <v>329</v>
-      </c>
-      <c r="E4" t="s">
-        <v>322</v>
-      </c>
-      <c r="F4" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B5" t="s">
+        <v>395</v>
+      </c>
+      <c r="C5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D5" t="s">
+        <v>335</v>
+      </c>
+      <c r="E5" t="s">
+        <v>323</v>
+      </c>
+      <c r="F5" t="s">
         <v>396</v>
-      </c>
-      <c r="C5" t="s">
-        <v>321</v>
-      </c>
-      <c r="D5" t="s">
-        <v>336</v>
-      </c>
-      <c r="E5" t="s">
-        <v>324</v>
-      </c>
-      <c r="F5" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B6" t="s">
+        <v>395</v>
+      </c>
+      <c r="C6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D6" t="s">
+        <v>334</v>
+      </c>
+      <c r="E6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F6" t="s">
         <v>396</v>
-      </c>
-      <c r="C6" t="s">
-        <v>337</v>
-      </c>
-      <c r="D6" t="s">
-        <v>335</v>
-      </c>
-      <c r="E6" t="s">
-        <v>330</v>
-      </c>
-      <c r="F6" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B7" t="s">
+        <v>395</v>
+      </c>
+      <c r="C7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E7" t="s">
+        <v>328</v>
+      </c>
+      <c r="F7" t="s">
+        <v>348</v>
+      </c>
+      <c r="G7" t="s">
+        <v>349</v>
+      </c>
+      <c r="H7" t="s">
         <v>396</v>
-      </c>
-      <c r="C7" t="s">
-        <v>335</v>
-      </c>
-      <c r="D7" t="s">
-        <v>337</v>
-      </c>
-      <c r="E7" t="s">
-        <v>329</v>
-      </c>
-      <c r="F7" t="s">
-        <v>349</v>
-      </c>
-      <c r="G7" t="s">
-        <v>350</v>
-      </c>
-      <c r="H7" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B8" t="s">
+        <v>395</v>
+      </c>
+      <c r="C8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D8" t="s">
+        <v>335</v>
+      </c>
+      <c r="E8" t="s">
+        <v>325</v>
+      </c>
+      <c r="F8" t="s">
         <v>396</v>
-      </c>
-      <c r="C8" t="s">
-        <v>322</v>
-      </c>
-      <c r="D8" t="s">
-        <v>336</v>
-      </c>
-      <c r="E8" t="s">
-        <v>326</v>
-      </c>
-      <c r="F8" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B9" t="s">
+        <v>395</v>
+      </c>
+      <c r="C9" t="s">
+        <v>320</v>
+      </c>
+      <c r="D9" t="s">
+        <v>335</v>
+      </c>
+      <c r="E9" t="s">
+        <v>349</v>
+      </c>
+      <c r="F9" t="s">
+        <v>347</v>
+      </c>
+      <c r="G9" t="s">
         <v>396</v>
-      </c>
-      <c r="C9" t="s">
-        <v>321</v>
-      </c>
-      <c r="D9" t="s">
-        <v>336</v>
-      </c>
-      <c r="E9" t="s">
-        <v>350</v>
-      </c>
-      <c r="F9" t="s">
-        <v>348</v>
-      </c>
-      <c r="G9" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B11" t="s">
         <v>405</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>331</v>
+      </c>
+      <c r="D11" t="s">
+        <v>336</v>
+      </c>
+      <c r="E11" t="s">
+        <v>335</v>
+      </c>
+      <c r="F11" t="s">
         <v>406</v>
-      </c>
-      <c r="C11" t="s">
-        <v>332</v>
-      </c>
-      <c r="D11" t="s">
-        <v>337</v>
-      </c>
-      <c r="E11" t="s">
-        <v>336</v>
-      </c>
-      <c r="F11" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B12" t="s">
+        <v>405</v>
+      </c>
+      <c r="C12" t="s">
+        <v>332</v>
+      </c>
+      <c r="D12" t="s">
+        <v>329</v>
+      </c>
+      <c r="E12" t="s">
         <v>406</v>
-      </c>
-      <c r="C12" t="s">
-        <v>333</v>
-      </c>
-      <c r="D12" t="s">
-        <v>330</v>
-      </c>
-      <c r="E12" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B13" t="s">
+        <v>405</v>
+      </c>
+      <c r="C13" t="s">
+        <v>326</v>
+      </c>
+      <c r="D13" t="s">
+        <v>324</v>
+      </c>
+      <c r="E13" t="s">
+        <v>330</v>
+      </c>
+      <c r="F13" t="s">
+        <v>320</v>
+      </c>
+      <c r="G13" t="s">
         <v>406</v>
-      </c>
-      <c r="C13" t="s">
-        <v>327</v>
-      </c>
-      <c r="D13" t="s">
-        <v>325</v>
-      </c>
-      <c r="E13" t="s">
-        <v>331</v>
-      </c>
-      <c r="F13" t="s">
-        <v>321</v>
-      </c>
-      <c r="G13" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B14" t="s">
+        <v>405</v>
+      </c>
+      <c r="C14" t="s">
+        <v>326</v>
+      </c>
+      <c r="D14" t="s">
+        <v>330</v>
+      </c>
+      <c r="E14" t="s">
+        <v>339</v>
+      </c>
+      <c r="F14" t="s">
+        <v>320</v>
+      </c>
+      <c r="G14" t="s">
         <v>406</v>
-      </c>
-      <c r="C14" t="s">
-        <v>327</v>
-      </c>
-      <c r="D14" t="s">
-        <v>331</v>
-      </c>
-      <c r="E14" t="s">
-        <v>340</v>
-      </c>
-      <c r="F14" t="s">
-        <v>321</v>
-      </c>
-      <c r="G14" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B15" t="s">
+        <v>405</v>
+      </c>
+      <c r="C15" t="s">
+        <v>326</v>
+      </c>
+      <c r="D15" t="s">
+        <v>330</v>
+      </c>
+      <c r="E15" t="s">
+        <v>320</v>
+      </c>
+      <c r="F15" t="s">
         <v>406</v>
-      </c>
-      <c r="C15" t="s">
-        <v>327</v>
-      </c>
-      <c r="D15" t="s">
-        <v>331</v>
-      </c>
-      <c r="E15" t="s">
-        <v>321</v>
-      </c>
-      <c r="F15" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B16" t="s">
+        <v>405</v>
+      </c>
+      <c r="C16" t="s">
+        <v>331</v>
+      </c>
+      <c r="D16" t="s">
+        <v>335</v>
+      </c>
+      <c r="E16" t="s">
+        <v>326</v>
+      </c>
+      <c r="F16" t="s">
+        <v>332</v>
+      </c>
+      <c r="G16" t="s">
+        <v>325</v>
+      </c>
+      <c r="H16" t="s">
         <v>406</v>
-      </c>
-      <c r="C16" t="s">
-        <v>332</v>
-      </c>
-      <c r="D16" t="s">
-        <v>336</v>
-      </c>
-      <c r="E16" t="s">
-        <v>327</v>
-      </c>
-      <c r="F16" t="s">
-        <v>333</v>
-      </c>
-      <c r="G16" t="s">
-        <v>326</v>
-      </c>
-      <c r="H16" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B17" t="s">
+        <v>405</v>
+      </c>
+      <c r="C17" t="s">
+        <v>328</v>
+      </c>
+      <c r="D17" t="s">
+        <v>322</v>
+      </c>
+      <c r="E17" t="s">
+        <v>324</v>
+      </c>
+      <c r="F17" t="s">
+        <v>338</v>
+      </c>
+      <c r="G17" t="s">
         <v>406</v>
-      </c>
-      <c r="C17" t="s">
-        <v>329</v>
-      </c>
-      <c r="D17" t="s">
-        <v>323</v>
-      </c>
-      <c r="E17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F17" t="s">
-        <v>339</v>
-      </c>
-      <c r="G17" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D18" t="s">
+        <v>334</v>
+      </c>
+      <c r="E18" t="s">
+        <v>329</v>
+      </c>
+      <c r="F18" t="s">
         <v>406</v>
-      </c>
-      <c r="C18" t="s">
-        <v>332</v>
-      </c>
-      <c r="D18" t="s">
-        <v>335</v>
-      </c>
-      <c r="E18" t="s">
-        <v>330</v>
-      </c>
-      <c r="F18" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B19" t="s">
+        <v>405</v>
+      </c>
+      <c r="C19" t="s">
+        <v>343</v>
+      </c>
+      <c r="D19" t="s">
+        <v>322</v>
+      </c>
+      <c r="E19" t="s">
+        <v>324</v>
+      </c>
+      <c r="F19" t="s">
+        <v>344</v>
+      </c>
+      <c r="G19" t="s">
         <v>406</v>
-      </c>
-      <c r="C19" t="s">
-        <v>344</v>
-      </c>
-      <c r="D19" t="s">
-        <v>323</v>
-      </c>
-      <c r="E19" t="s">
-        <v>325</v>
-      </c>
-      <c r="F19" t="s">
-        <v>345</v>
-      </c>
-      <c r="G19" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B20" t="s">
+        <v>405</v>
+      </c>
+      <c r="C20" t="s">
+        <v>338</v>
+      </c>
+      <c r="D20" t="s">
+        <v>344</v>
+      </c>
+      <c r="E20" t="s">
+        <v>343</v>
+      </c>
+      <c r="F20" t="s">
         <v>406</v>
-      </c>
-      <c r="C20" t="s">
-        <v>339</v>
-      </c>
-      <c r="D20" t="s">
-        <v>345</v>
-      </c>
-      <c r="E20" t="s">
-        <v>344</v>
-      </c>
-      <c r="F20" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B21" t="s">
+        <v>405</v>
+      </c>
+      <c r="C21" t="s">
+        <v>318</v>
+      </c>
+      <c r="D21" t="s">
+        <v>324</v>
+      </c>
+      <c r="E21" t="s">
+        <v>328</v>
+      </c>
+      <c r="F21" t="s">
         <v>406</v>
-      </c>
-      <c r="C21" t="s">
-        <v>319</v>
-      </c>
-      <c r="D21" t="s">
-        <v>325</v>
-      </c>
-      <c r="E21" t="s">
-        <v>329</v>
-      </c>
-      <c r="F21" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B22" t="s">
+        <v>405</v>
+      </c>
+      <c r="C22" t="s">
+        <v>320</v>
+      </c>
+      <c r="D22" t="s">
+        <v>347</v>
+      </c>
+      <c r="E22" t="s">
+        <v>348</v>
+      </c>
+      <c r="F22" t="s">
+        <v>349</v>
+      </c>
+      <c r="G22" t="s">
         <v>406</v>
-      </c>
-      <c r="C22" t="s">
-        <v>321</v>
-      </c>
-      <c r="D22" t="s">
-        <v>348</v>
-      </c>
-      <c r="E22" t="s">
-        <v>349</v>
-      </c>
-      <c r="F22" t="s">
-        <v>350</v>
-      </c>
-      <c r="G22" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B23" t="s">
+        <v>405</v>
+      </c>
+      <c r="C23" t="s">
+        <v>334</v>
+      </c>
+      <c r="D23" t="s">
+        <v>350</v>
+      </c>
+      <c r="E23" t="s">
         <v>406</v>
-      </c>
-      <c r="C23" t="s">
-        <v>335</v>
-      </c>
-      <c r="D23" t="s">
-        <v>351</v>
-      </c>
-      <c r="E23" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B25" t="s">
         <v>420</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>331</v>
+      </c>
+      <c r="D25" t="s">
+        <v>337</v>
+      </c>
+      <c r="E25" t="s">
+        <v>320</v>
+      </c>
+      <c r="F25" t="s">
+        <v>333</v>
+      </c>
+      <c r="G25" t="s">
+        <v>357</v>
+      </c>
+      <c r="H25" t="s">
         <v>421</v>
-      </c>
-      <c r="C25" t="s">
-        <v>332</v>
-      </c>
-      <c r="D25" t="s">
-        <v>338</v>
-      </c>
-      <c r="E25" t="s">
-        <v>321</v>
-      </c>
-      <c r="F25" t="s">
-        <v>334</v>
-      </c>
-      <c r="G25" t="s">
-        <v>358</v>
-      </c>
-      <c r="H25" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B26" t="s">
+        <v>420</v>
+      </c>
+      <c r="C26" t="s">
+        <v>339</v>
+      </c>
+      <c r="D26" t="s">
+        <v>340</v>
+      </c>
+      <c r="E26" t="s">
+        <v>332</v>
+      </c>
+      <c r="F26" t="s">
+        <v>343</v>
+      </c>
+      <c r="G26" t="s">
+        <v>357</v>
+      </c>
+      <c r="H26" t="s">
         <v>421</v>
-      </c>
-      <c r="C26" t="s">
-        <v>340</v>
-      </c>
-      <c r="D26" t="s">
-        <v>341</v>
-      </c>
-      <c r="E26" t="s">
-        <v>333</v>
-      </c>
-      <c r="F26" t="s">
-        <v>344</v>
-      </c>
-      <c r="G26" t="s">
-        <v>358</v>
-      </c>
-      <c r="H26" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B27" t="s">
+        <v>420</v>
+      </c>
+      <c r="C27" t="s">
+        <v>318</v>
+      </c>
+      <c r="D27" t="s">
+        <v>343</v>
+      </c>
+      <c r="E27" t="s">
+        <v>331</v>
+      </c>
+      <c r="F27" t="s">
+        <v>332</v>
+      </c>
+      <c r="G27" t="s">
+        <v>357</v>
+      </c>
+      <c r="H27" t="s">
+        <v>323</v>
+      </c>
+      <c r="I27" t="s">
         <v>421</v>
-      </c>
-      <c r="C27" t="s">
-        <v>319</v>
-      </c>
-      <c r="D27" t="s">
-        <v>344</v>
-      </c>
-      <c r="E27" t="s">
-        <v>332</v>
-      </c>
-      <c r="F27" t="s">
-        <v>333</v>
-      </c>
-      <c r="G27" t="s">
-        <v>358</v>
-      </c>
-      <c r="H27" t="s">
-        <v>324</v>
-      </c>
-      <c r="I27" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B28" t="s">
+        <v>420</v>
+      </c>
+      <c r="C28" t="s">
+        <v>335</v>
+      </c>
+      <c r="D28" t="s">
+        <v>336</v>
+      </c>
+      <c r="E28" t="s">
+        <v>357</v>
+      </c>
+      <c r="F28" t="s">
+        <v>345</v>
+      </c>
+      <c r="G28" t="s">
         <v>421</v>
-      </c>
-      <c r="C28" t="s">
-        <v>336</v>
-      </c>
-      <c r="D28" t="s">
-        <v>337</v>
-      </c>
-      <c r="E28" t="s">
-        <v>358</v>
-      </c>
-      <c r="F28" t="s">
-        <v>346</v>
-      </c>
-      <c r="G28" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B29" t="s">
+        <v>420</v>
+      </c>
+      <c r="C29" t="s">
+        <v>330</v>
+      </c>
+      <c r="D29" t="s">
+        <v>324</v>
+      </c>
+      <c r="E29" t="s">
+        <v>328</v>
+      </c>
+      <c r="F29" t="s">
+        <v>345</v>
+      </c>
+      <c r="G29" t="s">
         <v>421</v>
-      </c>
-      <c r="C29" t="s">
-        <v>331</v>
-      </c>
-      <c r="D29" t="s">
-        <v>325</v>
-      </c>
-      <c r="E29" t="s">
-        <v>329</v>
-      </c>
-      <c r="F29" t="s">
-        <v>346</v>
-      </c>
-      <c r="G29" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B30" t="s">
+        <v>420</v>
+      </c>
+      <c r="C30" t="s">
+        <v>338</v>
+      </c>
+      <c r="D30" t="s">
+        <v>345</v>
+      </c>
+      <c r="E30" t="s">
+        <v>349</v>
+      </c>
+      <c r="F30" t="s">
         <v>421</v>
-      </c>
-      <c r="C30" t="s">
-        <v>339</v>
-      </c>
-      <c r="D30" t="s">
-        <v>346</v>
-      </c>
-      <c r="E30" t="s">
-        <v>350</v>
-      </c>
-      <c r="F30" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B31" t="s">
+        <v>420</v>
+      </c>
+      <c r="C31" t="s">
+        <v>320</v>
+      </c>
+      <c r="D31" t="s">
+        <v>335</v>
+      </c>
+      <c r="E31" t="s">
+        <v>358</v>
+      </c>
+      <c r="F31" t="s">
+        <v>357</v>
+      </c>
+      <c r="G31" t="s">
+        <v>327</v>
+      </c>
+      <c r="H31" t="s">
+        <v>333</v>
+      </c>
+      <c r="I31" t="s">
         <v>421</v>
-      </c>
-      <c r="C31" t="s">
-        <v>321</v>
-      </c>
-      <c r="D31" t="s">
-        <v>336</v>
-      </c>
-      <c r="E31" t="s">
-        <v>359</v>
-      </c>
-      <c r="F31" t="s">
-        <v>358</v>
-      </c>
-      <c r="G31" t="s">
-        <v>328</v>
-      </c>
-      <c r="H31" t="s">
-        <v>334</v>
-      </c>
-      <c r="I31" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B32" t="s">
+        <v>420</v>
+      </c>
+      <c r="C32" t="s">
+        <v>322</v>
+      </c>
+      <c r="D32" t="s">
+        <v>344</v>
+      </c>
+      <c r="E32" t="s">
         <v>421</v>
-      </c>
-      <c r="C32" t="s">
-        <v>323</v>
-      </c>
-      <c r="D32" t="s">
-        <v>345</v>
-      </c>
-      <c r="E32" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B33" t="s">
+        <v>420</v>
+      </c>
+      <c r="C33" t="s">
+        <v>330</v>
+      </c>
+      <c r="D33" t="s">
+        <v>358</v>
+      </c>
+      <c r="E33" t="s">
+        <v>343</v>
+      </c>
+      <c r="F33" t="s">
+        <v>323</v>
+      </c>
+      <c r="G33" t="s">
         <v>421</v>
-      </c>
-      <c r="C33" t="s">
-        <v>331</v>
-      </c>
-      <c r="D33" t="s">
-        <v>359</v>
-      </c>
-      <c r="E33" t="s">
-        <v>344</v>
-      </c>
-      <c r="F33" t="s">
-        <v>324</v>
-      </c>
-      <c r="G33" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B34" t="s">
+        <v>420</v>
+      </c>
+      <c r="C34" t="s">
+        <v>321</v>
+      </c>
+      <c r="D34" t="s">
+        <v>337</v>
+      </c>
+      <c r="E34" t="s">
+        <v>323</v>
+      </c>
+      <c r="F34" t="s">
+        <v>327</v>
+      </c>
+      <c r="G34" t="s">
+        <v>326</v>
+      </c>
+      <c r="H34" t="s">
+        <v>359</v>
+      </c>
+      <c r="I34" t="s">
         <v>421</v>
-      </c>
-      <c r="C34" t="s">
-        <v>322</v>
-      </c>
-      <c r="D34" t="s">
-        <v>338</v>
-      </c>
-      <c r="E34" t="s">
-        <v>324</v>
-      </c>
-      <c r="F34" t="s">
-        <v>328</v>
-      </c>
-      <c r="G34" t="s">
-        <v>327</v>
-      </c>
-      <c r="H34" t="s">
-        <v>360</v>
-      </c>
-      <c r="I34" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B35" t="s">
+        <v>420</v>
+      </c>
+      <c r="C35" t="s">
+        <v>331</v>
+      </c>
+      <c r="D35" t="s">
+        <v>337</v>
+      </c>
+      <c r="E35" t="s">
+        <v>320</v>
+      </c>
+      <c r="F35" t="s">
+        <v>348</v>
+      </c>
+      <c r="G35" t="s">
+        <v>333</v>
+      </c>
+      <c r="H35" t="s">
         <v>421</v>
-      </c>
-      <c r="C35" t="s">
-        <v>332</v>
-      </c>
-      <c r="D35" t="s">
-        <v>338</v>
-      </c>
-      <c r="E35" t="s">
-        <v>321</v>
-      </c>
-      <c r="F35" t="s">
-        <v>349</v>
-      </c>
-      <c r="G35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H35" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B36" t="s">
+        <v>420</v>
+      </c>
+      <c r="C36" t="s">
+        <v>337</v>
+      </c>
+      <c r="D36" t="s">
+        <v>343</v>
+      </c>
+      <c r="E36" t="s">
+        <v>358</v>
+      </c>
+      <c r="F36" t="s">
+        <v>327</v>
+      </c>
+      <c r="G36" t="s">
+        <v>333</v>
+      </c>
+      <c r="H36" t="s">
         <v>421</v>
-      </c>
-      <c r="C36" t="s">
-        <v>338</v>
-      </c>
-      <c r="D36" t="s">
-        <v>344</v>
-      </c>
-      <c r="E36" t="s">
-        <v>359</v>
-      </c>
-      <c r="F36" t="s">
-        <v>328</v>
-      </c>
-      <c r="G36" t="s">
-        <v>334</v>
-      </c>
-      <c r="H36" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B37" t="s">
+        <v>420</v>
+      </c>
+      <c r="C37" t="s">
+        <v>322</v>
+      </c>
+      <c r="D37" t="s">
+        <v>344</v>
+      </c>
+      <c r="E37" t="s">
         <v>421</v>
-      </c>
-      <c r="C37" t="s">
-        <v>323</v>
-      </c>
-      <c r="D37" t="s">
-        <v>345</v>
-      </c>
-      <c r="E37" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B38" t="s">
+        <v>420</v>
+      </c>
+      <c r="C38" t="s">
+        <v>337</v>
+      </c>
+      <c r="D38" t="s">
+        <v>339</v>
+      </c>
+      <c r="E38" t="s">
+        <v>340</v>
+      </c>
+      <c r="F38" t="s">
+        <v>332</v>
+      </c>
+      <c r="G38" t="s">
         <v>421</v>
-      </c>
-      <c r="C38" t="s">
-        <v>338</v>
-      </c>
-      <c r="D38" t="s">
-        <v>340</v>
-      </c>
-      <c r="E38" t="s">
-        <v>341</v>
-      </c>
-      <c r="F38" t="s">
-        <v>333</v>
-      </c>
-      <c r="G38" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B39" t="s">
+        <v>420</v>
+      </c>
+      <c r="C39" t="s">
+        <v>337</v>
+      </c>
+      <c r="D39" t="s">
+        <v>360</v>
+      </c>
+      <c r="E39" t="s">
+        <v>359</v>
+      </c>
+      <c r="F39" t="s">
+        <v>327</v>
+      </c>
+      <c r="G39" t="s">
         <v>421</v>
-      </c>
-      <c r="C39" t="s">
-        <v>338</v>
-      </c>
-      <c r="D39" t="s">
-        <v>361</v>
-      </c>
-      <c r="E39" t="s">
-        <v>360</v>
-      </c>
-      <c r="F39" t="s">
-        <v>328</v>
-      </c>
-      <c r="G39" t="s">
-        <v>422</v>
       </c>
     </row>
   </sheetData>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -10,6 +10,7 @@
     <sheet name="素材" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="合成レシピ" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ステージドロップ品" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="奥義強化" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -48,6 +49,9 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -75,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -85,6 +89,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -25975,4 +25980,93 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>限界突破段階</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>通常:強化片</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>通常:小判</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>レア:強化片</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>レア:小判</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1→2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2→3</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3→4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4→5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5→6</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -2266,8 +2266,16 @@
           <t>804,141</t>
         </is>
       </c>
-      <c r="Z16" s="5" t="n"/>
-      <c r="AA16" s="5" t="n"/>
+      <c r="Z16" s="5" t="inlineStr">
+        <is>
+          <t>841,148</t>
+        </is>
+      </c>
+      <c r="AA16" s="5" t="inlineStr">
+        <is>
+          <t>877,154</t>
+        </is>
+      </c>
       <c r="AB16" s="5" t="n"/>
       <c r="AC16" s="5" t="n"/>
       <c r="AD16" s="5" t="n"/>
@@ -4309,8 +4317,16 @@
           <t>971,122</t>
         </is>
       </c>
-      <c r="AB37" s="1" t="n"/>
-      <c r="AC37" s="1" t="n"/>
+      <c r="AB37" s="1" t="inlineStr">
+        <is>
+          <t>1011,127</t>
+        </is>
+      </c>
+      <c r="AC37" s="1" t="inlineStr">
+        <is>
+          <t>1052,132</t>
+        </is>
+      </c>
       <c r="AD37" s="1" t="n"/>
       <c r="AE37" s="1" t="n"/>
       <c r="AF37" s="1" t="n"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -2276,7 +2276,11 @@
           <t>877,154</t>
         </is>
       </c>
-      <c r="AB16" s="5" t="n"/>
+      <c r="AB16" s="5" t="inlineStr">
+        <is>
+          <t>914,161</t>
+        </is>
+      </c>
       <c r="AC16" s="5" t="n"/>
       <c r="AD16" s="5" t="n"/>
       <c r="AE16" s="5" t="n"/>
@@ -2561,7 +2565,11 @@
           <t>1119,123</t>
         </is>
       </c>
-      <c r="AD19" s="5" t="n"/>
+      <c r="AD19" s="5" t="inlineStr">
+        <is>
+          <t>1162,128</t>
+        </is>
+      </c>
       <c r="AE19" s="5" t="n"/>
       <c r="AF19" s="5" t="n"/>
       <c r="AG19" s="5" t="inlineStr">

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -26025,7 +26025,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>限界突破段階</t>
+          <t>奥義レベル</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -23824,7 +23824,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>黒</t>
+          <t>レアドロップ</t>
         </is>
       </c>
     </row>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamasakoyuki/Desktop/pazugiri-clean/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62341CCF-3B47-E245-80C1-66CA0AD1DC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E400833-336E-B241-8D89-A439861145F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="629">
   <si>
     <t>刀剣男士番号</t>
   </si>
@@ -1540,6 +1540,535 @@
   </si>
   <si>
     <t>2000,242</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1034,163</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1113,176</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1074,169</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1153,182</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1193,188</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1233,195</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1350,169</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1393,174</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1436,179</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1480,185</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1523,190</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1567,196</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2050,249</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>紙2,大豆2,ふさふさの毛2,お花4</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">カミ </t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ダイズ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>k</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1814,187</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1955,202</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1455,182</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1415,177</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>573,92</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>611,98</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>649,104</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1138,181</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1176,188</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1495,187</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1280,169</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1324,175</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1368,181</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1293,135</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1339,140</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1385,145</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1431,150</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>793,86</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>839,91</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>932,101</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>666,97</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>705,103</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>744,109</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>783,115</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>822,121</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>687,110</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>725,116</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>763,122</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>801,129</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1610,201</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1653,206</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1697,212</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1582,235</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1098,113</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1145,118</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1193,123</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1241,128</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1288,133</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1336,138</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1383,143</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1439,199</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1480,205</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1521,211</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1169,206</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1206,212</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1242,219</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1279,225</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>705,72</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>752,77</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>799,81</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>846,86</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>893,91</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>940,96</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>987,101</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>753,88</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>793,93</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>833,98</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>779,102</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>825,108</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>870,114</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>916,120</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>962,126</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>773,93</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>818,98</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>863,104</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>908,109</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>954,115</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>717,105</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>759,111</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>801,117</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>843,123</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>885,130</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>697,76</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>739,81</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>779,85</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>820,90</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>861,95</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1536,192</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1616,202</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1576,197</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1067,127</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1115,133</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1164,139</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1212,145</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1261,151</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1309,156</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1357,162</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1406,168</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>600,88</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>640,94</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>680,100</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>720,106</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>760,112</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>800,118</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>840,124</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>915,88</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>963,93</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1011,98</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>640,106</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>678,112</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>753,124</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>791,131</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1201,140</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1245,145</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1290,150</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1334,155</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1379,161</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>25271</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>734,80</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>783,85</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>831,90</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>880,96</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>929,101</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>978,106</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1027,112</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>715,118</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1983,7 +2512,9 @@
     <col min="11" max="11" width="2.33203125" hidden="1" customWidth="1"/>
     <col min="12" max="13" width="2.1640625" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="2.5" hidden="1" customWidth="1"/>
-    <col min="15" max="48" width="6.83203125" customWidth="1"/>
+    <col min="15" max="29" width="6.83203125" customWidth="1"/>
+    <col min="30" max="30" width="7.1640625" customWidth="1"/>
+    <col min="31" max="48" width="6.83203125" customWidth="1"/>
     <col min="49" max="54" width="1.1640625" customWidth="1"/>
     <col min="55" max="55" width="28" customWidth="1"/>
     <col min="56" max="56" width="16.5" customWidth="1"/>
@@ -2241,7 +2772,9 @@
       <c r="AN2" s="5">
         <v>23083</v>
       </c>
-      <c r="AO2" s="5"/>
+      <c r="AO2" s="5" t="s">
+        <v>620</v>
+      </c>
       <c r="AP2" s="5">
         <v>27576</v>
       </c>
@@ -2398,9 +2931,15 @@
       <c r="AE4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="1"/>
+      <c r="AF4" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>525</v>
+      </c>
       <c r="AI4" s="1"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1"/>
@@ -2493,10 +3032,18 @@
       <c r="AD5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="AE5" s="1"/>
-      <c r="AF5" s="1"/>
-      <c r="AG5" s="1"/>
-      <c r="AH5" s="1"/>
+      <c r="AE5" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>529</v>
+      </c>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1"/>
@@ -2559,16 +3106,22 @@
       <c r="R6" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="S6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1" t="s">
+      <c r="T6" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="V6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1" t="s">
+      <c r="W6" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="X6" s="7" t="s">
         <v>64</v>
       </c>
       <c r="Y6" s="1"/>
@@ -2644,11 +3197,21 @@
       <c r="S7" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
+      <c r="T7" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="V7" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="W7" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="X7" s="8" t="s">
+        <v>537</v>
+      </c>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
       <c r="AA7" s="5"/>
@@ -2711,15 +3274,29 @@
       <c r="O8" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="S8" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="T8" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="U8" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="V8" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="W8" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="X8" s="7" t="s">
+        <v>541</v>
+      </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
@@ -2826,16 +3403,34 @@
       <c r="AF9" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="AG9" s="1"/>
-      <c r="AH9" s="1"/>
-      <c r="AI9" s="1"/>
-      <c r="AJ9" s="1"/>
-      <c r="AK9" s="1"/>
-      <c r="AL9" s="1"/>
-      <c r="AM9" s="1"/>
-      <c r="AN9" s="1"/>
-      <c r="AO9" s="1"/>
-      <c r="AP9" s="1"/>
+      <c r="AG9" s="7"/>
+      <c r="AH9" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="AI9" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="AJ9" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="AK9" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="AL9" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="AM9" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="AN9" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="AO9" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="AP9" s="1" t="s">
+        <v>544</v>
+      </c>
       <c r="AQ9" s="1"/>
       <c r="AR9" s="1"/>
       <c r="AS9" s="5"/>
@@ -2851,7 +3446,9 @@
       <c r="BC9" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="BD9" s="2"/>
+      <c r="BD9" s="10" t="s">
+        <v>512</v>
+      </c>
       <c r="BE9" s="2"/>
     </row>
     <row r="10" spans="1:57">
@@ -2917,7 +3514,9 @@
       <c r="AQ10" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="AR10" s="5"/>
+      <c r="AR10" s="5" t="s">
+        <v>545</v>
+      </c>
       <c r="AS10" s="5"/>
       <c r="AT10" s="5"/>
       <c r="AU10" s="5"/>
@@ -2975,13 +3574,27 @@
       <c r="Y11" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="Z11" s="1"/>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="1"/>
-      <c r="AC11" s="1"/>
-      <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
-      <c r="AF11" s="1"/>
+      <c r="Z11" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="AE11" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="AF11" s="1" t="s">
+        <v>552</v>
+      </c>
       <c r="AG11" s="1"/>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
@@ -3073,14 +3686,18 @@
       <c r="AN12" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="AO12" s="1"/>
-      <c r="AP12" s="1" t="s">
+      <c r="AO12" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="AP12" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="AQ12" s="1" t="s">
+      <c r="AQ12" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="AR12" s="1"/>
+      <c r="AR12" s="7" t="s">
+        <v>514</v>
+      </c>
       <c r="AS12" s="5"/>
       <c r="AT12" s="5"/>
       <c r="AU12" s="5"/>
@@ -3152,9 +3769,15 @@
       <c r="AK13" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="AL13" s="1"/>
-      <c r="AM13" s="1"/>
-      <c r="AN13" s="1"/>
+      <c r="AL13" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="AM13" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN13" s="1" t="s">
+        <v>555</v>
+      </c>
       <c r="AO13" s="1"/>
       <c r="AP13" s="1"/>
       <c r="AQ13" s="1"/>
@@ -3227,8 +3850,12 @@
       <c r="AF14" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="AG14" s="1"/>
-      <c r="AH14" s="1"/>
+      <c r="AG14" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="AH14" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="AI14" s="1"/>
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
@@ -3405,10 +4032,18 @@
       <c r="AH16" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="AI16" s="5"/>
-      <c r="AJ16" s="5"/>
-      <c r="AK16" s="5"/>
-      <c r="AL16" s="5"/>
+      <c r="AI16" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="AJ16" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="AK16" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="AL16" s="5" t="s">
+        <v>559</v>
+      </c>
       <c r="AM16" s="5"/>
       <c r="AN16" s="5"/>
       <c r="AO16" s="5"/>
@@ -3459,18 +4094,32 @@
       <c r="J17" t="s">
         <v>155</v>
       </c>
-      <c r="O17" s="1" t="s">
+      <c r="O17" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="S17" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="T17" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="U17" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="V17" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="W17" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="X17" s="7" t="s">
+        <v>566</v>
+      </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
@@ -3789,9 +4438,15 @@
       <c r="U21" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
+      <c r="V21" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="W21" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="X21" s="7" t="s">
+        <v>569</v>
+      </c>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
@@ -4028,12 +4683,24 @@
       <c r="AB24" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="AC24" s="1"/>
-      <c r="AD24" s="1"/>
-      <c r="AE24" s="1"/>
-      <c r="AF24" s="1"/>
-      <c r="AG24" s="1"/>
-      <c r="AH24" s="1"/>
+      <c r="AC24" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="AD24" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="AE24" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="AF24" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="AG24" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="AH24" s="7" t="s">
+        <v>504</v>
+      </c>
       <c r="AI24" s="1"/>
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
@@ -4173,11 +4840,21 @@
       <c r="S26" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-      <c r="X26" s="1"/>
+      <c r="T26" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="V26" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="W26" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="X26" s="7" t="s">
+        <v>574</v>
+      </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
@@ -4251,11 +4928,21 @@
       <c r="S27" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
+      <c r="T27" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="U27" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="V27" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="W27" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="X27" s="7" t="s">
+        <v>579</v>
+      </c>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
@@ -4329,11 +5016,21 @@
       <c r="S28" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
+      <c r="T28" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="U28" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="V28" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="W28" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="X28" s="7" t="s">
+        <v>584</v>
+      </c>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
@@ -4407,11 +5104,21 @@
       <c r="S29" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
+      <c r="T29" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="U29" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="V29" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="W29" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="X29" s="7" t="s">
+        <v>589</v>
+      </c>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
@@ -4904,7 +5611,9 @@
       <c r="AQ35" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="AR35" s="1"/>
+      <c r="AR35" s="7" t="s">
+        <v>511</v>
+      </c>
       <c r="AS35" s="5"/>
       <c r="AT35" s="5"/>
       <c r="AU35" s="5"/>
@@ -5076,12 +5785,24 @@
       <c r="AK37" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="AL37" s="1"/>
-      <c r="AM37" s="1"/>
-      <c r="AN37" s="1"/>
-      <c r="AO37" s="1"/>
-      <c r="AP37" s="1"/>
-      <c r="AQ37" s="1"/>
+      <c r="AL37" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="AM37" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="AN37" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="AO37" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="AP37" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="AQ37" s="1" t="s">
+        <v>591</v>
+      </c>
       <c r="AR37" s="1"/>
       <c r="AS37" s="5"/>
       <c r="AT37" s="5"/>
@@ -5147,14 +5868,30 @@
       <c r="X38" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="Y38" s="5"/>
-      <c r="Z38" s="5"/>
-      <c r="AA38" s="5"/>
-      <c r="AB38" s="1"/>
-      <c r="AC38" s="1"/>
-      <c r="AD38" s="1"/>
-      <c r="AE38" s="1"/>
-      <c r="AF38" s="1"/>
+      <c r="Y38" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="Z38" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="AA38" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="AB38" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="AC38" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="AD38" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="AE38" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="AF38" s="1" t="s">
+        <v>600</v>
+      </c>
       <c r="AG38" s="1"/>
       <c r="AH38" s="1"/>
       <c r="AI38" s="1"/>
@@ -5285,18 +6022,32 @@
       <c r="J40" t="s">
         <v>310</v>
       </c>
-      <c r="O40" s="1" t="s">
+      <c r="O40" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
-      <c r="R40" s="1"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1"/>
-      <c r="W40" s="1"/>
-      <c r="X40" s="1"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="S40" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="T40" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="U40" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="V40" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="W40" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="X40" s="7" t="s">
+        <v>607</v>
+      </c>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
@@ -5522,9 +6273,15 @@
       <c r="U43" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-      <c r="X43" s="1"/>
+      <c r="V43" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="W43" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="X43" s="7" t="s">
+        <v>610</v>
+      </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
@@ -5598,11 +6355,21 @@
       <c r="S44" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-      <c r="X44" s="1"/>
+      <c r="T44" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="U44" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="V44" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="W44" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="X44" s="7" t="s">
+        <v>614</v>
+      </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
@@ -5692,11 +6459,21 @@
       <c r="AC45" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="AD45" s="1"/>
-      <c r="AE45" s="1"/>
-      <c r="AF45" s="1"/>
-      <c r="AG45" s="1"/>
-      <c r="AH45" s="1"/>
+      <c r="AD45" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE45" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="AF45" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="AG45" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="AH45" s="1" t="s">
+        <v>619</v>
+      </c>
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
       <c r="AK45" s="1"/>
@@ -5756,13 +6533,27 @@
       </c>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
-      <c r="W46" s="1"/>
-      <c r="X46" s="1"/>
+      <c r="R46" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="T46" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="U46" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="W46" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="X46" s="1" t="s">
+        <v>627</v>
+      </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
@@ -24049,7 +24840,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="D3:D6 D8:D17 D21:D564" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"○"</formula1>
     </dataValidation>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -25597,7 +25597,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>バフ(守)</t>
+          <t>バフ(防)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -25820,7 +25820,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>バフ(守)</t>
+          <t>バフ(防)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -25894,7 +25894,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>バフ(守)</t>
+          <t>バフ(防)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -25968,7 +25968,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>バフ(守)</t>
+          <t>バフ(防)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>バフ(守)</t>
+          <t>バフ(防)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>バフ(守)</t>
+          <t>バフ(防)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -26338,7 +26338,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>バフ(守)</t>
+          <t>バフ(防)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -26491,7 +26491,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>バフ(守)</t>
+          <t>バフ(防)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -26572,11 +26572,6 @@
           <t>四葉のクローバー</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>43,9</t>
@@ -26730,7 +26725,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>バフ(守)</t>
+          <t>バフ(防)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -27060,7 +27055,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>バフ(守)</t>
+          <t>バフ(防)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -27137,11 +27132,6 @@
           <t>モチモチおはぎ</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
           <t>87,0</t>
@@ -27285,11 +27275,6 @@
           <t>富士と松</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
           <t>0,13</t>
@@ -27354,11 +27339,6 @@
           <t>2本の矢</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>43,0</t>
@@ -27423,11 +27403,6 @@
           <t>塩おにぎり</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
           <t>0,9</t>
@@ -27492,11 +27467,6 @@
           <t>のんびり屋の馬</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
           <t>19,2</t>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -25801,24 +25801,96 @@
           <t>0,11</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-      <c r="Y9" s="5" t="n"/>
-      <c r="Z9" s="5" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>0,12</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>0,13</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>0,16</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>0,19</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>0,20</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>0,21</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>0,23</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>0,25</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr">
+        <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="X9" s="5" t="inlineStr">
+        <is>
+          <t>0,27</t>
+        </is>
+      </c>
+      <c r="Y9" s="5" t="inlineStr">
+        <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="Z9" s="5" t="inlineStr">
+        <is>
+          <t>0,29</t>
+        </is>
+      </c>
       <c r="AA9" s="5" t="n"/>
       <c r="AB9" s="5" t="n"/>
       <c r="AC9" s="5" t="n"/>
@@ -28855,6 +28927,11 @@
           <t>絵馬経験値の勾玉・小</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>絵馬の経験値+200</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -28865,6 +28942,11 @@
       <c r="B57" t="inlineStr">
         <is>
           <t>絵馬経験値の勾玉・中</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>絵馬の経験値+800</t>
         </is>
       </c>
     </row>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -1332,16 +1332,56 @@
           <t>979,106</t>
         </is>
       </c>
-      <c r="Y6" s="1" t="n"/>
-      <c r="Z6" s="1" t="n"/>
-      <c r="AA6" s="1" t="n"/>
-      <c r="AB6" s="1" t="n"/>
-      <c r="AC6" s="1" t="n"/>
-      <c r="AD6" s="1" t="n"/>
-      <c r="AE6" s="1" t="n"/>
-      <c r="AF6" s="1" t="n"/>
-      <c r="AG6" s="1" t="n"/>
-      <c r="AH6" s="1" t="n"/>
+      <c r="Y6" s="1" t="inlineStr">
+        <is>
+          <t>1025,111</t>
+        </is>
+      </c>
+      <c r="Z6" s="1" t="inlineStr">
+        <is>
+          <t>1072,116</t>
+        </is>
+      </c>
+      <c r="AA6" s="1" t="inlineStr">
+        <is>
+          <t>1118,121</t>
+        </is>
+      </c>
+      <c r="AB6" s="1" t="inlineStr">
+        <is>
+          <t>1165,126</t>
+        </is>
+      </c>
+      <c r="AC6" s="1" t="inlineStr">
+        <is>
+          <t>1211,131</t>
+        </is>
+      </c>
+      <c r="AD6" s="1" t="inlineStr">
+        <is>
+          <t>1258,136</t>
+        </is>
+      </c>
+      <c r="AE6" s="1" t="inlineStr">
+        <is>
+          <t>1304,141</t>
+        </is>
+      </c>
+      <c r="AF6" s="1" t="inlineStr">
+        <is>
+          <t>1351,146</t>
+        </is>
+      </c>
+      <c r="AG6" s="1" t="inlineStr">
+        <is>
+          <t>1397,151</t>
+        </is>
+      </c>
+      <c r="AH6" s="1" t="inlineStr">
+        <is>
+          <t>1444,156</t>
+        </is>
+      </c>
       <c r="AI6" s="1" t="n"/>
       <c r="AJ6" s="1" t="n"/>
       <c r="AK6" s="1" t="n"/>
@@ -1362,7 +1402,11 @@
       <c r="AZ6" s="5" t="n"/>
       <c r="BA6" s="5" t="n"/>
       <c r="BB6" s="5" t="n"/>
-      <c r="BC6" s="1" t="n"/>
+      <c r="BC6" s="1" t="inlineStr">
+        <is>
+          <t>葉っぱ2,大豆2</t>
+        </is>
+      </c>
       <c r="BD6" s="1" t="n"/>
       <c r="BE6" s="1" t="n"/>
     </row>
@@ -1450,16 +1494,56 @@
           <t>822,121</t>
         </is>
       </c>
-      <c r="Y7" s="5" t="n"/>
-      <c r="Z7" s="5" t="n"/>
-      <c r="AA7" s="5" t="n"/>
-      <c r="AB7" s="5" t="n"/>
-      <c r="AC7" s="5" t="n"/>
-      <c r="AD7" s="5" t="n"/>
-      <c r="AE7" s="5" t="n"/>
-      <c r="AF7" s="5" t="n"/>
-      <c r="AG7" s="5" t="n"/>
-      <c r="AH7" s="5" t="n"/>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>861,126</t>
+        </is>
+      </c>
+      <c r="Z7" s="5" t="inlineStr">
+        <is>
+          <t>900,132</t>
+        </is>
+      </c>
+      <c r="AA7" s="5" t="inlineStr">
+        <is>
+          <t>939,138</t>
+        </is>
+      </c>
+      <c r="AB7" s="5" t="inlineStr">
+        <is>
+          <t>978,144</t>
+        </is>
+      </c>
+      <c r="AC7" s="5" t="inlineStr">
+        <is>
+          <t>1017,150</t>
+        </is>
+      </c>
+      <c r="AD7" s="5" t="inlineStr">
+        <is>
+          <t>1056,155</t>
+        </is>
+      </c>
+      <c r="AE7" s="5" t="inlineStr">
+        <is>
+          <t>1095,161</t>
+        </is>
+      </c>
+      <c r="AF7" s="5" t="inlineStr">
+        <is>
+          <t>1134,167</t>
+        </is>
+      </c>
+      <c r="AG7" s="5" t="inlineStr">
+        <is>
+          <t>1173,173</t>
+        </is>
+      </c>
+      <c r="AH7" s="5" t="inlineStr">
+        <is>
+          <t>1212,179</t>
+        </is>
+      </c>
       <c r="AI7" s="5" t="n"/>
       <c r="AJ7" s="5" t="n"/>
       <c r="AK7" s="5" t="n"/>
@@ -1480,6 +1564,11 @@
       <c r="AZ7" s="5" t="n"/>
       <c r="BA7" s="5" t="n"/>
       <c r="BB7" s="5" t="n"/>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>水2,丸太2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2394,15 +2483,51 @@
           <t>1176,188</t>
         </is>
       </c>
-      <c r="AI14" s="1" t="n"/>
-      <c r="AJ14" s="1" t="n"/>
-      <c r="AK14" s="1" t="n"/>
-      <c r="AL14" s="1" t="n"/>
-      <c r="AM14" s="1" t="n"/>
-      <c r="AN14" s="1" t="n"/>
-      <c r="AO14" s="1" t="n"/>
-      <c r="AP14" s="1" t="n"/>
-      <c r="AQ14" s="1" t="n"/>
+      <c r="AI14" s="1" t="inlineStr">
+        <is>
+          <t>1213,194</t>
+        </is>
+      </c>
+      <c r="AJ14" s="1" t="inlineStr">
+        <is>
+          <t>1251,200</t>
+        </is>
+      </c>
+      <c r="AK14" s="1" t="inlineStr">
+        <is>
+          <t>1289,206</t>
+        </is>
+      </c>
+      <c r="AL14" s="1" t="inlineStr">
+        <is>
+          <t>1327,212</t>
+        </is>
+      </c>
+      <c r="AM14" s="1" t="inlineStr">
+        <is>
+          <t>1365,218</t>
+        </is>
+      </c>
+      <c r="AN14" s="1" t="inlineStr">
+        <is>
+          <t>1402,224</t>
+        </is>
+      </c>
+      <c r="AO14" s="1" t="inlineStr">
+        <is>
+          <t>1440,230</t>
+        </is>
+      </c>
+      <c r="AP14" s="1" t="inlineStr">
+        <is>
+          <t>1478,236</t>
+        </is>
+      </c>
+      <c r="AQ14" s="1" t="inlineStr">
+        <is>
+          <t>1516,242</t>
+        </is>
+      </c>
       <c r="AR14" s="1" t="n"/>
       <c r="AS14" s="5" t="n"/>
       <c r="AT14" s="5" t="n"/>
@@ -2415,7 +2540,11 @@
       <c r="BA14" s="5" t="n"/>
       <c r="BB14" s="5" t="n"/>
       <c r="BC14" s="1" t="n"/>
-      <c r="BD14" s="1" t="n"/>
+      <c r="BD14" s="1" t="inlineStr">
+        <is>
+          <t>花の蜜2,大豆2,丸太2,火打ち石2</t>
+        </is>
+      </c>
       <c r="BE14" s="1" t="n"/>
     </row>
     <row r="15">
@@ -3826,16 +3955,56 @@
           <t>962,126</t>
         </is>
       </c>
-      <c r="Y26" s="1" t="n"/>
-      <c r="Z26" s="1" t="n"/>
-      <c r="AA26" s="1" t="n"/>
-      <c r="AB26" s="1" t="n"/>
-      <c r="AC26" s="1" t="n"/>
-      <c r="AD26" s="1" t="n"/>
-      <c r="AE26" s="1" t="n"/>
-      <c r="AF26" s="1" t="n"/>
-      <c r="AG26" s="1" t="n"/>
-      <c r="AH26" s="1" t="n"/>
+      <c r="Y26" s="1" t="inlineStr">
+        <is>
+          <t>1007,131</t>
+        </is>
+      </c>
+      <c r="Z26" s="1" t="inlineStr">
+        <is>
+          <t>1053,137</t>
+        </is>
+      </c>
+      <c r="AA26" s="1" t="inlineStr">
+        <is>
+          <t>1099,143</t>
+        </is>
+      </c>
+      <c r="AB26" s="1" t="inlineStr">
+        <is>
+          <t>1144,149</t>
+        </is>
+      </c>
+      <c r="AC26" s="1" t="inlineStr">
+        <is>
+          <t>1190,155</t>
+        </is>
+      </c>
+      <c r="AD26" s="1" t="inlineStr">
+        <is>
+          <t>1236,161</t>
+        </is>
+      </c>
+      <c r="AE26" s="1" t="inlineStr">
+        <is>
+          <t>1281,167</t>
+        </is>
+      </c>
+      <c r="AF26" s="1" t="inlineStr">
+        <is>
+          <t>1327,173</t>
+        </is>
+      </c>
+      <c r="AG26" s="1" t="inlineStr">
+        <is>
+          <t>1373,179</t>
+        </is>
+      </c>
+      <c r="AH26" s="1" t="inlineStr">
+        <is>
+          <t>1419,185</t>
+        </is>
+      </c>
       <c r="AI26" s="1" t="n"/>
       <c r="AJ26" s="1" t="n"/>
       <c r="AK26" s="1" t="n"/>
@@ -3856,7 +4025,11 @@
       <c r="AZ26" s="5" t="n"/>
       <c r="BA26" s="5" t="n"/>
       <c r="BB26" s="5" t="n"/>
-      <c r="BC26" s="2" t="n"/>
+      <c r="BC26" s="2" t="inlineStr">
+        <is>
+          <t>葉っぱ2,麦2</t>
+        </is>
+      </c>
       <c r="BD26" s="2" t="n"/>
       <c r="BE26" s="2" t="n"/>
     </row>
@@ -4064,16 +4237,56 @@
           <t>885,130</t>
         </is>
       </c>
-      <c r="Y28" s="1" t="n"/>
-      <c r="Z28" s="1" t="n"/>
-      <c r="AA28" s="1" t="n"/>
-      <c r="AB28" s="1" t="n"/>
-      <c r="AC28" s="1" t="n"/>
-      <c r="AD28" s="1" t="n"/>
-      <c r="AE28" s="1" t="n"/>
-      <c r="AF28" s="1" t="n"/>
-      <c r="AG28" s="1" t="n"/>
-      <c r="AH28" s="1" t="n"/>
+      <c r="Y28" s="1" t="inlineStr">
+        <is>
+          <t>926,136</t>
+        </is>
+      </c>
+      <c r="Z28" s="1" t="inlineStr">
+        <is>
+          <t>968,142</t>
+        </is>
+      </c>
+      <c r="AA28" s="1" t="inlineStr">
+        <is>
+          <t>1010,148</t>
+        </is>
+      </c>
+      <c r="AB28" s="1" t="inlineStr">
+        <is>
+          <t>1052,154</t>
+        </is>
+      </c>
+      <c r="AC28" s="1" t="inlineStr">
+        <is>
+          <t>1094,160</t>
+        </is>
+      </c>
+      <c r="AD28" s="1" t="inlineStr">
+        <is>
+          <t>1136,166</t>
+        </is>
+      </c>
+      <c r="AE28" s="1" t="inlineStr">
+        <is>
+          <t>1178,172</t>
+        </is>
+      </c>
+      <c r="AF28" s="1" t="inlineStr">
+        <is>
+          <t>1220,178</t>
+        </is>
+      </c>
+      <c r="AG28" s="1" t="inlineStr">
+        <is>
+          <t>1262,184</t>
+        </is>
+      </c>
+      <c r="AH28" s="1" t="inlineStr">
+        <is>
+          <t>1304,191</t>
+        </is>
+      </c>
       <c r="AI28" s="1" t="n"/>
       <c r="AJ28" s="1" t="n"/>
       <c r="AK28" s="1" t="n"/>
@@ -4094,7 +4307,11 @@
       <c r="AZ28" s="5" t="n"/>
       <c r="BA28" s="5" t="n"/>
       <c r="BB28" s="5" t="n"/>
-      <c r="BC28" s="2" t="n"/>
+      <c r="BC28" s="2" t="inlineStr">
+        <is>
+          <t>大豆2,丸太2</t>
+        </is>
+      </c>
       <c r="BD28" s="2" t="n"/>
       <c r="BE28" s="2" t="n"/>
     </row>
@@ -4182,16 +4399,56 @@
           <t>861,95</t>
         </is>
       </c>
-      <c r="Y29" s="1" t="n"/>
-      <c r="Z29" s="1" t="n"/>
-      <c r="AA29" s="1" t="n"/>
-      <c r="AB29" s="1" t="n"/>
-      <c r="AC29" s="1" t="n"/>
-      <c r="AD29" s="1" t="n"/>
-      <c r="AE29" s="1" t="n"/>
-      <c r="AF29" s="1" t="n"/>
-      <c r="AG29" s="1" t="n"/>
-      <c r="AH29" s="1" t="n"/>
+      <c r="Y29" s="1" t="inlineStr">
+        <is>
+          <t>901,99</t>
+        </is>
+      </c>
+      <c r="Z29" s="1" t="inlineStr">
+        <is>
+          <t>942,104</t>
+        </is>
+      </c>
+      <c r="AA29" s="1" t="inlineStr">
+        <is>
+          <t>983,108</t>
+        </is>
+      </c>
+      <c r="AB29" s="1" t="inlineStr">
+        <is>
+          <t>1024,113</t>
+        </is>
+      </c>
+      <c r="AC29" s="1" t="inlineStr">
+        <is>
+          <t>1065,117</t>
+        </is>
+      </c>
+      <c r="AD29" s="1" t="inlineStr">
+        <is>
+          <t>1105,122</t>
+        </is>
+      </c>
+      <c r="AE29" s="1" t="inlineStr">
+        <is>
+          <t>1146,126</t>
+        </is>
+      </c>
+      <c r="AF29" s="1" t="inlineStr">
+        <is>
+          <t>1187,131</t>
+        </is>
+      </c>
+      <c r="AG29" s="1" t="inlineStr">
+        <is>
+          <t>1228,135</t>
+        </is>
+      </c>
+      <c r="AH29" s="1" t="inlineStr">
+        <is>
+          <t>1269,140</t>
+        </is>
+      </c>
       <c r="AI29" s="1" t="n"/>
       <c r="AJ29" s="1" t="n"/>
       <c r="AK29" s="1" t="n"/>
@@ -4212,7 +4469,11 @@
       <c r="AZ29" s="5" t="n"/>
       <c r="BA29" s="5" t="n"/>
       <c r="BB29" s="5" t="n"/>
-      <c r="BC29" s="2" t="n"/>
+      <c r="BC29" s="2" t="inlineStr">
+        <is>
+          <t>水2,ふさふさの毛2</t>
+        </is>
+      </c>
       <c r="BD29" s="2" t="n"/>
       <c r="BE29" s="2" t="n"/>
     </row>
@@ -5435,16 +5696,56 @@
           <t>857,110</t>
         </is>
       </c>
-      <c r="Y39" s="1" t="n"/>
-      <c r="Z39" s="1" t="n"/>
-      <c r="AA39" s="1" t="n"/>
-      <c r="AB39" s="1" t="n"/>
-      <c r="AC39" s="1" t="n"/>
-      <c r="AD39" s="1" t="n"/>
-      <c r="AE39" s="1" t="n"/>
-      <c r="AF39" s="1" t="n"/>
-      <c r="AG39" s="1" t="n"/>
-      <c r="AH39" s="1" t="n"/>
+      <c r="Y39" s="1" t="inlineStr">
+        <is>
+          <t>897,115</t>
+        </is>
+      </c>
+      <c r="Z39" s="1" t="inlineStr">
+        <is>
+          <t>938,120</t>
+        </is>
+      </c>
+      <c r="AA39" s="1" t="inlineStr">
+        <is>
+          <t>979,125</t>
+        </is>
+      </c>
+      <c r="AB39" s="1" t="inlineStr">
+        <is>
+          <t>1019,131</t>
+        </is>
+      </c>
+      <c r="AC39" s="1" t="inlineStr">
+        <is>
+          <t>1060,136</t>
+        </is>
+      </c>
+      <c r="AD39" s="1" t="inlineStr">
+        <is>
+          <t>1101,141</t>
+        </is>
+      </c>
+      <c r="AE39" s="1" t="inlineStr">
+        <is>
+          <t>1141,147</t>
+        </is>
+      </c>
+      <c r="AF39" s="1" t="inlineStr">
+        <is>
+          <t>1182,152</t>
+        </is>
+      </c>
+      <c r="AG39" s="1" t="inlineStr">
+        <is>
+          <t>1223,157</t>
+        </is>
+      </c>
+      <c r="AH39" s="1" t="inlineStr">
+        <is>
+          <t>1264,163</t>
+        </is>
+      </c>
       <c r="AI39" s="1" t="n"/>
       <c r="AJ39" s="1" t="n"/>
       <c r="AK39" s="1" t="n"/>
@@ -5465,7 +5766,11 @@
       <c r="AZ39" s="5" t="n"/>
       <c r="BA39" s="5" t="n"/>
       <c r="BB39" s="5" t="n"/>
-      <c r="BC39" s="2" t="n"/>
+      <c r="BC39" s="2" t="inlineStr">
+        <is>
+          <t>水2,ふさふさの毛2</t>
+        </is>
+      </c>
       <c r="BD39" s="2" t="n"/>
       <c r="BE39" s="2" t="n"/>
     </row>
@@ -5888,16 +6193,56 @@
           <t>1011,98</t>
         </is>
       </c>
-      <c r="Y43" s="1" t="n"/>
-      <c r="Z43" s="1" t="n"/>
-      <c r="AA43" s="1" t="n"/>
-      <c r="AB43" s="1" t="n"/>
-      <c r="AC43" s="1" t="n"/>
-      <c r="AD43" s="1" t="n"/>
-      <c r="AE43" s="1" t="n"/>
-      <c r="AF43" s="1" t="n"/>
-      <c r="AG43" s="1" t="n"/>
-      <c r="AH43" s="1" t="n"/>
+      <c r="Y43" s="1" t="inlineStr">
+        <is>
+          <t>1059,102</t>
+        </is>
+      </c>
+      <c r="Z43" s="1" t="inlineStr">
+        <is>
+          <t>1107,107</t>
+        </is>
+      </c>
+      <c r="AA43" s="1" t="inlineStr">
+        <is>
+          <t>1155,111</t>
+        </is>
+      </c>
+      <c r="AB43" s="1" t="inlineStr">
+        <is>
+          <t>1203,116</t>
+        </is>
+      </c>
+      <c r="AC43" s="1" t="inlineStr">
+        <is>
+          <t>1251,121</t>
+        </is>
+      </c>
+      <c r="AD43" s="1" t="inlineStr">
+        <is>
+          <t>1299,125</t>
+        </is>
+      </c>
+      <c r="AE43" s="1" t="inlineStr">
+        <is>
+          <t>1347,130</t>
+        </is>
+      </c>
+      <c r="AF43" s="1" t="inlineStr">
+        <is>
+          <t>1395,134</t>
+        </is>
+      </c>
+      <c r="AG43" s="1" t="inlineStr">
+        <is>
+          <t>1443,139</t>
+        </is>
+      </c>
+      <c r="AH43" s="1" t="inlineStr">
+        <is>
+          <t>1491,144</t>
+        </is>
+      </c>
       <c r="AI43" s="1" t="n"/>
       <c r="AJ43" s="1" t="n"/>
       <c r="AK43" s="1" t="n"/>
@@ -5918,7 +6263,11 @@
       <c r="AZ43" s="5" t="n"/>
       <c r="BA43" s="5" t="n"/>
       <c r="BB43" s="5" t="n"/>
-      <c r="BC43" s="1" t="n"/>
+      <c r="BC43" s="1" t="inlineStr">
+        <is>
+          <t>ふさふさの毛2,麦2</t>
+        </is>
+      </c>
       <c r="BD43" s="1" t="n"/>
       <c r="BE43" s="1" t="n"/>
     </row>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -4118,16 +4118,56 @@
           <t>954,115</t>
         </is>
       </c>
-      <c r="Y27" s="1" t="n"/>
-      <c r="Z27" s="1" t="n"/>
-      <c r="AA27" s="1" t="n"/>
-      <c r="AB27" s="1" t="n"/>
-      <c r="AC27" s="1" t="n"/>
-      <c r="AD27" s="1" t="n"/>
-      <c r="AE27" s="1" t="n"/>
-      <c r="AF27" s="1" t="n"/>
-      <c r="AG27" s="1" t="n"/>
-      <c r="AH27" s="1" t="n"/>
+      <c r="Y27" s="1" t="inlineStr">
+        <is>
+          <t>999,120</t>
+        </is>
+      </c>
+      <c r="Z27" s="1" t="inlineStr">
+        <is>
+          <t>1044,126</t>
+        </is>
+      </c>
+      <c r="AA27" s="1" t="inlineStr">
+        <is>
+          <t>1089,131</t>
+        </is>
+      </c>
+      <c r="AB27" s="1" t="inlineStr">
+        <is>
+          <t>1135,137</t>
+        </is>
+      </c>
+      <c r="AC27" s="1" t="inlineStr">
+        <is>
+          <t>1180,142</t>
+        </is>
+      </c>
+      <c r="AD27" s="1" t="inlineStr">
+        <is>
+          <t>1225,148</t>
+        </is>
+      </c>
+      <c r="AE27" s="1" t="inlineStr">
+        <is>
+          <t>1271,153</t>
+        </is>
+      </c>
+      <c r="AF27" s="1" t="inlineStr">
+        <is>
+          <t>1316,159</t>
+        </is>
+      </c>
+      <c r="AG27" s="1" t="inlineStr">
+        <is>
+          <t>1361,164</t>
+        </is>
+      </c>
+      <c r="AH27" s="1" t="inlineStr">
+        <is>
+          <t>1407,170</t>
+        </is>
+      </c>
       <c r="AI27" s="1" t="n"/>
       <c r="AJ27" s="1" t="n"/>
       <c r="AK27" s="1" t="n"/>
@@ -4148,7 +4188,11 @@
       <c r="AZ27" s="5" t="n"/>
       <c r="BA27" s="5" t="n"/>
       <c r="BB27" s="5" t="n"/>
-      <c r="BC27" s="2" t="n"/>
+      <c r="BC27" s="2" t="inlineStr">
+        <is>
+          <t>ふさふさの毛2,麦2</t>
+        </is>
+      </c>
       <c r="BD27" s="2" t="n"/>
       <c r="BE27" s="2" t="n"/>
     </row>
@@ -5771,7 +5815,11 @@
           <t>水2,ふさふさの毛2</t>
         </is>
       </c>
-      <c r="BD39" s="2" t="n"/>
+      <c r="BD39" s="2" t="inlineStr">
+        <is>
+          <t>花の蜜2,ふさふさの毛4,丸太2,木の枝2</t>
+        </is>
+      </c>
       <c r="BE39" s="2" t="n"/>
     </row>
     <row r="40">
@@ -6956,13 +7004,41 @@
       </c>
       <c r="P49" s="1" t="n"/>
       <c r="Q49" s="1" t="n"/>
-      <c r="R49" s="1" t="n"/>
-      <c r="S49" s="1" t="n"/>
-      <c r="T49" s="1" t="n"/>
-      <c r="U49" s="1" t="n"/>
-      <c r="V49" s="1" t="n"/>
-      <c r="W49" s="1" t="n"/>
-      <c r="X49" s="1" t="n"/>
+      <c r="R49" s="1" t="inlineStr">
+        <is>
+          <t>575,75</t>
+        </is>
+      </c>
+      <c r="S49" s="1" t="inlineStr">
+        <is>
+          <t>613,80</t>
+        </is>
+      </c>
+      <c r="T49" s="1" t="inlineStr">
+        <is>
+          <t>652,85</t>
+        </is>
+      </c>
+      <c r="U49" s="1" t="inlineStr">
+        <is>
+          <t>690,90</t>
+        </is>
+      </c>
+      <c r="V49" s="1" t="inlineStr">
+        <is>
+          <t>728,95</t>
+        </is>
+      </c>
+      <c r="W49" s="1" t="inlineStr">
+        <is>
+          <t>766,100</t>
+        </is>
+      </c>
+      <c r="X49" s="1" t="inlineStr">
+        <is>
+          <t>805,105</t>
+        </is>
+      </c>
       <c r="Y49" s="1" t="n"/>
       <c r="Z49" s="1" t="n"/>
       <c r="AA49" s="1" t="n"/>
